--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="535">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -221,12 +221,6 @@
   </si>
   <si>
     <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE</t>
-  </si>
-  <si>
-    <t>OKREF03249 - {"path": "XWALTZ,XceleraCORE,XceleraSERVICE", "instance": "XceleraSERVICE", "symbol": "enable_ibias", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
@@ -427,12 +421,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog11/CELERAservice.v:166: error: port ``celkelvin_CELG'' is not a port of Xreference.
-1 error(s) during elaboration.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -457,6 +445,9 @@
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
   </si>
   <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
   </si>
   <si>
@@ -478,6 +469,9 @@
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
     <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
@@ -496,6 +490,9 @@
     <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
   </si>
   <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
   </si>
   <si>
@@ -514,16 +511,13 @@
     <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
   </si>
   <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 25, 'bytes': 25.0, 'noconns': 62, 'efficiency': '69.0%'}</t>
+    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
   </si>
   <si>
     <t>Project Summary</t>
@@ -1330,6 +1324,12 @@
     <t>DFTtm8t</t>
   </si>
   <si>
+    <t>dft_hex0x1A</t>
+  </si>
+  <si>
+    <t>0x1A</t>
+  </si>
+  <si>
     <t>dft_hex0x03</t>
   </si>
   <si>
@@ -1360,6 +1360,12 @@
     <t>dft_hex0x08</t>
   </si>
   <si>
+    <t>dft_hex0x1B</t>
+  </si>
+  <si>
+    <t>0x1B</t>
+  </si>
+  <si>
     <t>dft_hex0x09</t>
   </si>
   <si>
@@ -1375,6 +1381,15 @@
     <t>dft_hex0x0C</t>
   </si>
   <si>
+    <t>dft_hex0x1C</t>
+  </si>
+  <si>
+    <t>dft_hex0x1D</t>
+  </si>
+  <si>
+    <t>0x1D</t>
+  </si>
+  <si>
     <t>dft_hex0x0D</t>
   </si>
   <si>
@@ -1390,12 +1405,21 @@
     <t>dft_hex0x0F</t>
   </si>
   <si>
+    <t>dft_hex0x1E</t>
+  </si>
+  <si>
+    <t>0x1E</t>
+  </si>
+  <si>
     <t>dft_hex0x10</t>
   </si>
   <si>
     <t>dft_hex0x11</t>
   </si>
   <si>
+    <t>dft_hex0x1F</t>
+  </si>
+  <si>
     <t>dft_hex0x12</t>
   </si>
   <si>
@@ -1417,6 +1441,12 @@
     <t>dft_hex0x18</t>
   </si>
   <si>
+    <t>dft_hex0x20</t>
+  </si>
+  <si>
+    <t>0x20</t>
+  </si>
+  <si>
     <t>dft_hex0x19</t>
   </si>
   <si>
@@ -1444,18 +1474,18 @@
     <t>193</t>
   </si>
   <si>
+    <t>noconn</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
     <t>nand2</t>
   </si>
   <si>
     <t>148</t>
   </si>
   <si>
-    <t>noconn</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
     <t>dbuf</t>
   </si>
   <si>
@@ -1501,7 +1531,7 @@
     <t>dftmodule</t>
   </si>
   <si>
-    <t>25</t>
+    <t>32</t>
   </si>
   <si>
     <t>dfthijack</t>
@@ -1565,6 +1595,9 @@
   </si>
   <si>
     <t>amux2</t>
+  </si>
+  <si>
+    <t>wrapper</t>
   </si>
   <si>
     <t>vbuffer</t>
@@ -2014,7 +2047,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2079,82 +2112,72 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>41</v>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2169,7 +2192,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2189,7 +2212,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2204,7 +2227,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2219,17 +2242,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2244,12 +2267,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2264,17 +2287,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2289,12 +2312,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2309,7 +2332,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2324,157 +2347,152 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2489,7 +2507,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2719,17 +2737,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2739,222 +2757,257 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>136</v>
+      <c r="A29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="1" t="s">
-        <v>142</v>
+      <c r="A48" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="1" t="s">
-        <v>143</v>
+      <c r="A51" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="1" t="s">
-        <v>145</v>
+      <c r="A55" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="1" t="s">
-        <v>79</v>
+      <c r="A58" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2969,17 +3022,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2994,52 +3047,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3054,81 +3107,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" t="s">
         <v>162</v>
-      </c>
-      <c r="B5" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" t="s">
         <v>164</v>
-      </c>
-      <c r="B6" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" t="s">
         <v>168</v>
-      </c>
-      <c r="B9" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" t="s">
         <v>170</v>
-      </c>
-      <c r="B10" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3136,1268 +3189,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" t="s">
         <v>187</v>
-      </c>
-      <c r="B29" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" t="s">
         <v>191</v>
-      </c>
-      <c r="B32" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" t="s">
         <v>193</v>
-      </c>
-      <c r="B33" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" t="s">
         <v>195</v>
-      </c>
-      <c r="B34" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" t="s">
         <v>197</v>
-      </c>
-      <c r="B35" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>198</v>
+      </c>
+      <c r="B36" t="s">
         <v>199</v>
-      </c>
-      <c r="B36" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" t="s">
         <v>203</v>
-      </c>
-      <c r="B39" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" t="s">
         <v>208</v>
-      </c>
-      <c r="B43" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
+        <v>210</v>
+      </c>
+      <c r="B46" t="s">
         <v>211</v>
-      </c>
-      <c r="B46" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B51" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
+        <v>217</v>
+      </c>
+      <c r="B52" t="s">
         <v>218</v>
-      </c>
-      <c r="B52" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
+        <v>220</v>
+      </c>
+      <c r="B55" t="s">
         <v>221</v>
-      </c>
-      <c r="B55" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
+        <v>222</v>
+      </c>
+      <c r="B56" t="s">
         <v>223</v>
-      </c>
-      <c r="B56" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
+        <v>230</v>
+      </c>
+      <c r="B64" t="s">
         <v>231</v>
-      </c>
-      <c r="B64" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
+        <v>234</v>
+      </c>
+      <c r="B67" t="s">
         <v>235</v>
-      </c>
-      <c r="B67" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
+        <v>236</v>
+      </c>
+      <c r="B68" t="s">
         <v>237</v>
-      </c>
-      <c r="B68" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B69" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B70" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B78" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B79" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>248</v>
+      </c>
+      <c r="B80" t="s">
         <v>249</v>
-      </c>
-      <c r="B80" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" t="s">
         <v>251</v>
-      </c>
-      <c r="B81" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B88" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
+        <v>260</v>
+      </c>
+      <c r="B90" t="s">
         <v>261</v>
-      </c>
-      <c r="B90" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B91" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B92" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B93" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B94" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B95" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B96" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B97" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B98" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B99" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
+        <v>272</v>
+      </c>
+      <c r="B101" t="s">
         <v>273</v>
-      </c>
-      <c r="B101" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B102" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B103" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
+        <v>277</v>
+      </c>
+      <c r="B106" t="s">
         <v>278</v>
-      </c>
-      <c r="B106" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
+        <v>279</v>
+      </c>
+      <c r="B107" t="s">
         <v>280</v>
-      </c>
-      <c r="B107" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
+        <v>281</v>
+      </c>
+      <c r="B108" t="s">
         <v>282</v>
-      </c>
-      <c r="B108" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>283</v>
+      </c>
+      <c r="B109" t="s">
         <v>284</v>
-      </c>
-      <c r="B109" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>285</v>
+      </c>
+      <c r="B110" t="s">
         <v>286</v>
-      </c>
-      <c r="B110" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
+        <v>287</v>
+      </c>
+      <c r="B111" t="s">
         <v>288</v>
-      </c>
-      <c r="B111" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
+        <v>289</v>
+      </c>
+      <c r="B112" t="s">
         <v>290</v>
-      </c>
-      <c r="B112" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B113" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B116" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>294</v>
+      </c>
+      <c r="B117" t="s">
         <v>295</v>
-      </c>
-      <c r="B117" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>296</v>
+      </c>
+      <c r="B118" t="s">
         <v>297</v>
-      </c>
-      <c r="B118" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>298</v>
+      </c>
+      <c r="B119" t="s">
         <v>299</v>
-      </c>
-      <c r="B119" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>300</v>
+      </c>
+      <c r="B120" t="s">
         <v>301</v>
-      </c>
-      <c r="B120" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>302</v>
+      </c>
+      <c r="B121" t="s">
         <v>303</v>
-      </c>
-      <c r="B121" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
+        <v>304</v>
+      </c>
+      <c r="B122" t="s">
         <v>305</v>
-      </c>
-      <c r="B122" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B123" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B124" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B125" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
+        <v>309</v>
+      </c>
+      <c r="B126" t="s">
         <v>310</v>
-      </c>
-      <c r="B126" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
+        <v>311</v>
+      </c>
+      <c r="B127" t="s">
         <v>312</v>
-      </c>
-      <c r="B127" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
+        <v>313</v>
+      </c>
+      <c r="B128" t="s">
         <v>314</v>
-      </c>
-      <c r="B128" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>315</v>
+      </c>
+      <c r="B129" t="s">
         <v>316</v>
-      </c>
-      <c r="B129" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
+        <v>317</v>
+      </c>
+      <c r="B130" t="s">
         <v>318</v>
-      </c>
-      <c r="B130" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B131" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B132" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B133" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B134" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B135" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
+        <v>324</v>
+      </c>
+      <c r="B136" t="s">
         <v>325</v>
-      </c>
-      <c r="B136" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
+        <v>326</v>
+      </c>
+      <c r="B137" t="s">
         <v>327</v>
-      </c>
-      <c r="B137" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
+        <v>328</v>
+      </c>
+      <c r="B138" t="s">
         <v>329</v>
-      </c>
-      <c r="B138" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>330</v>
+      </c>
+      <c r="B139" t="s">
         <v>331</v>
-      </c>
-      <c r="B139" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
+        <v>332</v>
+      </c>
+      <c r="B140" t="s">
         <v>333</v>
-      </c>
-      <c r="B140" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B141" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B142" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B143" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B144" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B145" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B146" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B147" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B148" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
+        <v>342</v>
+      </c>
+      <c r="B149" t="s">
         <v>343</v>
-      </c>
-      <c r="B149" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
+        <v>344</v>
+      </c>
+      <c r="B150" t="s">
         <v>345</v>
-      </c>
-      <c r="B150" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
+        <v>346</v>
+      </c>
+      <c r="B151" t="s">
         <v>347</v>
-      </c>
-      <c r="B151" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
+        <v>348</v>
+      </c>
+      <c r="B152" t="s">
         <v>349</v>
-      </c>
-      <c r="B152" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
+        <v>350</v>
+      </c>
+      <c r="B153" t="s">
         <v>351</v>
-      </c>
-      <c r="B153" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>352</v>
+      </c>
+      <c r="B154" t="s">
         <v>353</v>
-      </c>
-      <c r="B154" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>354</v>
+      </c>
+      <c r="B155" t="s">
         <v>355</v>
-      </c>
-      <c r="B155" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>356</v>
+      </c>
+      <c r="B156" t="s">
         <v>357</v>
-      </c>
-      <c r="B156" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>358</v>
+      </c>
+      <c r="B157" t="s">
         <v>359</v>
-      </c>
-      <c r="B157" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>360</v>
+      </c>
+      <c r="B158" t="s">
         <v>361</v>
-      </c>
-      <c r="B158" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
+        <v>362</v>
+      </c>
+      <c r="B159" t="s">
         <v>363</v>
-      </c>
-      <c r="B159" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
+        <v>364</v>
+      </c>
+      <c r="B160" t="s">
         <v>365</v>
-      </c>
-      <c r="B160" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>366</v>
+      </c>
+      <c r="B161" t="s">
         <v>367</v>
-      </c>
-      <c r="B161" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>368</v>
+      </c>
+      <c r="B162" t="s">
         <v>369</v>
-      </c>
-      <c r="B162" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>370</v>
+      </c>
+      <c r="B163" t="s">
         <v>371</v>
-      </c>
-      <c r="B163" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>372</v>
+      </c>
+      <c r="B164" t="s">
         <v>373</v>
-      </c>
-      <c r="B164" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>374</v>
+      </c>
+      <c r="B165" t="s">
         <v>375</v>
-      </c>
-      <c r="B165" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B166" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B167" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B168" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B169" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>380</v>
+      </c>
+      <c r="B170" t="s">
         <v>381</v>
-      </c>
-      <c r="B170" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
+        <v>382</v>
+      </c>
+      <c r="B171" t="s">
         <v>383</v>
-      </c>
-      <c r="B171" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
+        <v>384</v>
+      </c>
+      <c r="B172" t="s">
         <v>385</v>
-      </c>
-      <c r="B172" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
+        <v>386</v>
+      </c>
+      <c r="B173" t="s">
         <v>387</v>
-      </c>
-      <c r="B173" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B174" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B175" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B176" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B177" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B178" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
+        <v>393</v>
+      </c>
+      <c r="B179" t="s">
         <v>394</v>
-      </c>
-      <c r="B179" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B180" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -4412,47 +4465,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4460,15 +4513,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4476,7 +4529,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -4491,7 +4544,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -4501,87 +4554,87 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C5" t="s">
+        <v>331</v>
+      </c>
+      <c r="D5" t="s">
         <v>412</v>
-      </c>
-      <c r="C5" t="s">
-        <v>332</v>
-      </c>
-      <c r="D5" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D6" t="s">
         <v>414</v>
-      </c>
-      <c r="C6" t="s">
-        <v>334</v>
-      </c>
-      <c r="D6" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C7" t="s">
         <v>416</v>
       </c>
-      <c r="C7" t="s">
-        <v>192</v>
-      </c>
       <c r="D7" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s">
+        <v>417</v>
+      </c>
+      <c r="C8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" t="s">
         <v>418</v>
-      </c>
-      <c r="C8" t="s">
-        <v>382</v>
-      </c>
-      <c r="D8" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4592,113 +4645,113 @@
         <v>419</v>
       </c>
       <c r="C9" t="s">
-        <v>420</v>
+        <v>381</v>
       </c>
       <c r="D9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
+        <v>420</v>
+      </c>
+      <c r="C10" t="s">
         <v>421</v>
       </c>
-      <c r="C10" t="s">
-        <v>422</v>
-      </c>
       <c r="D10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B11" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" t="s">
         <v>423</v>
       </c>
-      <c r="C11" t="s">
-        <v>424</v>
-      </c>
       <c r="D11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s">
+        <v>424</v>
+      </c>
+      <c r="C12" t="s">
         <v>425</v>
       </c>
-      <c r="C12" t="s">
-        <v>384</v>
-      </c>
       <c r="D12" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="B13" t="s">
         <v>426</v>
       </c>
       <c r="C13" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s">
         <v>427</v>
       </c>
       <c r="C14" t="s">
-        <v>388</v>
+        <v>428</v>
       </c>
       <c r="D14" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C15" t="s">
-        <v>429</v>
+        <v>385</v>
       </c>
       <c r="D15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s">
         <v>430</v>
       </c>
       <c r="C16" t="s">
-        <v>330</v>
+        <v>387</v>
       </c>
       <c r="D16" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s">
         <v>431</v>
@@ -4707,175 +4760,273 @@
         <v>432</v>
       </c>
       <c r="D17" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s">
         <v>433</v>
       </c>
       <c r="C18" t="s">
-        <v>434</v>
+        <v>329</v>
       </c>
       <c r="D18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="D19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s">
+        <v>435</v>
+      </c>
+      <c r="C20" t="s">
         <v>436</v>
       </c>
-      <c r="C20" t="s">
-        <v>302</v>
-      </c>
       <c r="D20" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
         <v>437</v>
       </c>
       <c r="C21" t="s">
-        <v>304</v>
+        <v>438</v>
       </c>
       <c r="D21" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B22" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C22" t="s">
-        <v>306</v>
+        <v>440</v>
       </c>
       <c r="D22" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="B23" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C23" t="s">
-        <v>311</v>
+        <v>261</v>
       </c>
       <c r="D23" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C24" t="s">
-        <v>313</v>
+        <v>443</v>
       </c>
       <c r="D24" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B25" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C25" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="D25" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C26" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="D26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C27" t="s">
-        <v>319</v>
+        <v>394</v>
       </c>
       <c r="D27" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B28" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C28" t="s">
-        <v>344</v>
+        <v>305</v>
       </c>
       <c r="D28" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C29" t="s">
-        <v>446</v>
+        <v>310</v>
       </c>
       <c r="D29" t="s">
-        <v>415</v>
+        <v>418</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>449</v>
+      </c>
+      <c r="C30" t="s">
+        <v>312</v>
+      </c>
+      <c r="D30" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" t="s">
+        <v>450</v>
+      </c>
+      <c r="C31" t="s">
+        <v>314</v>
+      </c>
+      <c r="D31" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>143</v>
+      </c>
+      <c r="B32" t="s">
+        <v>451</v>
+      </c>
+      <c r="C32" t="s">
+        <v>316</v>
+      </c>
+      <c r="D32" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>143</v>
+      </c>
+      <c r="B33" t="s">
+        <v>452</v>
+      </c>
+      <c r="C33" t="s">
+        <v>318</v>
+      </c>
+      <c r="D33" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>144</v>
+      </c>
+      <c r="B34" t="s">
+        <v>453</v>
+      </c>
+      <c r="C34" t="s">
+        <v>343</v>
+      </c>
+      <c r="D34" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" t="s">
+        <v>454</v>
+      </c>
+      <c r="C35" t="s">
+        <v>455</v>
+      </c>
+      <c r="D35" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C36" t="s">
+        <v>457</v>
+      </c>
+      <c r="D36" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -4885,12 +5036,12 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4900,482 +5051,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="B5" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="B6" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B7" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="B8" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="B9" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="B10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="B11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="B12" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B13" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="B14" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="B15" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="B16" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="B17" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="B18" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="B19" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="B20" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B21" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="B22" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="B23" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B24" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B25" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B26" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="B27" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B28" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B30" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B31" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="B32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B33" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="B35" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="B36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="B38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="B39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B40" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="B41" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B43" t="s">
-        <v>274</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="B44" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="B45" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="B46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="B47" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="B50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="B51" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="B52" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="B53" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="B54" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B55" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B56" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="B57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B58" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="B59" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="B60" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="B61" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="B62" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="B63" t="s">
-        <v>274</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>534</v>
+      </c>
+      <c r="B64" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="532">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -374,39 +374,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_13ab43f9_d8nsr.v:100: error: Unknown module type: fet_delay_timingskew_13ab43f9_d8nsr_pin
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_13ab43f9_d8nsr.v:127: error: Unknown module type: fet_delay_timingskew_13ab43f9_d8nsr_nout
-3 error(s) during elaboration.
-*** These modules were missing:
-        fet_delay_timingskew_13ab43f9_d8nsr_nout referenced 1 times.
-        fet_delay_timingskew_13ab43f9_d8nsr_pin referenced 1 times.
-***
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_0bb48130_d1nsr.v:100: error: Unknown module type: fet_delay_timingskew_0bb48130_d1nsr_pin
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_0bb48130_d1nsr.v:127: error: Unknown module type: fet_delay_timingskew_0bb48130_d1nsr_nout
-3 error(s) during elaboration.
-*** These modules were missing:
-        fet_delay_timingskew_0bb48130_d1nsr_nout referenced 1 times.
-        fet_delay_timingskew_0bb48130_d1nsr_pin referenced 1 times.
-***
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_afbafd68_d1nsr.v:100: error: Unknown module type: fet_delay_timingskew_afbafd68_d1nsr_pin
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_afbafd68_d1nsr.v:127: error: Unknown module type: fet_delay_timingskew_afbafd68_d1nsr_nout
-3 error(s) during elaboration.
-*** These modules were missing:
-        fet_delay_timingskew_afbafd68_d1nsr_nout referenced 1 times.
-        fet_delay_timingskew_afbafd68_d1nsr_pin referenced 1 times.
-***
 </t>
   </si>
   <si>
@@ -2347,7 +2314,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2478,21 +2445,6 @@
     <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2507,7 +2459,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2737,17 +2689,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2762,37 +2714,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -2802,42 +2754,42 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -2847,77 +2799,77 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -2927,22 +2879,22 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -2952,52 +2904,52 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:1">
@@ -3007,7 +2959,7 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3022,17 +2974,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3047,52 +2999,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -3107,81 +3059,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3189,1268 +3141,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B20" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B21" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B27" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B32" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B36" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B41" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B49" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B50" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B55" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B56" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B57" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B64" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B68" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B69" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B70" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B77" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B78" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B79" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B80" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B81" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B82" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B83" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B84" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B85" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B86" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B87" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B88" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B90" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B91" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B92" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B93" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B94" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B95" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B96" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B97" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B98" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B99" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B100" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B101" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B102" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B103" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B106" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B107" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B108" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B109" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B110" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B111" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B112" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B113" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B116" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B117" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B118" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B119" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B120" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B121" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B122" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B123" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B124" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B125" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B126" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B127" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B128" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B129" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B130" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B131" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B132" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B133" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B134" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B135" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B136" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B137" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B138" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B139" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B140" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B141" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B142" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B143" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B144" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B145" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B146" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B147" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B148" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B149" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B150" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B151" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B152" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B153" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B154" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B155" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B156" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B157" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B158" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B159" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B160" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B161" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B162" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B163" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B164" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B165" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B166" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B167" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B168" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B169" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B170" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B171" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B172" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B173" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B174" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B175" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B176" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B177" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B178" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B179" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B180" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -4465,47 +4417,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4513,15 +4465,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4529,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -4544,7 +4496,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -4559,82 +4511,82 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C7" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D7" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4642,13 +4594,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D9" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4656,69 +4608,69 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C10" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D10" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D11" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B12" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C12" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D12" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C13" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D13" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C14" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D14" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4726,153 +4678,153 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C15" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D15" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C16" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D16" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B17" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C17" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D17" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B18" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C18" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D18" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C19" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D19" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C20" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D20" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C21" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D21" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C22" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D22" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D23" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C24" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D24" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B25" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C25" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D25" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -4880,13 +4832,13 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C26" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D26" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -4894,27 +4846,27 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C27" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D27" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C28" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D28" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4922,13 +4874,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C29" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D29" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -4936,83 +4888,83 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C30" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D30" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B31" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C31" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D31" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B32" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C32" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D32" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B33" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C33" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D33" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B34" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C34" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D34" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C35" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D35" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5020,13 +4972,13 @@
         <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C36" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D36" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -5041,7 +4993,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5051,490 +5003,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B5" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B7" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B8" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B9" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B10" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B11" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B12" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B13" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B14" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B15" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B16" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B17" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B18" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B19" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B20" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B21" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B22" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B23" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B24" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B25" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B26" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B27" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B28" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B29" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B30" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B31" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B33" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B34" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B35" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B36" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B37" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B38" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B41" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B43" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B44" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B45" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B46" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B47" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B48" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B50" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B51" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B52" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B53" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B54" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B55" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B56" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B57" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B58" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B59" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B60" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B61" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B62" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B64" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="530">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -166,100 +166,7 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -378,26 +285,63 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:75: error: can not select part of scalar: a0
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:75: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:84: error: can not select part of scalar: a0
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:84: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:114: error: can not select part of scalar: a0
-/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:114: error: Failed to elaborate port expression.
-6 error(s) during elaboration.
+/celera/projects/Sunnyvale/software/WALTZ/verilog5/fetdn_9694dc46.v:52: error: Unknown module type: fet_fetdn_9694dc46_Xfet
+2 error(s) during elaboration.
+*** These modules were missing:
+        fet_fetdn_9694dc46_Xfet referenced 1 times.
+***
 </t>
   </si>
   <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24', 'bits': 24, 'noconns': 4, 'efficiency': '83.3%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER</t>
+  </si>
+  <si>
+    <t>{'name': 'drm64', 'bits': 64, 'noconns': 10, 'efficiency': '84.4%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 7, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+    <t>{'cells': 8, 'bytes': 29.0, 'noconns': 43, 'efficiency': '81.5%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
@@ -1258,6 +1202,63 @@
     <t>4</t>
   </si>
   <si>
+    <t>drm_hex0x01</t>
+  </si>
+  <si>
+    <t>drm24</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>drm_hex0x02</t>
+  </si>
+  <si>
+    <t>drm8</t>
+  </si>
+  <si>
+    <t>0x70</t>
+  </si>
+  <si>
+    <t>drm_hex0x03</t>
+  </si>
+  <si>
+    <t>drm64</t>
+  </si>
+  <si>
+    <t>0x78</t>
+  </si>
+  <si>
+    <t>drm_hex0x04</t>
+  </si>
+  <si>
+    <t>drm_hex0x05</t>
+  </si>
+  <si>
+    <t>0x05</t>
+  </si>
+  <si>
+    <t>drm56</t>
+  </si>
+  <si>
+    <t>0x58</t>
+  </si>
+  <si>
+    <t>drm_hex0x06</t>
+  </si>
+  <si>
+    <t>0x06</t>
+  </si>
+  <si>
+    <t>drm_hex0x07</t>
+  </si>
+  <si>
+    <t>0x07</t>
+  </si>
+  <si>
+    <t>drm_hex0x08</t>
+  </si>
+  <si>
     <t>DRM to Memory Check</t>
   </si>
   <si>
@@ -1267,6 +1268,9 @@
     <t>Allowed &lt;= 61</t>
   </si>
   <si>
+    <t>37.0</t>
+  </si>
+  <si>
     <t>61</t>
   </si>
   <si>
@@ -1309,21 +1313,12 @@
     <t>dft_hex0x05</t>
   </si>
   <si>
-    <t>0x05</t>
-  </si>
-  <si>
     <t>dft_hex0x06</t>
   </si>
   <si>
-    <t>0x06</t>
-  </si>
-  <si>
     <t>dft_hex0x07</t>
   </si>
   <si>
-    <t>0x07</t>
-  </si>
-  <si>
     <t>dft_hex0x08</t>
   </si>
   <si>
@@ -1444,7 +1439,7 @@
     <t>noconn</t>
   </si>
   <si>
-    <t>155</t>
+    <t>178</t>
   </si>
   <si>
     <t>nand2</t>
@@ -1525,7 +1520,7 @@
     <t>9</t>
   </si>
   <si>
-    <t>PEBBLEtielo</t>
+    <t>drmmodule</t>
   </si>
   <si>
     <t>dftprobeModel2</t>
@@ -1583,9 +1578,6 @@
   </si>
   <si>
     <t>capacitorfixed</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>voltage2current</t>
@@ -2014,137 +2006,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2159,7 +2031,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2179,7 +2051,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2194,7 +2066,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2209,17 +2081,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2234,12 +2106,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2254,17 +2126,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -2279,12 +2151,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2299,7 +2171,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2319,132 +2191,132 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2454,17 +2326,92 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2689,17 +2636,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2714,37 +2661,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -2754,42 +2701,42 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -2799,77 +2746,77 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -2879,22 +2826,22 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -2904,62 +2851,62 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2974,17 +2921,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2999,52 +2946,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -3059,81 +3006,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="B9" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3141,1268 +3088,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B33" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="B38" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="B39" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="B41" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B42" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="B43" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="B47" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="B48" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="B49" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="B51" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B52" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B55" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="B56" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="B57" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="B64" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="B67" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="B68" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="B69" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="B70" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="B77" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="B78" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B79" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B80" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="B81" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="B82" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="B83" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="B85" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="B86" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="B87" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="B88" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="B89" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="B90" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B91" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="B92" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="B93" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="B94" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="B95" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="B96" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="B97" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B98" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="B99" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="B100" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="B101" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="B102" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="B103" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="B106" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="B107" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="B108" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="B109" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="B110" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="B111" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="B112" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="B113" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="B116" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="B117" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="B118" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="B119" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B120" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="B121" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="B122" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="B123" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="B124" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="B125" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="B126" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="B127" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="B128" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="B129" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="B130" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B131" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="B132" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="B133" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="B134" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="B135" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="B136" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="B137" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="B138" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="B139" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="B140" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="B141" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="B142" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="B143" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="B144" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="B145" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="B146" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="B147" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="B148" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="B149" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B150" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="B151" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="B152" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="B153" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="B154" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="B155" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="B156" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="B157" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="B158" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="B159" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="B160" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="B161" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="B162" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="B163" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="B164" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="B165" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="B166" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="B167" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="B168" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="B169" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="B170" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="B171" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="B172" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="B173" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="B174" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="B175" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="B176" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="B177" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="B178" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="B179" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="B180" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -4412,76 +4359,380 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>401</v>
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D5" t="s">
+        <v>384</v>
+      </c>
+      <c r="E5" t="s">
+        <v>385</v>
+      </c>
+      <c r="F5" t="s">
+        <v>385</v>
+      </c>
+      <c r="G5" t="s">
+        <v>385</v>
+      </c>
+      <c r="H5" t="s">
+        <v>385</v>
+      </c>
+      <c r="I5" t="s">
+        <v>385</v>
+      </c>
+      <c r="J5" t="s">
+        <v>364</v>
+      </c>
+      <c r="K5" t="s">
+        <v>149</v>
+      </c>
+      <c r="L5" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>403</v>
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>386</v>
+      </c>
+      <c r="C6" t="s">
+        <v>312</v>
+      </c>
+      <c r="D6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E6" t="s">
+        <v>385</v>
+      </c>
+      <c r="F6" t="s">
+        <v>385</v>
+      </c>
+      <c r="G6" t="s">
+        <v>385</v>
+      </c>
+      <c r="H6" t="s">
+        <v>385</v>
+      </c>
+      <c r="I6" t="s">
+        <v>385</v>
+      </c>
+      <c r="J6" t="s">
+        <v>385</v>
+      </c>
+      <c r="K6" t="s">
+        <v>385</v>
+      </c>
+      <c r="L6" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" t="s">
+        <v>390</v>
+      </c>
+      <c r="E7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F7" t="s">
+        <v>280</v>
+      </c>
+      <c r="G7" t="s">
+        <v>149</v>
+      </c>
+      <c r="H7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I7" t="s">
+        <v>149</v>
+      </c>
+      <c r="J7" t="s">
+        <v>149</v>
+      </c>
+      <c r="K7" t="s">
+        <v>322</v>
+      </c>
+      <c r="L7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>392</v>
+      </c>
+      <c r="C8" t="s">
+        <v>360</v>
+      </c>
+      <c r="D8" t="s">
+        <v>387</v>
+      </c>
+      <c r="E8" t="s">
+        <v>385</v>
+      </c>
+      <c r="F8" t="s">
+        <v>385</v>
+      </c>
+      <c r="G8" t="s">
+        <v>385</v>
+      </c>
+      <c r="H8" t="s">
+        <v>385</v>
+      </c>
+      <c r="I8" t="s">
+        <v>385</v>
+      </c>
+      <c r="J8" t="s">
+        <v>385</v>
+      </c>
+      <c r="K8" t="s">
+        <v>385</v>
+      </c>
+      <c r="L8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" t="s">
+        <v>393</v>
+      </c>
+      <c r="C9" t="s">
+        <v>394</v>
+      </c>
+      <c r="D9" t="s">
+        <v>395</v>
+      </c>
+      <c r="E9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G9" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" t="s">
+        <v>149</v>
+      </c>
+      <c r="I9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J9" t="s">
+        <v>149</v>
+      </c>
+      <c r="K9" t="s">
+        <v>362</v>
+      </c>
+      <c r="L9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" t="s">
+        <v>397</v>
+      </c>
+      <c r="C10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D10" t="s">
+        <v>387</v>
+      </c>
+      <c r="E10" t="s">
+        <v>385</v>
+      </c>
+      <c r="F10" t="s">
+        <v>385</v>
+      </c>
+      <c r="G10" t="s">
+        <v>385</v>
+      </c>
+      <c r="H10" t="s">
+        <v>385</v>
+      </c>
+      <c r="I10" t="s">
+        <v>385</v>
+      </c>
+      <c r="J10" t="s">
+        <v>385</v>
+      </c>
+      <c r="K10" t="s">
+        <v>385</v>
+      </c>
+      <c r="L10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" t="s">
+        <v>399</v>
+      </c>
+      <c r="C11" t="s">
+        <v>400</v>
+      </c>
+      <c r="D11" t="s">
+        <v>395</v>
+      </c>
+      <c r="E11" t="s">
+        <v>385</v>
+      </c>
+      <c r="F11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" t="s">
+        <v>149</v>
+      </c>
+      <c r="H11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I11" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" t="s">
+        <v>149</v>
+      </c>
+      <c r="K11" t="s">
+        <v>149</v>
+      </c>
+      <c r="L11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>401</v>
+      </c>
+      <c r="C12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D12" t="s">
+        <v>387</v>
+      </c>
+      <c r="E12" t="s">
+        <v>385</v>
+      </c>
+      <c r="F12" t="s">
+        <v>385</v>
+      </c>
+      <c r="G12" t="s">
+        <v>385</v>
+      </c>
+      <c r="H12" t="s">
+        <v>385</v>
+      </c>
+      <c r="I12" t="s">
+        <v>385</v>
+      </c>
+      <c r="J12" t="s">
+        <v>385</v>
+      </c>
+      <c r="K12" t="s">
+        <v>385</v>
+      </c>
+      <c r="L12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>405</v>
+      </c>
+      <c r="B15" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -4496,7 +4747,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -4511,82 +4762,82 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C5" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="D5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C6" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="D6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C7" t="s">
+        <v>415</v>
+      </c>
+      <c r="D7" t="s">
         <v>413</v>
-      </c>
-      <c r="D7" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C8" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4594,13 +4845,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C9" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="D9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4608,69 +4859,69 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
+        <v>419</v>
+      </c>
+      <c r="C10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D10" t="s">
         <v>417</v>
-      </c>
-      <c r="C10" t="s">
-        <v>418</v>
-      </c>
-      <c r="D10" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C11" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="D11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B12" t="s">
         <v>421</v>
       </c>
       <c r="C12" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="D12" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C13" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B14" t="s">
+        <v>423</v>
+      </c>
+      <c r="C14" t="s">
         <v>424</v>
       </c>
-      <c r="C14" t="s">
-        <v>425</v>
-      </c>
       <c r="D14" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4678,153 +4929,153 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C15" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="D15" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C16" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="D16" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
+        <v>427</v>
+      </c>
+      <c r="C17" t="s">
         <v>428</v>
       </c>
-      <c r="C17" t="s">
-        <v>429</v>
-      </c>
       <c r="D17" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B18" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C18" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="D18" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C19" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="D19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
+        <v>431</v>
+      </c>
+      <c r="C20" t="s">
         <v>432</v>
       </c>
-      <c r="C20" t="s">
-        <v>433</v>
-      </c>
       <c r="D20" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
+        <v>433</v>
+      </c>
+      <c r="C21" t="s">
         <v>434</v>
       </c>
-      <c r="C21" t="s">
-        <v>435</v>
-      </c>
       <c r="D21" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B22" t="s">
+        <v>435</v>
+      </c>
+      <c r="C22" t="s">
         <v>436</v>
       </c>
-      <c r="C22" t="s">
-        <v>437</v>
-      </c>
       <c r="D22" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B23" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C23" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="D23" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B24" t="s">
+        <v>438</v>
+      </c>
+      <c r="C24" t="s">
         <v>439</v>
       </c>
-      <c r="C24" t="s">
-        <v>440</v>
-      </c>
       <c r="D24" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C25" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="D25" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -4832,13 +5083,13 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C26" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="D26" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -4846,27 +5097,27 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C27" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="D27" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B28" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C28" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="D28" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4874,13 +5125,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C29" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="D29" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -4888,97 +5139,97 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C30" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="D30" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="B31" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C31" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="D31" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B32" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C32" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="D32" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B33" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C33" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="D33" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C34" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="D34" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s">
+        <v>450</v>
+      </c>
+      <c r="C35" t="s">
         <v>451</v>
       </c>
-      <c r="C35" t="s">
-        <v>452</v>
-      </c>
       <c r="D35" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
+        <v>452</v>
+      </c>
+      <c r="C36" t="s">
         <v>453</v>
       </c>
-      <c r="C36" t="s">
-        <v>454</v>
-      </c>
       <c r="D36" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -4988,12 +5239,12 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5003,490 +5254,482 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>457</v>
+      </c>
+      <c r="B5" t="s">
         <v>458</v>
-      </c>
-      <c r="B5" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>459</v>
+      </c>
+      <c r="B6" t="s">
         <v>460</v>
-      </c>
-      <c r="B6" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>461</v>
+      </c>
+      <c r="B7" t="s">
         <v>462</v>
-      </c>
-      <c r="B7" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>463</v>
+      </c>
+      <c r="B8" t="s">
         <v>464</v>
-      </c>
-      <c r="B8" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>465</v>
+      </c>
+      <c r="B9" t="s">
         <v>466</v>
-      </c>
-      <c r="B9" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B12" t="s">
         <v>470</v>
-      </c>
-      <c r="B12" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
+        <v>471</v>
+      </c>
+      <c r="B13" t="s">
         <v>472</v>
-      </c>
-      <c r="B13" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
+        <v>473</v>
+      </c>
+      <c r="B14" t="s">
         <v>474</v>
-      </c>
-      <c r="B14" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
+        <v>475</v>
+      </c>
+      <c r="B15" t="s">
         <v>476</v>
-      </c>
-      <c r="B15" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
+        <v>477</v>
+      </c>
+      <c r="B16" t="s">
         <v>478</v>
-      </c>
-      <c r="B16" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>479</v>
+      </c>
+      <c r="B17" t="s">
         <v>480</v>
-      </c>
-      <c r="B17" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
+        <v>481</v>
+      </c>
+      <c r="B18" t="s">
         <v>482</v>
-      </c>
-      <c r="B18" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B19" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
+        <v>484</v>
+      </c>
+      <c r="B20" t="s">
         <v>485</v>
-      </c>
-      <c r="B20" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B21" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
+        <v>487</v>
+      </c>
+      <c r="B22" t="s">
         <v>488</v>
-      </c>
-      <c r="B22" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B23" t="s">
-        <v>489</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B24" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B25" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B26" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B27" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B28" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B29" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B30" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B31" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B32" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B33" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B34" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B35" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B36" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B37" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B38" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B39" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B40" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B41" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B42" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B43" t="s">
-        <v>200</v>
+        <v>252</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B44" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B45" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B46" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B47" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B48" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B49" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B51" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B52" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B53" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B54" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B55" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B56" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B57" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B58" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B59" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B60" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B61" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B62" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B63" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>531</v>
-      </c>
-      <c r="B64" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -5651,7 +5894,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -5661,42 +5904,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="532">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -166,7 +166,100 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUTOPDELAY", "instance": "XUTOPDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -285,63 +378,26 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog5/fetdn_9694dc46.v:52: error: Unknown module type: fet_fetdn_9694dc46_Xfet
-2 error(s) during elaboration.
-*** These modules were missing:
-        fet_fetdn_9694dc46_Xfet referenced 1 times.
-***
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:75: error: can not select part of scalar: a0
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:75: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:84: error: can not select part of scalar: a0
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:84: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:114: error: can not select part of scalar: a0
+/celera/projects/Sunnyvale/software/WALTZ/verilog9/REGULATIONwaltz0COMPENSATION.v:114: error: Failed to elaborate port expression.
+6 error(s) during elaboration.
 </t>
   </si>
   <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 4, 'efficiency': '83.3%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER</t>
-  </si>
-  <si>
-    <t>{'name': 'drm64', 'bits': 64, 'noconns': 10, 'efficiency': '84.4%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION</t>
-  </si>
-  <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 7, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSEQUENCER</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE</t>
-  </si>
-  <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 8, 'bytes': 29.0, 'noconns': 43, 'efficiency': '81.5%'}</t>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
@@ -1202,123 +1258,72 @@
     <t>4</t>
   </si>
   <si>
-    <t>drm_hex0x01</t>
-  </si>
-  <si>
-    <t>drm24</t>
-  </si>
-  <si>
-    <t>na</t>
-  </si>
-  <si>
-    <t>drm_hex0x02</t>
-  </si>
-  <si>
-    <t>drm8</t>
-  </si>
-  <si>
-    <t>0x70</t>
-  </si>
-  <si>
-    <t>drm_hex0x03</t>
-  </si>
-  <si>
-    <t>drm64</t>
-  </si>
-  <si>
-    <t>0x78</t>
-  </si>
-  <si>
-    <t>drm_hex0x04</t>
-  </si>
-  <si>
-    <t>drm_hex0x05</t>
+    <t>DRM to Memory Check</t>
+  </si>
+  <si>
+    <t>TOTAL dec</t>
+  </si>
+  <si>
+    <t>Allowed &lt;= 61</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>Register Summary</t>
+  </si>
+  <si>
+    <t>DFT Summary</t>
+  </si>
+  <si>
+    <t>TMA</t>
+  </si>
+  <si>
+    <t>dft_hex0x01</t>
+  </si>
+  <si>
+    <t>DFTtm8</t>
+  </si>
+  <si>
+    <t>dft_hex0x02</t>
+  </si>
+  <si>
+    <t>DFTtm8t</t>
+  </si>
+  <si>
+    <t>dft_hex0x1A</t>
+  </si>
+  <si>
+    <t>0x1A</t>
+  </si>
+  <si>
+    <t>dft_hex0x03</t>
+  </si>
+  <si>
+    <t>DFTtm8d</t>
+  </si>
+  <si>
+    <t>dft_hex0x04</t>
+  </si>
+  <si>
+    <t>dft_hex0x05</t>
   </si>
   <si>
     <t>0x05</t>
   </si>
   <si>
-    <t>drm56</t>
-  </si>
-  <si>
-    <t>0x58</t>
-  </si>
-  <si>
-    <t>drm_hex0x06</t>
+    <t>dft_hex0x06</t>
   </si>
   <si>
     <t>0x06</t>
   </si>
   <si>
-    <t>drm_hex0x07</t>
+    <t>dft_hex0x07</t>
   </si>
   <si>
     <t>0x07</t>
   </si>
   <si>
-    <t>drm_hex0x08</t>
-  </si>
-  <si>
-    <t>DRM to Memory Check</t>
-  </si>
-  <si>
-    <t>TOTAL dec</t>
-  </si>
-  <si>
-    <t>Allowed &lt;= 61</t>
-  </si>
-  <si>
-    <t>37.0</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>Register Summary</t>
-  </si>
-  <si>
-    <t>DFT Summary</t>
-  </si>
-  <si>
-    <t>TMA</t>
-  </si>
-  <si>
-    <t>dft_hex0x01</t>
-  </si>
-  <si>
-    <t>DFTtm8</t>
-  </si>
-  <si>
-    <t>dft_hex0x02</t>
-  </si>
-  <si>
-    <t>DFTtm8t</t>
-  </si>
-  <si>
-    <t>dft_hex0x1A</t>
-  </si>
-  <si>
-    <t>0x1A</t>
-  </si>
-  <si>
-    <t>dft_hex0x03</t>
-  </si>
-  <si>
-    <t>DFTtm8d</t>
-  </si>
-  <si>
-    <t>dft_hex0x04</t>
-  </si>
-  <si>
-    <t>dft_hex0x05</t>
-  </si>
-  <si>
-    <t>dft_hex0x06</t>
-  </si>
-  <si>
-    <t>dft_hex0x07</t>
-  </si>
-  <si>
     <t>dft_hex0x08</t>
   </si>
   <si>
@@ -1439,7 +1444,7 @@
     <t>noconn</t>
   </si>
   <si>
-    <t>178</t>
+    <t>155</t>
   </si>
   <si>
     <t>nand2</t>
@@ -1520,7 +1525,7 @@
     <t>9</t>
   </si>
   <si>
-    <t>drmmodule</t>
+    <t>PEBBLEtielo</t>
   </si>
   <si>
     <t>dftprobeModel2</t>
@@ -1578,6 +1583,9 @@
   </si>
   <si>
     <t>capacitorfixed</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>voltage2current</t>
@@ -2006,17 +2014,137 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2031,7 +2159,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2051,7 +2179,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2066,7 +2194,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2081,17 +2209,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2106,12 +2234,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2126,17 +2254,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2151,12 +2279,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2171,7 +2299,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2191,132 +2319,132 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2326,92 +2454,17 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>93</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2636,17 +2689,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2661,37 +2714,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -2701,42 +2754,42 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -2746,77 +2799,77 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -2826,22 +2879,22 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -2851,62 +2904,62 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2921,17 +2974,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2946,52 +2999,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -3006,81 +3059,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="B11" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3088,1268 +3141,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="B20" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B21" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B32" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="B36" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="B49" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B50" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B55" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="B56" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B57" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B64" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B68" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B69" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="B70" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B77" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B78" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B79" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B80" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="B81" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="B82" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B83" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="B84" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="B86" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B87" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="B88" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B90" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="B91" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B92" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="B93" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B94" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="B95" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B96" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="B97" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B98" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B99" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B100" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B101" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B102" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B103" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B106" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="B107" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="B108" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="B109" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="B110" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="B111" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B112" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="B113" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B116" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B117" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="B118" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B119" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="B120" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="B121" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B122" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="B123" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="B124" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="B125" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B126" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B127" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B128" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="B129" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="B130" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B131" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B132" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B133" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B134" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B135" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B136" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B137" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B138" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="B139" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="B140" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B141" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="B142" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="B143" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B144" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="B145" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="B146" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B147" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="B148" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="B149" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="B150" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="B151" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="B152" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="B153" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="B154" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="B155" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="B156" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="B157" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B158" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="B159" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="B160" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="B161" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="B162" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="B163" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B164" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B165" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B166" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="B167" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="B168" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="B169" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="B170" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="B171" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="B172" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="B173" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="B174" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="B175" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="B176" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="B177" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="B178" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="B179" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="B180" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -4359,380 +4412,76 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" t="s">
-        <v>383</v>
-      </c>
-      <c r="C5" t="s">
-        <v>310</v>
-      </c>
-      <c r="D5" t="s">
-        <v>384</v>
-      </c>
-      <c r="E5" t="s">
-        <v>385</v>
-      </c>
-      <c r="F5" t="s">
-        <v>385</v>
-      </c>
-      <c r="G5" t="s">
-        <v>385</v>
-      </c>
-      <c r="H5" t="s">
-        <v>385</v>
-      </c>
-      <c r="I5" t="s">
-        <v>385</v>
-      </c>
-      <c r="J5" t="s">
-        <v>364</v>
-      </c>
-      <c r="K5" t="s">
-        <v>149</v>
-      </c>
-      <c r="L5" t="s">
-        <v>149</v>
+      <c r="A5" s="1" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>386</v>
-      </c>
-      <c r="C6" t="s">
-        <v>312</v>
-      </c>
-      <c r="D6" t="s">
-        <v>387</v>
-      </c>
-      <c r="E6" t="s">
-        <v>385</v>
-      </c>
-      <c r="F6" t="s">
-        <v>385</v>
-      </c>
-      <c r="G6" t="s">
-        <v>385</v>
-      </c>
-      <c r="H6" t="s">
-        <v>385</v>
-      </c>
-      <c r="I6" t="s">
-        <v>385</v>
-      </c>
-      <c r="J6" t="s">
-        <v>385</v>
-      </c>
-      <c r="K6" t="s">
-        <v>385</v>
-      </c>
-      <c r="L6" t="s">
-        <v>388</v>
+      <c r="A6" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>389</v>
-      </c>
-      <c r="C7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" t="s">
-        <v>390</v>
-      </c>
-      <c r="E7" t="s">
-        <v>149</v>
-      </c>
-      <c r="F7" t="s">
-        <v>280</v>
-      </c>
-      <c r="G7" t="s">
-        <v>149</v>
-      </c>
-      <c r="H7" t="s">
-        <v>149</v>
-      </c>
-      <c r="I7" t="s">
-        <v>149</v>
-      </c>
-      <c r="J7" t="s">
-        <v>149</v>
-      </c>
-      <c r="K7" t="s">
-        <v>322</v>
-      </c>
-      <c r="L7" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>392</v>
-      </c>
-      <c r="C8" t="s">
-        <v>360</v>
-      </c>
-      <c r="D8" t="s">
-        <v>387</v>
-      </c>
-      <c r="E8" t="s">
-        <v>385</v>
-      </c>
-      <c r="F8" t="s">
-        <v>385</v>
-      </c>
-      <c r="G8" t="s">
-        <v>385</v>
-      </c>
-      <c r="H8" t="s">
-        <v>385</v>
-      </c>
-      <c r="I8" t="s">
-        <v>385</v>
-      </c>
-      <c r="J8" t="s">
-        <v>385</v>
-      </c>
-      <c r="K8" t="s">
-        <v>385</v>
-      </c>
-      <c r="L8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" t="s">
-        <v>393</v>
-      </c>
-      <c r="C9" t="s">
-        <v>394</v>
-      </c>
-      <c r="D9" t="s">
-        <v>395</v>
-      </c>
-      <c r="E9" t="s">
-        <v>385</v>
-      </c>
-      <c r="F9" t="s">
-        <v>149</v>
-      </c>
-      <c r="G9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H9" t="s">
-        <v>149</v>
-      </c>
-      <c r="I9" t="s">
-        <v>149</v>
-      </c>
-      <c r="J9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K9" t="s">
-        <v>362</v>
-      </c>
-      <c r="L9" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" t="s">
-        <v>397</v>
-      </c>
-      <c r="C10" t="s">
-        <v>398</v>
-      </c>
-      <c r="D10" t="s">
-        <v>387</v>
-      </c>
-      <c r="E10" t="s">
-        <v>385</v>
-      </c>
-      <c r="F10" t="s">
-        <v>385</v>
-      </c>
-      <c r="G10" t="s">
-        <v>385</v>
-      </c>
-      <c r="H10" t="s">
-        <v>385</v>
-      </c>
-      <c r="I10" t="s">
-        <v>385</v>
-      </c>
-      <c r="J10" t="s">
-        <v>385</v>
-      </c>
-      <c r="K10" t="s">
-        <v>385</v>
-      </c>
-      <c r="L10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" t="s">
-        <v>399</v>
-      </c>
-      <c r="C11" t="s">
-        <v>400</v>
-      </c>
-      <c r="D11" t="s">
-        <v>395</v>
-      </c>
-      <c r="E11" t="s">
-        <v>385</v>
-      </c>
-      <c r="F11" t="s">
-        <v>149</v>
-      </c>
-      <c r="G11" t="s">
-        <v>149</v>
-      </c>
-      <c r="H11" t="s">
-        <v>149</v>
-      </c>
-      <c r="I11" t="s">
-        <v>149</v>
-      </c>
-      <c r="J11" t="s">
-        <v>149</v>
-      </c>
-      <c r="K11" t="s">
-        <v>149</v>
-      </c>
-      <c r="L11" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>401</v>
-      </c>
-      <c r="C12" t="s">
-        <v>362</v>
-      </c>
-      <c r="D12" t="s">
-        <v>387</v>
-      </c>
-      <c r="E12" t="s">
-        <v>385</v>
-      </c>
-      <c r="F12" t="s">
-        <v>385</v>
-      </c>
-      <c r="G12" t="s">
-        <v>385</v>
-      </c>
-      <c r="H12" t="s">
-        <v>385</v>
-      </c>
-      <c r="I12" t="s">
-        <v>385</v>
-      </c>
-      <c r="J12" t="s">
-        <v>385</v>
-      </c>
-      <c r="K12" t="s">
-        <v>385</v>
-      </c>
-      <c r="L12" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="B14" s="1" t="s">
         <v>404</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>405</v>
-      </c>
-      <c r="B15" t="s">
-        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -4747,7 +4496,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -4762,82 +4511,82 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C5" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C6" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C7" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="D8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4845,13 +4594,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C9" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D9" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4859,69 +4608,69 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C10" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="D10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
+        <v>419</v>
+      </c>
+      <c r="C11" t="s">
         <v>420</v>
       </c>
-      <c r="C11" t="s">
-        <v>398</v>
-      </c>
       <c r="D11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B12" t="s">
         <v>421</v>
       </c>
       <c r="C12" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="D12" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C13" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="D13" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D14" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4929,153 +4678,153 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C15" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="D15" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C16" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="D16" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C17" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D17" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B18" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C18" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="D18" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C19" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="D19" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C20" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D20" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D21" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C22" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D22" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C23" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="D23" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C24" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D24" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="B25" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C25" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="D25" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5083,13 +4832,13 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C26" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="D26" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5097,27 +4846,27 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C27" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="D27" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C28" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="D28" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -5125,13 +4874,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C29" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -5139,97 +4888,97 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C30" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="D30" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="B31" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C31" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="D31" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B32" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C32" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="D32" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B33" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C33" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="D33" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="B34" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C34" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="D34" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C35" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D35" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C36" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D36" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -5239,12 +4988,12 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5254,482 +5003,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B8" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B11" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B15" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B16" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B17" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B18" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
+        <v>484</v>
+      </c>
+      <c r="B19" t="s">
         <v>483</v>
-      </c>
-      <c r="B19" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B20" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
+        <v>487</v>
+      </c>
+      <c r="B21" t="s">
         <v>486</v>
-      </c>
-      <c r="B21" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B22" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
+        <v>490</v>
+      </c>
+      <c r="B23" t="s">
         <v>489</v>
-      </c>
-      <c r="B23" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B24" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B25" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B26" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B27" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B28" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B29" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B30" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B31" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B32" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B33" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B34" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B35" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B36" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B37" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B38" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B39" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B40" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B41" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B42" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B43" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B44" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B45" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B46" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B47" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B48" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B49" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B50" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B51" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B52" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B53" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B54" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B55" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B56" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B57" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B58" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B59" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B60" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B61" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B62" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s">
-        <v>252</v>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>531</v>
+      </c>
+      <c r="B64" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -5894,7 +5651,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -5904,7 +5661,42 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -30,16 +30,17 @@
     <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
     <sheet name="Project Summary" sheetId="22" r:id="rId22"/>
     <sheet name="Design Params and Codes" sheetId="23" r:id="rId23"/>
-    <sheet name="Register Summary" sheetId="24" r:id="rId24"/>
-    <sheet name="DFT Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="Nesto Usage Report" sheetId="26" r:id="rId26"/>
+    <sheet name="DRM Summary" sheetId="24" r:id="rId24"/>
+    <sheet name="Register Summary" sheetId="25" r:id="rId25"/>
+    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
+    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="833">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -131,10 +132,7 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>No Shorted Input Nets found.</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -146,7 +144,460 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_496698b1_XU8_be4c5eaa_XDEBUG(ten_496698b1_XU8_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_5e7931f3_XU7_be4c5eaa_XDEBUG(ten_5e7931f3_XU7_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7bb789c1_XU3_be4c5eaa_XDEBUG(ten_7bb789c1_XU3_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_bdb7126b_XU6_be4c5eaa_XDEBUG(ten_bdb7126b_XU6_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fc840bff_XU4_be4c5eaa_XDEBUG(ten_fc840bff_XU4_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_38b575fc_XU10_be4c5eaa_XDEBUG(ten_38b575fc_XU10_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_71505146_XU19_be4c5eaa_XDEBUG(ten_71505146_XU19_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_b20889dd_XU21_be4c5eaa_XDEBUG(ten_b20889dd_XU21_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f614d104_XU20_be4c5eaa_XDEBUG(ten_f614d104_XU20_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN(ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN(global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN(global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_016e5221_XU14_76edd7de_XCONTROL(ten_016e5221_XU14_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_10af5487_XU89_76edd7de_XCONTROL(ten_10af5487_XU89_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_1c924704_XU94_76edd7de_XCONTROL(ten_1c924704_XU94_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_250e1d7b_XU96_76edd7de_XCONTROL(ten_250e1d7b_XU96_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_3a54983a_XU93_76edd7de_XCONTROL(ten_3a54983a_XU93_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_5dbb5861_XU98_76edd7de_XCONTROL(ten_5dbb5861_XU98_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_78907f64_XU97_76edd7de_XCONTROL(ten_78907f64_XU97_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_9e0c6a0f_XU20_76edd7de_XCONTROL(ten_9e0c6a0f_XU20_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_a9541403_XU99_76edd7de_XCONTROL(ten_a9541403_XU99_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_b275df66_XU92_76edd7de_XCONTROL(ten_b275df66_XU92_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_c406e2e9_XU16_76edd7de_XCONTROL(ten_c406e2e9_XU16_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_dc7df0cc_XU18_76edd7de_XCONTROL(ten_dc7df0cc_XU18_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e1c50519_XU90_76edd7de_XCONTROL(ten_e1c50519_XU90_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e41e5cb3_XU95_76edd7de_XCONTROL(ten_e41e5cb3_XU95_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_efe3dfd4_XU91_76edd7de_XCONTROL(ten_efe3dfd4_XU91_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW(global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_2a0216d2_XU20_c1b82e6f_XDEBUG(ten_2a0216d2_XU20_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_32f97a89_XU11_c1b82e6f_XDEBUG(ten_32f97a89_XU11_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_34071f1d_XU15_c1b82e6f_XDEBUG(ten_34071f1d_XU15_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_3788e0aa_XU16_c1b82e6f_XDEBUG(ten_3788e0aa_XU16_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_e5798d25_XU18_c1b82e6f_XDEBUG(ten_e5798d25_XU18_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f83f6ba2_XU10_c1b82e6f_XDEBUG(ten_f83f6ba2_XU10_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fcfb2c12_XU12_c1b82e6f_XDEBUG(ten_fcfb2c12_XU12_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_af379456_XU5_c1b82e6f_XDEBUG(ten_hijack_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG(ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_cboot_35156756_XU17_f604d85e_XTOPSW(global_cboot_35156756_XU17_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW(global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW(ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW(global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW(ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6044b743_XU7_4c867da6_XDEBUG(ten_6044b743_XU7_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e48a0c0_XU2_4c867da6_XDEBUG(ten_7e48a0c0_XU2_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e6d3e04_XU1_4c867da6_XDEBUG(ten_7e6d3e04_XU1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_0b40c959_XU6_4c867da6_XDEBUG(ten_hijack_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_54e727e4_XU15_4c867da6_XDEBUG(ten_hijack_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9929432d_XU17_4c867da6_XDEBUG(ten_hijack_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG(ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG(ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9929432d_XU17_4c867da6_XDEBUG(ten_hijacki_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN(ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_14c9168a_XU7_1cec7299_XDEBUG(ten_14c9168a_XU7_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6d67c253_XU1_1cec7299_XDEBUG(ten_6d67c253_XU1_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_c69fe1aa_XU8_1cec7299_XDEBUG(ten_c69fe1aa_XU8_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1d78f0e4_XU13_1cec7299_XDEBUG(ten_1d78f0e4_XU13_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d748b831_XU15_1cec7299_XDEBUG(ten_d748b831_XU15_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f4762d45_XU11_1cec7299_XDEBUG(ten_f4762d45_XU11_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_6613b2af_XU3_1cec7299_XDEBUG(ten_hijack_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c541f94b_XU16_1cec7299_XDEBUG(ten_hijack_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG(ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG(ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG(ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_e96a4067_XU8_811a9a05_XMAIN(global_vbuffer_e96a4067_XU8_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN(ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_70e67769_XU3_811a9a05_XMAIN(global_comparator_70e67769_XU3_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_ddbf938d_XU22_811a9a05_XMAIN(global_comparator_ddbf938d_XU22_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_resistordivider_37d49b79_XU17_811a9a05_XMAIN(global_resistordivider_37d49b79_XU17_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_162b659f_XU9_f255c70e_XDEBUG(ten_162b659f_XU9_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_83ff2716_XU8_f255c70e_XDEBUG(ten_83ff2716_XU8_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_913fa695_XU7_f255c70e_XDEBUG(ten_913fa695_XU7_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_95483466_XU2_f255c70e_XDEBUG(ten_95483466_XU2_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d922ca5f_XU6_f255c70e_XDEBUG(ten_d922ca5f_XU6_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_de422ccd_XU11_f255c70e_XDEBUG(ten_hijack_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG(ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_gm_e44d2b4d_Xgm1_10783060_XMAIN(global_gm_e44d2b4d_Xgm1_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clamp_b8eb1a18_XU7_10783060_XMAIN(global_clamp_b8eb1a18_XU7_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_866ca25c_XU9_10783060_XMAIN(global_vbuffer_866ca25c_XU9_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_5c7dff44_XU10_10783060_XMAIN(global_comparator_5c7dff44_XU10_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_voltage2current_4215aede_XU3_10783060_XMAIN(global_voltage2current_4215aede_XU3_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_0721e5d9_XU56_5c792007_XSEQUENCER(ten_0721e5d9_XU56_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_2958f818_XU61_5c792007_XSEQUENCER(ten_2958f818_XU61_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_29fa69a5_XU60_5c792007_XSEQUENCER(ten_29fa69a5_XU60_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_3bd9bacc_XU59_5c792007_XSEQUENCER(ten_3bd9bacc_XU59_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_445acf01_XU57_5c792007_XSEQUENCER(ten_445acf01_XU57_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4c7ada73_XU65_5c792007_XSEQUENCER(ten_4c7ada73_XU65_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4d227e72_XU55_5c792007_XSEQUENCER(ten_4d227e72_XU55_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_6cd23b02_XU66_5c792007_XSEQUENCER(ten_6cd23b02_XU66_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_70525239_XU58_5c792007_XSEQUENCER(ten_70525239_XU58_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_950364d7_XU54_5c792007_XSEQUENCER(ten_950364d7_XU54_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9d829c39_XU62_5c792007_XSEQUENCER(ten_9d829c39_XU62_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9ef032e9_XU63_5c792007_XSEQUENCER(ten_9ef032e9_XU63_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_e8d90cd0_XU64_5c792007_XSEQUENCER(ten_e8d90cd0_XU64_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1955111b_XU7_63f6e3c4_XDEBUG(ten_1955111b_XU7_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_742857bf_XU2_63f6e3c4_XDEBUG(ten_742857bf_XU2_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_a6a0ac97_XU3_63f6e3c4_XDEBUG(ten_a6a0ac97_XU3_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ec5776d4_XU6_63f6e3c4_XDEBUG(ten_ec5776d4_XU6_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_cd882763_XU15_63f6e3c4_XDEBUG(ten_cd882763_XU15_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_ref_553d3e5b_XU4_2345cd7b_XMAIN(ten_ref_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN(ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_reference_553d3e5b_XU4_2345cd7b_XMAIN(global_reference_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN(global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_75c89176_XU16_2345cd7b_XMAIN(global_comparator_75c89176_XU16_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_81f80d4d_XU8_88e49508_XDEBUG(ten_81f80d4d_XU8_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ed87e5db_XU5_88e49508_XDEBUG(ten_ed87e5db_XU5_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f665b623_XU6_88e49508_XDEBUG(ten_f665b623_XU6_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_528f048c_XU10_88e49508_XDEBUG(ten_528f048c_XU10_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_297df8ef_XU1_88e49508_XDEBUG(ten_hijack_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_dcf795e2_XU14_88e49508_XDEBUG(ten_hijack_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_297df8ef_XU1_88e49508_XDEBUG(ten_hijacki_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG(ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_dac_0cc08401_XU5_b48f6491_XMAIN8(global_dac_0cc08401_XU5_b48f6491_XMAIN8)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8(global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -161,6 +612,420 @@
     <t>No Connects - Inputs</t>
   </si>
   <si>
+    <t>ten_496698b1_XU8_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_496698b1_XU8_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5e7931f3_XU7_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_5e7931f3_XU7_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7bb789c1_XU3_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7bb789c1_XU3_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_bdb7126b_XU6_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_bdb7126b_XU6_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fc840bff_XU4_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fc840bff_XU4_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_38b575fc_XU10_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_38b575fc_XU10_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_71505146_XU19_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_71505146_XU19_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b20889dd_XU21_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_b20889dd_XU21_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f614d104_XU20_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f614d104_XU20_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_016e5221_XU14_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_016e5221_XU14_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_10af5487_XU89_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_10af5487_XU89_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1c924704_XU94_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_1c924704_XU94_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_250e1d7b_XU96_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_250e1d7b_XU96_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3a54983a_XU93_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_3a54983a_XU93_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5dbb5861_XU98_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_5dbb5861_XU98_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_78907f64_XU97_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_78907f64_XU97_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9e0c6a0f_XU20_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_9e0c6a0f_XU20_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a9541403_XU99_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_a9541403_XU99_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b275df66_XU92_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_b275df66_XU92_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c406e2e9_XU16_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_c406e2e9_XU16_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_dc7df0cc_XU18_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_dc7df0cc_XU18_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e1c50519_XU90_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e1c50519_XU90_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e41e5cb3_XU95_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e41e5cb3_XU95_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_efe3dfd4_XU91_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_efe3dfd4_XU91_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2a0216d2_XU20_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_2a0216d2_XU20_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_32f97a89_XU11_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_32f97a89_XU11_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_34071f1d_XU15_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_34071f1d_XU15_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3788e0aa_XU16_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_3788e0aa_XU16_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e5798d25_XU18_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_e5798d25_XU18_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f83f6ba2_XU10_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f83f6ba2_XU10_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fcfb2c12_XU12_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fcfb2c12_XU12_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_cboot_35156756_XU17_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_cboot_35156756_XU17_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6044b743_XU7_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6044b743_XU7_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e48a0c0_XU2_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e48a0c0_XU2_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e6d3e04_XU1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e6d3e04_XU1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_14c9168a_XU7_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_14c9168a_XU7_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6d67c253_XU1_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6d67c253_XU1_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c69fe1aa_XU8_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_c69fe1aa_XU8_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1d78f0e4_XU13_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1d78f0e4_XU13_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d748b831_XU15_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d748b831_XU15_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f4762d45_XU11_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f4762d45_XU11_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_e96a4067_XU8_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_e96a4067_XU8_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_70e67769_XU3_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_70e67769_XU3_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_ddbf938d_XU22_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_ddbf938d_XU22_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_resistordivider_37d49b79_XU17_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_162b659f_XU9_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_162b659f_XU9_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_83ff2716_XU8_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_83ff2716_XU8_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_913fa695_XU7_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_913fa695_XU7_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_95483466_XU2_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_95483466_XU2_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d922ca5f_XU6_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d922ca5f_XU6_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_gm_e44d2b4d_Xgm1_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_gm_e44d2b4d_Xgm1_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clamp_b8eb1a18_XU7_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_clamp_b8eb1a18_XU7_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_866ca25c_XU9_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_866ca25c_XU9_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_5c7dff44_XU10_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_5c7dff44_XU10_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_voltage2current_4215aede_XU3_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_voltage2current_4215aede_XU3_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_0721e5d9_XU56_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_0721e5d9_XU56_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2958f818_XU61_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_2958f818_XU61_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_29fa69a5_XU60_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_29fa69a5_XU60_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3bd9bacc_XU59_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_3bd9bacc_XU59_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_445acf01_XU57_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_445acf01_XU57_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4c7ada73_XU65_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4c7ada73_XU65_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4d227e72_XU55_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4d227e72_XU55_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6cd23b02_XU66_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_6cd23b02_XU66_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_70525239_XU58_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_70525239_XU58_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_950364d7_XU54_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_950364d7_XU54_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9d829c39_XU62_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9d829c39_XU62_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9ef032e9_XU63_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9ef032e9_XU63_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e8d90cd0_XU64_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_e8d90cd0_XU64_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1955111b_XU7_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1955111b_XU7_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_742857bf_XU2_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_742857bf_XU2_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a6a0ac97_XU3_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_a6a0ac97_XU3_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ec5776d4_XU6_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ec5776d4_XU6_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_cd882763_XU15_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_cd882763_XU15_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ref_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_ref_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_reference_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_reference_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_75c89176_XU16_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_75c89176_XU16_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_81f80d4d_XU8_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_81f80d4d_XU8_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ed87e5db_XU5_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ed87e5db_XU5_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f665b623_XU6_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f665b623_XU6_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_528f048c_XU10_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_528f048c_XU10_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_dac_0cc08401_XU5_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_dac_0cc08401_XU5_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
     <t>Mixed Mode Conflicts</t>
   </si>
   <si>
@@ -173,9 +1038,6 @@
     <t>D to A Tree</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
-  </si>
-  <si>
     <t>Xoscillator1</t>
   </si>
   <si>
@@ -183,6 +1045,33 @@
   </si>
   <si>
     <t>Errors</t>
+  </si>
+  <si>
+    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
+  </si>
+  <si>
+    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
   </si>
   <si>
     <t>Cell Length Exceed Max 50</t>
@@ -279,139 +1168,97 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK</t>
   </si>
   <si>
+    <t>{'name': 'drm24', 'bits': 24, 'noconns': 4, 'efficiency': '83.3%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER</t>
+  </si>
+  <si>
+    <t>{'name': 'drm64', 'bits': 64, 'noconns': 10, 'efficiency': '84.4%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 7, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSEQUENCER</t>
+  </si>
+  <si>
     <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+    <t>XWALTZ,XceleraCORE,XSERVICE</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
   </si>
   <si>
     <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
+    <t>{'cells': 8, 'bytes': 29.0, 'noconns': 43, 'efficiency': '81.5%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
-  </si>
-  <si>
     <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
-  </si>
-  <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
-  </si>
-  <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
+    <t>{'cells': 44, 'bytes': 44.0, 'noconns': 44, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>Project Summary</t>
@@ -1161,27 +2008,111 @@
     <t>measure_reset_command</t>
   </si>
   <si>
+    <t>DRM Summary</t>
+  </si>
+  <si>
+    <t>Addresses</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Instance</t>
+  </si>
+  <si>
+    <t>TMB</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>drm_hex0x01</t>
+  </si>
+  <si>
+    <t>drm24</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>drm_hex0x02</t>
+  </si>
+  <si>
+    <t>drm8</t>
+  </si>
+  <si>
+    <t>0x70</t>
+  </si>
+  <si>
+    <t>drm_hex0x03</t>
+  </si>
+  <si>
+    <t>drm64</t>
+  </si>
+  <si>
+    <t>0x63</t>
+  </si>
+  <si>
+    <t>drm_hex0x04</t>
+  </si>
+  <si>
+    <t>drm_hex0x05</t>
+  </si>
+  <si>
+    <t>0x05</t>
+  </si>
+  <si>
+    <t>drm56</t>
+  </si>
+  <si>
+    <t>0x58</t>
+  </si>
+  <si>
+    <t>drm_hex0x06</t>
+  </si>
+  <si>
+    <t>0x06</t>
+  </si>
+  <si>
+    <t>drm_hex0x07</t>
+  </si>
+  <si>
+    <t>0x07</t>
+  </si>
+  <si>
+    <t>drm_hex0x08</t>
+  </si>
+  <si>
+    <t>DRM to Memory Check</t>
+  </si>
+  <si>
+    <t>TOTAL dec</t>
+  </si>
+  <si>
+    <t>Allowed &lt;= 61</t>
+  </si>
+  <si>
+    <t>37.0</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
     <t>Register Summary</t>
   </si>
   <si>
     <t>DFT Summary</t>
   </si>
   <si>
-    <t>Addresses</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Instance</t>
-  </si>
-  <si>
     <t>TMA</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>dft_hex0x01</t>
   </si>
   <si>
@@ -1191,51 +2122,66 @@
     <t>dft_hex0x02</t>
   </si>
   <si>
+    <t>DFTtm8d</t>
+  </si>
+  <si>
+    <t>dft_hex0x16</t>
+  </si>
+  <si>
+    <t>dft_hex0x17</t>
+  </si>
+  <si>
+    <t>dft_hex0x03</t>
+  </si>
+  <si>
+    <t>dft_hex0x04</t>
+  </si>
+  <si>
+    <t>dft_hex0x18</t>
+  </si>
+  <si>
+    <t>dft_hex0x19</t>
+  </si>
+  <si>
+    <t>0x19</t>
+  </si>
+  <si>
+    <t>dft_hex0x05</t>
+  </si>
+  <si>
+    <t>dft_hex0x06</t>
+  </si>
+  <si>
+    <t>dft_hex0x07</t>
+  </si>
+  <si>
     <t>DFTtm8t</t>
   </si>
   <si>
+    <t>dft_hex0x08</t>
+  </si>
+  <si>
     <t>dft_hex0x1A</t>
   </si>
   <si>
     <t>0x1A</t>
   </si>
   <si>
-    <t>dft_hex0x03</t>
-  </si>
-  <si>
-    <t>DFTtm8d</t>
-  </si>
-  <si>
-    <t>dft_hex0x04</t>
-  </si>
-  <si>
-    <t>dft_hex0x05</t>
-  </si>
-  <si>
-    <t>0x05</t>
-  </si>
-  <si>
-    <t>dft_hex0x06</t>
-  </si>
-  <si>
-    <t>0x06</t>
-  </si>
-  <si>
-    <t>dft_hex0x07</t>
-  </si>
-  <si>
-    <t>0x07</t>
-  </si>
-  <si>
-    <t>dft_hex0x08</t>
-  </si>
-  <si>
     <t>dft_hex0x1B</t>
   </si>
   <si>
     <t>0x1B</t>
   </si>
   <si>
+    <t>dft_hex0x1C</t>
+  </si>
+  <si>
+    <t>dft_hex0x1D</t>
+  </si>
+  <si>
+    <t>0x1D</t>
+  </si>
+  <si>
     <t>dft_hex0x09</t>
   </si>
   <si>
@@ -1248,24 +2194,54 @@
     <t>0x0B</t>
   </si>
   <si>
+    <t>dft_hex0x1E</t>
+  </si>
+  <si>
+    <t>0x1E</t>
+  </si>
+  <si>
+    <t>dft_hex0x1F</t>
+  </si>
+  <si>
+    <t>dft_hex0x20</t>
+  </si>
+  <si>
+    <t>0x20</t>
+  </si>
+  <si>
+    <t>dft_hex0x21</t>
+  </si>
+  <si>
+    <t>0x21</t>
+  </si>
+  <si>
     <t>dft_hex0x0C</t>
   </si>
   <si>
-    <t>dft_hex0x1C</t>
-  </si>
-  <si>
-    <t>dft_hex0x1D</t>
-  </si>
-  <si>
-    <t>0x1D</t>
-  </si>
-  <si>
     <t>dft_hex0x0D</t>
   </si>
   <si>
     <t>0x0D</t>
   </si>
   <si>
+    <t>dft_hex0x22</t>
+  </si>
+  <si>
+    <t>0x22</t>
+  </si>
+  <si>
+    <t>dft_hex0x23</t>
+  </si>
+  <si>
+    <t>0x23</t>
+  </si>
+  <si>
+    <t>dft_hex0x24</t>
+  </si>
+  <si>
+    <t>0x24</t>
+  </si>
+  <si>
     <t>dft_hex0x0E</t>
   </si>
   <si>
@@ -1275,10 +2251,16 @@
     <t>dft_hex0x0F</t>
   </si>
   <si>
-    <t>dft_hex0x1E</t>
-  </si>
-  <si>
-    <t>0x1E</t>
+    <t>dft_hex0x25</t>
+  </si>
+  <si>
+    <t>0x25</t>
+  </si>
+  <si>
+    <t>dft_hex0x26</t>
+  </si>
+  <si>
+    <t>0x26</t>
   </si>
   <si>
     <t>dft_hex0x10</t>
@@ -1287,7 +2269,16 @@
     <t>dft_hex0x11</t>
   </si>
   <si>
-    <t>dft_hex0x1F</t>
+    <t>dft_hex0x27</t>
+  </si>
+  <si>
+    <t>0x27</t>
+  </si>
+  <si>
+    <t>dft_hex0x28</t>
+  </si>
+  <si>
+    <t>0x28</t>
   </si>
   <si>
     <t>dft_hex0x12</t>
@@ -1296,31 +2287,34 @@
     <t>dft_hex0x13</t>
   </si>
   <si>
+    <t>dft_hex0x29</t>
+  </si>
+  <si>
+    <t>0x29</t>
+  </si>
+  <si>
+    <t>dft_hex0x2A</t>
+  </si>
+  <si>
+    <t>0x2A</t>
+  </si>
+  <si>
     <t>dft_hex0x14</t>
   </si>
   <si>
     <t>dft_hex0x15</t>
   </si>
   <si>
-    <t>dft_hex0x16</t>
-  </si>
-  <si>
-    <t>dft_hex0x17</t>
-  </si>
-  <si>
-    <t>dft_hex0x18</t>
-  </si>
-  <si>
-    <t>dft_hex0x20</t>
-  </si>
-  <si>
-    <t>0x20</t>
-  </si>
-  <si>
-    <t>dft_hex0x19</t>
-  </si>
-  <si>
-    <t>0x19</t>
+    <t>dft_hex0x2B</t>
+  </si>
+  <si>
+    <t>0x2B</t>
+  </si>
+  <si>
+    <t>dft_hex0x2C</t>
+  </si>
+  <si>
+    <t>0x2C</t>
   </si>
   <si>
     <t>Nesto Usage Report</t>
@@ -1341,7 +2335,7 @@
     <t>noconn</t>
   </si>
   <si>
-    <t>198</t>
+    <t>211</t>
   </si>
   <si>
     <t>inv</t>
@@ -1365,9 +2359,6 @@
     <t>nor3</t>
   </si>
   <si>
-    <t>61</t>
-  </si>
-  <si>
     <t>dftprobeModel0</t>
   </si>
   <si>
@@ -1389,6 +2380,12 @@
     <t>45</t>
   </si>
   <si>
+    <t>dftmodule</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
     <t>srlatch</t>
   </si>
   <si>
@@ -1401,12 +2398,6 @@
     <t>35</t>
   </si>
   <si>
-    <t>dftmodule</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
     <t>dfthijack</t>
   </si>
   <si>
@@ -1416,37 +2407,28 @@
     <t>dff</t>
   </si>
   <si>
+    <t>tie</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>datamap0</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>drmmodule</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>tie</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>datamap0</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>dftprobeModel2</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>resistor</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>oneshot</t>
@@ -1931,7 +2913,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1951,7 +2933,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1966,7 +2948,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -1981,17 +2963,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -2001,17 +2983,62 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -2026,17 +3053,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -2051,12 +3078,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -2071,7 +3098,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2091,127 +3118,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>356</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>362</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>363</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>368</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>369</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>75</v>
+        <v>371</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -2221,162 +3248,92 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>78</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>381</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>85</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>384</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>385</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>90</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -2391,17 +3348,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -2621,257 +3578,277 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>100</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>104</v>
+      <c r="A8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
+      <c r="A11" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>85</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>107</v>
+      <c r="A18" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>396</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>16</v>
+      <c r="A23" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>111</v>
+      <c r="A25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>398</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>393</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>395</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>395</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>113</v>
+      <c r="A33" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>114</v>
+      <c r="A36" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>391</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>115</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>116</v>
+        <v>380</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>391</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="1" t="s">
-        <v>18</v>
+      <c r="A44" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>118</v>
+        <v>401</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>92</v>
+      <c r="A47" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>402</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>25</v>
+      <c r="A51" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>117</v>
+      <c r="A53" s="1" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>119</v>
+      <c r="A55" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>110</v>
+        <v>391</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>101</v>
+      <c r="A58" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>103</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="1" t="s">
-        <v>120</v>
+      <c r="A62" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>103</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -2886,17 +3863,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -2911,52 +3888,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>130</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -2971,81 +3948,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>415</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>134</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>135</v>
+        <v>417</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>419</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>421</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>423</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>142</v>
+        <v>424</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>425</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>145</v>
+        <v>427</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>147</v>
+        <v>429</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>430</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3053,1268 +4030,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>150</v>
+        <v>432</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>151</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>153</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>154</v>
+        <v>436</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>135</v>
+        <v>417</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>136</v>
+        <v>418</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>155</v>
+        <v>437</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>438</v>
       </c>
       <c r="B21" t="s">
-        <v>138</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>157</v>
+        <v>439</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>135</v>
+        <v>417</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>136</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>159</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>135</v>
+        <v>417</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>136</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>442</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>161</v>
+        <v>443</v>
       </c>
       <c r="B28" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>162</v>
+        <v>444</v>
       </c>
       <c r="B29" t="s">
-        <v>163</v>
+        <v>445</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>446</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>165</v>
+        <v>447</v>
       </c>
       <c r="B31" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>166</v>
+        <v>448</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>449</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>168</v>
+        <v>450</v>
       </c>
       <c r="B33" t="s">
-        <v>169</v>
+        <v>451</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>170</v>
+        <v>452</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>453</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>172</v>
+        <v>454</v>
       </c>
       <c r="B35" t="s">
-        <v>173</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>174</v>
+        <v>456</v>
       </c>
       <c r="B36" t="s">
-        <v>175</v>
+        <v>457</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>176</v>
+        <v>458</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>177</v>
+        <v>459</v>
       </c>
       <c r="B38" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>178</v>
+        <v>460</v>
       </c>
       <c r="B39" t="s">
-        <v>179</v>
+        <v>461</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>180</v>
+        <v>462</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>181</v>
+        <v>463</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>182</v>
+        <v>464</v>
       </c>
       <c r="B42" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>183</v>
+        <v>465</v>
       </c>
       <c r="B43" t="s">
-        <v>184</v>
+        <v>466</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>185</v>
+        <v>467</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>135</v>
+        <v>417</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>136</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>468</v>
       </c>
       <c r="B46" t="s">
-        <v>187</v>
+        <v>469</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>188</v>
+        <v>470</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>420</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>189</v>
+        <v>471</v>
       </c>
       <c r="B48" t="s">
-        <v>179</v>
+        <v>461</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>190</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s">
-        <v>138</v>
+        <v>420</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>191</v>
+        <v>473</v>
       </c>
       <c r="B50" t="s">
-        <v>138</v>
+        <v>420</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>192</v>
+        <v>474</v>
       </c>
       <c r="B51" t="s">
-        <v>193</v>
+        <v>475</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>194</v>
+        <v>476</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>195</v>
+        <v>477</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>135</v>
+        <v>417</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>136</v>
+        <v>418</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>196</v>
+        <v>478</v>
       </c>
       <c r="B55" t="s">
-        <v>197</v>
+        <v>479</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>198</v>
+        <v>480</v>
       </c>
       <c r="B56" t="s">
-        <v>199</v>
+        <v>481</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>200</v>
+        <v>482</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>201</v>
+        <v>483</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>135</v>
+        <v>417</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>136</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>202</v>
+        <v>484</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>203</v>
+        <v>485</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>486</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>205</v>
+        <v>487</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>206</v>
+        <v>488</v>
       </c>
       <c r="B64" t="s">
-        <v>207</v>
+        <v>489</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>208</v>
+        <v>490</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>209</v>
+        <v>491</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>210</v>
+        <v>492</v>
       </c>
       <c r="B67" t="s">
-        <v>211</v>
+        <v>493</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>212</v>
+        <v>494</v>
       </c>
       <c r="B68" t="s">
-        <v>213</v>
+        <v>495</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>214</v>
+        <v>496</v>
       </c>
       <c r="B69" t="s">
-        <v>211</v>
+        <v>493</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>215</v>
+        <v>497</v>
       </c>
       <c r="B70" t="s">
-        <v>213</v>
+        <v>495</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>216</v>
+        <v>498</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>217</v>
+        <v>499</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>218</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>219</v>
+        <v>501</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>220</v>
+        <v>502</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>135</v>
+        <v>417</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>136</v>
+        <v>418</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>221</v>
+        <v>503</v>
       </c>
       <c r="B77" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>222</v>
+        <v>504</v>
       </c>
       <c r="B78" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>223</v>
+        <v>505</v>
       </c>
       <c r="B79" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>224</v>
+        <v>506</v>
       </c>
       <c r="B80" t="s">
-        <v>225</v>
+        <v>507</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>226</v>
+        <v>508</v>
       </c>
       <c r="B81" t="s">
-        <v>227</v>
+        <v>509</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>228</v>
+        <v>510</v>
       </c>
       <c r="B82" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>229</v>
+        <v>511</v>
       </c>
       <c r="B83" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>230</v>
+        <v>512</v>
       </c>
       <c r="B84" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="B85" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>232</v>
+        <v>514</v>
       </c>
       <c r="B86" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>233</v>
+        <v>515</v>
       </c>
       <c r="B87" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>234</v>
+        <v>516</v>
       </c>
       <c r="B88" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>235</v>
+        <v>517</v>
       </c>
       <c r="B89" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>236</v>
+        <v>518</v>
       </c>
       <c r="B90" t="s">
-        <v>237</v>
+        <v>519</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>238</v>
+        <v>520</v>
       </c>
       <c r="B91" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>239</v>
+        <v>521</v>
       </c>
       <c r="B92" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>240</v>
+        <v>522</v>
       </c>
       <c r="B93" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>241</v>
+        <v>523</v>
       </c>
       <c r="B94" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>242</v>
+        <v>524</v>
       </c>
       <c r="B95" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>243</v>
+        <v>525</v>
       </c>
       <c r="B96" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>244</v>
+        <v>526</v>
       </c>
       <c r="B97" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>245</v>
+        <v>527</v>
       </c>
       <c r="B98" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>246</v>
+        <v>528</v>
       </c>
       <c r="B99" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>247</v>
+        <v>529</v>
       </c>
       <c r="B100" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>248</v>
+        <v>530</v>
       </c>
       <c r="B101" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>250</v>
+        <v>532</v>
       </c>
       <c r="B102" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>251</v>
+        <v>533</v>
       </c>
       <c r="B103" t="s">
-        <v>171</v>
+        <v>453</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>252</v>
+        <v>534</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>135</v>
+        <v>417</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>136</v>
+        <v>418</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>253</v>
+        <v>535</v>
       </c>
       <c r="B106" t="s">
-        <v>254</v>
+        <v>536</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>255</v>
+        <v>537</v>
       </c>
       <c r="B107" t="s">
-        <v>256</v>
+        <v>538</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>257</v>
+        <v>539</v>
       </c>
       <c r="B108" t="s">
-        <v>258</v>
+        <v>540</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>259</v>
+        <v>541</v>
       </c>
       <c r="B109" t="s">
-        <v>260</v>
+        <v>542</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>261</v>
+        <v>543</v>
       </c>
       <c r="B110" t="s">
-        <v>262</v>
+        <v>544</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>263</v>
+        <v>545</v>
       </c>
       <c r="B111" t="s">
-        <v>264</v>
+        <v>546</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>265</v>
+        <v>547</v>
       </c>
       <c r="B112" t="s">
-        <v>266</v>
+        <v>548</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>267</v>
+        <v>549</v>
       </c>
       <c r="B113" t="s">
-        <v>193</v>
+        <v>475</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>268</v>
+        <v>550</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>135</v>
+        <v>417</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>136</v>
+        <v>418</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>269</v>
+        <v>551</v>
       </c>
       <c r="B116" t="s">
-        <v>184</v>
+        <v>466</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>270</v>
+        <v>552</v>
       </c>
       <c r="B117" t="s">
-        <v>271</v>
+        <v>553</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>272</v>
+        <v>554</v>
       </c>
       <c r="B118" t="s">
-        <v>273</v>
+        <v>555</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>274</v>
+        <v>556</v>
       </c>
       <c r="B119" t="s">
-        <v>275</v>
+        <v>557</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>276</v>
+        <v>558</v>
       </c>
       <c r="B120" t="s">
-        <v>277</v>
+        <v>559</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>278</v>
+        <v>560</v>
       </c>
       <c r="B121" t="s">
-        <v>279</v>
+        <v>561</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>280</v>
+        <v>562</v>
       </c>
       <c r="B122" t="s">
-        <v>281</v>
+        <v>563</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>282</v>
+        <v>564</v>
       </c>
       <c r="B123" t="s">
-        <v>277</v>
+        <v>559</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>283</v>
+        <v>565</v>
       </c>
       <c r="B124" t="s">
-        <v>279</v>
+        <v>561</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>284</v>
+        <v>566</v>
       </c>
       <c r="B125" t="s">
-        <v>281</v>
+        <v>563</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>285</v>
+        <v>567</v>
       </c>
       <c r="B126" t="s">
-        <v>286</v>
+        <v>568</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>287</v>
+        <v>569</v>
       </c>
       <c r="B127" t="s">
-        <v>288</v>
+        <v>570</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>289</v>
+        <v>571</v>
       </c>
       <c r="B128" t="s">
-        <v>290</v>
+        <v>572</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>291</v>
+        <v>573</v>
       </c>
       <c r="B129" t="s">
-        <v>292</v>
+        <v>574</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>293</v>
+        <v>575</v>
       </c>
       <c r="B130" t="s">
-        <v>294</v>
+        <v>576</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>245</v>
+        <v>527</v>
       </c>
       <c r="B131" t="s">
-        <v>295</v>
+        <v>577</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>246</v>
+        <v>528</v>
       </c>
       <c r="B132" t="s">
-        <v>296</v>
+        <v>578</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>248</v>
+        <v>530</v>
       </c>
       <c r="B133" t="s">
-        <v>297</v>
+        <v>579</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>247</v>
+        <v>529</v>
       </c>
       <c r="B134" t="s">
-        <v>298</v>
+        <v>580</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>299</v>
+        <v>581</v>
       </c>
       <c r="B135" t="s">
-        <v>184</v>
+        <v>466</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>300</v>
+        <v>582</v>
       </c>
       <c r="B136" t="s">
-        <v>301</v>
+        <v>583</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>302</v>
+        <v>584</v>
       </c>
       <c r="B137" t="s">
-        <v>303</v>
+        <v>585</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>304</v>
+        <v>586</v>
       </c>
       <c r="B138" t="s">
-        <v>305</v>
+        <v>587</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>306</v>
+        <v>588</v>
       </c>
       <c r="B139" t="s">
-        <v>307</v>
+        <v>589</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>308</v>
+        <v>590</v>
       </c>
       <c r="B140" t="s">
-        <v>309</v>
+        <v>591</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>310</v>
+        <v>592</v>
       </c>
       <c r="B141" t="s">
-        <v>277</v>
+        <v>559</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>311</v>
+        <v>593</v>
       </c>
       <c r="B142" t="s">
-        <v>279</v>
+        <v>561</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>312</v>
+        <v>594</v>
       </c>
       <c r="B143" t="s">
-        <v>281</v>
+        <v>563</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>313</v>
+        <v>595</v>
       </c>
       <c r="B144" t="s">
-        <v>286</v>
+        <v>568</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>314</v>
+        <v>596</v>
       </c>
       <c r="B145" t="s">
-        <v>288</v>
+        <v>570</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>315</v>
+        <v>597</v>
       </c>
       <c r="B146" t="s">
-        <v>290</v>
+        <v>572</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>316</v>
+        <v>598</v>
       </c>
       <c r="B147" t="s">
-        <v>292</v>
+        <v>574</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>317</v>
+        <v>599</v>
       </c>
       <c r="B148" t="s">
-        <v>294</v>
+        <v>576</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>318</v>
+        <v>600</v>
       </c>
       <c r="B149" t="s">
-        <v>319</v>
+        <v>601</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>320</v>
+        <v>602</v>
       </c>
       <c r="B150" t="s">
-        <v>321</v>
+        <v>603</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>322</v>
+        <v>604</v>
       </c>
       <c r="B151" t="s">
-        <v>323</v>
+        <v>605</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>324</v>
+        <v>606</v>
       </c>
       <c r="B152" t="s">
-        <v>325</v>
+        <v>607</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>326</v>
+        <v>608</v>
       </c>
       <c r="B153" t="s">
-        <v>327</v>
+        <v>609</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>328</v>
+        <v>610</v>
       </c>
       <c r="B154" t="s">
-        <v>329</v>
+        <v>611</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>330</v>
+        <v>612</v>
       </c>
       <c r="B155" t="s">
-        <v>331</v>
+        <v>613</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>332</v>
+        <v>614</v>
       </c>
       <c r="B156" t="s">
-        <v>333</v>
+        <v>615</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>334</v>
+        <v>616</v>
       </c>
       <c r="B157" t="s">
-        <v>335</v>
+        <v>617</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>336</v>
+        <v>618</v>
       </c>
       <c r="B158" t="s">
-        <v>337</v>
+        <v>619</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>338</v>
+        <v>620</v>
       </c>
       <c r="B159" t="s">
-        <v>339</v>
+        <v>621</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>340</v>
+        <v>622</v>
       </c>
       <c r="B160" t="s">
-        <v>341</v>
+        <v>623</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>342</v>
+        <v>624</v>
       </c>
       <c r="B161" t="s">
-        <v>343</v>
+        <v>625</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>344</v>
+        <v>626</v>
       </c>
       <c r="B162" t="s">
-        <v>345</v>
+        <v>627</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>346</v>
+        <v>628</v>
       </c>
       <c r="B163" t="s">
-        <v>347</v>
+        <v>629</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>348</v>
+        <v>630</v>
       </c>
       <c r="B164" t="s">
-        <v>349</v>
+        <v>631</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>350</v>
+        <v>632</v>
       </c>
       <c r="B165" t="s">
-        <v>351</v>
+        <v>633</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>352</v>
+        <v>634</v>
       </c>
       <c r="B166" t="s">
-        <v>325</v>
+        <v>607</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>353</v>
+        <v>635</v>
       </c>
       <c r="B167" t="s">
-        <v>307</v>
+        <v>589</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>354</v>
+        <v>636</v>
       </c>
       <c r="B168" t="s">
-        <v>309</v>
+        <v>591</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="B169" t="s">
-        <v>167</v>
+        <v>449</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>356</v>
+        <v>638</v>
       </c>
       <c r="B170" t="s">
-        <v>357</v>
+        <v>639</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>358</v>
+        <v>640</v>
       </c>
       <c r="B171" t="s">
-        <v>359</v>
+        <v>641</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>360</v>
+        <v>642</v>
       </c>
       <c r="B172" t="s">
-        <v>361</v>
+        <v>643</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>362</v>
+        <v>644</v>
       </c>
       <c r="B173" t="s">
-        <v>363</v>
+        <v>645</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>364</v>
+        <v>646</v>
       </c>
       <c r="B174" t="s">
-        <v>146</v>
+        <v>428</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>365</v>
+        <v>647</v>
       </c>
       <c r="B175" t="s">
-        <v>277</v>
+        <v>559</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>366</v>
+        <v>648</v>
       </c>
       <c r="B176" t="s">
-        <v>279</v>
+        <v>561</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>367</v>
+        <v>649</v>
       </c>
       <c r="B177" t="s">
-        <v>319</v>
+        <v>601</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>368</v>
+        <v>650</v>
       </c>
       <c r="B178" t="s">
-        <v>303</v>
+        <v>585</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>369</v>
+        <v>651</v>
       </c>
       <c r="B179" t="s">
-        <v>370</v>
+        <v>652</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>371</v>
+        <v>653</v>
       </c>
       <c r="B180" t="s">
-        <v>307</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -4324,12 +5301,380 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" t="s">
+        <v>662</v>
+      </c>
+      <c r="C5" t="s">
+        <v>589</v>
+      </c>
+      <c r="D5" t="s">
+        <v>663</v>
+      </c>
+      <c r="E5" t="s">
+        <v>664</v>
+      </c>
+      <c r="F5" t="s">
+        <v>664</v>
+      </c>
+      <c r="G5" t="s">
+        <v>664</v>
+      </c>
+      <c r="H5" t="s">
+        <v>664</v>
+      </c>
+      <c r="I5" t="s">
+        <v>664</v>
+      </c>
+      <c r="J5" t="s">
+        <v>643</v>
+      </c>
+      <c r="K5" t="s">
+        <v>428</v>
+      </c>
+      <c r="L5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>665</v>
+      </c>
+      <c r="C6" t="s">
+        <v>591</v>
+      </c>
+      <c r="D6" t="s">
+        <v>666</v>
+      </c>
+      <c r="E6" t="s">
+        <v>664</v>
+      </c>
+      <c r="F6" t="s">
+        <v>664</v>
+      </c>
+      <c r="G6" t="s">
+        <v>664</v>
+      </c>
+      <c r="H6" t="s">
+        <v>664</v>
+      </c>
+      <c r="I6" t="s">
+        <v>664</v>
+      </c>
+      <c r="J6" t="s">
+        <v>664</v>
+      </c>
+      <c r="K6" t="s">
+        <v>664</v>
+      </c>
+      <c r="L6" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B7" t="s">
+        <v>668</v>
+      </c>
+      <c r="C7" t="s">
+        <v>449</v>
+      </c>
+      <c r="D7" t="s">
+        <v>669</v>
+      </c>
+      <c r="E7" t="s">
+        <v>428</v>
+      </c>
+      <c r="F7" t="s">
+        <v>559</v>
+      </c>
+      <c r="G7" t="s">
+        <v>428</v>
+      </c>
+      <c r="H7" t="s">
+        <v>428</v>
+      </c>
+      <c r="I7" t="s">
+        <v>428</v>
+      </c>
+      <c r="J7" t="s">
+        <v>428</v>
+      </c>
+      <c r="K7" t="s">
+        <v>601</v>
+      </c>
+      <c r="L7" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>671</v>
+      </c>
+      <c r="C8" t="s">
+        <v>639</v>
+      </c>
+      <c r="D8" t="s">
+        <v>666</v>
+      </c>
+      <c r="E8" t="s">
+        <v>664</v>
+      </c>
+      <c r="F8" t="s">
+        <v>664</v>
+      </c>
+      <c r="G8" t="s">
+        <v>664</v>
+      </c>
+      <c r="H8" t="s">
+        <v>664</v>
+      </c>
+      <c r="I8" t="s">
+        <v>664</v>
+      </c>
+      <c r="J8" t="s">
+        <v>664</v>
+      </c>
+      <c r="K8" t="s">
+        <v>664</v>
+      </c>
+      <c r="L8" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>380</v>
+      </c>
+      <c r="B9" t="s">
+        <v>672</v>
+      </c>
+      <c r="C9" t="s">
+        <v>673</v>
+      </c>
+      <c r="D9" t="s">
+        <v>674</v>
+      </c>
+      <c r="E9" t="s">
+        <v>664</v>
+      </c>
+      <c r="F9" t="s">
+        <v>428</v>
+      </c>
+      <c r="G9" t="s">
+        <v>428</v>
+      </c>
+      <c r="H9" t="s">
+        <v>428</v>
+      </c>
+      <c r="I9" t="s">
+        <v>428</v>
+      </c>
+      <c r="J9" t="s">
+        <v>428</v>
+      </c>
+      <c r="K9" t="s">
+        <v>641</v>
+      </c>
+      <c r="L9" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>382</v>
+      </c>
+      <c r="B10" t="s">
+        <v>676</v>
+      </c>
+      <c r="C10" t="s">
+        <v>677</v>
+      </c>
+      <c r="D10" t="s">
+        <v>666</v>
+      </c>
+      <c r="E10" t="s">
+        <v>664</v>
+      </c>
+      <c r="F10" t="s">
+        <v>664</v>
+      </c>
+      <c r="G10" t="s">
+        <v>664</v>
+      </c>
+      <c r="H10" t="s">
+        <v>664</v>
+      </c>
+      <c r="I10" t="s">
+        <v>664</v>
+      </c>
+      <c r="J10" t="s">
+        <v>664</v>
+      </c>
+      <c r="K10" t="s">
+        <v>664</v>
+      </c>
+      <c r="L10" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>384</v>
+      </c>
+      <c r="B11" t="s">
+        <v>678</v>
+      </c>
+      <c r="C11" t="s">
+        <v>679</v>
+      </c>
+      <c r="D11" t="s">
+        <v>674</v>
+      </c>
+      <c r="E11" t="s">
+        <v>664</v>
+      </c>
+      <c r="F11" t="s">
+        <v>428</v>
+      </c>
+      <c r="G11" t="s">
+        <v>428</v>
+      </c>
+      <c r="H11" t="s">
+        <v>428</v>
+      </c>
+      <c r="I11" t="s">
+        <v>428</v>
+      </c>
+      <c r="J11" t="s">
+        <v>428</v>
+      </c>
+      <c r="K11" t="s">
+        <v>428</v>
+      </c>
+      <c r="L11" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>680</v>
+      </c>
+      <c r="C12" t="s">
+        <v>641</v>
+      </c>
+      <c r="D12" t="s">
+        <v>666</v>
+      </c>
+      <c r="E12" t="s">
+        <v>664</v>
+      </c>
+      <c r="F12" t="s">
+        <v>664</v>
+      </c>
+      <c r="G12" t="s">
+        <v>664</v>
+      </c>
+      <c r="H12" t="s">
+        <v>664</v>
+      </c>
+      <c r="I12" t="s">
+        <v>664</v>
+      </c>
+      <c r="J12" t="s">
+        <v>664</v>
+      </c>
+      <c r="K12" t="s">
+        <v>664</v>
+      </c>
+      <c r="L12" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="1" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>684</v>
+      </c>
+      <c r="B15" t="s">
+        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -4339,479 +5684,12 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" t="s">
-        <v>379</v>
-      </c>
-      <c r="C5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D5" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" t="s">
-        <v>381</v>
-      </c>
-      <c r="C6" t="s">
-        <v>309</v>
-      </c>
-      <c r="D6" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" t="s">
-        <v>383</v>
-      </c>
-      <c r="C7" t="s">
-        <v>384</v>
-      </c>
-      <c r="D7" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" t="s">
-        <v>385</v>
-      </c>
-      <c r="C8" t="s">
-        <v>167</v>
-      </c>
-      <c r="D8" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>387</v>
-      </c>
-      <c r="C9" t="s">
-        <v>357</v>
-      </c>
-      <c r="D9" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>388</v>
-      </c>
-      <c r="C10" t="s">
-        <v>389</v>
-      </c>
-      <c r="D10" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" t="s">
-        <v>390</v>
-      </c>
-      <c r="C11" t="s">
-        <v>391</v>
-      </c>
-      <c r="D11" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" t="s">
-        <v>392</v>
-      </c>
-      <c r="C12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D12" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" t="s">
-        <v>394</v>
-      </c>
-      <c r="C13" t="s">
-        <v>359</v>
-      </c>
-      <c r="D13" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" t="s">
-        <v>395</v>
-      </c>
-      <c r="C14" t="s">
-        <v>396</v>
-      </c>
-      <c r="D14" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>397</v>
-      </c>
-      <c r="C15" t="s">
-        <v>361</v>
-      </c>
-      <c r="D15" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" t="s">
-        <v>398</v>
-      </c>
-      <c r="C16" t="s">
-        <v>363</v>
-      </c>
-      <c r="D16" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>111</v>
-      </c>
-      <c r="B17" t="s">
-        <v>399</v>
-      </c>
-      <c r="C17" t="s">
-        <v>400</v>
-      </c>
-      <c r="D17" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" t="s">
-        <v>401</v>
-      </c>
-      <c r="C18" t="s">
-        <v>305</v>
-      </c>
-      <c r="D18" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" t="s">
-        <v>402</v>
-      </c>
-      <c r="C19" t="s">
-        <v>303</v>
-      </c>
-      <c r="D19" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" t="s">
-        <v>403</v>
-      </c>
-      <c r="C20" t="s">
-        <v>404</v>
-      </c>
-      <c r="D20" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" t="s">
-        <v>405</v>
-      </c>
-      <c r="C21" t="s">
-        <v>406</v>
-      </c>
-      <c r="D21" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" t="s">
-        <v>407</v>
-      </c>
-      <c r="C22" t="s">
-        <v>408</v>
-      </c>
-      <c r="D22" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>114</v>
-      </c>
-      <c r="B23" t="s">
-        <v>409</v>
-      </c>
-      <c r="C23" t="s">
-        <v>237</v>
-      </c>
-      <c r="D23" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>114</v>
-      </c>
-      <c r="B24" t="s">
-        <v>410</v>
-      </c>
-      <c r="C24" t="s">
-        <v>411</v>
-      </c>
-      <c r="D24" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>116</v>
-      </c>
-      <c r="B25" t="s">
-        <v>412</v>
-      </c>
-      <c r="C25" t="s">
-        <v>277</v>
-      </c>
-      <c r="D25" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" t="s">
-        <v>413</v>
-      </c>
-      <c r="C26" t="s">
-        <v>279</v>
-      </c>
-      <c r="D26" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" t="s">
-        <v>414</v>
-      </c>
-      <c r="C27" t="s">
-        <v>370</v>
-      </c>
-      <c r="D27" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>92</v>
-      </c>
-      <c r="B28" t="s">
-        <v>415</v>
-      </c>
-      <c r="C28" t="s">
-        <v>281</v>
-      </c>
-      <c r="D28" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
-        <v>416</v>
-      </c>
-      <c r="C29" t="s">
-        <v>286</v>
-      </c>
-      <c r="D29" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" t="s">
-        <v>417</v>
-      </c>
-      <c r="C30" t="s">
-        <v>288</v>
-      </c>
-      <c r="D30" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>119</v>
-      </c>
-      <c r="B31" t="s">
-        <v>418</v>
-      </c>
-      <c r="C31" t="s">
-        <v>290</v>
-      </c>
-      <c r="D31" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" t="s">
-        <v>419</v>
-      </c>
-      <c r="C32" t="s">
-        <v>292</v>
-      </c>
-      <c r="D32" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" t="s">
-        <v>420</v>
-      </c>
-      <c r="C33" t="s">
-        <v>294</v>
-      </c>
-      <c r="D33" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>120</v>
-      </c>
-      <c r="B34" t="s">
-        <v>421</v>
-      </c>
-      <c r="C34" t="s">
-        <v>319</v>
-      </c>
-      <c r="D34" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>120</v>
-      </c>
-      <c r="B35" t="s">
-        <v>422</v>
-      </c>
-      <c r="C35" t="s">
-        <v>423</v>
-      </c>
-      <c r="D35" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" t="s">
-        <v>424</v>
-      </c>
-      <c r="C36" t="s">
-        <v>425</v>
-      </c>
-      <c r="D36" t="s">
-        <v>382</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>
@@ -4821,12 +5699,662 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B5" t="s">
+        <v>689</v>
+      </c>
+      <c r="C5" t="s">
+        <v>589</v>
+      </c>
+      <c r="D5" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B6" t="s">
+        <v>691</v>
+      </c>
+      <c r="C6" t="s">
+        <v>591</v>
+      </c>
+      <c r="D6" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B7" t="s">
+        <v>693</v>
+      </c>
+      <c r="C7" t="s">
+        <v>574</v>
+      </c>
+      <c r="D7" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>374</v>
+      </c>
+      <c r="B8" t="s">
+        <v>694</v>
+      </c>
+      <c r="C8" t="s">
+        <v>576</v>
+      </c>
+      <c r="D8" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>695</v>
+      </c>
+      <c r="C9" t="s">
+        <v>449</v>
+      </c>
+      <c r="D9" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>696</v>
+      </c>
+      <c r="C10" t="s">
+        <v>639</v>
+      </c>
+      <c r="D10" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>697</v>
+      </c>
+      <c r="C11" t="s">
+        <v>601</v>
+      </c>
+      <c r="D11" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>698</v>
+      </c>
+      <c r="C12" t="s">
+        <v>699</v>
+      </c>
+      <c r="D12" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>377</v>
+      </c>
+      <c r="B13" t="s">
+        <v>700</v>
+      </c>
+      <c r="C13" t="s">
+        <v>673</v>
+      </c>
+      <c r="D13" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>377</v>
+      </c>
+      <c r="B14" t="s">
+        <v>701</v>
+      </c>
+      <c r="C14" t="s">
+        <v>677</v>
+      </c>
+      <c r="D14" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>377</v>
+      </c>
+      <c r="B15" t="s">
+        <v>702</v>
+      </c>
+      <c r="C15" t="s">
+        <v>679</v>
+      </c>
+      <c r="D15" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>377</v>
+      </c>
+      <c r="B16" t="s">
+        <v>704</v>
+      </c>
+      <c r="C16" t="s">
+        <v>641</v>
+      </c>
+      <c r="D16" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>377</v>
+      </c>
+      <c r="B17" t="s">
+        <v>705</v>
+      </c>
+      <c r="C17" t="s">
+        <v>706</v>
+      </c>
+      <c r="D17" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>377</v>
+      </c>
+      <c r="B18" t="s">
+        <v>707</v>
+      </c>
+      <c r="C18" t="s">
+        <v>708</v>
+      </c>
+      <c r="D18" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>377</v>
+      </c>
+      <c r="B19" t="s">
+        <v>709</v>
+      </c>
+      <c r="C19" t="s">
+        <v>585</v>
+      </c>
+      <c r="D19" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>377</v>
+      </c>
+      <c r="B20" t="s">
+        <v>710</v>
+      </c>
+      <c r="C20" t="s">
+        <v>711</v>
+      </c>
+      <c r="D20" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>712</v>
+      </c>
+      <c r="C21" t="s">
+        <v>643</v>
+      </c>
+      <c r="D21" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>713</v>
+      </c>
+      <c r="C22" t="s">
+        <v>645</v>
+      </c>
+      <c r="D22" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>714</v>
+      </c>
+      <c r="C23" t="s">
+        <v>715</v>
+      </c>
+      <c r="D23" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>716</v>
+      </c>
+      <c r="C24" t="s">
+        <v>717</v>
+      </c>
+      <c r="D24" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" t="s">
+        <v>718</v>
+      </c>
+      <c r="C25" t="s">
+        <v>652</v>
+      </c>
+      <c r="D25" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>719</v>
+      </c>
+      <c r="C26" t="s">
+        <v>720</v>
+      </c>
+      <c r="D26" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" t="s">
+        <v>721</v>
+      </c>
+      <c r="C27" t="s">
+        <v>722</v>
+      </c>
+      <c r="D27" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>399</v>
+      </c>
+      <c r="B28" t="s">
+        <v>723</v>
+      </c>
+      <c r="C28" t="s">
+        <v>587</v>
+      </c>
+      <c r="D28" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>399</v>
+      </c>
+      <c r="B29" t="s">
+        <v>724</v>
+      </c>
+      <c r="C29" t="s">
+        <v>725</v>
+      </c>
+      <c r="D29" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>399</v>
+      </c>
+      <c r="B30" t="s">
+        <v>726</v>
+      </c>
+      <c r="C30" t="s">
+        <v>727</v>
+      </c>
+      <c r="D30" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>399</v>
+      </c>
+      <c r="B31" t="s">
+        <v>728</v>
+      </c>
+      <c r="C31" t="s">
+        <v>729</v>
+      </c>
+      <c r="D31" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>399</v>
+      </c>
+      <c r="B32" t="s">
+        <v>730</v>
+      </c>
+      <c r="C32" t="s">
+        <v>731</v>
+      </c>
+      <c r="D32" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>380</v>
+      </c>
+      <c r="B33" t="s">
+        <v>732</v>
+      </c>
+      <c r="C33" t="s">
+        <v>733</v>
+      </c>
+      <c r="D33" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>380</v>
+      </c>
+      <c r="B34" t="s">
+        <v>734</v>
+      </c>
+      <c r="C34" t="s">
+        <v>519</v>
+      </c>
+      <c r="D34" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>380</v>
+      </c>
+      <c r="B35" t="s">
+        <v>735</v>
+      </c>
+      <c r="C35" t="s">
+        <v>736</v>
+      </c>
+      <c r="D35" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>380</v>
+      </c>
+      <c r="B36" t="s">
+        <v>737</v>
+      </c>
+      <c r="C36" t="s">
+        <v>738</v>
+      </c>
+      <c r="D36" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>382</v>
+      </c>
+      <c r="B37" t="s">
+        <v>739</v>
+      </c>
+      <c r="C37" t="s">
+        <v>559</v>
+      </c>
+      <c r="D37" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>382</v>
+      </c>
+      <c r="B38" t="s">
+        <v>740</v>
+      </c>
+      <c r="C38" t="s">
+        <v>561</v>
+      </c>
+      <c r="D38" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>382</v>
+      </c>
+      <c r="B39" t="s">
+        <v>741</v>
+      </c>
+      <c r="C39" t="s">
+        <v>742</v>
+      </c>
+      <c r="D39" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>382</v>
+      </c>
+      <c r="B40" t="s">
+        <v>743</v>
+      </c>
+      <c r="C40" t="s">
+        <v>744</v>
+      </c>
+      <c r="D40" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>384</v>
+      </c>
+      <c r="B41" t="s">
+        <v>745</v>
+      </c>
+      <c r="C41" t="s">
+        <v>563</v>
+      </c>
+      <c r="D41" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>384</v>
+      </c>
+      <c r="B42" t="s">
+        <v>746</v>
+      </c>
+      <c r="C42" t="s">
+        <v>568</v>
+      </c>
+      <c r="D42" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>384</v>
+      </c>
+      <c r="B43" t="s">
+        <v>747</v>
+      </c>
+      <c r="C43" t="s">
+        <v>748</v>
+      </c>
+      <c r="D43" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>384</v>
+      </c>
+      <c r="B44" t="s">
+        <v>749</v>
+      </c>
+      <c r="C44" t="s">
+        <v>750</v>
+      </c>
+      <c r="D44" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" t="s">
+        <v>751</v>
+      </c>
+      <c r="C45" t="s">
+        <v>570</v>
+      </c>
+      <c r="D45" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" t="s">
+        <v>752</v>
+      </c>
+      <c r="C46" t="s">
+        <v>572</v>
+      </c>
+      <c r="D46" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>753</v>
+      </c>
+      <c r="C47" t="s">
+        <v>754</v>
+      </c>
+      <c r="D47" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s">
+        <v>755</v>
+      </c>
+      <c r="C48" t="s">
+        <v>756</v>
+      </c>
+      <c r="D48" t="s">
+        <v>703</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>757</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4836,482 +6364,482 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>427</v>
+        <v>758</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>428</v>
+        <v>759</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>429</v>
+        <v>760</v>
       </c>
       <c r="B5" t="s">
-        <v>430</v>
+        <v>761</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>431</v>
+        <v>762</v>
       </c>
       <c r="B6" t="s">
-        <v>432</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>433</v>
+        <v>764</v>
       </c>
       <c r="B7" t="s">
-        <v>434</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>435</v>
+        <v>766</v>
       </c>
       <c r="B8" t="s">
-        <v>436</v>
+        <v>767</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>437</v>
+        <v>768</v>
       </c>
       <c r="B9" t="s">
-        <v>438</v>
+        <v>769</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>439</v>
+        <v>770</v>
       </c>
       <c r="B10" t="s">
-        <v>440</v>
+        <v>685</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>441</v>
+        <v>771</v>
       </c>
       <c r="B11" t="s">
-        <v>440</v>
+        <v>685</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>442</v>
+        <v>772</v>
       </c>
       <c r="B12" t="s">
-        <v>443</v>
+        <v>773</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>444</v>
+        <v>774</v>
       </c>
       <c r="B13" t="s">
-        <v>445</v>
+        <v>775</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>446</v>
+        <v>776</v>
       </c>
       <c r="B14" t="s">
-        <v>447</v>
+        <v>777</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>448</v>
+        <v>778</v>
       </c>
       <c r="B15" t="s">
-        <v>449</v>
+        <v>779</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>450</v>
+        <v>780</v>
       </c>
       <c r="B16" t="s">
-        <v>451</v>
+        <v>781</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>452</v>
+        <v>782</v>
       </c>
       <c r="B17" t="s">
-        <v>453</v>
+        <v>783</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>454</v>
+        <v>784</v>
       </c>
       <c r="B18" t="s">
-        <v>455</v>
+        <v>785</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>456</v>
+        <v>786</v>
       </c>
       <c r="B19" t="s">
-        <v>455</v>
+        <v>785</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>457</v>
+        <v>787</v>
       </c>
       <c r="B20" t="s">
-        <v>458</v>
+        <v>788</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>459</v>
+        <v>789</v>
       </c>
       <c r="B21" t="s">
-        <v>460</v>
+        <v>788</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>461</v>
+        <v>790</v>
       </c>
       <c r="B22" t="s">
-        <v>460</v>
+        <v>791</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>462</v>
+        <v>792</v>
       </c>
       <c r="B23" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>464</v>
+        <v>793</v>
       </c>
       <c r="B24" t="s">
-        <v>465</v>
+        <v>660</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>466</v>
+        <v>794</v>
       </c>
       <c r="B25" t="s">
-        <v>467</v>
+        <v>661</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>468</v>
+        <v>795</v>
       </c>
       <c r="B26" t="s">
-        <v>467</v>
+        <v>661</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>469</v>
+        <v>796</v>
       </c>
       <c r="B27" t="s">
-        <v>467</v>
+        <v>661</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>470</v>
+        <v>797</v>
       </c>
       <c r="B28" t="s">
-        <v>467</v>
+        <v>661</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>471</v>
+        <v>798</v>
       </c>
       <c r="B29" t="s">
-        <v>467</v>
+        <v>661</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>472</v>
+        <v>799</v>
       </c>
       <c r="B30" t="s">
-        <v>467</v>
+        <v>661</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>473</v>
+        <v>800</v>
       </c>
       <c r="B31" t="s">
-        <v>256</v>
+        <v>538</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>474</v>
+        <v>801</v>
       </c>
       <c r="B32" t="s">
-        <v>256</v>
+        <v>538</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>475</v>
+        <v>802</v>
       </c>
       <c r="B33" t="s">
-        <v>256</v>
+        <v>538</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>476</v>
+        <v>803</v>
       </c>
       <c r="B34" t="s">
-        <v>256</v>
+        <v>538</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>477</v>
+        <v>804</v>
       </c>
       <c r="B35" t="s">
-        <v>256</v>
+        <v>538</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>478</v>
+        <v>805</v>
       </c>
       <c r="B36" t="s">
-        <v>179</v>
+        <v>461</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>479</v>
+        <v>806</v>
       </c>
       <c r="B37" t="s">
-        <v>179</v>
+        <v>461</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>480</v>
+        <v>807</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>461</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>481</v>
+        <v>808</v>
       </c>
       <c r="B39" t="s">
-        <v>179</v>
+        <v>461</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>482</v>
+        <v>809</v>
       </c>
       <c r="B40" t="s">
-        <v>179</v>
+        <v>461</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>483</v>
+        <v>810</v>
       </c>
       <c r="B41" t="s">
-        <v>179</v>
+        <v>461</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>484</v>
+        <v>811</v>
       </c>
       <c r="B42" t="s">
-        <v>179</v>
+        <v>461</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>485</v>
+        <v>812</v>
       </c>
       <c r="B43" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>486</v>
+        <v>813</v>
       </c>
       <c r="B44" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>487</v>
+        <v>814</v>
       </c>
       <c r="B45" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>488</v>
+        <v>815</v>
       </c>
       <c r="B46" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>489</v>
+        <v>816</v>
       </c>
       <c r="B47" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>490</v>
+        <v>817</v>
       </c>
       <c r="B48" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>491</v>
+        <v>818</v>
       </c>
       <c r="B49" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>492</v>
+        <v>819</v>
       </c>
       <c r="B50" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>493</v>
+        <v>820</v>
       </c>
       <c r="B51" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>494</v>
+        <v>821</v>
       </c>
       <c r="B52" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>495</v>
+        <v>822</v>
       </c>
       <c r="B53" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>496</v>
+        <v>823</v>
       </c>
       <c r="B54" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>497</v>
+        <v>824</v>
       </c>
       <c r="B55" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>498</v>
+        <v>825</v>
       </c>
       <c r="B56" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>499</v>
+        <v>826</v>
       </c>
       <c r="B57" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>500</v>
+        <v>827</v>
       </c>
       <c r="B58" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>501</v>
+        <v>828</v>
       </c>
       <c r="B59" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>502</v>
+        <v>829</v>
       </c>
       <c r="B60" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>503</v>
+        <v>830</v>
       </c>
       <c r="B61" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>504</v>
+        <v>831</v>
       </c>
       <c r="B62" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>505</v>
+        <v>832</v>
       </c>
       <c r="B63" t="s">
-        <v>249</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -5346,7 +6874,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -5356,17 +6884,12 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -5381,7 +6904,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5391,7 +6914,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -5401,12 +6924,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5416,7 +6939,782 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -5431,7 +7729,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5441,7 +7739,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -5456,7 +7754,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5471,17 +7769,787 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="932">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -132,7 +132,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>No Shorted Input Nets found.</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -144,21 +147,1257 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_496698b1_XU8_be4c5eaa_XDEBUG(ten_496698b1_XU8_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_5e7931f3_XU7_be4c5eaa_XDEBUG(ten_5e7931f3_XU7_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7bb789c1_XU3_be4c5eaa_XDEBUG(ten_7bb789c1_XU3_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_bdb7126b_XU6_be4c5eaa_XDEBUG(ten_bdb7126b_XU6_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fc840bff_XU4_be4c5eaa_XDEBUG(ten_fc840bff_XU4_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_38b575fc_XU10_be4c5eaa_XDEBUG(ten_38b575fc_XU10_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_71505146_XU19_be4c5eaa_XDEBUG(ten_71505146_XU19_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_b20889dd_XU21_be4c5eaa_XDEBUG(ten_b20889dd_XU21_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f614d104_XU20_be4c5eaa_XDEBUG(ten_f614d104_XU20_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN(ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN(global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN(global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_016e5221_XU14_76edd7de_XCONTROL(ten_016e5221_XU14_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_10af5487_XU89_76edd7de_XCONTROL(ten_10af5487_XU89_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_1c924704_XU94_76edd7de_XCONTROL(ten_1c924704_XU94_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_250e1d7b_XU96_76edd7de_XCONTROL(ten_250e1d7b_XU96_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_3a54983a_XU93_76edd7de_XCONTROL(ten_3a54983a_XU93_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_5dbb5861_XU98_76edd7de_XCONTROL(ten_5dbb5861_XU98_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_78907f64_XU97_76edd7de_XCONTROL(ten_78907f64_XU97_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_9e0c6a0f_XU20_76edd7de_XCONTROL(ten_9e0c6a0f_XU20_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_a9541403_XU99_76edd7de_XCONTROL(ten_a9541403_XU99_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_b275df66_XU92_76edd7de_XCONTROL(ten_b275df66_XU92_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_c406e2e9_XU16_76edd7de_XCONTROL(ten_c406e2e9_XU16_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_dc7df0cc_XU18_76edd7de_XCONTROL(ten_dc7df0cc_XU18_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e1c50519_XU90_76edd7de_XCONTROL(ten_e1c50519_XU90_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_e41e5cb3_XU95_76edd7de_XCONTROL(ten_e41e5cb3_XU95_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.ten_efe3dfd4_XU91_76edd7de_XCONTROL(ten_efe3dfd4_XU91_76edd7de_XCONTROL)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW(global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XBOTSW.ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_2a0216d2_XU20_c1b82e6f_XDEBUG(ten_2a0216d2_XU20_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_32f97a89_XU11_c1b82e6f_XDEBUG(ten_32f97a89_XU11_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_34071f1d_XU15_c1b82e6f_XDEBUG(ten_34071f1d_XU15_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_3788e0aa_XU16_c1b82e6f_XDEBUG(ten_3788e0aa_XU16_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_e5798d25_XU18_c1b82e6f_XDEBUG(ten_e5798d25_XU18_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f83f6ba2_XU10_c1b82e6f_XDEBUG(ten_f83f6ba2_XU10_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_fcfb2c12_XU12_c1b82e6f_XDEBUG(ten_fcfb2c12_XU12_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_af379456_XU5_c1b82e6f_XDEBUG(ten_hijack_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG(ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_cboot_35156756_XU17_f604d85e_XTOPSW(global_cboot_35156756_XU17_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW(global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW(ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW(global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XTOPSW.ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW(ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6044b743_XU7_4c867da6_XDEBUG(ten_6044b743_XU7_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e48a0c0_XU2_4c867da6_XDEBUG(ten_7e48a0c0_XU2_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_7e6d3e04_XU1_4c867da6_XDEBUG(ten_7e6d3e04_XU1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_0b40c959_XU6_4c867da6_XDEBUG(ten_hijack_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_54e727e4_XU15_4c867da6_XDEBUG(ten_hijack_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9929432d_XU17_4c867da6_XDEBUG(ten_hijack_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG(ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG(ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9929432d_XU17_4c867da6_XDEBUG(ten_hijacki_9929432d_XU17_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN(ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_14c9168a_XU7_1cec7299_XDEBUG(ten_14c9168a_XU7_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6d67c253_XU1_1cec7299_XDEBUG(ten_6d67c253_XU1_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_c69fe1aa_XU8_1cec7299_XDEBUG(ten_c69fe1aa_XU8_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1d78f0e4_XU13_1cec7299_XDEBUG(ten_1d78f0e4_XU13_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d748b831_XU15_1cec7299_XDEBUG(ten_d748b831_XU15_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f4762d45_XU11_1cec7299_XDEBUG(ten_f4762d45_XU11_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_6613b2af_XU3_1cec7299_XDEBUG(ten_hijack_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_c541f94b_XU16_1cec7299_XDEBUG(ten_hijack_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG(ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG(ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG(ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_e96a4067_XU8_811a9a05_XMAIN(global_vbuffer_e96a4067_XU8_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN(ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_70e67769_XU3_811a9a05_XMAIN(global_comparator_70e67769_XU3_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_ddbf938d_XU22_811a9a05_XMAIN(global_comparator_ddbf938d_XU22_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_resistordivider_37d49b79_XU17_811a9a05_XMAIN(global_resistordivider_37d49b79_XU17_811a9a05_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_162b659f_XU9_f255c70e_XDEBUG(ten_162b659f_XU9_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_83ff2716_XU8_f255c70e_XDEBUG(ten_83ff2716_XU8_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_913fa695_XU7_f255c70e_XDEBUG(ten_913fa695_XU7_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_95483466_XU2_f255c70e_XDEBUG(ten_95483466_XU2_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_d922ca5f_XU6_f255c70e_XDEBUG(ten_d922ca5f_XU6_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_de422ccd_XU11_f255c70e_XDEBUG(ten_hijack_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG(ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_gm_e44d2b4d_Xgm1_10783060_XMAIN(global_gm_e44d2b4d_Xgm1_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_clamp_b8eb1a18_XU7_10783060_XMAIN(global_clamp_b8eb1a18_XU7_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbuffer_866ca25c_XU9_10783060_XMAIN(global_vbuffer_866ca25c_XU9_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_5c7dff44_XU10_10783060_XMAIN(global_comparator_5c7dff44_XU10_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_voltage2current_4215aede_XU3_10783060_XMAIN(global_voltage2current_4215aede_XU3_10783060_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_0721e5d9_XU56_5c792007_XSEQUENCER(ten_0721e5d9_XU56_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_2958f818_XU61_5c792007_XSEQUENCER(ten_2958f818_XU61_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_29fa69a5_XU60_5c792007_XSEQUENCER(ten_29fa69a5_XU60_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_3bd9bacc_XU59_5c792007_XSEQUENCER(ten_3bd9bacc_XU59_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_445acf01_XU57_5c792007_XSEQUENCER(ten_445acf01_XU57_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4c7ada73_XU65_5c792007_XSEQUENCER(ten_4c7ada73_XU65_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_4d227e72_XU55_5c792007_XSEQUENCER(ten_4d227e72_XU55_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_6cd23b02_XU66_5c792007_XSEQUENCER(ten_6cd23b02_XU66_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_70525239_XU58_5c792007_XSEQUENCER(ten_70525239_XU58_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_950364d7_XU54_5c792007_XSEQUENCER(ten_950364d7_XU54_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9d829c39_XU62_5c792007_XSEQUENCER(ten_9d829c39_XU62_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_9ef032e9_XU63_5c792007_XSEQUENCER(ten_9ef032e9_XU63_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XSEQUENCER.ten_e8d90cd0_XU64_5c792007_XSEQUENCER(ten_e8d90cd0_XU64_5c792007_XSEQUENCER)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_1955111b_XU7_63f6e3c4_XDEBUG(ten_1955111b_XU7_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_742857bf_XU2_63f6e3c4_XDEBUG(ten_742857bf_XU2_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_a6a0ac97_XU3_63f6e3c4_XDEBUG(ten_a6a0ac97_XU3_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ec5776d4_XU6_63f6e3c4_XDEBUG(ten_ec5776d4_XU6_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_cd882763_XU15_63f6e3c4_XDEBUG(ten_cd882763_XU15_63f6e3c4_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_ref_553d3e5b_XU4_2345cd7b_XMAIN(ten_ref_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN(ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_reference_553d3e5b_XU4_2345cd7b_XMAIN(global_reference_553d3e5b_XU4_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN(global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.global_comparator_75c89176_XU16_2345cd7b_XMAIN(global_comparator_75c89176_XU16_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_81f80d4d_XU8_88e49508_XDEBUG(ten_81f80d4d_XU8_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_ed87e5db_XU5_88e49508_XDEBUG(ten_ed87e5db_XU5_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_f665b623_XU6_88e49508_XDEBUG(ten_f665b623_XU6_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_528f048c_XU10_88e49508_XDEBUG(ten_528f048c_XU10_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_297df8ef_XU1_88e49508_XDEBUG(ten_hijack_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijack_dcf795e2_XU14_88e49508_XDEBUG(ten_hijack_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_297df8ef_XU1_88e49508_XDEBUG(ten_hijacki_297df8ef_XU1_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG(ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_dac_0cc08401_XU5_b48f6491_XMAIN8(global_dac_0cc08401_XU5_b48f6491_XMAIN8)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8(global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
   </si>
   <si>
+    <t>ten_496698b1_XU8_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_496698b1_XU8_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5e7931f3_XU7_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_5e7931f3_XU7_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7bb789c1_XU3_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7bb789c1_XU3_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_bdb7126b_XU6_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_bdb7126b_XU6_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fc840bff_XU4_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fc840bff_XU4_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_38b575fc_XU10_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_38b575fc_XU10_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_71505146_XU19_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_71505146_XU19_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b20889dd_XU21_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_b20889dd_XU21_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f614d104_XU20_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f614d104_XU20_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>ten_016e5221_XU14_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_016e5221_XU14_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_10af5487_XU89_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_10af5487_XU89_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1c924704_XU94_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_1c924704_XU94_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_250e1d7b_XU96_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_250e1d7b_XU96_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3a54983a_XU93_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_3a54983a_XU93_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_5dbb5861_XU98_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_5dbb5861_XU98_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_78907f64_XU97_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_78907f64_XU97_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9e0c6a0f_XU20_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_9e0c6a0f_XU20_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a9541403_XU99_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_a9541403_XU99_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_b275df66_XU92_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_b275df66_XU92_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c406e2e9_XU16_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_c406e2e9_XU16_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_dc7df0cc_XU18_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_dc7df0cc_XU18_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e1c50519_XU90_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e1c50519_XU90_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e41e5cb3_XU95_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e41e5cb3_XU95_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_efe3dfd4_XU91_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_efe3dfd4_XU91_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2a0216d2_XU20_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_2a0216d2_XU20_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_32f97a89_XU11_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_32f97a89_XU11_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_34071f1d_XU15_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_34071f1d_XU15_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3788e0aa_XU16_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_3788e0aa_XU16_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e5798d25_XU18_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_e5798d25_XU18_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f83f6ba2_XU10_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f83f6ba2_XU10_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_fcfb2c12_XU12_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fcfb2c12_XU12_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_cboot_35156756_XU17_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_cboot_35156756_XU17_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_6044b743_XU7_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6044b743_XU7_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e48a0c0_XU2_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e48a0c0_XU2_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_7e6d3e04_XU1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e6d3e04_XU1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>ten_14c9168a_XU7_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_14c9168a_XU7_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6d67c253_XU1_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6d67c253_XU1_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_c69fe1aa_XU8_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_c69fe1aa_XU8_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_1d78f0e4_XU13_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1d78f0e4_XU13_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d748b831_XU15_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d748b831_XU15_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f4762d45_XU11_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f4762d45_XU11_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_e96a4067_XU8_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_e96a4067_XU8_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_70e67769_XU3_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_70e67769_XU3_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_ddbf938d_XU22_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_ddbf938d_XU22_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_resistordivider_37d49b79_XU17_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_162b659f_XU9_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_162b659f_XU9_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_83ff2716_XU8_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_83ff2716_XU8_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_913fa695_XU7_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_913fa695_XU7_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_95483466_XU2_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_95483466_XU2_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_d922ca5f_XU6_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d922ca5f_XU6_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>global_gm_e44d2b4d_Xgm1_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_gm_e44d2b4d_Xgm1_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_clamp_b8eb1a18_XU7_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_clamp_b8eb1a18_XU7_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbuffer_866ca25c_XU9_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_866ca25c_XU9_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_5c7dff44_XU10_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_5c7dff44_XU10_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_voltage2current_4215aede_XU3_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_voltage2current_4215aede_XU3_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_0721e5d9_XU56_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_0721e5d9_XU56_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_2958f818_XU61_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_2958f818_XU61_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_29fa69a5_XU60_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_29fa69a5_XU60_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_3bd9bacc_XU59_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_3bd9bacc_XU59_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_445acf01_XU57_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_445acf01_XU57_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4c7ada73_XU65_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4c7ada73_XU65_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_4d227e72_XU55_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4d227e72_XU55_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_6cd23b02_XU66_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_6cd23b02_XU66_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_70525239_XU58_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_70525239_XU58_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_950364d7_XU54_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_950364d7_XU54_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9d829c39_XU62_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9d829c39_XU62_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_9ef032e9_XU63_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9ef032e9_XU63_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_e8d90cd0_XU64_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_e8d90cd0_XU64_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>ten_1955111b_XU7_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1955111b_XU7_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_742857bf_XU2_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_742857bf_XU2_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_a6a0ac97_XU3_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_a6a0ac97_XU3_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ec5776d4_XU6_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ec5776d4_XU6_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_cd882763_XU15_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_cd882763_XU15_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ref_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_ref_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_reference_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_reference_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_comparator_75c89176_XU16_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_75c89176_XU16_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_81f80d4d_XU8_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_81f80d4d_XU8_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_ed87e5db_XU5_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ed87e5db_XU5_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_f665b623_XU6_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f665b623_XU6_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_528f048c_XU10_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_528f048c_XU10_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijack_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_dac_0cc08401_XU5_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_dac_0cc08401_XU5_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>Mixed Mode Conflicts</t>
   </si>
   <si>
@@ -171,9 +1410,6 @@
     <t>D to A Tree</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
-  </si>
-  <si>
     <t>Xoscillator1</t>
   </si>
   <si>
@@ -181,6 +1417,33 @@
   </si>
   <si>
     <t>Errors</t>
+  </si>
+  <si>
+    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
+  </si>
+  <si>
+    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
+  </si>
+  <si>
+    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
   </si>
   <si>
     <t>Cell Length Exceed Max 50</t>
@@ -277,61 +1540,70 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 4, 'efficiency': '83.3%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+    <t>DRM Efficiency Summary</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER</t>
   </si>
   <si>
-    <t>{'name': 'drm64', 'bits': 64, 'noconns': 10, 'efficiency': '84.4%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XREGULATION</t>
   </si>
   <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 7, 'efficiency': '87.5%'}</t>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSEQUENCER</t>
   </si>
   <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSERVICE</t>
   </si>
   <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>DRM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 8, 'bytes': 29.0, 'noconns': 43, 'efficiency': '81.5%'}</t>
-  </si>
-  <si>
-    <t>DFT Efficiency</t>
-  </si>
-  <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+    <t>{'cells': 44, 'bytes': 44.0, 'noconns': 44, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>Project Summary</t>
@@ -340,16 +1612,16 @@
     <t>Package Stats</t>
   </si>
   <si>
-    <t>needed: 0</t>
+    <t>needed: 2</t>
   </si>
   <si>
     <t>spares: 0</t>
   </si>
   <si>
-    <t>algorithm: 0 - No compression needed</t>
-  </si>
-  <si>
-    <t>piggyback: []</t>
+    <t>algorithm: 6 - Piggybacks</t>
+  </si>
+  <si>
+    <t>piggyback: ['DFTSCL', 'DFTSDA']</t>
   </si>
   <si>
     <t>user_pads: 12</t>
@@ -379,12 +1651,15 @@
     <t>add_dft</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>add_dbufdft</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>add_dbufdft</t>
-  </si>
-  <si>
     <t>dft_ignore_bricks</t>
   </si>
   <si>
@@ -430,9 +1705,6 @@
     <t>add_drm</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>drm_ignore_bricks</t>
   </si>
   <si>
@@ -1105,85 +2377,238 @@
     <t>4</t>
   </si>
   <si>
-    <t>drm_hex0x01</t>
-  </si>
-  <si>
-    <t>drm24</t>
-  </si>
-  <si>
-    <t>na</t>
-  </si>
-  <si>
-    <t>drm_hex0x02</t>
-  </si>
-  <si>
-    <t>drm8</t>
-  </si>
-  <si>
-    <t>0x70</t>
-  </si>
-  <si>
-    <t>drm_hex0x03</t>
-  </si>
-  <si>
-    <t>drm64</t>
-  </si>
-  <si>
-    <t>0x63</t>
-  </si>
-  <si>
-    <t>drm_hex0x04</t>
-  </si>
-  <si>
-    <t>drm_hex0x05</t>
+    <t>DRM to Memory Check</t>
+  </si>
+  <si>
+    <t>TOTAL dec</t>
+  </si>
+  <si>
+    <t>Allowed &lt;= 61</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>Register Summary</t>
+  </si>
+  <si>
+    <t>DFT Summary</t>
+  </si>
+  <si>
+    <t>TMA</t>
+  </si>
+  <si>
+    <t>dft_hex0x01</t>
+  </si>
+  <si>
+    <t>DFTtm8</t>
+  </si>
+  <si>
+    <t>dft_hex0x02</t>
+  </si>
+  <si>
+    <t>DFTtm8d</t>
+  </si>
+  <si>
+    <t>dft_hex0x16</t>
+  </si>
+  <si>
+    <t>dft_hex0x17</t>
+  </si>
+  <si>
+    <t>dft_hex0x03</t>
+  </si>
+  <si>
+    <t>dft_hex0x04</t>
+  </si>
+  <si>
+    <t>dft_hex0x18</t>
+  </si>
+  <si>
+    <t>dft_hex0x19</t>
+  </si>
+  <si>
+    <t>0x19</t>
+  </si>
+  <si>
+    <t>dft_hex0x05</t>
   </si>
   <si>
     <t>0x05</t>
   </si>
   <si>
-    <t>drm56</t>
-  </si>
-  <si>
-    <t>0x58</t>
-  </si>
-  <si>
-    <t>drm_hex0x06</t>
+    <t>dft_hex0x06</t>
   </si>
   <si>
     <t>0x06</t>
   </si>
   <si>
-    <t>drm_hex0x07</t>
+    <t>dft_hex0x07</t>
   </si>
   <si>
     <t>0x07</t>
   </si>
   <si>
-    <t>drm_hex0x08</t>
-  </si>
-  <si>
-    <t>DRM to Memory Check</t>
-  </si>
-  <si>
-    <t>TOTAL dec</t>
-  </si>
-  <si>
-    <t>Allowed &lt;= 61</t>
-  </si>
-  <si>
-    <t>37.0</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>Register Summary</t>
-  </si>
-  <si>
-    <t>DFT Summary</t>
-  </si>
-  <si>
-    <t>TMA</t>
+    <t>DFTtm8t</t>
+  </si>
+  <si>
+    <t>dft_hex0x08</t>
+  </si>
+  <si>
+    <t>dft_hex0x1A</t>
+  </si>
+  <si>
+    <t>0x1A</t>
+  </si>
+  <si>
+    <t>dft_hex0x1B</t>
+  </si>
+  <si>
+    <t>0x1B</t>
+  </si>
+  <si>
+    <t>dft_hex0x1C</t>
+  </si>
+  <si>
+    <t>dft_hex0x1D</t>
+  </si>
+  <si>
+    <t>0x1D</t>
+  </si>
+  <si>
+    <t>dft_hex0x09</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B</t>
+  </si>
+  <si>
+    <t>0x0B</t>
+  </si>
+  <si>
+    <t>dft_hex0x1E</t>
+  </si>
+  <si>
+    <t>0x1E</t>
+  </si>
+  <si>
+    <t>dft_hex0x1F</t>
+  </si>
+  <si>
+    <t>dft_hex0x20</t>
+  </si>
+  <si>
+    <t>0x20</t>
+  </si>
+  <si>
+    <t>dft_hex0x21</t>
+  </si>
+  <si>
+    <t>0x21</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D</t>
+  </si>
+  <si>
+    <t>0x0D</t>
+  </si>
+  <si>
+    <t>dft_hex0x22</t>
+  </si>
+  <si>
+    <t>0x22</t>
+  </si>
+  <si>
+    <t>dft_hex0x23</t>
+  </si>
+  <si>
+    <t>0x23</t>
+  </si>
+  <si>
+    <t>dft_hex0x24</t>
+  </si>
+  <si>
+    <t>0x24</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E</t>
+  </si>
+  <si>
+    <t>0x0E</t>
+  </si>
+  <si>
+    <t>dft_hex0x0F</t>
+  </si>
+  <si>
+    <t>dft_hex0x25</t>
+  </si>
+  <si>
+    <t>0x25</t>
+  </si>
+  <si>
+    <t>dft_hex0x26</t>
+  </si>
+  <si>
+    <t>0x26</t>
+  </si>
+  <si>
+    <t>dft_hex0x10</t>
+  </si>
+  <si>
+    <t>dft_hex0x11</t>
+  </si>
+  <si>
+    <t>dft_hex0x27</t>
+  </si>
+  <si>
+    <t>0x27</t>
+  </si>
+  <si>
+    <t>dft_hex0x28</t>
+  </si>
+  <si>
+    <t>0x28</t>
+  </si>
+  <si>
+    <t>dft_hex0x12</t>
+  </si>
+  <si>
+    <t>dft_hex0x13</t>
+  </si>
+  <si>
+    <t>dft_hex0x29</t>
+  </si>
+  <si>
+    <t>0x29</t>
+  </si>
+  <si>
+    <t>dft_hex0x2A</t>
+  </si>
+  <si>
+    <t>0x2A</t>
+  </si>
+  <si>
+    <t>dft_hex0x14</t>
+  </si>
+  <si>
+    <t>dft_hex0x15</t>
+  </si>
+  <si>
+    <t>dft_hex0x2B</t>
+  </si>
+  <si>
+    <t>0x2B</t>
+  </si>
+  <si>
+    <t>dft_hex0x2C</t>
+  </si>
+  <si>
+    <t>0x2C</t>
   </si>
   <si>
     <t>Nesto Usage Report</t>
@@ -1210,7 +2635,7 @@
     <t>noconn</t>
   </si>
   <si>
-    <t>157</t>
+    <t>168</t>
   </si>
   <si>
     <t>nand2</t>
@@ -1228,6 +2653,9 @@
     <t>nor3</t>
   </si>
   <si>
+    <t>dftprobeModel0</t>
+  </si>
+  <si>
     <t>delayfixed</t>
   </si>
   <si>
@@ -1246,6 +2674,12 @@
     <t>45</t>
   </si>
   <si>
+    <t>dftmodule</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
     <t>srlatch</t>
   </si>
   <si>
@@ -1258,72 +2692,72 @@
     <t>35</t>
   </si>
   <si>
+    <t>dfthijack</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>dff</t>
+  </si>
+  <si>
+    <t>tie</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>datamap0</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>dftprobeModel2</t>
+  </si>
+  <si>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
+    <t>resistor</t>
+  </si>
+  <si>
+    <t>oneshot</t>
+  </si>
+  <si>
+    <t>fetdn</t>
+  </si>
+  <si>
+    <t>currentlimitfet</t>
+  </si>
+  <si>
+    <t>comparatornoctlpins</t>
+  </si>
+  <si>
+    <t>ESDminiClamp6</t>
+  </si>
+  <si>
+    <t>timingskew</t>
+  </si>
+  <si>
+    <t>switchpulldown</t>
+  </si>
+  <si>
+    <t>resistordivider</t>
+  </si>
+  <si>
+    <t>delayclock</t>
+  </si>
+  <si>
+    <t>amux2</t>
+  </si>
+  <si>
     <t>wrapper</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>dff</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>tie</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>datamap0</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>drmmodule</t>
-  </si>
-  <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>resistor</t>
-  </si>
-  <si>
-    <t>oneshot</t>
-  </si>
-  <si>
-    <t>fetdn</t>
-  </si>
-  <si>
-    <t>currentlimitfet</t>
-  </si>
-  <si>
-    <t>comparatornoctlpins</t>
-  </si>
-  <si>
-    <t>ESDminiClamp6</t>
-  </si>
-  <si>
-    <t>timingskew</t>
-  </si>
-  <si>
-    <t>switchpulldown</t>
-  </si>
-  <si>
-    <t>resistordivider</t>
-  </si>
-  <si>
-    <t>delayclock</t>
-  </si>
-  <si>
-    <t>amux2</t>
-  </si>
-  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1340,6 +2774,9 @@
   </si>
   <si>
     <t>capacitorfixed</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>voltage2current</t>
@@ -1773,7 +3210,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1793,7 +3230,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1808,7 +3245,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -1823,17 +3260,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -1843,17 +3280,62 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -1868,17 +3350,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -1893,12 +3375,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -1913,7 +3395,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1933,127 +3415,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>53</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>57</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>58</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>59</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>60</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>61</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>62</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>484</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>485</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>486</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>66</v>
+        <v>487</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>67</v>
+        <v>488</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>68</v>
+        <v>489</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>69</v>
+        <v>490</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>70</v>
+        <v>491</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>71</v>
+        <v>492</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>72</v>
+        <v>493</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>494</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>74</v>
+        <v>495</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -2063,92 +3545,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2163,17 +3570,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -2393,17 +3800,277 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -2418,17 +4085,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -2443,52 +4110,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>104</v>
+        <v>528</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -2503,81 +4170,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>530</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>107</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>534</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>535</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>536</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>538</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>539</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>540</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>542</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>544</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>545</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2585,1268 +4252,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>547</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>548</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>549</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>550</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>126</v>
+        <v>551</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>552</v>
       </c>
       <c r="B20" t="s">
-        <v>128</v>
+        <v>537</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>553</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>130</v>
+        <v>554</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>131</v>
+        <v>555</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>132</v>
+        <v>556</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>133</v>
+        <v>557</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>558</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>135</v>
+        <v>559</v>
       </c>
       <c r="B29" t="s">
-        <v>136</v>
+        <v>560</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>561</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>138</v>
+        <v>562</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>563</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>564</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>141</v>
+        <v>565</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>566</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>143</v>
+        <v>567</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>568</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>145</v>
+        <v>569</v>
       </c>
       <c r="B35" t="s">
-        <v>146</v>
+        <v>570</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>147</v>
+        <v>571</v>
       </c>
       <c r="B36" t="s">
-        <v>148</v>
+        <v>572</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>149</v>
+        <v>573</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>150</v>
+        <v>574</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>151</v>
+        <v>575</v>
       </c>
       <c r="B39" t="s">
-        <v>152</v>
+        <v>576</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>153</v>
+        <v>577</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>154</v>
+        <v>578</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>155</v>
+        <v>579</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>156</v>
+        <v>580</v>
       </c>
       <c r="B43" t="s">
-        <v>157</v>
+        <v>581</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>158</v>
+        <v>582</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>159</v>
+        <v>583</v>
       </c>
       <c r="B46" t="s">
-        <v>160</v>
+        <v>584</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>585</v>
       </c>
       <c r="B47" t="s">
-        <v>128</v>
+        <v>535</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>162</v>
+        <v>586</v>
       </c>
       <c r="B48" t="s">
-        <v>152</v>
+        <v>576</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>587</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>535</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>588</v>
       </c>
       <c r="B50" t="s">
-        <v>128</v>
+        <v>535</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>589</v>
       </c>
       <c r="B51" t="s">
-        <v>166</v>
+        <v>590</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>591</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>168</v>
+        <v>592</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>169</v>
+        <v>593</v>
       </c>
       <c r="B55" t="s">
-        <v>170</v>
+        <v>594</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>171</v>
+        <v>595</v>
       </c>
       <c r="B56" t="s">
-        <v>172</v>
+        <v>596</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>173</v>
+        <v>597</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>174</v>
+        <v>598</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>175</v>
+        <v>599</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>176</v>
+        <v>600</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>177</v>
+        <v>601</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>178</v>
+        <v>602</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>179</v>
+        <v>603</v>
       </c>
       <c r="B64" t="s">
-        <v>180</v>
+        <v>604</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>181</v>
+        <v>605</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>182</v>
+        <v>606</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>183</v>
+        <v>607</v>
       </c>
       <c r="B67" t="s">
-        <v>184</v>
+        <v>608</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>185</v>
+        <v>609</v>
       </c>
       <c r="B68" t="s">
-        <v>186</v>
+        <v>610</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>187</v>
+        <v>611</v>
       </c>
       <c r="B69" t="s">
-        <v>184</v>
+        <v>608</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>188</v>
+        <v>612</v>
       </c>
       <c r="B70" t="s">
-        <v>186</v>
+        <v>610</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>189</v>
+        <v>613</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>190</v>
+        <v>614</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>191</v>
+        <v>615</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>192</v>
+        <v>616</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>193</v>
+        <v>617</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>194</v>
+        <v>618</v>
       </c>
       <c r="B77" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>195</v>
+        <v>619</v>
       </c>
       <c r="B78" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>196</v>
+        <v>620</v>
       </c>
       <c r="B79" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>197</v>
+        <v>621</v>
       </c>
       <c r="B80" t="s">
-        <v>198</v>
+        <v>622</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>199</v>
+        <v>623</v>
       </c>
       <c r="B81" t="s">
-        <v>200</v>
+        <v>624</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>201</v>
+        <v>625</v>
       </c>
       <c r="B82" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>202</v>
+        <v>626</v>
       </c>
       <c r="B83" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>203</v>
+        <v>627</v>
       </c>
       <c r="B84" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>204</v>
+        <v>628</v>
       </c>
       <c r="B85" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>205</v>
+        <v>629</v>
       </c>
       <c r="B86" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>206</v>
+        <v>630</v>
       </c>
       <c r="B87" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>207</v>
+        <v>631</v>
       </c>
       <c r="B88" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>208</v>
+        <v>632</v>
       </c>
       <c r="B89" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>209</v>
+        <v>633</v>
       </c>
       <c r="B90" t="s">
-        <v>210</v>
+        <v>634</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>211</v>
+        <v>635</v>
       </c>
       <c r="B91" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>212</v>
+        <v>636</v>
       </c>
       <c r="B92" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>213</v>
+        <v>637</v>
       </c>
       <c r="B93" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>214</v>
+        <v>638</v>
       </c>
       <c r="B94" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>215</v>
+        <v>639</v>
       </c>
       <c r="B95" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>216</v>
+        <v>640</v>
       </c>
       <c r="B96" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>217</v>
+        <v>641</v>
       </c>
       <c r="B97" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>218</v>
+        <v>642</v>
       </c>
       <c r="B98" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>219</v>
+        <v>643</v>
       </c>
       <c r="B99" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>220</v>
+        <v>644</v>
       </c>
       <c r="B100" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>221</v>
+        <v>645</v>
       </c>
       <c r="B101" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>223</v>
+        <v>647</v>
       </c>
       <c r="B102" t="s">
-        <v>111</v>
+        <v>537</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>224</v>
+        <v>648</v>
       </c>
       <c r="B103" t="s">
-        <v>144</v>
+        <v>568</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>225</v>
+        <v>649</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>226</v>
+        <v>650</v>
       </c>
       <c r="B106" t="s">
-        <v>227</v>
+        <v>651</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>228</v>
+        <v>652</v>
       </c>
       <c r="B107" t="s">
-        <v>229</v>
+        <v>653</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>230</v>
+        <v>654</v>
       </c>
       <c r="B108" t="s">
-        <v>231</v>
+        <v>655</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>232</v>
+        <v>656</v>
       </c>
       <c r="B109" t="s">
-        <v>233</v>
+        <v>657</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>234</v>
+        <v>658</v>
       </c>
       <c r="B110" t="s">
-        <v>235</v>
+        <v>659</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>236</v>
+        <v>660</v>
       </c>
       <c r="B111" t="s">
-        <v>237</v>
+        <v>661</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>238</v>
+        <v>662</v>
       </c>
       <c r="B112" t="s">
-        <v>239</v>
+        <v>663</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>240</v>
+        <v>664</v>
       </c>
       <c r="B113" t="s">
-        <v>166</v>
+        <v>590</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>241</v>
+        <v>665</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>242</v>
+        <v>666</v>
       </c>
       <c r="B116" t="s">
-        <v>157</v>
+        <v>581</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>243</v>
+        <v>667</v>
       </c>
       <c r="B117" t="s">
-        <v>244</v>
+        <v>668</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>245</v>
+        <v>669</v>
       </c>
       <c r="B118" t="s">
-        <v>246</v>
+        <v>670</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>247</v>
+        <v>671</v>
       </c>
       <c r="B119" t="s">
-        <v>248</v>
+        <v>672</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>249</v>
+        <v>673</v>
       </c>
       <c r="B120" t="s">
-        <v>250</v>
+        <v>674</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>251</v>
+        <v>675</v>
       </c>
       <c r="B121" t="s">
-        <v>252</v>
+        <v>676</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>253</v>
+        <v>677</v>
       </c>
       <c r="B122" t="s">
-        <v>254</v>
+        <v>678</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>255</v>
+        <v>679</v>
       </c>
       <c r="B123" t="s">
-        <v>250</v>
+        <v>674</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>256</v>
+        <v>680</v>
       </c>
       <c r="B124" t="s">
-        <v>252</v>
+        <v>676</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>257</v>
+        <v>681</v>
       </c>
       <c r="B125" t="s">
-        <v>254</v>
+        <v>678</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>258</v>
+        <v>682</v>
       </c>
       <c r="B126" t="s">
-        <v>259</v>
+        <v>683</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>260</v>
+        <v>684</v>
       </c>
       <c r="B127" t="s">
-        <v>261</v>
+        <v>685</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>262</v>
+        <v>686</v>
       </c>
       <c r="B128" t="s">
-        <v>263</v>
+        <v>687</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>264</v>
+        <v>688</v>
       </c>
       <c r="B129" t="s">
-        <v>265</v>
+        <v>689</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>266</v>
+        <v>690</v>
       </c>
       <c r="B130" t="s">
-        <v>267</v>
+        <v>691</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>218</v>
+        <v>642</v>
       </c>
       <c r="B131" t="s">
-        <v>268</v>
+        <v>692</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>219</v>
+        <v>643</v>
       </c>
       <c r="B132" t="s">
-        <v>269</v>
+        <v>693</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>221</v>
+        <v>645</v>
       </c>
       <c r="B133" t="s">
-        <v>270</v>
+        <v>694</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>220</v>
+        <v>644</v>
       </c>
       <c r="B134" t="s">
-        <v>271</v>
+        <v>695</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>272</v>
+        <v>696</v>
       </c>
       <c r="B135" t="s">
-        <v>157</v>
+        <v>581</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>273</v>
+        <v>697</v>
       </c>
       <c r="B136" t="s">
-        <v>274</v>
+        <v>698</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>275</v>
+        <v>699</v>
       </c>
       <c r="B137" t="s">
-        <v>276</v>
+        <v>700</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>277</v>
+        <v>701</v>
       </c>
       <c r="B138" t="s">
-        <v>278</v>
+        <v>702</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>279</v>
+        <v>703</v>
       </c>
       <c r="B139" t="s">
-        <v>280</v>
+        <v>704</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>281</v>
+        <v>705</v>
       </c>
       <c r="B140" t="s">
-        <v>282</v>
+        <v>706</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>283</v>
+        <v>707</v>
       </c>
       <c r="B141" t="s">
-        <v>250</v>
+        <v>674</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>284</v>
+        <v>708</v>
       </c>
       <c r="B142" t="s">
-        <v>252</v>
+        <v>676</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>285</v>
+        <v>709</v>
       </c>
       <c r="B143" t="s">
-        <v>254</v>
+        <v>678</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>286</v>
+        <v>710</v>
       </c>
       <c r="B144" t="s">
-        <v>259</v>
+        <v>683</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>287</v>
+        <v>711</v>
       </c>
       <c r="B145" t="s">
-        <v>261</v>
+        <v>685</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>288</v>
+        <v>712</v>
       </c>
       <c r="B146" t="s">
-        <v>263</v>
+        <v>687</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>289</v>
+        <v>713</v>
       </c>
       <c r="B147" t="s">
-        <v>265</v>
+        <v>689</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>290</v>
+        <v>714</v>
       </c>
       <c r="B148" t="s">
-        <v>267</v>
+        <v>691</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>291</v>
+        <v>715</v>
       </c>
       <c r="B149" t="s">
-        <v>292</v>
+        <v>716</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>293</v>
+        <v>717</v>
       </c>
       <c r="B150" t="s">
-        <v>294</v>
+        <v>718</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>295</v>
+        <v>719</v>
       </c>
       <c r="B151" t="s">
-        <v>296</v>
+        <v>720</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>297</v>
+        <v>721</v>
       </c>
       <c r="B152" t="s">
-        <v>298</v>
+        <v>722</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>299</v>
+        <v>723</v>
       </c>
       <c r="B153" t="s">
-        <v>300</v>
+        <v>724</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>301</v>
+        <v>725</v>
       </c>
       <c r="B154" t="s">
-        <v>302</v>
+        <v>726</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>303</v>
+        <v>727</v>
       </c>
       <c r="B155" t="s">
-        <v>304</v>
+        <v>728</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>305</v>
+        <v>729</v>
       </c>
       <c r="B156" t="s">
-        <v>306</v>
+        <v>730</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>307</v>
+        <v>731</v>
       </c>
       <c r="B157" t="s">
-        <v>308</v>
+        <v>732</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>309</v>
+        <v>733</v>
       </c>
       <c r="B158" t="s">
-        <v>310</v>
+        <v>734</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>311</v>
+        <v>735</v>
       </c>
       <c r="B159" t="s">
-        <v>312</v>
+        <v>736</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>313</v>
+        <v>737</v>
       </c>
       <c r="B160" t="s">
-        <v>314</v>
+        <v>738</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>315</v>
+        <v>739</v>
       </c>
       <c r="B161" t="s">
-        <v>316</v>
+        <v>740</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>317</v>
+        <v>741</v>
       </c>
       <c r="B162" t="s">
-        <v>318</v>
+        <v>742</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>319</v>
+        <v>743</v>
       </c>
       <c r="B163" t="s">
-        <v>320</v>
+        <v>744</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>321</v>
+        <v>745</v>
       </c>
       <c r="B164" t="s">
-        <v>322</v>
+        <v>746</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>323</v>
+        <v>747</v>
       </c>
       <c r="B165" t="s">
-        <v>324</v>
+        <v>748</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>325</v>
+        <v>749</v>
       </c>
       <c r="B166" t="s">
-        <v>298</v>
+        <v>722</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>326</v>
+        <v>750</v>
       </c>
       <c r="B167" t="s">
-        <v>280</v>
+        <v>704</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>327</v>
+        <v>751</v>
       </c>
       <c r="B168" t="s">
-        <v>282</v>
+        <v>706</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>328</v>
+        <v>752</v>
       </c>
       <c r="B169" t="s">
-        <v>140</v>
+        <v>564</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>329</v>
+        <v>753</v>
       </c>
       <c r="B170" t="s">
-        <v>330</v>
+        <v>754</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>331</v>
+        <v>755</v>
       </c>
       <c r="B171" t="s">
-        <v>332</v>
+        <v>756</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>333</v>
+        <v>757</v>
       </c>
       <c r="B172" t="s">
-        <v>334</v>
+        <v>758</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>335</v>
+        <v>759</v>
       </c>
       <c r="B173" t="s">
-        <v>336</v>
+        <v>760</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>337</v>
+        <v>761</v>
       </c>
       <c r="B174" t="s">
-        <v>118</v>
+        <v>543</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>338</v>
+        <v>762</v>
       </c>
       <c r="B175" t="s">
-        <v>250</v>
+        <v>674</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>339</v>
+        <v>763</v>
       </c>
       <c r="B176" t="s">
-        <v>252</v>
+        <v>676</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>340</v>
+        <v>764</v>
       </c>
       <c r="B177" t="s">
-        <v>292</v>
+        <v>716</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>341</v>
+        <v>765</v>
       </c>
       <c r="B178" t="s">
-        <v>276</v>
+        <v>700</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>342</v>
+        <v>766</v>
       </c>
       <c r="B179" t="s">
-        <v>343</v>
+        <v>767</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>344</v>
+        <v>768</v>
       </c>
       <c r="B180" t="s">
-        <v>280</v>
+        <v>704</v>
       </c>
     </row>
   </sheetData>
@@ -3856,380 +5523,76 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>769</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>346</v>
+        <v>770</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>347</v>
+        <v>771</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>348</v>
+        <v>772</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>349</v>
+        <v>773</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>350</v>
+        <v>774</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>351</v>
+        <v>775</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>144</v>
+        <v>568</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>231</v>
+        <v>655</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>352</v>
+        <v>776</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>229</v>
+        <v>653</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>152</v>
+        <v>576</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" t="s">
-        <v>353</v>
-      </c>
-      <c r="C5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D5" t="s">
-        <v>354</v>
-      </c>
-      <c r="E5" t="s">
-        <v>355</v>
-      </c>
-      <c r="F5" t="s">
-        <v>355</v>
-      </c>
-      <c r="G5" t="s">
-        <v>355</v>
-      </c>
-      <c r="H5" t="s">
-        <v>355</v>
-      </c>
-      <c r="I5" t="s">
-        <v>355</v>
-      </c>
-      <c r="J5" t="s">
-        <v>334</v>
-      </c>
-      <c r="K5" t="s">
-        <v>118</v>
-      </c>
-      <c r="L5" t="s">
-        <v>118</v>
+      <c r="A5" s="1" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" t="s">
-        <v>282</v>
-      </c>
-      <c r="D6" t="s">
-        <v>357</v>
-      </c>
-      <c r="E6" t="s">
-        <v>355</v>
-      </c>
-      <c r="F6" t="s">
-        <v>355</v>
-      </c>
-      <c r="G6" t="s">
-        <v>355</v>
-      </c>
-      <c r="H6" t="s">
-        <v>355</v>
-      </c>
-      <c r="I6" t="s">
-        <v>355</v>
-      </c>
-      <c r="J6" t="s">
-        <v>355</v>
-      </c>
-      <c r="K6" t="s">
-        <v>355</v>
-      </c>
-      <c r="L6" t="s">
-        <v>358</v>
+      <c r="A6" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>359</v>
-      </c>
-      <c r="C7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" t="s">
-        <v>360</v>
-      </c>
-      <c r="E7" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" t="s">
-        <v>250</v>
-      </c>
-      <c r="G7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H7" t="s">
-        <v>118</v>
-      </c>
-      <c r="I7" t="s">
-        <v>118</v>
-      </c>
-      <c r="J7" t="s">
-        <v>118</v>
-      </c>
-      <c r="K7" t="s">
-        <v>292</v>
-      </c>
-      <c r="L7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>362</v>
-      </c>
-      <c r="C8" t="s">
-        <v>330</v>
-      </c>
-      <c r="D8" t="s">
-        <v>357</v>
-      </c>
-      <c r="E8" t="s">
-        <v>355</v>
-      </c>
-      <c r="F8" t="s">
-        <v>355</v>
-      </c>
-      <c r="G8" t="s">
-        <v>355</v>
-      </c>
-      <c r="H8" t="s">
-        <v>355</v>
-      </c>
-      <c r="I8" t="s">
-        <v>355</v>
-      </c>
-      <c r="J8" t="s">
-        <v>355</v>
-      </c>
-      <c r="K8" t="s">
-        <v>355</v>
-      </c>
-      <c r="L8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" t="s">
-        <v>363</v>
-      </c>
-      <c r="C9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D9" t="s">
-        <v>365</v>
-      </c>
-      <c r="E9" t="s">
-        <v>355</v>
-      </c>
-      <c r="F9" t="s">
-        <v>118</v>
-      </c>
-      <c r="G9" t="s">
-        <v>118</v>
-      </c>
-      <c r="H9" t="s">
-        <v>118</v>
-      </c>
-      <c r="I9" t="s">
-        <v>118</v>
-      </c>
-      <c r="J9" t="s">
-        <v>118</v>
-      </c>
-      <c r="K9" t="s">
-        <v>332</v>
-      </c>
-      <c r="L9" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" t="s">
-        <v>367</v>
-      </c>
-      <c r="C10" t="s">
-        <v>368</v>
-      </c>
-      <c r="D10" t="s">
-        <v>357</v>
-      </c>
-      <c r="E10" t="s">
-        <v>355</v>
-      </c>
-      <c r="F10" t="s">
-        <v>355</v>
-      </c>
-      <c r="G10" t="s">
-        <v>355</v>
-      </c>
-      <c r="H10" t="s">
-        <v>355</v>
-      </c>
-      <c r="I10" t="s">
-        <v>355</v>
-      </c>
-      <c r="J10" t="s">
-        <v>355</v>
-      </c>
-      <c r="K10" t="s">
-        <v>355</v>
-      </c>
-      <c r="L10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" t="s">
-        <v>369</v>
-      </c>
-      <c r="C11" t="s">
-        <v>370</v>
-      </c>
-      <c r="D11" t="s">
-        <v>365</v>
-      </c>
-      <c r="E11" t="s">
-        <v>355</v>
-      </c>
-      <c r="F11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H11" t="s">
-        <v>118</v>
-      </c>
-      <c r="I11" t="s">
-        <v>118</v>
-      </c>
-      <c r="J11" t="s">
-        <v>118</v>
-      </c>
-      <c r="K11" t="s">
-        <v>118</v>
-      </c>
-      <c r="L11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>371</v>
-      </c>
-      <c r="C12" t="s">
-        <v>332</v>
-      </c>
-      <c r="D12" t="s">
-        <v>357</v>
-      </c>
-      <c r="E12" t="s">
-        <v>355</v>
-      </c>
-      <c r="F12" t="s">
-        <v>355</v>
-      </c>
-      <c r="G12" t="s">
-        <v>355</v>
-      </c>
-      <c r="H12" t="s">
-        <v>355</v>
-      </c>
-      <c r="I12" t="s">
-        <v>355</v>
-      </c>
-      <c r="J12" t="s">
-        <v>355</v>
-      </c>
-      <c r="K12" t="s">
-        <v>355</v>
-      </c>
-      <c r="L12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>375</v>
-      </c>
-      <c r="B15" t="s">
-        <v>376</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -4244,7 +5607,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>781</v>
       </c>
     </row>
   </sheetData>
@@ -4254,31 +5617,647 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>782</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>346</v>
+        <v>770</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>347</v>
+        <v>771</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>348</v>
+        <v>772</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>379</v>
+        <v>783</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>350</v>
+        <v>774</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>784</v>
+      </c>
+      <c r="C5" t="s">
+        <v>704</v>
+      </c>
+      <c r="D5" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>786</v>
+      </c>
+      <c r="C6" t="s">
+        <v>706</v>
+      </c>
+      <c r="D6" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>788</v>
+      </c>
+      <c r="C7" t="s">
+        <v>689</v>
+      </c>
+      <c r="D7" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>789</v>
+      </c>
+      <c r="C8" t="s">
+        <v>691</v>
+      </c>
+      <c r="D8" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>790</v>
+      </c>
+      <c r="C9" t="s">
+        <v>564</v>
+      </c>
+      <c r="D9" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>791</v>
+      </c>
+      <c r="C10" t="s">
+        <v>754</v>
+      </c>
+      <c r="D10" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>792</v>
+      </c>
+      <c r="C11" t="s">
+        <v>716</v>
+      </c>
+      <c r="D11" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>793</v>
+      </c>
+      <c r="C12" t="s">
+        <v>794</v>
+      </c>
+      <c r="D12" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>506</v>
+      </c>
+      <c r="B13" t="s">
+        <v>795</v>
+      </c>
+      <c r="C13" t="s">
+        <v>796</v>
+      </c>
+      <c r="D13" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>506</v>
+      </c>
+      <c r="B14" t="s">
+        <v>797</v>
+      </c>
+      <c r="C14" t="s">
+        <v>798</v>
+      </c>
+      <c r="D14" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>506</v>
+      </c>
+      <c r="B15" t="s">
+        <v>799</v>
+      </c>
+      <c r="C15" t="s">
+        <v>800</v>
+      </c>
+      <c r="D15" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>506</v>
+      </c>
+      <c r="B16" t="s">
+        <v>802</v>
+      </c>
+      <c r="C16" t="s">
+        <v>756</v>
+      </c>
+      <c r="D16" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>506</v>
+      </c>
+      <c r="B17" t="s">
+        <v>803</v>
+      </c>
+      <c r="C17" t="s">
+        <v>804</v>
+      </c>
+      <c r="D17" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>506</v>
+      </c>
+      <c r="B18" t="s">
+        <v>805</v>
+      </c>
+      <c r="C18" t="s">
+        <v>806</v>
+      </c>
+      <c r="D18" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B19" t="s">
+        <v>807</v>
+      </c>
+      <c r="C19" t="s">
+        <v>700</v>
+      </c>
+      <c r="D19" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>506</v>
+      </c>
+      <c r="B20" t="s">
+        <v>808</v>
+      </c>
+      <c r="C20" t="s">
+        <v>809</v>
+      </c>
+      <c r="D20" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>810</v>
+      </c>
+      <c r="C21" t="s">
+        <v>758</v>
+      </c>
+      <c r="D21" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>811</v>
+      </c>
+      <c r="C22" t="s">
+        <v>760</v>
+      </c>
+      <c r="D22" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>812</v>
+      </c>
+      <c r="C23" t="s">
+        <v>813</v>
+      </c>
+      <c r="D23" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>814</v>
+      </c>
+      <c r="C24" t="s">
+        <v>815</v>
+      </c>
+      <c r="D24" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" t="s">
+        <v>816</v>
+      </c>
+      <c r="C25" t="s">
+        <v>767</v>
+      </c>
+      <c r="D25" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>817</v>
+      </c>
+      <c r="C26" t="s">
+        <v>818</v>
+      </c>
+      <c r="D26" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" t="s">
+        <v>819</v>
+      </c>
+      <c r="C27" t="s">
+        <v>820</v>
+      </c>
+      <c r="D27" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>511</v>
+      </c>
+      <c r="B28" t="s">
+        <v>821</v>
+      </c>
+      <c r="C28" t="s">
+        <v>702</v>
+      </c>
+      <c r="D28" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>511</v>
+      </c>
+      <c r="B29" t="s">
+        <v>822</v>
+      </c>
+      <c r="C29" t="s">
+        <v>823</v>
+      </c>
+      <c r="D29" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>511</v>
+      </c>
+      <c r="B30" t="s">
+        <v>824</v>
+      </c>
+      <c r="C30" t="s">
+        <v>825</v>
+      </c>
+      <c r="D30" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>511</v>
+      </c>
+      <c r="B31" t="s">
+        <v>826</v>
+      </c>
+      <c r="C31" t="s">
+        <v>827</v>
+      </c>
+      <c r="D31" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>511</v>
+      </c>
+      <c r="B32" t="s">
+        <v>828</v>
+      </c>
+      <c r="C32" t="s">
+        <v>829</v>
+      </c>
+      <c r="D32" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>513</v>
+      </c>
+      <c r="B33" t="s">
+        <v>830</v>
+      </c>
+      <c r="C33" t="s">
+        <v>831</v>
+      </c>
+      <c r="D33" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>513</v>
+      </c>
+      <c r="B34" t="s">
+        <v>832</v>
+      </c>
+      <c r="C34" t="s">
+        <v>634</v>
+      </c>
+      <c r="D34" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>513</v>
+      </c>
+      <c r="B35" t="s">
+        <v>833</v>
+      </c>
+      <c r="C35" t="s">
+        <v>834</v>
+      </c>
+      <c r="D35" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>513</v>
+      </c>
+      <c r="B36" t="s">
+        <v>835</v>
+      </c>
+      <c r="C36" t="s">
+        <v>836</v>
+      </c>
+      <c r="D36" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>515</v>
+      </c>
+      <c r="B37" t="s">
+        <v>837</v>
+      </c>
+      <c r="C37" t="s">
+        <v>674</v>
+      </c>
+      <c r="D37" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>515</v>
+      </c>
+      <c r="B38" t="s">
+        <v>838</v>
+      </c>
+      <c r="C38" t="s">
+        <v>676</v>
+      </c>
+      <c r="D38" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>515</v>
+      </c>
+      <c r="B39" t="s">
+        <v>839</v>
+      </c>
+      <c r="C39" t="s">
+        <v>840</v>
+      </c>
+      <c r="D39" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>515</v>
+      </c>
+      <c r="B40" t="s">
+        <v>841</v>
+      </c>
+      <c r="C40" t="s">
+        <v>842</v>
+      </c>
+      <c r="D40" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>517</v>
+      </c>
+      <c r="B41" t="s">
+        <v>843</v>
+      </c>
+      <c r="C41" t="s">
+        <v>678</v>
+      </c>
+      <c r="D41" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>517</v>
+      </c>
+      <c r="B42" t="s">
+        <v>844</v>
+      </c>
+      <c r="C42" t="s">
+        <v>683</v>
+      </c>
+      <c r="D42" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>517</v>
+      </c>
+      <c r="B43" t="s">
+        <v>845</v>
+      </c>
+      <c r="C43" t="s">
+        <v>846</v>
+      </c>
+      <c r="D43" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>517</v>
+      </c>
+      <c r="B44" t="s">
+        <v>847</v>
+      </c>
+      <c r="C44" t="s">
+        <v>848</v>
+      </c>
+      <c r="D44" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" t="s">
+        <v>849</v>
+      </c>
+      <c r="C45" t="s">
+        <v>685</v>
+      </c>
+      <c r="D45" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" t="s">
+        <v>850</v>
+      </c>
+      <c r="C46" t="s">
+        <v>687</v>
+      </c>
+      <c r="D46" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>851</v>
+      </c>
+      <c r="C47" t="s">
+        <v>852</v>
+      </c>
+      <c r="D47" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s">
+        <v>853</v>
+      </c>
+      <c r="C48" t="s">
+        <v>854</v>
+      </c>
+      <c r="D48" t="s">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -4288,12 +6267,12 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>855</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4303,458 +6282,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>381</v>
+        <v>856</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>382</v>
+        <v>857</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>383</v>
+        <v>858</v>
       </c>
       <c r="B5" t="s">
-        <v>384</v>
+        <v>859</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>385</v>
+        <v>860</v>
       </c>
       <c r="B6" t="s">
-        <v>386</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>387</v>
+        <v>862</v>
       </c>
       <c r="B7" t="s">
-        <v>388</v>
+        <v>863</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>389</v>
+        <v>864</v>
       </c>
       <c r="B8" t="s">
-        <v>390</v>
+        <v>865</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>391</v>
+        <v>866</v>
       </c>
       <c r="B9" t="s">
-        <v>392</v>
+        <v>867</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>393</v>
+        <v>868</v>
       </c>
       <c r="B10" t="s">
-        <v>376</v>
+        <v>780</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>394</v>
+        <v>869</v>
       </c>
       <c r="B11" t="s">
-        <v>395</v>
+        <v>780</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>396</v>
+        <v>870</v>
       </c>
       <c r="B12" t="s">
-        <v>397</v>
+        <v>871</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>398</v>
+        <v>872</v>
       </c>
       <c r="B13" t="s">
-        <v>399</v>
+        <v>873</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>400</v>
+        <v>874</v>
       </c>
       <c r="B14" t="s">
-        <v>401</v>
+        <v>875</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>402</v>
+        <v>876</v>
       </c>
       <c r="B15" t="s">
-        <v>403</v>
+        <v>877</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>404</v>
+        <v>878</v>
       </c>
       <c r="B16" t="s">
-        <v>405</v>
+        <v>879</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>406</v>
+        <v>880</v>
       </c>
       <c r="B17" t="s">
-        <v>407</v>
+        <v>881</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>408</v>
+        <v>882</v>
       </c>
       <c r="B18" t="s">
-        <v>409</v>
+        <v>883</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>410</v>
+        <v>884</v>
       </c>
       <c r="B19" t="s">
-        <v>409</v>
+        <v>883</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>411</v>
+        <v>885</v>
       </c>
       <c r="B20" t="s">
-        <v>412</v>
+        <v>886</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>413</v>
+        <v>887</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>886</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>414</v>
+        <v>888</v>
       </c>
       <c r="B22" t="s">
-        <v>166</v>
+        <v>889</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>415</v>
+        <v>890</v>
       </c>
       <c r="B23" t="s">
-        <v>352</v>
+        <v>775</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>416</v>
+        <v>891</v>
       </c>
       <c r="B24" t="s">
-        <v>352</v>
+        <v>568</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>417</v>
+        <v>892</v>
       </c>
       <c r="B25" t="s">
-        <v>352</v>
+        <v>776</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>418</v>
+        <v>893</v>
       </c>
       <c r="B26" t="s">
-        <v>352</v>
+        <v>776</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>419</v>
+        <v>894</v>
       </c>
       <c r="B27" t="s">
-        <v>352</v>
+        <v>776</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>420</v>
+        <v>895</v>
       </c>
       <c r="B28" t="s">
-        <v>352</v>
+        <v>776</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>421</v>
+        <v>896</v>
       </c>
       <c r="B29" t="s">
-        <v>229</v>
+        <v>776</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>422</v>
+        <v>897</v>
       </c>
       <c r="B30" t="s">
-        <v>229</v>
+        <v>776</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>423</v>
+        <v>898</v>
       </c>
       <c r="B31" t="s">
-        <v>229</v>
+        <v>653</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>424</v>
+        <v>899</v>
       </c>
       <c r="B32" t="s">
-        <v>229</v>
+        <v>653</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>425</v>
+        <v>900</v>
       </c>
       <c r="B33" t="s">
-        <v>229</v>
+        <v>653</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>426</v>
+        <v>901</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>653</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>427</v>
+        <v>902</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>653</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>428</v>
+        <v>903</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
+        <v>576</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>429</v>
+        <v>904</v>
       </c>
       <c r="B37" t="s">
-        <v>152</v>
+        <v>576</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>430</v>
+        <v>905</v>
       </c>
       <c r="B38" t="s">
-        <v>152</v>
+        <v>576</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>431</v>
+        <v>906</v>
       </c>
       <c r="B39" t="s">
-        <v>152</v>
+        <v>576</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>432</v>
+        <v>907</v>
       </c>
       <c r="B40" t="s">
-        <v>222</v>
+        <v>576</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>433</v>
+        <v>908</v>
       </c>
       <c r="B41" t="s">
-        <v>222</v>
+        <v>576</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>434</v>
+        <v>909</v>
       </c>
       <c r="B42" t="s">
-        <v>222</v>
+        <v>576</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>435</v>
+        <v>910</v>
       </c>
       <c r="B43" t="s">
-        <v>222</v>
+        <v>576</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>436</v>
+        <v>911</v>
       </c>
       <c r="B44" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>437</v>
+        <v>912</v>
       </c>
       <c r="B45" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>438</v>
+        <v>913</v>
       </c>
       <c r="B46" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>439</v>
+        <v>914</v>
       </c>
       <c r="B47" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>440</v>
+        <v>915</v>
       </c>
       <c r="B48" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>441</v>
+        <v>916</v>
       </c>
       <c r="B49" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>442</v>
+        <v>917</v>
       </c>
       <c r="B50" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>443</v>
+        <v>918</v>
       </c>
       <c r="B51" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>444</v>
+        <v>919</v>
       </c>
       <c r="B52" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>445</v>
+        <v>920</v>
       </c>
       <c r="B53" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>446</v>
+        <v>921</v>
       </c>
       <c r="B54" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>447</v>
+        <v>922</v>
       </c>
       <c r="B55" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>448</v>
+        <v>923</v>
       </c>
       <c r="B56" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>449</v>
+        <v>924</v>
       </c>
       <c r="B57" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>450</v>
+        <v>925</v>
       </c>
       <c r="B58" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>451</v>
+        <v>926</v>
       </c>
       <c r="B59" t="s">
-        <v>222</v>
+        <v>646</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>452</v>
+        <v>927</v>
       </c>
       <c r="B60" t="s">
-        <v>222</v>
+        <v>646</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>928</v>
+      </c>
+      <c r="B61" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>929</v>
+      </c>
+      <c r="B62" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>930</v>
+      </c>
+      <c r="B63" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>931</v>
+      </c>
+      <c r="B64" t="s">
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -4789,7 +6800,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4799,12 +6810,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -4819,7 +6835,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4829,7 +6845,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4839,12 +6855,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4854,7 +6870,1082 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -4864,22 +7955,52 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -4889,17 +8010,52 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4909,17 +8065,1097 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="621">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -150,54 +150,6 @@
     <t>(!!! MUST FIX !!! - not allowed)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_496698b1_XU8_be4c5eaa_XDEBUG(ten_496698b1_XU8_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_5e7931f3_XU7_be4c5eaa_XDEBUG(ten_5e7931f3_XU7_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_7bb789c1_XU3_be4c5eaa_XDEBUG(ten_7bb789c1_XU3_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_bdb7126b_XU6_be4c5eaa_XDEBUG(ten_bdb7126b_XU6_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_fc840bff_XU4_be4c5eaa_XDEBUG(ten_fc840bff_XU4_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_38b575fc_XU10_be4c5eaa_XDEBUG(ten_38b575fc_XU10_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_71505146_XU19_be4c5eaa_XDEBUG(ten_71505146_XU19_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_b20889dd_XU21_be4c5eaa_XDEBUG(ten_b20889dd_XU21_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_f614d104_XU20_be4c5eaa_XDEBUG(ten_f614d104_XU20_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN(ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN(global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN(global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN)</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK</t>
   </si>
   <si>
@@ -213,51 +165,6 @@
     <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
   </si>
   <si>
-    <t>Floating pin XCONTROL.ten_016e5221_XU14_76edd7de_XCONTROL(ten_016e5221_XU14_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_10af5487_XU89_76edd7de_XCONTROL(ten_10af5487_XU89_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_1c924704_XU94_76edd7de_XCONTROL(ten_1c924704_XU94_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_250e1d7b_XU96_76edd7de_XCONTROL(ten_250e1d7b_XU96_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_3a54983a_XU93_76edd7de_XCONTROL(ten_3a54983a_XU93_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_5dbb5861_XU98_76edd7de_XCONTROL(ten_5dbb5861_XU98_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_78907f64_XU97_76edd7de_XCONTROL(ten_78907f64_XU97_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_9e0c6a0f_XU20_76edd7de_XCONTROL(ten_9e0c6a0f_XU20_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_a9541403_XU99_76edd7de_XCONTROL(ten_a9541403_XU99_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_b275df66_XU92_76edd7de_XCONTROL(ten_b275df66_XU92_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_c406e2e9_XU16_76edd7de_XCONTROL(ten_c406e2e9_XU16_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_dc7df0cc_XU18_76edd7de_XCONTROL(ten_dc7df0cc_XU18_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_e1c50519_XU90_76edd7de_XCONTROL(ten_e1c50519_XU90_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_e41e5cb3_XU95_76edd7de_XCONTROL(ten_e41e5cb3_XU95_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_efe3dfd4_XU91_76edd7de_XCONTROL(ten_efe3dfd4_XU91_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
     <t>Floating pin XALGORITHM.enableFAULT(121)</t>
   </si>
   <si>
@@ -318,231 +225,15 @@
     <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW(global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_2a0216d2_XU20_c1b82e6f_XDEBUG(ten_2a0216d2_XU20_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_32f97a89_XU11_c1b82e6f_XDEBUG(ten_32f97a89_XU11_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_34071f1d_XU15_c1b82e6f_XDEBUG(ten_34071f1d_XU15_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_3788e0aa_XU16_c1b82e6f_XDEBUG(ten_3788e0aa_XU16_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_e5798d25_XU18_c1b82e6f_XDEBUG(ten_e5798d25_XU18_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_f83f6ba2_XU10_c1b82e6f_XDEBUG(ten_f83f6ba2_XU10_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_fcfb2c12_XU12_c1b82e6f_XDEBUG(ten_fcfb2c12_XU12_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_af379456_XU5_c1b82e6f_XDEBUG(ten_hijack_af379456_XU5_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG(ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XTOPSW.global_cboot_35156756_XU17_f604d85e_XTOPSW(global_cboot_35156756_XU17_f604d85e_XTOPSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XTOPSW.global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW(global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XTOPSW.ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW(ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XTOPSW.global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW(global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XTOPSW.ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW(ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW)</t>
-  </si>
-  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_6044b743_XU7_4c867da6_XDEBUG(ten_6044b743_XU7_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_7e48a0c0_XU2_4c867da6_XDEBUG(ten_7e48a0c0_XU2_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_7e6d3e04_XU1_4c867da6_XDEBUG(ten_7e6d3e04_XU1_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_0b40c959_XU6_4c867da6_XDEBUG(ten_hijack_0b40c959_XU6_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_54e727e4_XU15_4c867da6_XDEBUG(ten_hijack_54e727e4_XU15_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_9929432d_XU17_4c867da6_XDEBUG(ten_hijack_9929432d_XU17_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG(ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG(ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_9929432d_XU17_4c867da6_XDEBUG(ten_hijacki_9929432d_XU17_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN(ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN)</t>
-  </si>
-  <si>
     <t>Floating pin XMAIN.mode_hiccup(45)</t>
   </si>
   <si>
     <t>Floating pin XMAIN.blank_thermal(46)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_14c9168a_XU7_1cec7299_XDEBUG(ten_14c9168a_XU7_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_6d67c253_XU1_1cec7299_XDEBUG(ten_6d67c253_XU1_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_c69fe1aa_XU8_1cec7299_XDEBUG(ten_c69fe1aa_XU8_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_1d78f0e4_XU13_1cec7299_XDEBUG(ten_1d78f0e4_XU13_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_d748b831_XU15_1cec7299_XDEBUG(ten_d748b831_XU15_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_f4762d45_XU11_1cec7299_XDEBUG(ten_f4762d45_XU11_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_6613b2af_XU3_1cec7299_XDEBUG(ten_hijack_6613b2af_XU3_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_c541f94b_XU16_1cec7299_XDEBUG(ten_hijack_c541f94b_XU16_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG(ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG(ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG(ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_vbuffer_e96a4067_XU8_811a9a05_XMAIN(global_vbuffer_e96a4067_XU8_811a9a05_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN(ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_comparator_70e67769_XU3_811a9a05_XMAIN(global_comparator_70e67769_XU3_811a9a05_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_comparator_ddbf938d_XU22_811a9a05_XMAIN(global_comparator_ddbf938d_XU22_811a9a05_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_resistordivider_37d49b79_XU17_811a9a05_XMAIN(global_resistordivider_37d49b79_XU17_811a9a05_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_162b659f_XU9_f255c70e_XDEBUG(ten_162b659f_XU9_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_83ff2716_XU8_f255c70e_XDEBUG(ten_83ff2716_XU8_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_913fa695_XU7_f255c70e_XDEBUG(ten_913fa695_XU7_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_95483466_XU2_f255c70e_XDEBUG(ten_95483466_XU2_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_d922ca5f_XU6_f255c70e_XDEBUG(ten_d922ca5f_XU6_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_de422ccd_XU11_f255c70e_XDEBUG(ten_hijack_de422ccd_XU11_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG(ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
     <t>Floating pin XU10.enable_switch(58)</t>
   </si>
   <si>
@@ -570,63 +261,6 @@
     <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_gm_e44d2b4d_Xgm1_10783060_XMAIN(global_gm_e44d2b4d_Xgm1_10783060_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_clamp_b8eb1a18_XU7_10783060_XMAIN(global_clamp_b8eb1a18_XU7_10783060_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_vbuffer_866ca25c_XU9_10783060_XMAIN(global_vbuffer_866ca25c_XU9_10783060_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_comparator_5c7dff44_XU10_10783060_XMAIN(global_comparator_5c7dff44_XU10_10783060_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_voltage2current_4215aede_XU3_10783060_XMAIN(global_voltage2current_4215aede_XU3_10783060_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_0721e5d9_XU56_5c792007_XSEQUENCER(ten_0721e5d9_XU56_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_2958f818_XU61_5c792007_XSEQUENCER(ten_2958f818_XU61_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_29fa69a5_XU60_5c792007_XSEQUENCER(ten_29fa69a5_XU60_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_3bd9bacc_XU59_5c792007_XSEQUENCER(ten_3bd9bacc_XU59_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_445acf01_XU57_5c792007_XSEQUENCER(ten_445acf01_XU57_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_4c7ada73_XU65_5c792007_XSEQUENCER(ten_4c7ada73_XU65_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_4d227e72_XU55_5c792007_XSEQUENCER(ten_4d227e72_XU55_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_6cd23b02_XU66_5c792007_XSEQUENCER(ten_6cd23b02_XU66_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_70525239_XU58_5c792007_XSEQUENCER(ten_70525239_XU58_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_950364d7_XU54_5c792007_XSEQUENCER(ten_950364d7_XU54_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_9d829c39_XU62_5c792007_XSEQUENCER(ten_9d829c39_XU62_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_9ef032e9_XU63_5c792007_XSEQUENCER(ten_9ef032e9_XU63_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_e8d90cd0_XU64_5c792007_XSEQUENCER(ten_e8d90cd0_XU64_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
     <t>Floating pin XMAIN.STATEcontrol0(80)</t>
   </si>
   <si>
@@ -639,777 +273,279 @@
     <t>Floating pin XMAIN.STATEcontrol3(83)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_1955111b_XU7_63f6e3c4_XDEBUG(ten_1955111b_XU7_63f6e3c4_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_742857bf_XU2_63f6e3c4_XDEBUG(ten_742857bf_XU2_63f6e3c4_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_a6a0ac97_XU3_63f6e3c4_XDEBUG(ten_a6a0ac97_XU3_63f6e3c4_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_ec5776d4_XU6_63f6e3c4_XDEBUG(ten_ec5776d4_XU6_63f6e3c4_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_cd882763_XU15_63f6e3c4_XDEBUG(ten_cd882763_XU15_63f6e3c4_XDEBUG)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_ref_553d3e5b_XU4_2345cd7b_XMAIN(ten_ref_553d3e5b_XU4_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN(ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_reference_553d3e5b_XU4_2345cd7b_XMAIN(global_reference_553d3e5b_XU4_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN(global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_comparator_75c89176_XU16_2345cd7b_XMAIN(global_comparator_75c89176_XU16_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_81f80d4d_XU8_88e49508_XDEBUG(ten_81f80d4d_XU8_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_ed87e5db_XU5_88e49508_XDEBUG(ten_ed87e5db_XU5_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_f665b623_XU6_88e49508_XDEBUG(ten_f665b623_XU6_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_528f048c_XU10_88e49508_XDEBUG(ten_528f048c_XU10_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_297df8ef_XU1_88e49508_XDEBUG(ten_hijack_297df8ef_XU1_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_dcf795e2_XU14_88e49508_XDEBUG(ten_hijack_dcf795e2_XU14_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_297df8ef_XU1_88e49508_XDEBUG(ten_hijacki_297df8ef_XU1_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG(ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG)</t>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
+  </si>
+  <si>
+    <t>Floating Outputs</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
+  </si>
+  <si>
+    <t>No Connects - Outputs</t>
+  </si>
+  <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>Mixed Mode Conflicts</t>
+  </si>
+  <si>
+    <t>Ring Core IO check report</t>
+  </si>
+  <si>
+    <t>No issues found</t>
+  </si>
+  <si>
+    <t>D to A Tree</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
   </si>
   <si>
-    <t>Floating pin XMAIN8.global_dac_0cc08401_XU5_b48f6491_XMAIN8(global_dac_0cc08401_XU5_b48f6491_XMAIN8)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8(global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.halfway(36)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
-  </si>
-  <si>
-    <t>Floating Outputs</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
-  </si>
-  <si>
-    <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>ten_496698b1_XU8_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_496698b1_XU8_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_5e7931f3_XU7_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_5e7931f3_XU7_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_7bb789c1_XU3_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7bb789c1_XU3_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_bdb7126b_XU6_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_bdb7126b_XU6_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_fc840bff_XU4_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fc840bff_XU4_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_38b575fc_XU10_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_38b575fc_XU10_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_71505146_XU19_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_71505146_XU19_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_b20889dd_XU21_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_b20889dd_XU21_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_f614d104_XU20_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f614d104_XU20_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>ten_016e5221_XU14_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_016e5221_XU14_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_10af5487_XU89_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_10af5487_XU89_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_1c924704_XU94_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_1c924704_XU94_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_250e1d7b_XU96_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_250e1d7b_XU96_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_3a54983a_XU93_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_3a54983a_XU93_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_5dbb5861_XU98_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_5dbb5861_XU98_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_78907f64_XU97_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_78907f64_XU97_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_9e0c6a0f_XU20_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_9e0c6a0f_XU20_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_a9541403_XU99_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_a9541403_XU99_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_b275df66_XU92_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_b275df66_XU92_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_c406e2e9_XU16_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_c406e2e9_XU16_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_dc7df0cc_XU18_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_dc7df0cc_XU18_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_e1c50519_XU90_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e1c50519_XU90_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_e41e5cb3_XU95_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e41e5cb3_XU95_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_efe3dfd4_XU91_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_efe3dfd4_XU91_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_2a0216d2_XU20_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_2a0216d2_XU20_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_32f97a89_XU11_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_32f97a89_XU11_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_34071f1d_XU15_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_34071f1d_XU15_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_3788e0aa_XU16_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_3788e0aa_XU16_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_e5798d25_XU18_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_e5798d25_XU18_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_f83f6ba2_XU10_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f83f6ba2_XU10_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_fcfb2c12_XU12_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fcfb2c12_XU12_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_cboot_35156756_XU17_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_cboot_35156756_XU17_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_6044b743_XU7_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6044b743_XU7_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_7e48a0c0_XU2_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e48a0c0_XU2_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_7e6d3e04_XU1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e6d3e04_XU1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>ten_14c9168a_XU7_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_14c9168a_XU7_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_6d67c253_XU1_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6d67c253_XU1_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_c69fe1aa_XU8_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_c69fe1aa_XU8_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_1d78f0e4_XU13_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1d78f0e4_XU13_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_d748b831_XU15_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d748b831_XU15_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_f4762d45_XU11_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f4762d45_XU11_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_vbuffer_e96a4067_XU8_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_e96a4067_XU8_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_comparator_70e67769_XU3_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_70e67769_XU3_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_comparator_ddbf938d_XU22_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_ddbf938d_XU22_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_resistordivider_37d49b79_XU17_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_162b659f_XU9_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_162b659f_XU9_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_83ff2716_XU8_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_83ff2716_XU8_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_913fa695_XU7_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_913fa695_XU7_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_95483466_XU2_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_95483466_XU2_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_d922ca5f_XU6_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d922ca5f_XU6_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>global_gm_e44d2b4d_Xgm1_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_gm_e44d2b4d_Xgm1_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_clamp_b8eb1a18_XU7_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_clamp_b8eb1a18_XU7_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_vbuffer_866ca25c_XU9_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_866ca25c_XU9_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_comparator_5c7dff44_XU10_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_5c7dff44_XU10_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_voltage2current_4215aede_XU3_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_voltage2current_4215aede_XU3_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_0721e5d9_XU56_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_0721e5d9_XU56_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_2958f818_XU61_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_2958f818_XU61_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_29fa69a5_XU60_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_29fa69a5_XU60_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_3bd9bacc_XU59_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_3bd9bacc_XU59_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_445acf01_XU57_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_445acf01_XU57_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_4c7ada73_XU65_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4c7ada73_XU65_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_4d227e72_XU55_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4d227e72_XU55_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_6cd23b02_XU66_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_6cd23b02_XU66_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_70525239_XU58_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_70525239_XU58_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_950364d7_XU54_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_950364d7_XU54_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_9d829c39_XU62_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9d829c39_XU62_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_9ef032e9_XU63_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9ef032e9_XU63_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_e8d90cd0_XU64_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_e8d90cd0_XU64_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>ten_1955111b_XU7_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1955111b_XU7_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_742857bf_XU2_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_742857bf_XU2_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_a6a0ac97_XU3_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_a6a0ac97_XU3_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_ec5776d4_XU6_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ec5776d4_XU6_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_cd882763_XU15_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_cd882763_XU15_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_ref_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_ref_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_reference_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_reference_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_comparator_75c89176_XU16_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_75c89176_XU16_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_81f80d4d_XU8_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_81f80d4d_XU8_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_ed87e5db_XU5_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ed87e5db_XU5_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_f665b623_XU6_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f665b623_XU6_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_528f048c_XU10_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_528f048c_XU10_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_dac_0cc08401_XU5_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_dac_0cc08401_XU5_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>Mixed Mode Conflicts</t>
-  </si>
-  <si>
-    <t>Ring Core IO check report</t>
-  </si>
-  <si>
-    <t>No issues found</t>
-  </si>
-  <si>
-    <t>D to A Tree</t>
-  </si>
-  <si>
     <t>Xoscillator1</t>
   </si>
   <si>
@@ -1417,33 +553,6 @@
   </si>
   <si>
     <t>Errors</t>
-  </si>
-  <si>
-    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
-  </si>
-  <si>
-    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
-  </si>
-  <si>
-    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
   </si>
   <si>
     <t>Cell Length Exceed Max 50</t>
@@ -1552,10 +661,22 @@
     <t>DFT Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
     <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
@@ -1564,7 +685,22 @@
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER</t>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
@@ -1573,37 +709,40 @@
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD</t>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSEQUENCER</t>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE</t>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
   </si>
   <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 44, 'bytes': 44.0, 'noconns': 44, 'efficiency': '87.5%'}</t>
+    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
   </si>
   <si>
     <t>Project Summary</t>
@@ -2407,210 +1546,138 @@
     <t>dft_hex0x02</t>
   </si>
   <si>
+    <t>DFTtm8t</t>
+  </si>
+  <si>
+    <t>dft_hex0x1A</t>
+  </si>
+  <si>
+    <t>0x1A</t>
+  </si>
+  <si>
+    <t>dft_hex0x03</t>
+  </si>
+  <si>
     <t>DFTtm8d</t>
   </si>
   <si>
+    <t>dft_hex0x04</t>
+  </si>
+  <si>
+    <t>dft_hex0x05</t>
+  </si>
+  <si>
+    <t>0x05</t>
+  </si>
+  <si>
+    <t>dft_hex0x06</t>
+  </si>
+  <si>
+    <t>0x06</t>
+  </si>
+  <si>
+    <t>dft_hex0x07</t>
+  </si>
+  <si>
+    <t>0x07</t>
+  </si>
+  <si>
+    <t>dft_hex0x08</t>
+  </si>
+  <si>
+    <t>dft_hex0x1B</t>
+  </si>
+  <si>
+    <t>0x1B</t>
+  </si>
+  <si>
+    <t>dft_hex0x09</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B</t>
+  </si>
+  <si>
+    <t>0x0B</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C</t>
+  </si>
+  <si>
+    <t>dft_hex0x1C</t>
+  </si>
+  <si>
+    <t>dft_hex0x1D</t>
+  </si>
+  <si>
+    <t>0x1D</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D</t>
+  </si>
+  <si>
+    <t>0x0D</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E</t>
+  </si>
+  <si>
+    <t>0x0E</t>
+  </si>
+  <si>
+    <t>dft_hex0x0F</t>
+  </si>
+  <si>
+    <t>dft_hex0x1E</t>
+  </si>
+  <si>
+    <t>0x1E</t>
+  </si>
+  <si>
+    <t>dft_hex0x10</t>
+  </si>
+  <si>
+    <t>dft_hex0x11</t>
+  </si>
+  <si>
+    <t>dft_hex0x1F</t>
+  </si>
+  <si>
+    <t>dft_hex0x12</t>
+  </si>
+  <si>
+    <t>dft_hex0x13</t>
+  </si>
+  <si>
+    <t>dft_hex0x14</t>
+  </si>
+  <si>
+    <t>dft_hex0x15</t>
+  </si>
+  <si>
     <t>dft_hex0x16</t>
   </si>
   <si>
     <t>dft_hex0x17</t>
   </si>
   <si>
-    <t>dft_hex0x03</t>
-  </si>
-  <si>
-    <t>dft_hex0x04</t>
-  </si>
-  <si>
     <t>dft_hex0x18</t>
   </si>
   <si>
+    <t>dft_hex0x20</t>
+  </si>
+  <si>
+    <t>0x20</t>
+  </si>
+  <si>
     <t>dft_hex0x19</t>
   </si>
   <si>
     <t>0x19</t>
   </si>
   <si>
-    <t>dft_hex0x05</t>
-  </si>
-  <si>
-    <t>0x05</t>
-  </si>
-  <si>
-    <t>dft_hex0x06</t>
-  </si>
-  <si>
-    <t>0x06</t>
-  </si>
-  <si>
-    <t>dft_hex0x07</t>
-  </si>
-  <si>
-    <t>0x07</t>
-  </si>
-  <si>
-    <t>DFTtm8t</t>
-  </si>
-  <si>
-    <t>dft_hex0x08</t>
-  </si>
-  <si>
-    <t>dft_hex0x1A</t>
-  </si>
-  <si>
-    <t>0x1A</t>
-  </si>
-  <si>
-    <t>dft_hex0x1B</t>
-  </si>
-  <si>
-    <t>0x1B</t>
-  </si>
-  <si>
-    <t>dft_hex0x1C</t>
-  </si>
-  <si>
-    <t>dft_hex0x1D</t>
-  </si>
-  <si>
-    <t>0x1D</t>
-  </si>
-  <si>
-    <t>dft_hex0x09</t>
-  </si>
-  <si>
-    <t>dft_hex0x0A</t>
-  </si>
-  <si>
-    <t>dft_hex0x0B</t>
-  </si>
-  <si>
-    <t>0x0B</t>
-  </si>
-  <si>
-    <t>dft_hex0x1E</t>
-  </si>
-  <si>
-    <t>0x1E</t>
-  </si>
-  <si>
-    <t>dft_hex0x1F</t>
-  </si>
-  <si>
-    <t>dft_hex0x20</t>
-  </si>
-  <si>
-    <t>0x20</t>
-  </si>
-  <si>
-    <t>dft_hex0x21</t>
-  </si>
-  <si>
-    <t>0x21</t>
-  </si>
-  <si>
-    <t>dft_hex0x0C</t>
-  </si>
-  <si>
-    <t>dft_hex0x0D</t>
-  </si>
-  <si>
-    <t>0x0D</t>
-  </si>
-  <si>
-    <t>dft_hex0x22</t>
-  </si>
-  <si>
-    <t>0x22</t>
-  </si>
-  <si>
-    <t>dft_hex0x23</t>
-  </si>
-  <si>
-    <t>0x23</t>
-  </si>
-  <si>
-    <t>dft_hex0x24</t>
-  </si>
-  <si>
-    <t>0x24</t>
-  </si>
-  <si>
-    <t>dft_hex0x0E</t>
-  </si>
-  <si>
-    <t>0x0E</t>
-  </si>
-  <si>
-    <t>dft_hex0x0F</t>
-  </si>
-  <si>
-    <t>dft_hex0x25</t>
-  </si>
-  <si>
-    <t>0x25</t>
-  </si>
-  <si>
-    <t>dft_hex0x26</t>
-  </si>
-  <si>
-    <t>0x26</t>
-  </si>
-  <si>
-    <t>dft_hex0x10</t>
-  </si>
-  <si>
-    <t>dft_hex0x11</t>
-  </si>
-  <si>
-    <t>dft_hex0x27</t>
-  </si>
-  <si>
-    <t>0x27</t>
-  </si>
-  <si>
-    <t>dft_hex0x28</t>
-  </si>
-  <si>
-    <t>0x28</t>
-  </si>
-  <si>
-    <t>dft_hex0x12</t>
-  </si>
-  <si>
-    <t>dft_hex0x13</t>
-  </si>
-  <si>
-    <t>dft_hex0x29</t>
-  </si>
-  <si>
-    <t>0x29</t>
-  </si>
-  <si>
-    <t>dft_hex0x2A</t>
-  </si>
-  <si>
-    <t>0x2A</t>
-  </si>
-  <si>
-    <t>dft_hex0x14</t>
-  </si>
-  <si>
-    <t>dft_hex0x15</t>
-  </si>
-  <si>
-    <t>dft_hex0x2B</t>
-  </si>
-  <si>
-    <t>0x2B</t>
-  </si>
-  <si>
-    <t>dft_hex0x2C</t>
-  </si>
-  <si>
-    <t>0x2C</t>
-  </si>
-  <si>
     <t>Nesto Usage Report</t>
   </si>
   <si>
@@ -2632,16 +1699,16 @@
     <t>193</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
     <t>noconn</t>
   </si>
   <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>148</t>
+    <t>131</t>
   </si>
   <si>
     <t>dbuf</t>
@@ -2674,22 +1741,22 @@
     <t>45</t>
   </si>
   <si>
+    <t>srlatch</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>nor2</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
     <t>dftmodule</t>
   </si>
   <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>srlatch</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>nor2</t>
-  </si>
-  <si>
-    <t>35</t>
+    <t>32</t>
   </si>
   <si>
     <t>dfthijack</t>
@@ -3210,7 +2277,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>452</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3230,7 +2297,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>453</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3245,7 +2312,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>454</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3260,17 +2327,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>455</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>456</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -3280,62 +2347,17 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>457</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>467</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3350,17 +2372,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>468</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>458</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>469</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3375,12 +2397,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>470</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>458</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3395,7 +2417,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>471</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3415,127 +2437,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>472</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>473</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>474</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>475</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>476</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>477</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>478</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>479</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>480</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>481</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>482</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>483</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>484</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>485</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>486</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>487</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>488</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>489</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>490</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>491</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>492</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>493</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>494</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>495</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>496</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3550,7 +2572,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>497</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3570,17 +2592,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>498</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>499</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>500</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -3800,277 +2822,257 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>501</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>502</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>503</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>502</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
+      <c r="A8" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>505</v>
+      <c r="A11" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>504</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>505</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>506</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>502</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>507</v>
+      <c r="A18" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>508</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>502</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>504</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>509</v>
+      <c r="A23" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>504</v>
+      <c r="A25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>507</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>510</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>504</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>507</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>507</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="1" t="s">
-        <v>511</v>
+      <c r="A33" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>507</v>
+      <c r="A36" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>502</v>
+        <v>206</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>507</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>512</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>513</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>502</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>502</v>
+      <c r="A44" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>514</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>504</v>
+      <c r="A47" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>516</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>516</v>
+      <c r="A51" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="1" t="s">
-        <v>517</v>
+      <c r="A53" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>509</v>
+      <c r="A55" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>502</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="1" t="s">
-        <v>26</v>
+      <c r="A58" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>502</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>502</v>
+      <c r="A62" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>514</v>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -4085,17 +3087,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>518</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>499</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>519</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -4110,52 +3112,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>520</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>521</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>522</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>523</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>524</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>525</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>526</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>527</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>528</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>529</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4170,81 +3172,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>530</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>531</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>534</v>
+        <v>247</v>
       </c>
       <c r="B5" t="s">
-        <v>535</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>536</v>
+        <v>249</v>
       </c>
       <c r="B6" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>538</v>
+        <v>251</v>
       </c>
       <c r="B7" t="s">
-        <v>537</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>539</v>
+        <v>252</v>
       </c>
       <c r="B8" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>540</v>
+        <v>253</v>
       </c>
       <c r="B9" t="s">
-        <v>541</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>542</v>
+        <v>255</v>
       </c>
       <c r="B10" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>544</v>
+        <v>257</v>
       </c>
       <c r="B11" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>545</v>
+        <v>258</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -4252,1268 +3254,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>546</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>547</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>548</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>549</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>550</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>551</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>552</v>
+        <v>265</v>
       </c>
       <c r="B20" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>553</v>
+        <v>266</v>
       </c>
       <c r="B21" t="s">
-        <v>537</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>554</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>555</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>556</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>557</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>558</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>559</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s">
-        <v>560</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>561</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>562</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>563</v>
+        <v>276</v>
       </c>
       <c r="B32" t="s">
-        <v>564</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>565</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s">
-        <v>566</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>567</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>569</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s">
-        <v>570</v>
+        <v>283</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>571</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s">
-        <v>572</v>
+        <v>285</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>573</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>574</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>575</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>577</v>
+        <v>290</v>
       </c>
       <c r="B40" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>578</v>
+        <v>291</v>
       </c>
       <c r="B41" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>579</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>580</v>
+        <v>293</v>
       </c>
       <c r="B43" t="s">
-        <v>581</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>582</v>
+        <v>295</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>583</v>
+        <v>296</v>
       </c>
       <c r="B46" t="s">
-        <v>584</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>585</v>
+        <v>298</v>
       </c>
       <c r="B47" t="s">
-        <v>535</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>586</v>
+        <v>299</v>
       </c>
       <c r="B48" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>587</v>
+        <v>300</v>
       </c>
       <c r="B49" t="s">
-        <v>535</v>
+        <v>248</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>588</v>
+        <v>301</v>
       </c>
       <c r="B50" t="s">
-        <v>535</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>589</v>
+        <v>302</v>
       </c>
       <c r="B51" t="s">
-        <v>590</v>
+        <v>303</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>591</v>
+        <v>304</v>
       </c>
       <c r="B52" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>592</v>
+        <v>305</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>593</v>
+        <v>306</v>
       </c>
       <c r="B55" t="s">
-        <v>594</v>
+        <v>307</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>595</v>
+        <v>308</v>
       </c>
       <c r="B56" t="s">
-        <v>596</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>597</v>
+        <v>310</v>
       </c>
       <c r="B57" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>598</v>
+        <v>311</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>599</v>
+        <v>312</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>600</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>601</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>602</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>603</v>
+        <v>316</v>
       </c>
       <c r="B64" t="s">
-        <v>604</v>
+        <v>317</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>605</v>
+        <v>318</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>606</v>
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>607</v>
+        <v>320</v>
       </c>
       <c r="B67" t="s">
-        <v>608</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>609</v>
+        <v>322</v>
       </c>
       <c r="B68" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>611</v>
+        <v>324</v>
       </c>
       <c r="B69" t="s">
-        <v>608</v>
+        <v>321</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>612</v>
+        <v>325</v>
       </c>
       <c r="B70" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>613</v>
+        <v>326</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>614</v>
+        <v>327</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>615</v>
+        <v>328</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>616</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>617</v>
+        <v>330</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>618</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>619</v>
+        <v>332</v>
       </c>
       <c r="B78" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>620</v>
+        <v>333</v>
       </c>
       <c r="B79" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>621</v>
+        <v>334</v>
       </c>
       <c r="B80" t="s">
-        <v>622</v>
+        <v>335</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>623</v>
+        <v>336</v>
       </c>
       <c r="B81" t="s">
-        <v>624</v>
+        <v>337</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>625</v>
+        <v>338</v>
       </c>
       <c r="B82" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>626</v>
+        <v>339</v>
       </c>
       <c r="B83" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>627</v>
+        <v>340</v>
       </c>
       <c r="B84" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>628</v>
+        <v>341</v>
       </c>
       <c r="B85" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>629</v>
+        <v>342</v>
       </c>
       <c r="B86" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>630</v>
+        <v>343</v>
       </c>
       <c r="B87" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>631</v>
+        <v>344</v>
       </c>
       <c r="B88" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>632</v>
+        <v>345</v>
       </c>
       <c r="B89" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>633</v>
+        <v>346</v>
       </c>
       <c r="B90" t="s">
-        <v>634</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>635</v>
+        <v>348</v>
       </c>
       <c r="B91" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>636</v>
+        <v>349</v>
       </c>
       <c r="B92" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>637</v>
+        <v>350</v>
       </c>
       <c r="B93" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>638</v>
+        <v>351</v>
       </c>
       <c r="B94" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>639</v>
+        <v>352</v>
       </c>
       <c r="B95" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>640</v>
+        <v>353</v>
       </c>
       <c r="B96" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>641</v>
+        <v>354</v>
       </c>
       <c r="B97" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>642</v>
+        <v>355</v>
       </c>
       <c r="B98" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>643</v>
+        <v>356</v>
       </c>
       <c r="B99" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>644</v>
+        <v>357</v>
       </c>
       <c r="B100" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>645</v>
+        <v>358</v>
       </c>
       <c r="B101" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>647</v>
+        <v>360</v>
       </c>
       <c r="B102" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>648</v>
+        <v>361</v>
       </c>
       <c r="B103" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>649</v>
+        <v>362</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>650</v>
+        <v>363</v>
       </c>
       <c r="B106" t="s">
-        <v>651</v>
+        <v>364</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>652</v>
+        <v>365</v>
       </c>
       <c r="B107" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>654</v>
+        <v>367</v>
       </c>
       <c r="B108" t="s">
-        <v>655</v>
+        <v>368</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>656</v>
+        <v>369</v>
       </c>
       <c r="B109" t="s">
-        <v>657</v>
+        <v>370</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>658</v>
+        <v>371</v>
       </c>
       <c r="B110" t="s">
-        <v>659</v>
+        <v>372</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>660</v>
+        <v>373</v>
       </c>
       <c r="B111" t="s">
-        <v>661</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>662</v>
+        <v>375</v>
       </c>
       <c r="B112" t="s">
-        <v>663</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>664</v>
+        <v>377</v>
       </c>
       <c r="B113" t="s">
-        <v>590</v>
+        <v>303</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>665</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>666</v>
+        <v>379</v>
       </c>
       <c r="B116" t="s">
-        <v>581</v>
+        <v>294</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>667</v>
+        <v>380</v>
       </c>
       <c r="B117" t="s">
-        <v>668</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>669</v>
+        <v>382</v>
       </c>
       <c r="B118" t="s">
-        <v>670</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>671</v>
+        <v>384</v>
       </c>
       <c r="B119" t="s">
-        <v>672</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>673</v>
+        <v>386</v>
       </c>
       <c r="B120" t="s">
-        <v>674</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>675</v>
+        <v>388</v>
       </c>
       <c r="B121" t="s">
-        <v>676</v>
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>677</v>
+        <v>390</v>
       </c>
       <c r="B122" t="s">
-        <v>678</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>679</v>
+        <v>392</v>
       </c>
       <c r="B123" t="s">
-        <v>674</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>680</v>
+        <v>393</v>
       </c>
       <c r="B124" t="s">
-        <v>676</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>681</v>
+        <v>394</v>
       </c>
       <c r="B125" t="s">
-        <v>678</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>682</v>
+        <v>395</v>
       </c>
       <c r="B126" t="s">
-        <v>683</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>684</v>
+        <v>397</v>
       </c>
       <c r="B127" t="s">
-        <v>685</v>
+        <v>398</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>686</v>
+        <v>399</v>
       </c>
       <c r="B128" t="s">
-        <v>687</v>
+        <v>400</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>688</v>
+        <v>401</v>
       </c>
       <c r="B129" t="s">
-        <v>689</v>
+        <v>402</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>690</v>
+        <v>403</v>
       </c>
       <c r="B130" t="s">
-        <v>691</v>
+        <v>404</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>642</v>
+        <v>355</v>
       </c>
       <c r="B131" t="s">
-        <v>692</v>
+        <v>405</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>643</v>
+        <v>356</v>
       </c>
       <c r="B132" t="s">
-        <v>693</v>
+        <v>406</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>645</v>
+        <v>358</v>
       </c>
       <c r="B133" t="s">
-        <v>694</v>
+        <v>407</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>644</v>
+        <v>357</v>
       </c>
       <c r="B134" t="s">
-        <v>695</v>
+        <v>408</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>696</v>
+        <v>409</v>
       </c>
       <c r="B135" t="s">
-        <v>581</v>
+        <v>294</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>697</v>
+        <v>410</v>
       </c>
       <c r="B136" t="s">
-        <v>698</v>
+        <v>411</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>699</v>
+        <v>412</v>
       </c>
       <c r="B137" t="s">
-        <v>700</v>
+        <v>413</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>701</v>
+        <v>414</v>
       </c>
       <c r="B138" t="s">
-        <v>702</v>
+        <v>415</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>703</v>
+        <v>416</v>
       </c>
       <c r="B139" t="s">
-        <v>704</v>
+        <v>417</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>705</v>
+        <v>418</v>
       </c>
       <c r="B140" t="s">
-        <v>706</v>
+        <v>419</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>707</v>
+        <v>420</v>
       </c>
       <c r="B141" t="s">
-        <v>674</v>
+        <v>387</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>708</v>
+        <v>421</v>
       </c>
       <c r="B142" t="s">
-        <v>676</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>709</v>
+        <v>422</v>
       </c>
       <c r="B143" t="s">
-        <v>678</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>710</v>
+        <v>423</v>
       </c>
       <c r="B144" t="s">
-        <v>683</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>711</v>
+        <v>424</v>
       </c>
       <c r="B145" t="s">
-        <v>685</v>
+        <v>398</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>712</v>
+        <v>425</v>
       </c>
       <c r="B146" t="s">
-        <v>687</v>
+        <v>400</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>713</v>
+        <v>426</v>
       </c>
       <c r="B147" t="s">
-        <v>689</v>
+        <v>402</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>714</v>
+        <v>427</v>
       </c>
       <c r="B148" t="s">
-        <v>691</v>
+        <v>404</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>715</v>
+        <v>428</v>
       </c>
       <c r="B149" t="s">
-        <v>716</v>
+        <v>429</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>717</v>
+        <v>430</v>
       </c>
       <c r="B150" t="s">
-        <v>718</v>
+        <v>431</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>719</v>
+        <v>432</v>
       </c>
       <c r="B151" t="s">
-        <v>720</v>
+        <v>433</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>721</v>
+        <v>434</v>
       </c>
       <c r="B152" t="s">
-        <v>722</v>
+        <v>435</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>723</v>
+        <v>436</v>
       </c>
       <c r="B153" t="s">
-        <v>724</v>
+        <v>437</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>725</v>
+        <v>438</v>
       </c>
       <c r="B154" t="s">
-        <v>726</v>
+        <v>439</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>727</v>
+        <v>440</v>
       </c>
       <c r="B155" t="s">
-        <v>728</v>
+        <v>441</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>729</v>
+        <v>442</v>
       </c>
       <c r="B156" t="s">
-        <v>730</v>
+        <v>443</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>731</v>
+        <v>444</v>
       </c>
       <c r="B157" t="s">
-        <v>732</v>
+        <v>445</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>733</v>
+        <v>446</v>
       </c>
       <c r="B158" t="s">
-        <v>734</v>
+        <v>447</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>735</v>
+        <v>448</v>
       </c>
       <c r="B159" t="s">
-        <v>736</v>
+        <v>449</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>737</v>
+        <v>450</v>
       </c>
       <c r="B160" t="s">
-        <v>738</v>
+        <v>451</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>739</v>
+        <v>452</v>
       </c>
       <c r="B161" t="s">
-        <v>740</v>
+        <v>453</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>741</v>
+        <v>454</v>
       </c>
       <c r="B162" t="s">
-        <v>742</v>
+        <v>455</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>743</v>
+        <v>456</v>
       </c>
       <c r="B163" t="s">
-        <v>744</v>
+        <v>457</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>745</v>
+        <v>458</v>
       </c>
       <c r="B164" t="s">
-        <v>746</v>
+        <v>459</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>747</v>
+        <v>460</v>
       </c>
       <c r="B165" t="s">
-        <v>748</v>
+        <v>461</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>749</v>
+        <v>462</v>
       </c>
       <c r="B166" t="s">
-        <v>722</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>750</v>
+        <v>463</v>
       </c>
       <c r="B167" t="s">
-        <v>704</v>
+        <v>417</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>751</v>
+        <v>464</v>
       </c>
       <c r="B168" t="s">
-        <v>706</v>
+        <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>752</v>
+        <v>465</v>
       </c>
       <c r="B169" t="s">
-        <v>564</v>
+        <v>277</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>753</v>
+        <v>466</v>
       </c>
       <c r="B170" t="s">
-        <v>754</v>
+        <v>467</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>755</v>
+        <v>468</v>
       </c>
       <c r="B171" t="s">
-        <v>756</v>
+        <v>469</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>757</v>
+        <v>470</v>
       </c>
       <c r="B172" t="s">
-        <v>758</v>
+        <v>471</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>759</v>
+        <v>472</v>
       </c>
       <c r="B173" t="s">
-        <v>760</v>
+        <v>473</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>761</v>
+        <v>474</v>
       </c>
       <c r="B174" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>762</v>
+        <v>475</v>
       </c>
       <c r="B175" t="s">
-        <v>674</v>
+        <v>387</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>763</v>
+        <v>476</v>
       </c>
       <c r="B176" t="s">
-        <v>676</v>
+        <v>389</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>764</v>
+        <v>477</v>
       </c>
       <c r="B177" t="s">
-        <v>716</v>
+        <v>429</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>765</v>
+        <v>478</v>
       </c>
       <c r="B178" t="s">
-        <v>700</v>
+        <v>413</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>766</v>
+        <v>479</v>
       </c>
       <c r="B179" t="s">
-        <v>767</v>
+        <v>480</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>768</v>
+        <v>481</v>
       </c>
       <c r="B180" t="s">
-        <v>704</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -5528,47 +4530,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>769</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>770</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>771</v>
+        <v>484</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>772</v>
+        <v>485</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>773</v>
+        <v>486</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>774</v>
+        <v>487</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>775</v>
+        <v>488</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>655</v>
+        <v>368</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -5576,15 +4578,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>777</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>778</v>
+        <v>491</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>779</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -5592,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>780</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -5607,7 +4609,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>781</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -5617,647 +4619,479 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>782</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>770</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>771</v>
+        <v>484</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>772</v>
+        <v>485</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>783</v>
+        <v>496</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>774</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="B5" t="s">
-        <v>784</v>
+        <v>497</v>
       </c>
       <c r="C5" t="s">
-        <v>704</v>
+        <v>417</v>
       </c>
       <c r="D5" t="s">
-        <v>785</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="B6" t="s">
-        <v>786</v>
+        <v>499</v>
       </c>
       <c r="C6" t="s">
-        <v>706</v>
+        <v>419</v>
       </c>
       <c r="D6" t="s">
-        <v>787</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="B7" t="s">
-        <v>788</v>
+        <v>501</v>
       </c>
       <c r="C7" t="s">
-        <v>689</v>
+        <v>502</v>
       </c>
       <c r="D7" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>209</v>
       </c>
       <c r="B8" t="s">
-        <v>789</v>
+        <v>503</v>
       </c>
       <c r="C8" t="s">
-        <v>691</v>
+        <v>277</v>
       </c>
       <c r="D8" t="s">
-        <v>787</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>790</v>
+        <v>505</v>
       </c>
       <c r="C9" t="s">
-        <v>564</v>
+        <v>467</v>
       </c>
       <c r="D9" t="s">
-        <v>787</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>791</v>
+        <v>506</v>
       </c>
       <c r="C10" t="s">
-        <v>754</v>
+        <v>507</v>
       </c>
       <c r="D10" t="s">
-        <v>787</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>213</v>
       </c>
       <c r="B11" t="s">
-        <v>792</v>
+        <v>508</v>
       </c>
       <c r="C11" t="s">
-        <v>716</v>
+        <v>509</v>
       </c>
       <c r="D11" t="s">
-        <v>787</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>214</v>
       </c>
       <c r="B12" t="s">
-        <v>793</v>
+        <v>510</v>
       </c>
       <c r="C12" t="s">
-        <v>794</v>
+        <v>511</v>
       </c>
       <c r="D12" t="s">
-        <v>787</v>
+        <v>504</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>506</v>
+        <v>214</v>
       </c>
       <c r="B13" t="s">
-        <v>795</v>
+        <v>512</v>
       </c>
       <c r="C13" t="s">
-        <v>796</v>
+        <v>469</v>
       </c>
       <c r="D13" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>506</v>
+        <v>214</v>
       </c>
       <c r="B14" t="s">
-        <v>797</v>
+        <v>513</v>
       </c>
       <c r="C14" t="s">
-        <v>798</v>
+        <v>514</v>
       </c>
       <c r="D14" t="s">
-        <v>787</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>506</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>799</v>
+        <v>515</v>
       </c>
       <c r="C15" t="s">
-        <v>800</v>
+        <v>471</v>
       </c>
       <c r="D15" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="B16" t="s">
-        <v>802</v>
+        <v>516</v>
       </c>
       <c r="C16" t="s">
-        <v>756</v>
+        <v>473</v>
       </c>
       <c r="D16" t="s">
-        <v>801</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s">
-        <v>803</v>
+        <v>517</v>
       </c>
       <c r="C17" t="s">
-        <v>804</v>
+        <v>518</v>
       </c>
       <c r="D17" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s">
-        <v>805</v>
+        <v>519</v>
       </c>
       <c r="C18" t="s">
-        <v>806</v>
+        <v>415</v>
       </c>
       <c r="D18" t="s">
-        <v>787</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s">
-        <v>807</v>
+        <v>520</v>
       </c>
       <c r="C19" t="s">
-        <v>700</v>
+        <v>413</v>
       </c>
       <c r="D19" t="s">
-        <v>801</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s">
-        <v>808</v>
+        <v>521</v>
       </c>
       <c r="C20" t="s">
-        <v>809</v>
+        <v>522</v>
       </c>
       <c r="D20" t="s">
-        <v>801</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s">
-        <v>810</v>
+        <v>523</v>
       </c>
       <c r="C21" t="s">
-        <v>758</v>
+        <v>524</v>
       </c>
       <c r="D21" t="s">
-        <v>787</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s">
-        <v>811</v>
+        <v>525</v>
       </c>
       <c r="C22" t="s">
-        <v>760</v>
+        <v>526</v>
       </c>
       <c r="D22" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s">
-        <v>812</v>
+        <v>527</v>
       </c>
       <c r="C23" t="s">
-        <v>813</v>
+        <v>347</v>
       </c>
       <c r="D23" t="s">
-        <v>801</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s">
-        <v>814</v>
+        <v>528</v>
       </c>
       <c r="C24" t="s">
-        <v>815</v>
+        <v>529</v>
       </c>
       <c r="D24" t="s">
-        <v>787</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s">
-        <v>816</v>
+        <v>530</v>
       </c>
       <c r="C25" t="s">
-        <v>767</v>
+        <v>387</v>
       </c>
       <c r="D25" t="s">
-        <v>801</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>817</v>
+        <v>531</v>
       </c>
       <c r="C26" t="s">
-        <v>818</v>
+        <v>389</v>
       </c>
       <c r="D26" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>819</v>
+        <v>532</v>
       </c>
       <c r="C27" t="s">
-        <v>820</v>
+        <v>480</v>
       </c>
       <c r="D27" t="s">
-        <v>801</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>511</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s">
-        <v>821</v>
+        <v>533</v>
       </c>
       <c r="C28" t="s">
-        <v>702</v>
+        <v>391</v>
       </c>
       <c r="D28" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>511</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>822</v>
+        <v>534</v>
       </c>
       <c r="C29" t="s">
-        <v>823</v>
+        <v>396</v>
       </c>
       <c r="D29" t="s">
-        <v>801</v>
+        <v>504</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>511</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>824</v>
+        <v>535</v>
       </c>
       <c r="C30" t="s">
-        <v>825</v>
+        <v>398</v>
       </c>
       <c r="D30" t="s">
-        <v>785</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>511</v>
+        <v>228</v>
       </c>
       <c r="B31" t="s">
-        <v>826</v>
+        <v>536</v>
       </c>
       <c r="C31" t="s">
-        <v>827</v>
+        <v>400</v>
       </c>
       <c r="D31" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>511</v>
+        <v>229</v>
       </c>
       <c r="B32" t="s">
-        <v>828</v>
+        <v>537</v>
       </c>
       <c r="C32" t="s">
-        <v>829</v>
+        <v>402</v>
       </c>
       <c r="D32" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>513</v>
+        <v>229</v>
       </c>
       <c r="B33" t="s">
-        <v>830</v>
+        <v>538</v>
       </c>
       <c r="C33" t="s">
-        <v>831</v>
+        <v>404</v>
       </c>
       <c r="D33" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>513</v>
+        <v>230</v>
       </c>
       <c r="B34" t="s">
-        <v>832</v>
+        <v>539</v>
       </c>
       <c r="C34" t="s">
-        <v>634</v>
+        <v>429</v>
       </c>
       <c r="D34" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>513</v>
+        <v>230</v>
       </c>
       <c r="B35" t="s">
-        <v>833</v>
+        <v>540</v>
       </c>
       <c r="C35" t="s">
-        <v>834</v>
+        <v>541</v>
       </c>
       <c r="D35" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>513</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s">
-        <v>835</v>
+        <v>542</v>
       </c>
       <c r="C36" t="s">
-        <v>836</v>
+        <v>543</v>
       </c>
       <c r="D36" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>515</v>
-      </c>
-      <c r="B37" t="s">
-        <v>837</v>
-      </c>
-      <c r="C37" t="s">
-        <v>674</v>
-      </c>
-      <c r="D37" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="s">
-        <v>515</v>
-      </c>
-      <c r="B38" t="s">
-        <v>838</v>
-      </c>
-      <c r="C38" t="s">
-        <v>676</v>
-      </c>
-      <c r="D38" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>515</v>
-      </c>
-      <c r="B39" t="s">
-        <v>839</v>
-      </c>
-      <c r="C39" t="s">
-        <v>840</v>
-      </c>
-      <c r="D39" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
-        <v>515</v>
-      </c>
-      <c r="B40" t="s">
-        <v>841</v>
-      </c>
-      <c r="C40" t="s">
-        <v>842</v>
-      </c>
-      <c r="D40" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>517</v>
-      </c>
-      <c r="B41" t="s">
-        <v>843</v>
-      </c>
-      <c r="C41" t="s">
-        <v>678</v>
-      </c>
-      <c r="D41" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" t="s">
-        <v>517</v>
-      </c>
-      <c r="B42" t="s">
-        <v>844</v>
-      </c>
-      <c r="C42" t="s">
-        <v>683</v>
-      </c>
-      <c r="D42" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" t="s">
-        <v>517</v>
-      </c>
-      <c r="B43" t="s">
-        <v>845</v>
-      </c>
-      <c r="C43" t="s">
-        <v>846</v>
-      </c>
-      <c r="D43" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>517</v>
-      </c>
-      <c r="B44" t="s">
-        <v>847</v>
-      </c>
-      <c r="C44" t="s">
-        <v>848</v>
-      </c>
-      <c r="D44" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>26</v>
-      </c>
-      <c r="B45" t="s">
-        <v>849</v>
-      </c>
-      <c r="C45" t="s">
-        <v>685</v>
-      </c>
-      <c r="D45" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>26</v>
-      </c>
-      <c r="B46" t="s">
-        <v>850</v>
-      </c>
-      <c r="C46" t="s">
-        <v>687</v>
-      </c>
-      <c r="D46" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>26</v>
-      </c>
-      <c r="B47" t="s">
-        <v>851</v>
-      </c>
-      <c r="C47" t="s">
-        <v>852</v>
-      </c>
-      <c r="D47" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>26</v>
-      </c>
-      <c r="B48" t="s">
-        <v>853</v>
-      </c>
-      <c r="C48" t="s">
-        <v>854</v>
-      </c>
-      <c r="D48" t="s">
-        <v>801</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -6272,7 +5106,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>855</v>
+        <v>544</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6282,490 +5116,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>856</v>
+        <v>545</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>857</v>
+        <v>546</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>858</v>
+        <v>547</v>
       </c>
       <c r="B5" t="s">
-        <v>859</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>860</v>
+        <v>549</v>
       </c>
       <c r="B6" t="s">
-        <v>861</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>862</v>
+        <v>551</v>
       </c>
       <c r="B7" t="s">
-        <v>863</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>864</v>
+        <v>553</v>
       </c>
       <c r="B8" t="s">
-        <v>865</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>866</v>
+        <v>555</v>
       </c>
       <c r="B9" t="s">
-        <v>867</v>
+        <v>556</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>868</v>
+        <v>557</v>
       </c>
       <c r="B10" t="s">
-        <v>780</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>869</v>
+        <v>558</v>
       </c>
       <c r="B11" t="s">
-        <v>780</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>870</v>
+        <v>559</v>
       </c>
       <c r="B12" t="s">
-        <v>871</v>
+        <v>560</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>872</v>
+        <v>561</v>
       </c>
       <c r="B13" t="s">
-        <v>873</v>
+        <v>562</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>874</v>
+        <v>563</v>
       </c>
       <c r="B14" t="s">
-        <v>875</v>
+        <v>564</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>876</v>
+        <v>565</v>
       </c>
       <c r="B15" t="s">
-        <v>877</v>
+        <v>566</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>878</v>
+        <v>567</v>
       </c>
       <c r="B16" t="s">
-        <v>879</v>
+        <v>568</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>880</v>
+        <v>569</v>
       </c>
       <c r="B17" t="s">
-        <v>881</v>
+        <v>570</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>882</v>
+        <v>571</v>
       </c>
       <c r="B18" t="s">
-        <v>883</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>884</v>
+        <v>573</v>
       </c>
       <c r="B19" t="s">
-        <v>883</v>
+        <v>572</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>885</v>
+        <v>574</v>
       </c>
       <c r="B20" t="s">
-        <v>886</v>
+        <v>575</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>887</v>
+        <v>576</v>
       </c>
       <c r="B21" t="s">
-        <v>886</v>
+        <v>575</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>888</v>
+        <v>577</v>
       </c>
       <c r="B22" t="s">
-        <v>889</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>890</v>
+        <v>579</v>
       </c>
       <c r="B23" t="s">
-        <v>775</v>
+        <v>488</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>891</v>
+        <v>580</v>
       </c>
       <c r="B24" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>892</v>
+        <v>581</v>
       </c>
       <c r="B25" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>893</v>
+        <v>582</v>
       </c>
       <c r="B26" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>894</v>
+        <v>583</v>
       </c>
       <c r="B27" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>895</v>
+        <v>584</v>
       </c>
       <c r="B28" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>896</v>
+        <v>585</v>
       </c>
       <c r="B29" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>897</v>
+        <v>586</v>
       </c>
       <c r="B30" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>898</v>
+        <v>587</v>
       </c>
       <c r="B31" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>899</v>
+        <v>588</v>
       </c>
       <c r="B32" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>900</v>
+        <v>589</v>
       </c>
       <c r="B33" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>901</v>
+        <v>590</v>
       </c>
       <c r="B34" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>902</v>
+        <v>591</v>
       </c>
       <c r="B35" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>903</v>
+        <v>592</v>
       </c>
       <c r="B36" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>904</v>
+        <v>593</v>
       </c>
       <c r="B37" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>905</v>
+        <v>594</v>
       </c>
       <c r="B38" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>906</v>
+        <v>595</v>
       </c>
       <c r="B39" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>907</v>
+        <v>596</v>
       </c>
       <c r="B40" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>908</v>
+        <v>597</v>
       </c>
       <c r="B41" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>909</v>
+        <v>598</v>
       </c>
       <c r="B42" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>910</v>
+        <v>599</v>
       </c>
       <c r="B43" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>911</v>
+        <v>600</v>
       </c>
       <c r="B44" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>912</v>
+        <v>601</v>
       </c>
       <c r="B45" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>913</v>
+        <v>602</v>
       </c>
       <c r="B46" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>914</v>
+        <v>603</v>
       </c>
       <c r="B47" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>915</v>
+        <v>604</v>
       </c>
       <c r="B48" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>916</v>
+        <v>605</v>
       </c>
       <c r="B49" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>917</v>
+        <v>606</v>
       </c>
       <c r="B50" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>918</v>
+        <v>607</v>
       </c>
       <c r="B51" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>919</v>
+        <v>608</v>
       </c>
       <c r="B52" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>920</v>
+        <v>609</v>
       </c>
       <c r="B53" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>921</v>
+        <v>610</v>
       </c>
       <c r="B54" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>922</v>
+        <v>611</v>
       </c>
       <c r="B55" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>923</v>
+        <v>612</v>
       </c>
       <c r="B56" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>924</v>
+        <v>613</v>
       </c>
       <c r="B57" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>925</v>
+        <v>614</v>
       </c>
       <c r="B58" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>926</v>
+        <v>615</v>
       </c>
       <c r="B59" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>927</v>
+        <v>616</v>
       </c>
       <c r="B60" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>928</v>
+        <v>617</v>
       </c>
       <c r="B61" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>929</v>
+        <v>618</v>
       </c>
       <c r="B62" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>930</v>
+        <v>619</v>
       </c>
       <c r="B63" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>931</v>
+        <v>620</v>
       </c>
       <c r="B64" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -6855,7 +5689,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A244"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -6899,1053 +5733,298 @@
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>42</v>
+      <c r="A12" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>5</v>
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>64</v>
+      <c r="A38" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>67</v>
+      <c r="A41" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>71</v>
+      <c r="A45" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>74</v>
+      <c r="A48" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="1" t="s">
-        <v>11</v>
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>80</v>
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>86</v>
+      <c r="A64" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>90</v>
+      <c r="A68" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="1" t="s">
-        <v>92</v>
+      <c r="A71" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1">
-      <c r="A157" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1">
-      <c r="A167" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1">
-      <c r="A180" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1">
-      <c r="A184" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1">
-      <c r="A186" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1">
-      <c r="A187" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1">
-      <c r="A189" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1">
-      <c r="A190" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1">
-      <c r="A191" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1">
-      <c r="A193" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1">
-      <c r="A195" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1">
-      <c r="A197" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1">
-      <c r="A198" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1">
-      <c r="A199" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1">
-      <c r="A200" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1">
-      <c r="A201" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1">
-      <c r="A202" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1">
-      <c r="A204" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1">
-      <c r="A205" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1">
-      <c r="A206" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1">
-      <c r="A207" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1">
-      <c r="A209" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1">
-      <c r="A210" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1">
-      <c r="A211" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1">
-      <c r="A212" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1">
-      <c r="A213" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1">
-      <c r="A214" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1">
-      <c r="A216" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1">
-      <c r="A217" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1">
-      <c r="A218" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1">
-      <c r="A219" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1">
-      <c r="A220" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1">
-      <c r="A221" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1">
-      <c r="A222" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1">
-      <c r="A223" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1">
-      <c r="A224" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1">
-      <c r="A226" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1">
-      <c r="A227" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1">
-      <c r="A228" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1">
-      <c r="A230" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1">
-      <c r="A231" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1">
-      <c r="A232" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1">
-      <c r="A234" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1">
-      <c r="A235" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1">
-      <c r="A236" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1">
-      <c r="A237" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1">
-      <c r="A238" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1">
-      <c r="A239" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1">
-      <c r="A240" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1">
-      <c r="A241" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1">
-      <c r="A242" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1">
-      <c r="A243" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1">
-      <c r="A244" t="s">
-        <v>241</v>
+      <c r="A80" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -7960,47 +6039,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>230</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>246</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>247</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>248</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>249</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -8015,47 +6094,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>250</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>230</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>252</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>253</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>254</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>255</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>256</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>257</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -8065,12 +6144,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A243"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>258</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -8080,1082 +6159,327 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>259</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>260</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>261</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>262</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>264</v>
+      <c r="A9" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>265</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>266</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>267</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>268</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>269</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>270</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>271</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>272</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>273</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>274</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>276</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>5</v>
+      <c r="A27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>277</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>278</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>279</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>280</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>281</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>282</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>284</v>
+      <c r="A35" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>285</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>287</v>
+      <c r="A38" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>288</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>289</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>291</v>
+      <c r="A42" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>292</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>294</v>
+      <c r="A45" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>295</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>296</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="1" t="s">
-        <v>11</v>
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>297</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>298</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>299</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>300</v>
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>301</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>302</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>303</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>304</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>306</v>
+      <c r="A61" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>307</v>
+        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>308</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>310</v>
+      <c r="A65" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>311</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>92</v>
+      <c r="A68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>312</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>313</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>314</v>
+        <v>155</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>315</v>
+        <v>156</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>316</v>
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>317</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>318</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="1" t="s">
-        <v>100</v>
+      <c r="A77" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1">
-      <c r="A180" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1">
-      <c r="A184" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1">
-      <c r="A186" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1">
-      <c r="A187" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1">
-      <c r="A189" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1">
-      <c r="A190" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1">
-      <c r="A191" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1">
-      <c r="A195" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1">
-      <c r="A196" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1">
-      <c r="A197" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1">
-      <c r="A198" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1">
-      <c r="A199" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1">
-      <c r="A201" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1">
-      <c r="A202" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1">
-      <c r="A203" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1">
-      <c r="A204" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1">
-      <c r="A205" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1">
-      <c r="A206" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1">
-      <c r="A207" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1">
-      <c r="A209" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1">
-      <c r="A210" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1">
-      <c r="A211" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1">
-      <c r="A213" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1">
-      <c r="A214" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1">
-      <c r="A215" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1">
-      <c r="A216" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1">
-      <c r="A217" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1">
-      <c r="A218" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1">
-      <c r="A219" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1">
-      <c r="A220" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1">
-      <c r="A221" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1">
-      <c r="A223" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1">
-      <c r="A224" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1">
-      <c r="A225" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1">
-      <c r="A227" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1">
-      <c r="A228" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1">
-      <c r="A229" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1">
-      <c r="A231" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1">
-      <c r="A232" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1">
-      <c r="A233" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1">
-      <c r="A234" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1">
-      <c r="A235" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1">
-      <c r="A236" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1">
-      <c r="A237" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1">
-      <c r="A238" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1">
-      <c r="A239" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1">
-      <c r="A240" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1">
-      <c r="A241" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1">
-      <c r="A242" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1">
-      <c r="A243" t="s">
-        <v>451</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -30,17 +30,16 @@
     <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
     <sheet name="Project Summary" sheetId="22" r:id="rId22"/>
     <sheet name="Design Params and Codes" sheetId="23" r:id="rId23"/>
-    <sheet name="DRM Summary" sheetId="24" r:id="rId24"/>
-    <sheet name="Register Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
-    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
+    <sheet name="Register Summary" sheetId="24" r:id="rId24"/>
+    <sheet name="DFT Summary" sheetId="25" r:id="rId25"/>
+    <sheet name="Nesto Usage Report" sheetId="26" r:id="rId26"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="434">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -132,10 +131,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
-  </si>
-  <si>
-    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
+  </si>
+  <si>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -147,388 +146,19 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.fcm(59)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_bottom(60)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_refresh(61)</t>
-  </si>
-  <si>
-    <t>Floating pin XU21.i0(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU22.i0(49)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XU11.enable_switchb(102)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.mode_hiccup(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.blank_thermal(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XU10.enable_switch(58)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(35)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(34)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(33)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(49)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.halfway(36)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
+    <t>No Floating Output Nets found.</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -649,118 +279,94 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
+  </si>
+  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
+    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>DFM Efficiency Summary</t>
+  </si>
+  <si>
     <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
   </si>
   <si>
-    <t>DFT Efficiency</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
-  </si>
-  <si>
-    <t>DFM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
-  </si>
-  <si>
     <t>Project Summary</t>
   </si>
   <si>
     <t>Package Stats</t>
   </si>
   <si>
-    <t>needed: 2</t>
+    <t>needed: 0</t>
   </si>
   <si>
     <t>spares: 0</t>
   </si>
   <si>
-    <t>algorithm: 6 - Piggybacks</t>
-  </si>
-  <si>
-    <t>piggyback: ['DFTSCL', 'DFTSDA']</t>
+    <t>algorithm: 0 - No compression needed</t>
+  </si>
+  <si>
+    <t>piggyback: []</t>
   </si>
   <si>
     <t>user_pads: 12</t>
@@ -790,18 +396,18 @@
     <t>add_dft</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>add_dbufdft</t>
+  </si>
+  <si>
+    <t>dft_ignore_bricks</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>add_dbufdft</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>dft_ignore_bricks</t>
-  </si>
-  <si>
     <t>dft_measure</t>
   </si>
   <si>
@@ -1492,7 +1098,10 @@
     <t>measure_reset_command</t>
   </si>
   <si>
-    <t>DRM Summary</t>
+    <t>Register Summary</t>
+  </si>
+  <si>
+    <t>DFT Summary</t>
   </si>
   <si>
     <t>Addresses</t>
@@ -1504,294 +1113,129 @@
     <t>Instance</t>
   </si>
   <si>
-    <t>TMB</t>
+    <t>TMA</t>
   </si>
   <si>
     <t>type</t>
   </si>
   <si>
-    <t>7</t>
+    <t>Nesto Usage Report</t>
+  </si>
+  <si>
+    <t>Nesto</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>pinprobe</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>inv</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>noconn</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>dbuf</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>nor3</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>delayfixed</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>nand3</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>celeranoconn</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>srlatch</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>nor2</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>wrapper</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>dff</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>drmmodule</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>tie</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>datamap0</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
+    <t>resistor</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>DRM to Memory Check</t>
-  </si>
-  <si>
-    <t>TOTAL dec</t>
-  </si>
-  <si>
-    <t>Allowed &lt;= 61</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>Register Summary</t>
-  </si>
-  <si>
-    <t>DFT Summary</t>
-  </si>
-  <si>
-    <t>TMA</t>
-  </si>
-  <si>
-    <t>dft_hex0x01</t>
-  </si>
-  <si>
-    <t>DFTtm8</t>
-  </si>
-  <si>
-    <t>dft_hex0x02</t>
-  </si>
-  <si>
-    <t>DFTtm8t</t>
-  </si>
-  <si>
-    <t>dft_hex0x1A</t>
-  </si>
-  <si>
-    <t>0x1A</t>
-  </si>
-  <si>
-    <t>dft_hex0x03</t>
-  </si>
-  <si>
-    <t>DFTtm8d</t>
-  </si>
-  <si>
-    <t>dft_hex0x04</t>
-  </si>
-  <si>
-    <t>dft_hex0x05</t>
-  </si>
-  <si>
-    <t>0x05</t>
-  </si>
-  <si>
-    <t>dft_hex0x06</t>
-  </si>
-  <si>
-    <t>0x06</t>
-  </si>
-  <si>
-    <t>dft_hex0x07</t>
-  </si>
-  <si>
-    <t>0x07</t>
-  </si>
-  <si>
-    <t>dft_hex0x08</t>
-  </si>
-  <si>
-    <t>dft_hex0x1B</t>
-  </si>
-  <si>
-    <t>0x1B</t>
-  </si>
-  <si>
-    <t>dft_hex0x09</t>
-  </si>
-  <si>
-    <t>dft_hex0x0A</t>
-  </si>
-  <si>
-    <t>dft_hex0x0B</t>
-  </si>
-  <si>
-    <t>0x0B</t>
-  </si>
-  <si>
-    <t>dft_hex0x0C</t>
-  </si>
-  <si>
-    <t>dft_hex0x1C</t>
-  </si>
-  <si>
-    <t>dft_hex0x1D</t>
-  </si>
-  <si>
-    <t>0x1D</t>
-  </si>
-  <si>
-    <t>dft_hex0x0D</t>
-  </si>
-  <si>
-    <t>0x0D</t>
-  </si>
-  <si>
-    <t>dft_hex0x0E</t>
-  </si>
-  <si>
-    <t>0x0E</t>
-  </si>
-  <si>
-    <t>dft_hex0x0F</t>
-  </si>
-  <si>
-    <t>dft_hex0x1E</t>
-  </si>
-  <si>
-    <t>0x1E</t>
-  </si>
-  <si>
-    <t>dft_hex0x10</t>
-  </si>
-  <si>
-    <t>dft_hex0x11</t>
-  </si>
-  <si>
-    <t>dft_hex0x1F</t>
-  </si>
-  <si>
-    <t>dft_hex0x12</t>
-  </si>
-  <si>
-    <t>dft_hex0x13</t>
-  </si>
-  <si>
-    <t>dft_hex0x14</t>
-  </si>
-  <si>
-    <t>dft_hex0x15</t>
-  </si>
-  <si>
-    <t>dft_hex0x16</t>
-  </si>
-  <si>
-    <t>dft_hex0x17</t>
-  </si>
-  <si>
-    <t>dft_hex0x18</t>
-  </si>
-  <si>
-    <t>dft_hex0x20</t>
-  </si>
-  <si>
-    <t>0x20</t>
-  </si>
-  <si>
-    <t>dft_hex0x19</t>
-  </si>
-  <si>
-    <t>0x19</t>
-  </si>
-  <si>
-    <t>Nesto Usage Report</t>
-  </si>
-  <si>
-    <t>Nesto</t>
-  </si>
-  <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>pinprobe</t>
-  </si>
-  <si>
-    <t>1082</t>
-  </si>
-  <si>
-    <t>inv</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>noconn</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>dbuf</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>nor3</t>
-  </si>
-  <si>
-    <t>dftprobeModel0</t>
-  </si>
-  <si>
-    <t>delayfixed</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>nand3</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>celeranoconn</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>srlatch</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>nor2</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>dftmodule</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>dfthijack</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>dff</t>
-  </si>
-  <si>
-    <t>tie</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>datamap0</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>dftprobeModel2</t>
-  </si>
-  <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>resistor</t>
-  </si>
-  <si>
     <t>oneshot</t>
   </si>
   <si>
@@ -1822,9 +1266,6 @@
     <t>amux2</t>
   </si>
   <si>
-    <t>wrapper</t>
-  </si>
-  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1841,9 +1282,6 @@
   </si>
   <si>
     <t>capacitorfixed</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>voltage2current</t>
@@ -2277,7 +1715,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2297,7 +1735,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2312,7 +1750,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2327,17 +1765,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2352,12 +1790,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2372,17 +1810,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2397,12 +1835,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2417,7 +1855,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2437,127 +1875,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>177</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>178</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>179</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>180</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>182</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>183</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>184</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>185</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>187</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>188</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>190</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>191</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>193</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>194</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>196</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>197</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>199</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2567,17 +2005,162 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2592,17 +2175,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2822,257 +2405,17 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>208</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3087,17 +2430,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>232</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3112,52 +2455,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>234</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>235</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>236</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>237</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>239</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>240</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>241</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>242</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3172,81 +2515,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>244</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>247</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>249</v>
+        <v>118</v>
       </c>
       <c r="B6" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s">
-        <v>248</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>252</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>253</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>254</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>255</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>257</v>
+        <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>258</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3254,1268 +2597,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>259</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>261</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>262</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>263</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>264</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s">
-        <v>250</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>266</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
-        <v>248</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>267</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>268</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>269</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>270</v>
+        <v>139</v>
       </c>
       <c r="B27" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>271</v>
+        <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>272</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
-        <v>273</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>274</v>
+        <v>143</v>
       </c>
       <c r="B30" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>275</v>
+        <v>144</v>
       </c>
       <c r="B31" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>276</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>277</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>278</v>
+        <v>147</v>
       </c>
       <c r="B33" t="s">
-        <v>279</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>280</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>282</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
-        <v>283</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>284</v>
+        <v>153</v>
       </c>
       <c r="B36" t="s">
-        <v>285</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>286</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>287</v>
+        <v>156</v>
       </c>
       <c r="B38" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>288</v>
+        <v>157</v>
       </c>
       <c r="B39" t="s">
-        <v>289</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
       <c r="B40" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>291</v>
+        <v>160</v>
       </c>
       <c r="B41" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>292</v>
+        <v>161</v>
       </c>
       <c r="B42" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>293</v>
+        <v>162</v>
       </c>
       <c r="B43" t="s">
-        <v>294</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>295</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>296</v>
+        <v>165</v>
       </c>
       <c r="B46" t="s">
-        <v>297</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>298</v>
+        <v>167</v>
       </c>
       <c r="B47" t="s">
-        <v>248</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>299</v>
+        <v>168</v>
       </c>
       <c r="B48" t="s">
-        <v>289</v>
+        <v>158</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>300</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
-        <v>248</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>301</v>
+        <v>170</v>
       </c>
       <c r="B50" t="s">
-        <v>248</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>302</v>
+        <v>171</v>
       </c>
       <c r="B51" t="s">
-        <v>303</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>304</v>
+        <v>173</v>
       </c>
       <c r="B52" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>305</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>306</v>
+        <v>175</v>
       </c>
       <c r="B55" t="s">
-        <v>307</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>308</v>
+        <v>177</v>
       </c>
       <c r="B56" t="s">
-        <v>309</v>
+        <v>178</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>310</v>
+        <v>179</v>
       </c>
       <c r="B57" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>311</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>312</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>313</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>314</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>315</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>316</v>
+        <v>185</v>
       </c>
       <c r="B64" t="s">
-        <v>317</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>318</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>319</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>320</v>
+        <v>189</v>
       </c>
       <c r="B67" t="s">
-        <v>321</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>322</v>
+        <v>191</v>
       </c>
       <c r="B68" t="s">
-        <v>323</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>324</v>
+        <v>193</v>
       </c>
       <c r="B69" t="s">
-        <v>321</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>325</v>
+        <v>194</v>
       </c>
       <c r="B70" t="s">
-        <v>323</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>326</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>328</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>329</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>330</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>331</v>
+        <v>200</v>
       </c>
       <c r="B77" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>332</v>
+        <v>201</v>
       </c>
       <c r="B78" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>333</v>
+        <v>202</v>
       </c>
       <c r="B79" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>334</v>
+        <v>203</v>
       </c>
       <c r="B80" t="s">
-        <v>335</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>336</v>
+        <v>205</v>
       </c>
       <c r="B81" t="s">
-        <v>337</v>
+        <v>206</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>338</v>
+        <v>207</v>
       </c>
       <c r="B82" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>339</v>
+        <v>208</v>
       </c>
       <c r="B83" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>340</v>
+        <v>209</v>
       </c>
       <c r="B84" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>341</v>
+        <v>210</v>
       </c>
       <c r="B85" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>342</v>
+        <v>211</v>
       </c>
       <c r="B86" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>343</v>
+        <v>212</v>
       </c>
       <c r="B87" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>344</v>
+        <v>213</v>
       </c>
       <c r="B88" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>345</v>
+        <v>214</v>
       </c>
       <c r="B89" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>346</v>
+        <v>215</v>
       </c>
       <c r="B90" t="s">
-        <v>347</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>348</v>
+        <v>217</v>
       </c>
       <c r="B91" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>349</v>
+        <v>218</v>
       </c>
       <c r="B92" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>350</v>
+        <v>219</v>
       </c>
       <c r="B93" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>351</v>
+        <v>220</v>
       </c>
       <c r="B94" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>352</v>
+        <v>221</v>
       </c>
       <c r="B95" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>353</v>
+        <v>222</v>
       </c>
       <c r="B96" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>354</v>
+        <v>223</v>
       </c>
       <c r="B97" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>355</v>
+        <v>224</v>
       </c>
       <c r="B98" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>356</v>
+        <v>225</v>
       </c>
       <c r="B99" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>357</v>
+        <v>226</v>
       </c>
       <c r="B100" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>358</v>
+        <v>227</v>
       </c>
       <c r="B101" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>360</v>
+        <v>229</v>
       </c>
       <c r="B102" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>361</v>
+        <v>230</v>
       </c>
       <c r="B103" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>362</v>
+        <v>231</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>363</v>
+        <v>232</v>
       </c>
       <c r="B106" t="s">
-        <v>364</v>
+        <v>233</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>365</v>
+        <v>234</v>
       </c>
       <c r="B107" t="s">
-        <v>366</v>
+        <v>235</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>367</v>
+        <v>236</v>
       </c>
       <c r="B108" t="s">
-        <v>368</v>
+        <v>237</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>369</v>
+        <v>238</v>
       </c>
       <c r="B109" t="s">
-        <v>370</v>
+        <v>239</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>371</v>
+        <v>240</v>
       </c>
       <c r="B110" t="s">
-        <v>372</v>
+        <v>241</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>373</v>
+        <v>242</v>
       </c>
       <c r="B111" t="s">
-        <v>374</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>375</v>
+        <v>244</v>
       </c>
       <c r="B112" t="s">
-        <v>376</v>
+        <v>245</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>377</v>
+        <v>246</v>
       </c>
       <c r="B113" t="s">
-        <v>303</v>
+        <v>172</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>378</v>
+        <v>247</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>379</v>
+        <v>248</v>
       </c>
       <c r="B116" t="s">
-        <v>294</v>
+        <v>163</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>380</v>
+        <v>249</v>
       </c>
       <c r="B117" t="s">
-        <v>381</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>382</v>
+        <v>251</v>
       </c>
       <c r="B118" t="s">
-        <v>383</v>
+        <v>252</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>384</v>
+        <v>253</v>
       </c>
       <c r="B119" t="s">
-        <v>385</v>
+        <v>254</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>386</v>
+        <v>255</v>
       </c>
       <c r="B120" t="s">
-        <v>387</v>
+        <v>256</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>388</v>
+        <v>257</v>
       </c>
       <c r="B121" t="s">
-        <v>389</v>
+        <v>258</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>390</v>
+        <v>259</v>
       </c>
       <c r="B122" t="s">
-        <v>391</v>
+        <v>260</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>392</v>
+        <v>261</v>
       </c>
       <c r="B123" t="s">
-        <v>387</v>
+        <v>256</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>393</v>
+        <v>262</v>
       </c>
       <c r="B124" t="s">
-        <v>389</v>
+        <v>258</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>394</v>
+        <v>263</v>
       </c>
       <c r="B125" t="s">
-        <v>391</v>
+        <v>260</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>395</v>
+        <v>264</v>
       </c>
       <c r="B126" t="s">
-        <v>396</v>
+        <v>265</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>397</v>
+        <v>266</v>
       </c>
       <c r="B127" t="s">
-        <v>398</v>
+        <v>267</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>399</v>
+        <v>268</v>
       </c>
       <c r="B128" t="s">
-        <v>400</v>
+        <v>269</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>401</v>
+        <v>270</v>
       </c>
       <c r="B129" t="s">
-        <v>402</v>
+        <v>271</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>403</v>
+        <v>272</v>
       </c>
       <c r="B130" t="s">
-        <v>404</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>355</v>
+        <v>224</v>
       </c>
       <c r="B131" t="s">
-        <v>405</v>
+        <v>274</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>356</v>
+        <v>225</v>
       </c>
       <c r="B132" t="s">
-        <v>406</v>
+        <v>275</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>358</v>
+        <v>227</v>
       </c>
       <c r="B133" t="s">
-        <v>407</v>
+        <v>276</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>357</v>
+        <v>226</v>
       </c>
       <c r="B134" t="s">
-        <v>408</v>
+        <v>277</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>409</v>
+        <v>278</v>
       </c>
       <c r="B135" t="s">
-        <v>294</v>
+        <v>163</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>410</v>
+        <v>279</v>
       </c>
       <c r="B136" t="s">
-        <v>411</v>
+        <v>280</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>412</v>
+        <v>281</v>
       </c>
       <c r="B137" t="s">
-        <v>413</v>
+        <v>282</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>414</v>
+        <v>283</v>
       </c>
       <c r="B138" t="s">
-        <v>415</v>
+        <v>284</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>416</v>
+        <v>285</v>
       </c>
       <c r="B139" t="s">
-        <v>417</v>
+        <v>286</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>418</v>
+        <v>287</v>
       </c>
       <c r="B140" t="s">
-        <v>419</v>
+        <v>288</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>420</v>
+        <v>289</v>
       </c>
       <c r="B141" t="s">
-        <v>387</v>
+        <v>256</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>421</v>
+        <v>290</v>
       </c>
       <c r="B142" t="s">
-        <v>389</v>
+        <v>258</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>422</v>
+        <v>291</v>
       </c>
       <c r="B143" t="s">
-        <v>391</v>
+        <v>260</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>423</v>
+        <v>292</v>
       </c>
       <c r="B144" t="s">
-        <v>396</v>
+        <v>265</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>424</v>
+        <v>293</v>
       </c>
       <c r="B145" t="s">
-        <v>398</v>
+        <v>267</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>425</v>
+        <v>294</v>
       </c>
       <c r="B146" t="s">
-        <v>400</v>
+        <v>269</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>426</v>
+        <v>295</v>
       </c>
       <c r="B147" t="s">
-        <v>402</v>
+        <v>271</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>427</v>
+        <v>296</v>
       </c>
       <c r="B148" t="s">
-        <v>404</v>
+        <v>273</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>428</v>
+        <v>297</v>
       </c>
       <c r="B149" t="s">
-        <v>429</v>
+        <v>298</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>430</v>
+        <v>299</v>
       </c>
       <c r="B150" t="s">
-        <v>431</v>
+        <v>300</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>432</v>
+        <v>301</v>
       </c>
       <c r="B151" t="s">
-        <v>433</v>
+        <v>302</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>434</v>
+        <v>303</v>
       </c>
       <c r="B152" t="s">
-        <v>435</v>
+        <v>304</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>436</v>
+        <v>305</v>
       </c>
       <c r="B153" t="s">
-        <v>437</v>
+        <v>306</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>438</v>
+        <v>307</v>
       </c>
       <c r="B154" t="s">
-        <v>439</v>
+        <v>308</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>440</v>
+        <v>309</v>
       </c>
       <c r="B155" t="s">
-        <v>441</v>
+        <v>310</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>442</v>
+        <v>311</v>
       </c>
       <c r="B156" t="s">
-        <v>443</v>
+        <v>312</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>444</v>
+        <v>313</v>
       </c>
       <c r="B157" t="s">
-        <v>445</v>
+        <v>314</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>446</v>
+        <v>315</v>
       </c>
       <c r="B158" t="s">
-        <v>447</v>
+        <v>316</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>448</v>
+        <v>317</v>
       </c>
       <c r="B159" t="s">
-        <v>449</v>
+        <v>318</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>450</v>
+        <v>319</v>
       </c>
       <c r="B160" t="s">
-        <v>451</v>
+        <v>320</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>452</v>
+        <v>321</v>
       </c>
       <c r="B161" t="s">
-        <v>453</v>
+        <v>322</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>454</v>
+        <v>323</v>
       </c>
       <c r="B162" t="s">
-        <v>455</v>
+        <v>324</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>456</v>
+        <v>325</v>
       </c>
       <c r="B163" t="s">
-        <v>457</v>
+        <v>326</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>458</v>
+        <v>327</v>
       </c>
       <c r="B164" t="s">
-        <v>459</v>
+        <v>328</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>460</v>
+        <v>329</v>
       </c>
       <c r="B165" t="s">
-        <v>461</v>
+        <v>330</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>462</v>
+        <v>331</v>
       </c>
       <c r="B166" t="s">
-        <v>435</v>
+        <v>304</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>463</v>
+        <v>332</v>
       </c>
       <c r="B167" t="s">
-        <v>417</v>
+        <v>286</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>464</v>
+        <v>333</v>
       </c>
       <c r="B168" t="s">
-        <v>419</v>
+        <v>288</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>465</v>
+        <v>334</v>
       </c>
       <c r="B169" t="s">
-        <v>277</v>
+        <v>146</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>466</v>
+        <v>335</v>
       </c>
       <c r="B170" t="s">
-        <v>467</v>
+        <v>336</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>468</v>
+        <v>337</v>
       </c>
       <c r="B171" t="s">
-        <v>469</v>
+        <v>338</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>470</v>
+        <v>339</v>
       </c>
       <c r="B172" t="s">
-        <v>471</v>
+        <v>340</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>472</v>
+        <v>341</v>
       </c>
       <c r="B173" t="s">
-        <v>473</v>
+        <v>342</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>474</v>
+        <v>343</v>
       </c>
       <c r="B174" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>475</v>
+        <v>344</v>
       </c>
       <c r="B175" t="s">
-        <v>387</v>
+        <v>256</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>476</v>
+        <v>345</v>
       </c>
       <c r="B176" t="s">
-        <v>389</v>
+        <v>258</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>477</v>
+        <v>346</v>
       </c>
       <c r="B177" t="s">
-        <v>429</v>
+        <v>298</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>478</v>
+        <v>347</v>
       </c>
       <c r="B178" t="s">
-        <v>413</v>
+        <v>282</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>479</v>
+        <v>348</v>
       </c>
       <c r="B179" t="s">
-        <v>480</v>
+        <v>349</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>481</v>
+        <v>350</v>
       </c>
       <c r="B180" t="s">
-        <v>417</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4525,76 +3868,12 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>493</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -4604,12 +3883,31 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>494</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -4619,494 +3917,12 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" t="s">
-        <v>497</v>
-      </c>
-      <c r="C5" t="s">
-        <v>417</v>
-      </c>
-      <c r="D5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B6" t="s">
-        <v>499</v>
-      </c>
-      <c r="C6" t="s">
-        <v>419</v>
-      </c>
-      <c r="D6" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" t="s">
-        <v>501</v>
-      </c>
-      <c r="C7" t="s">
-        <v>502</v>
-      </c>
-      <c r="D7" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>209</v>
-      </c>
-      <c r="B8" t="s">
-        <v>503</v>
-      </c>
-      <c r="C8" t="s">
-        <v>277</v>
-      </c>
-      <c r="D8" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>505</v>
-      </c>
-      <c r="C9" t="s">
-        <v>467</v>
-      </c>
-      <c r="D9" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>506</v>
-      </c>
-      <c r="C10" t="s">
-        <v>507</v>
-      </c>
-      <c r="D10" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>213</v>
-      </c>
-      <c r="B11" t="s">
-        <v>508</v>
-      </c>
-      <c r="C11" t="s">
-        <v>509</v>
-      </c>
-      <c r="D11" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>214</v>
-      </c>
-      <c r="B12" t="s">
-        <v>510</v>
-      </c>
-      <c r="C12" t="s">
-        <v>511</v>
-      </c>
-      <c r="D12" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>214</v>
-      </c>
-      <c r="B13" t="s">
-        <v>512</v>
-      </c>
-      <c r="C13" t="s">
-        <v>469</v>
-      </c>
-      <c r="D13" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>214</v>
-      </c>
-      <c r="B14" t="s">
-        <v>513</v>
-      </c>
-      <c r="C14" t="s">
-        <v>514</v>
-      </c>
-      <c r="D14" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>515</v>
-      </c>
-      <c r="C15" t="s">
-        <v>471</v>
-      </c>
-      <c r="D15" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>218</v>
-      </c>
-      <c r="B16" t="s">
-        <v>516</v>
-      </c>
-      <c r="C16" t="s">
-        <v>473</v>
-      </c>
-      <c r="D16" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>218</v>
-      </c>
-      <c r="B17" t="s">
-        <v>517</v>
-      </c>
-      <c r="C17" t="s">
-        <v>518</v>
-      </c>
-      <c r="D17" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>218</v>
-      </c>
-      <c r="B18" t="s">
-        <v>519</v>
-      </c>
-      <c r="C18" t="s">
-        <v>415</v>
-      </c>
-      <c r="D18" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>218</v>
-      </c>
-      <c r="B19" t="s">
-        <v>520</v>
-      </c>
-      <c r="C19" t="s">
-        <v>413</v>
-      </c>
-      <c r="D19" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>218</v>
-      </c>
-      <c r="B20" t="s">
-        <v>521</v>
-      </c>
-      <c r="C20" t="s">
-        <v>522</v>
-      </c>
-      <c r="D20" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>221</v>
-      </c>
-      <c r="B21" t="s">
-        <v>523</v>
-      </c>
-      <c r="C21" t="s">
-        <v>524</v>
-      </c>
-      <c r="D21" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>222</v>
-      </c>
-      <c r="B22" t="s">
-        <v>525</v>
-      </c>
-      <c r="C22" t="s">
-        <v>526</v>
-      </c>
-      <c r="D22" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>222</v>
-      </c>
-      <c r="B23" t="s">
-        <v>527</v>
-      </c>
-      <c r="C23" t="s">
-        <v>347</v>
-      </c>
-      <c r="D23" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>222</v>
-      </c>
-      <c r="B24" t="s">
-        <v>528</v>
-      </c>
-      <c r="C24" t="s">
-        <v>529</v>
-      </c>
-      <c r="D24" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>224</v>
-      </c>
-      <c r="B25" t="s">
-        <v>530</v>
-      </c>
-      <c r="C25" t="s">
-        <v>387</v>
-      </c>
-      <c r="D25" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" t="s">
-        <v>531</v>
-      </c>
-      <c r="C26" t="s">
-        <v>389</v>
-      </c>
-      <c r="D26" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" t="s">
-        <v>532</v>
-      </c>
-      <c r="C27" t="s">
-        <v>480</v>
-      </c>
-      <c r="D27" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>227</v>
-      </c>
-      <c r="B28" t="s">
-        <v>533</v>
-      </c>
-      <c r="C28" t="s">
-        <v>391</v>
-      </c>
-      <c r="D28" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
-        <v>534</v>
-      </c>
-      <c r="C29" t="s">
-        <v>396</v>
-      </c>
-      <c r="D29" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" t="s">
-        <v>535</v>
-      </c>
-      <c r="C30" t="s">
-        <v>398</v>
-      </c>
-      <c r="D30" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>228</v>
-      </c>
-      <c r="B31" t="s">
-        <v>536</v>
-      </c>
-      <c r="C31" t="s">
-        <v>400</v>
-      </c>
-      <c r="D31" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>229</v>
-      </c>
-      <c r="B32" t="s">
-        <v>537</v>
-      </c>
-      <c r="C32" t="s">
-        <v>402</v>
-      </c>
-      <c r="D32" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>229</v>
-      </c>
-      <c r="B33" t="s">
-        <v>538</v>
-      </c>
-      <c r="C33" t="s">
-        <v>404</v>
-      </c>
-      <c r="D33" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>230</v>
-      </c>
-      <c r="B34" t="s">
-        <v>539</v>
-      </c>
-      <c r="C34" t="s">
-        <v>429</v>
-      </c>
-      <c r="D34" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>230</v>
-      </c>
-      <c r="B35" t="s">
-        <v>540</v>
-      </c>
-      <c r="C35" t="s">
-        <v>541</v>
-      </c>
-      <c r="D35" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>167</v>
-      </c>
-      <c r="B36" t="s">
-        <v>542</v>
-      </c>
-      <c r="C36" t="s">
-        <v>543</v>
-      </c>
-      <c r="D36" t="s">
-        <v>500</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>544</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5116,490 +3932,458 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>545</v>
+        <v>359</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>546</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>547</v>
+        <v>361</v>
       </c>
       <c r="B5" t="s">
-        <v>548</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>549</v>
+        <v>363</v>
       </c>
       <c r="B6" t="s">
-        <v>550</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>551</v>
+        <v>365</v>
       </c>
       <c r="B7" t="s">
-        <v>552</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>553</v>
+        <v>367</v>
       </c>
       <c r="B8" t="s">
-        <v>554</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>555</v>
+        <v>369</v>
       </c>
       <c r="B9" t="s">
-        <v>556</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>557</v>
+        <v>371</v>
       </c>
       <c r="B10" t="s">
-        <v>493</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>558</v>
+        <v>373</v>
       </c>
       <c r="B11" t="s">
-        <v>493</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>559</v>
+        <v>375</v>
       </c>
       <c r="B12" t="s">
-        <v>560</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>561</v>
+        <v>377</v>
       </c>
       <c r="B13" t="s">
-        <v>562</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>563</v>
+        <v>379</v>
       </c>
       <c r="B14" t="s">
-        <v>564</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>565</v>
+        <v>381</v>
       </c>
       <c r="B15" t="s">
-        <v>566</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>567</v>
+        <v>383</v>
       </c>
       <c r="B16" t="s">
-        <v>568</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>569</v>
+        <v>385</v>
       </c>
       <c r="B17" t="s">
-        <v>570</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>571</v>
+        <v>387</v>
       </c>
       <c r="B18" t="s">
-        <v>572</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>573</v>
+        <v>389</v>
       </c>
       <c r="B19" t="s">
-        <v>572</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>574</v>
+        <v>391</v>
       </c>
       <c r="B20" t="s">
-        <v>575</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>576</v>
+        <v>392</v>
       </c>
       <c r="B21" t="s">
-        <v>575</v>
+        <v>393</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>577</v>
+        <v>394</v>
       </c>
       <c r="B22" t="s">
-        <v>578</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>579</v>
+        <v>395</v>
       </c>
       <c r="B23" t="s">
-        <v>488</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>580</v>
+        <v>397</v>
       </c>
       <c r="B24" t="s">
-        <v>281</v>
+        <v>396</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>581</v>
+        <v>398</v>
       </c>
       <c r="B25" t="s">
-        <v>489</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>582</v>
+        <v>399</v>
       </c>
       <c r="B26" t="s">
-        <v>489</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>583</v>
+        <v>400</v>
       </c>
       <c r="B27" t="s">
-        <v>489</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>584</v>
+        <v>401</v>
       </c>
       <c r="B28" t="s">
-        <v>489</v>
+        <v>396</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>585</v>
+        <v>402</v>
       </c>
       <c r="B29" t="s">
-        <v>489</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>586</v>
+        <v>403</v>
       </c>
       <c r="B30" t="s">
-        <v>489</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>587</v>
+        <v>404</v>
       </c>
       <c r="B31" t="s">
-        <v>366</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>588</v>
+        <v>405</v>
       </c>
       <c r="B32" t="s">
-        <v>366</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>589</v>
+        <v>406</v>
       </c>
       <c r="B33" t="s">
-        <v>366</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>590</v>
+        <v>407</v>
       </c>
       <c r="B34" t="s">
-        <v>366</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>591</v>
+        <v>408</v>
       </c>
       <c r="B35" t="s">
-        <v>366</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>592</v>
+        <v>409</v>
       </c>
       <c r="B36" t="s">
-        <v>289</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>593</v>
+        <v>410</v>
       </c>
       <c r="B37" t="s">
-        <v>289</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>594</v>
+        <v>411</v>
       </c>
       <c r="B38" t="s">
-        <v>289</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>595</v>
+        <v>412</v>
       </c>
       <c r="B39" t="s">
-        <v>289</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>596</v>
+        <v>413</v>
       </c>
       <c r="B40" t="s">
-        <v>289</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>597</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s">
-        <v>289</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>598</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s">
-        <v>289</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>599</v>
+        <v>416</v>
       </c>
       <c r="B43" t="s">
-        <v>289</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>600</v>
+        <v>417</v>
       </c>
       <c r="B44" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>601</v>
+        <v>418</v>
       </c>
       <c r="B45" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>602</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>603</v>
+        <v>420</v>
       </c>
       <c r="B47" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>604</v>
+        <v>421</v>
       </c>
       <c r="B48" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>605</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>606</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>607</v>
+        <v>424</v>
       </c>
       <c r="B51" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>608</v>
+        <v>425</v>
       </c>
       <c r="B52" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>609</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>610</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>611</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>612</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>613</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>614</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>615</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>616</v>
+        <v>433</v>
       </c>
       <c r="B60" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>617</v>
-      </c>
-      <c r="B61" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>618</v>
-      </c>
-      <c r="B62" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>619</v>
-      </c>
-      <c r="B63" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>620</v>
-      </c>
-      <c r="B64" t="s">
-        <v>359</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -5689,7 +4473,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -5705,326 +4489,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -6034,52 +4498,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -6089,52 +4523,17 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>106</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6144,342 +4543,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>162</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -30,16 +30,17 @@
     <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
     <sheet name="Project Summary" sheetId="22" r:id="rId22"/>
     <sheet name="Design Params and Codes" sheetId="23" r:id="rId23"/>
-    <sheet name="Register Summary" sheetId="24" r:id="rId24"/>
-    <sheet name="DFT Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="Nesto Usage Report" sheetId="26" r:id="rId26"/>
+    <sheet name="DRM Summary" sheetId="24" r:id="rId24"/>
+    <sheet name="Register Summary" sheetId="25" r:id="rId25"/>
+    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
+    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="509">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -131,10 +132,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -146,7 +147,142 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraCORE.PORB97836(PORB97836)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -159,6 +295,135 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>PORB97836 - {"path": "XWALTZ,XceleraCORE", "instance": "XceleraCORE", "symbol": "PORB97836", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -279,67 +544,13 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
@@ -348,9 +559,6 @@
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
-  </si>
-  <si>
     <t>Project Summary</t>
   </si>
   <si>
@@ -1098,27 +1306,51 @@
     <t>measure_reset_command</t>
   </si>
   <si>
+    <t>DRM Summary</t>
+  </si>
+  <si>
+    <t>Addresses</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Instance</t>
+  </si>
+  <si>
+    <t>TMB</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>DRM to Memory Check</t>
+  </si>
+  <si>
+    <t>TOTAL dec</t>
+  </si>
+  <si>
+    <t>Allowed &lt;= 61</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
     <t>Register Summary</t>
   </si>
   <si>
     <t>DFT Summary</t>
   </si>
   <si>
-    <t>Addresses</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Instance</t>
-  </si>
-  <si>
     <t>TMA</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>Nesto Usage Report</t>
   </si>
   <si>
@@ -1140,30 +1372,27 @@
     <t>193</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>dbuf</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>noconn</t>
   </si>
   <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>dbuf</t>
-  </si>
-  <si>
-    <t>122</t>
+    <t>114</t>
   </si>
   <si>
     <t>nor3</t>
   </si>
   <si>
-    <t>61</t>
-  </si>
-  <si>
     <t>delayfixed</t>
   </si>
   <si>
@@ -1206,10 +1435,10 @@
     <t>16</t>
   </si>
   <si>
-    <t>drmmodule</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>tie</t>
@@ -1227,15 +1456,9 @@
     <t>9</t>
   </si>
   <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
     <t>resistor</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>oneshot</t>
   </si>
   <si>
@@ -1282,6 +1505,9 @@
   </si>
   <si>
     <t>capacitorfixed</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>voltage2current</t>
@@ -1715,7 +1941,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1735,7 +1961,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1750,7 +1976,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1765,17 +1991,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1790,12 +2016,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1810,17 +2036,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1835,12 +2061,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1855,7 +2081,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1875,127 +2101,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2005,162 +2231,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2175,17 +2256,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2410,7 +2491,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2430,17 +2511,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2455,52 +2536,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2515,81 +2596,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>185</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>187</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>193</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>196</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2597,1268 +2678,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>133</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>136</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>138</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="B39" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>159</v>
+        <v>228</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>160</v>
+        <v>229</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="B43" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="B46" t="s">
-        <v>166</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>167</v>
+        <v>236</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="B48" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="B49" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>239</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>171</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s">
-        <v>117</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>174</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="B55" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="B56" t="s">
-        <v>178</v>
+        <v>247</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>180</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>181</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>182</v>
+        <v>251</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>183</v>
+        <v>252</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="B64" t="s">
-        <v>186</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>187</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>188</v>
+        <v>257</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="B67" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="B68" t="s">
-        <v>192</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>193</v>
+        <v>262</v>
       </c>
       <c r="B69" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="B70" t="s">
-        <v>192</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>196</v>
+        <v>265</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>197</v>
+        <v>266</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>198</v>
+        <v>267</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>199</v>
+        <v>268</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>200</v>
+        <v>269</v>
       </c>
       <c r="B77" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>201</v>
+        <v>270</v>
       </c>
       <c r="B78" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>202</v>
+        <v>271</v>
       </c>
       <c r="B79" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>203</v>
+        <v>272</v>
       </c>
       <c r="B80" t="s">
-        <v>204</v>
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>205</v>
+        <v>274</v>
       </c>
       <c r="B81" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="B82" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="B83" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>209</v>
+        <v>278</v>
       </c>
       <c r="B84" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="B85" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>211</v>
+        <v>280</v>
       </c>
       <c r="B86" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>212</v>
+        <v>281</v>
       </c>
       <c r="B87" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>213</v>
+        <v>282</v>
       </c>
       <c r="B88" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>214</v>
+        <v>283</v>
       </c>
       <c r="B89" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>215</v>
+        <v>284</v>
       </c>
       <c r="B90" t="s">
-        <v>216</v>
+        <v>285</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="B91" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>218</v>
+        <v>287</v>
       </c>
       <c r="B92" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>219</v>
+        <v>288</v>
       </c>
       <c r="B93" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="B94" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>221</v>
+        <v>290</v>
       </c>
       <c r="B95" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>222</v>
+        <v>291</v>
       </c>
       <c r="B96" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>223</v>
+        <v>292</v>
       </c>
       <c r="B97" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>224</v>
+        <v>293</v>
       </c>
       <c r="B98" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>225</v>
+        <v>294</v>
       </c>
       <c r="B99" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>226</v>
+        <v>295</v>
       </c>
       <c r="B100" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="B101" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>229</v>
+        <v>298</v>
       </c>
       <c r="B102" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="B103" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>231</v>
+        <v>300</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>232</v>
+        <v>301</v>
       </c>
       <c r="B106" t="s">
-        <v>233</v>
+        <v>302</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>234</v>
+        <v>303</v>
       </c>
       <c r="B107" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>236</v>
+        <v>305</v>
       </c>
       <c r="B108" t="s">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>238</v>
+        <v>307</v>
       </c>
       <c r="B109" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>240</v>
+        <v>309</v>
       </c>
       <c r="B110" t="s">
-        <v>241</v>
+        <v>310</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>242</v>
+        <v>311</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>312</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>244</v>
+        <v>313</v>
       </c>
       <c r="B112" t="s">
-        <v>245</v>
+        <v>314</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>246</v>
+        <v>315</v>
       </c>
       <c r="B113" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>247</v>
+        <v>316</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="B116" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>249</v>
+        <v>318</v>
       </c>
       <c r="B117" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>251</v>
+        <v>320</v>
       </c>
       <c r="B118" t="s">
-        <v>252</v>
+        <v>321</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>253</v>
+        <v>322</v>
       </c>
       <c r="B119" t="s">
-        <v>254</v>
+        <v>323</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>255</v>
+        <v>324</v>
       </c>
       <c r="B120" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>257</v>
+        <v>326</v>
       </c>
       <c r="B121" t="s">
-        <v>258</v>
+        <v>327</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="B122" t="s">
-        <v>260</v>
+        <v>329</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>261</v>
+        <v>330</v>
       </c>
       <c r="B123" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>262</v>
+        <v>331</v>
       </c>
       <c r="B124" t="s">
-        <v>258</v>
+        <v>327</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>263</v>
+        <v>332</v>
       </c>
       <c r="B125" t="s">
-        <v>260</v>
+        <v>329</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>264</v>
+        <v>333</v>
       </c>
       <c r="B126" t="s">
-        <v>265</v>
+        <v>334</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>266</v>
+        <v>335</v>
       </c>
       <c r="B127" t="s">
-        <v>267</v>
+        <v>336</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>268</v>
+        <v>337</v>
       </c>
       <c r="B128" t="s">
-        <v>269</v>
+        <v>338</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>270</v>
+        <v>339</v>
       </c>
       <c r="B129" t="s">
-        <v>271</v>
+        <v>340</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>272</v>
+        <v>341</v>
       </c>
       <c r="B130" t="s">
-        <v>273</v>
+        <v>342</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>224</v>
+        <v>293</v>
       </c>
       <c r="B131" t="s">
-        <v>274</v>
+        <v>343</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>225</v>
+        <v>294</v>
       </c>
       <c r="B132" t="s">
-        <v>275</v>
+        <v>344</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="B133" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>226</v>
+        <v>295</v>
       </c>
       <c r="B134" t="s">
-        <v>277</v>
+        <v>346</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>278</v>
+        <v>347</v>
       </c>
       <c r="B135" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>279</v>
+        <v>348</v>
       </c>
       <c r="B136" t="s">
-        <v>280</v>
+        <v>349</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>281</v>
+        <v>350</v>
       </c>
       <c r="B137" t="s">
-        <v>282</v>
+        <v>351</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="B138" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="B139" t="s">
-        <v>286</v>
+        <v>355</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>287</v>
+        <v>356</v>
       </c>
       <c r="B140" t="s">
-        <v>288</v>
+        <v>357</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>289</v>
+        <v>358</v>
       </c>
       <c r="B141" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>290</v>
+        <v>359</v>
       </c>
       <c r="B142" t="s">
-        <v>258</v>
+        <v>327</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>291</v>
+        <v>360</v>
       </c>
       <c r="B143" t="s">
-        <v>260</v>
+        <v>329</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>292</v>
+        <v>361</v>
       </c>
       <c r="B144" t="s">
-        <v>265</v>
+        <v>334</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>293</v>
+        <v>362</v>
       </c>
       <c r="B145" t="s">
-        <v>267</v>
+        <v>336</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>294</v>
+        <v>363</v>
       </c>
       <c r="B146" t="s">
-        <v>269</v>
+        <v>338</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>295</v>
+        <v>364</v>
       </c>
       <c r="B147" t="s">
-        <v>271</v>
+        <v>340</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>296</v>
+        <v>365</v>
       </c>
       <c r="B148" t="s">
-        <v>273</v>
+        <v>342</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>297</v>
+        <v>366</v>
       </c>
       <c r="B149" t="s">
-        <v>298</v>
+        <v>367</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>299</v>
+        <v>368</v>
       </c>
       <c r="B150" t="s">
-        <v>300</v>
+        <v>369</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>301</v>
+        <v>370</v>
       </c>
       <c r="B151" t="s">
-        <v>302</v>
+        <v>371</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>303</v>
+        <v>372</v>
       </c>
       <c r="B152" t="s">
-        <v>304</v>
+        <v>373</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>305</v>
+        <v>374</v>
       </c>
       <c r="B153" t="s">
-        <v>306</v>
+        <v>375</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>307</v>
+        <v>376</v>
       </c>
       <c r="B154" t="s">
-        <v>308</v>
+        <v>377</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>309</v>
+        <v>378</v>
       </c>
       <c r="B155" t="s">
-        <v>310</v>
+        <v>379</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>311</v>
+        <v>380</v>
       </c>
       <c r="B156" t="s">
-        <v>312</v>
+        <v>381</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>313</v>
+        <v>382</v>
       </c>
       <c r="B157" t="s">
-        <v>314</v>
+        <v>383</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>315</v>
+        <v>384</v>
       </c>
       <c r="B158" t="s">
-        <v>316</v>
+        <v>385</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>317</v>
+        <v>386</v>
       </c>
       <c r="B159" t="s">
-        <v>318</v>
+        <v>387</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>319</v>
+        <v>388</v>
       </c>
       <c r="B160" t="s">
-        <v>320</v>
+        <v>389</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>321</v>
+        <v>390</v>
       </c>
       <c r="B161" t="s">
-        <v>322</v>
+        <v>391</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>323</v>
+        <v>392</v>
       </c>
       <c r="B162" t="s">
-        <v>324</v>
+        <v>393</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>325</v>
+        <v>394</v>
       </c>
       <c r="B163" t="s">
-        <v>326</v>
+        <v>395</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>327</v>
+        <v>396</v>
       </c>
       <c r="B164" t="s">
-        <v>328</v>
+        <v>397</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>329</v>
+        <v>398</v>
       </c>
       <c r="B165" t="s">
-        <v>330</v>
+        <v>399</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>331</v>
+        <v>400</v>
       </c>
       <c r="B166" t="s">
-        <v>304</v>
+        <v>373</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>332</v>
+        <v>401</v>
       </c>
       <c r="B167" t="s">
-        <v>286</v>
+        <v>355</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>333</v>
+        <v>402</v>
       </c>
       <c r="B168" t="s">
-        <v>288</v>
+        <v>357</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>334</v>
+        <v>403</v>
       </c>
       <c r="B169" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>335</v>
+        <v>404</v>
       </c>
       <c r="B170" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>337</v>
+        <v>406</v>
       </c>
       <c r="B171" t="s">
-        <v>338</v>
+        <v>407</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>339</v>
+        <v>408</v>
       </c>
       <c r="B172" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>341</v>
+        <v>410</v>
       </c>
       <c r="B173" t="s">
-        <v>342</v>
+        <v>411</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>343</v>
+        <v>412</v>
       </c>
       <c r="B174" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>344</v>
+        <v>413</v>
       </c>
       <c r="B175" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>345</v>
+        <v>414</v>
       </c>
       <c r="B176" t="s">
-        <v>258</v>
+        <v>327</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>346</v>
+        <v>415</v>
       </c>
       <c r="B177" t="s">
-        <v>298</v>
+        <v>367</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>347</v>
+        <v>416</v>
       </c>
       <c r="B178" t="s">
-        <v>282</v>
+        <v>351</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>348</v>
+        <v>417</v>
       </c>
       <c r="B179" t="s">
-        <v>349</v>
+        <v>418</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>350</v>
+        <v>419</v>
       </c>
       <c r="B180" t="s">
-        <v>286</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -3868,12 +3949,76 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -3883,31 +4028,12 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>357</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -3917,12 +4043,46 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3932,458 +4092,458 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>436</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>360</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>361</v>
+        <v>438</v>
       </c>
       <c r="B5" t="s">
-        <v>362</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>363</v>
+        <v>440</v>
       </c>
       <c r="B6" t="s">
-        <v>364</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>365</v>
+        <v>442</v>
       </c>
       <c r="B7" t="s">
-        <v>366</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>367</v>
+        <v>444</v>
       </c>
       <c r="B8" t="s">
-        <v>368</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>369</v>
+        <v>446</v>
       </c>
       <c r="B9" t="s">
-        <v>370</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>371</v>
+        <v>448</v>
       </c>
       <c r="B10" t="s">
-        <v>372</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>373</v>
+        <v>449</v>
       </c>
       <c r="B11" t="s">
-        <v>374</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>375</v>
+        <v>451</v>
       </c>
       <c r="B12" t="s">
-        <v>376</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>377</v>
+        <v>453</v>
       </c>
       <c r="B13" t="s">
-        <v>378</v>
+        <v>454</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>379</v>
+        <v>455</v>
       </c>
       <c r="B14" t="s">
-        <v>380</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>381</v>
+        <v>457</v>
       </c>
       <c r="B15" t="s">
-        <v>382</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>383</v>
+        <v>459</v>
       </c>
       <c r="B16" t="s">
-        <v>384</v>
+        <v>460</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>385</v>
+        <v>461</v>
       </c>
       <c r="B17" t="s">
-        <v>386</v>
+        <v>462</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>387</v>
+        <v>463</v>
       </c>
       <c r="B18" t="s">
-        <v>388</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>389</v>
+        <v>465</v>
       </c>
       <c r="B19" t="s">
-        <v>390</v>
+        <v>466</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>391</v>
+        <v>467</v>
       </c>
       <c r="B20" t="s">
-        <v>390</v>
+        <v>466</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>392</v>
+        <v>468</v>
       </c>
       <c r="B21" t="s">
-        <v>393</v>
+        <v>469</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>394</v>
+        <v>470</v>
       </c>
       <c r="B22" t="s">
-        <v>172</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>395</v>
+        <v>471</v>
       </c>
       <c r="B23" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>397</v>
+        <v>472</v>
       </c>
       <c r="B24" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>398</v>
+        <v>473</v>
       </c>
       <c r="B25" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>399</v>
+        <v>474</v>
       </c>
       <c r="B26" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="B27" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>401</v>
+        <v>476</v>
       </c>
       <c r="B28" t="s">
-        <v>396</v>
+        <v>304</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>402</v>
+        <v>477</v>
       </c>
       <c r="B29" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>403</v>
+        <v>478</v>
       </c>
       <c r="B30" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>404</v>
+        <v>479</v>
       </c>
       <c r="B31" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>405</v>
+        <v>480</v>
       </c>
       <c r="B32" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>406</v>
+        <v>481</v>
       </c>
       <c r="B33" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>407</v>
+        <v>482</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>408</v>
+        <v>483</v>
       </c>
       <c r="B35" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>409</v>
+        <v>484</v>
       </c>
       <c r="B36" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>410</v>
+        <v>485</v>
       </c>
       <c r="B37" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>411</v>
+        <v>486</v>
       </c>
       <c r="B38" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>412</v>
+        <v>487</v>
       </c>
       <c r="B39" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>413</v>
+        <v>488</v>
       </c>
       <c r="B40" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>414</v>
+        <v>489</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>415</v>
+        <v>490</v>
       </c>
       <c r="B42" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>416</v>
+        <v>491</v>
       </c>
       <c r="B43" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>417</v>
+        <v>492</v>
       </c>
       <c r="B44" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>418</v>
+        <v>493</v>
       </c>
       <c r="B45" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>419</v>
+        <v>494</v>
       </c>
       <c r="B46" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>420</v>
+        <v>495</v>
       </c>
       <c r="B47" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>421</v>
+        <v>496</v>
       </c>
       <c r="B48" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>422</v>
+        <v>497</v>
       </c>
       <c r="B49" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>423</v>
+        <v>498</v>
       </c>
       <c r="B50" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>424</v>
+        <v>499</v>
       </c>
       <c r="B51" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>425</v>
+        <v>500</v>
       </c>
       <c r="B52" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>426</v>
+        <v>501</v>
       </c>
       <c r="B53" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>427</v>
+        <v>502</v>
       </c>
       <c r="B54" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>428</v>
+        <v>503</v>
       </c>
       <c r="B55" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>429</v>
+        <v>504</v>
       </c>
       <c r="B56" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>430</v>
+        <v>505</v>
       </c>
       <c r="B57" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>431</v>
+        <v>506</v>
       </c>
       <c r="B58" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>432</v>
+        <v>507</v>
       </c>
       <c r="B59" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>433</v>
+        <v>508</v>
       </c>
       <c r="B60" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -4473,7 +4633,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4489,6 +4649,276 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4503,7 +4933,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4513,7 +4943,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -4528,7 +4958,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4543,17 +4973,282 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -30,17 +30,16 @@
     <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
     <sheet name="Project Summary" sheetId="22" r:id="rId22"/>
     <sheet name="Design Params and Codes" sheetId="23" r:id="rId23"/>
-    <sheet name="DRM Summary" sheetId="24" r:id="rId24"/>
-    <sheet name="Register Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
-    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
+    <sheet name="Register Summary" sheetId="24" r:id="rId24"/>
+    <sheet name="DFT Summary" sheetId="25" r:id="rId25"/>
+    <sheet name="Nesto Usage Report" sheetId="26" r:id="rId26"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="506">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -132,10 +131,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
-  </si>
-  <si>
-    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
+  </si>
+  <si>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -147,142 +146,7 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.fcm(59)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_bottom(60)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_refresh(61)</t>
-  </si>
-  <si>
-    <t>Floating pin XU21.i0(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU22.i0(49)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XU11.enable_switchb(102)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.mode_hiccup(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.blank_thermal(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XU10.enable_switch(58)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(35)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(34)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(33)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(49)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.halfway(36)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
-  </si>
-  <si>
-    <t>XWALTZ</t>
-  </si>
-  <si>
-    <t>Floating pin XceleraCORE.PORB97836(PORB97836)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -295,135 +159,6 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>PORB97836 - {"path": "XWALTZ,XceleraCORE", "instance": "XceleraCORE", "symbol": "PORB97836", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -544,37 +279,157 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
+  </si>
+  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
+  </si>
+  <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
+    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
+  </si>
+  <si>
     <t>Project Summary</t>
   </si>
   <si>
     <t>Package Stats</t>
   </si>
   <si>
-    <t>needed: 0</t>
+    <t>needed: 2</t>
   </si>
   <si>
     <t>spares: 0</t>
   </si>
   <si>
-    <t>algorithm: 0 - No compression needed</t>
-  </si>
-  <si>
-    <t>piggyback: []</t>
+    <t>algorithm: 6 - Piggybacks</t>
+  </si>
+  <si>
+    <t>piggyback: ['DFTSCL', 'DFTSDA']</t>
   </si>
   <si>
     <t>user_pads: 12</t>
@@ -604,18 +459,18 @@
     <t>add_dft</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>add_dbufdft</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>add_dbufdft</t>
-  </si>
-  <si>
     <t>dft_ignore_bricks</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>dft_measure</t>
   </si>
   <si>
@@ -1306,7 +1161,10 @@
     <t>measure_reset_command</t>
   </si>
   <si>
-    <t>DRM Summary</t>
+    <t>Register Summary</t>
+  </si>
+  <si>
+    <t>DFT Summary</t>
   </si>
   <si>
     <t>Addresses</t>
@@ -1318,177 +1176,312 @@
     <t>Instance</t>
   </si>
   <si>
-    <t>TMB</t>
+    <t>TMA</t>
   </si>
   <si>
     <t>type</t>
   </si>
   <si>
+    <t>dft_hex0x01</t>
+  </si>
+  <si>
+    <t>DFTtm8</t>
+  </si>
+  <si>
+    <t>dft_hex0x02</t>
+  </si>
+  <si>
+    <t>DFTtm8t</t>
+  </si>
+  <si>
+    <t>dft_hex0x1A</t>
+  </si>
+  <si>
+    <t>0x1A</t>
+  </si>
+  <si>
+    <t>dft_hex0x03</t>
+  </si>
+  <si>
+    <t>DFTtm8d</t>
+  </si>
+  <si>
+    <t>dft_hex0x04</t>
+  </si>
+  <si>
+    <t>dft_hex0x05</t>
+  </si>
+  <si>
+    <t>0x05</t>
+  </si>
+  <si>
+    <t>dft_hex0x06</t>
+  </si>
+  <si>
+    <t>0x06</t>
+  </si>
+  <si>
+    <t>dft_hex0x07</t>
+  </si>
+  <si>
+    <t>0x07</t>
+  </si>
+  <si>
+    <t>dft_hex0x08</t>
+  </si>
+  <si>
+    <t>dft_hex0x1B</t>
+  </si>
+  <si>
+    <t>0x1B</t>
+  </si>
+  <si>
+    <t>dft_hex0x09</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B</t>
+  </si>
+  <si>
+    <t>0x0B</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C</t>
+  </si>
+  <si>
+    <t>dft_hex0x1C</t>
+  </si>
+  <si>
+    <t>dft_hex0x1D</t>
+  </si>
+  <si>
+    <t>0x1D</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D</t>
+  </si>
+  <si>
+    <t>0x0D</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E</t>
+  </si>
+  <si>
+    <t>0x0E</t>
+  </si>
+  <si>
+    <t>dft_hex0x0F</t>
+  </si>
+  <si>
+    <t>dft_hex0x1E</t>
+  </si>
+  <si>
+    <t>0x1E</t>
+  </si>
+  <si>
+    <t>dft_hex0x10</t>
+  </si>
+  <si>
+    <t>dft_hex0x11</t>
+  </si>
+  <si>
+    <t>dft_hex0x1F</t>
+  </si>
+  <si>
+    <t>dft_hex0x12</t>
+  </si>
+  <si>
+    <t>dft_hex0x13</t>
+  </si>
+  <si>
+    <t>dft_hex0x14</t>
+  </si>
+  <si>
+    <t>dft_hex0x15</t>
+  </si>
+  <si>
+    <t>dft_hex0x16</t>
+  </si>
+  <si>
+    <t>dft_hex0x17</t>
+  </si>
+  <si>
+    <t>dft_hex0x18</t>
+  </si>
+  <si>
+    <t>dft_hex0x20</t>
+  </si>
+  <si>
+    <t>0x20</t>
+  </si>
+  <si>
+    <t>dft_hex0x19</t>
+  </si>
+  <si>
+    <t>0x19</t>
+  </si>
+  <si>
+    <t>Nesto Usage Report</t>
+  </si>
+  <si>
+    <t>Nesto</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>pinprobe</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>noconn</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>inv</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>dbuf</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>nor3</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>dftprobeModel0</t>
+  </si>
+  <si>
+    <t>delayfixed</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>nand3</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>celeranoconn</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>srlatch</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>nor2</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>dftmodule</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>dfthijack</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>dff</t>
+  </si>
+  <si>
+    <t>drmmodule</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>tie</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>datamap0</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>dftprobeModel2</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
+    <t>resistor</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>DRM to Memory Check</t>
-  </si>
-  <si>
-    <t>TOTAL dec</t>
-  </si>
-  <si>
-    <t>Allowed &lt;= 61</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>Register Summary</t>
-  </si>
-  <si>
-    <t>DFT Summary</t>
-  </si>
-  <si>
-    <t>TMA</t>
-  </si>
-  <si>
-    <t>Nesto Usage Report</t>
-  </si>
-  <si>
-    <t>Nesto</t>
-  </si>
-  <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>pinprobe</t>
-  </si>
-  <si>
-    <t>1082</t>
-  </si>
-  <si>
-    <t>inv</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>dbuf</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>noconn</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>nor3</t>
-  </si>
-  <si>
-    <t>delayfixed</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>nand3</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>celeranoconn</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>srlatch</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>nor2</t>
-  </si>
-  <si>
-    <t>35</t>
+    <t>oneshot</t>
+  </si>
+  <si>
+    <t>fetdn</t>
+  </si>
+  <si>
+    <t>currentlimitfet</t>
+  </si>
+  <si>
+    <t>comparatornoctlpins</t>
+  </si>
+  <si>
+    <t>ESDminiClamp6</t>
+  </si>
+  <si>
+    <t>timingskew</t>
+  </si>
+  <si>
+    <t>switchpulldown</t>
+  </si>
+  <si>
+    <t>resistordivider</t>
+  </si>
+  <si>
+    <t>delayclock</t>
+  </si>
+  <si>
+    <t>amux2</t>
   </si>
   <si>
     <t>wrapper</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>dff</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>tie</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>datamap0</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>resistor</t>
-  </si>
-  <si>
-    <t>oneshot</t>
-  </si>
-  <si>
-    <t>fetdn</t>
-  </si>
-  <si>
-    <t>currentlimitfet</t>
-  </si>
-  <si>
-    <t>comparatornoctlpins</t>
-  </si>
-  <si>
-    <t>ESDminiClamp6</t>
-  </si>
-  <si>
-    <t>timingskew</t>
-  </si>
-  <si>
-    <t>switchpulldown</t>
-  </si>
-  <si>
-    <t>resistordivider</t>
-  </si>
-  <si>
-    <t>delayclock</t>
-  </si>
-  <si>
-    <t>amux2</t>
-  </si>
-  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1505,9 +1498,6 @@
   </si>
   <si>
     <t>capacitorfixed</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>voltage2current</t>
@@ -1941,7 +1931,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1961,7 +1951,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1976,7 +1966,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1991,17 +1981,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2016,12 +2006,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2036,17 +2026,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2061,12 +2051,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2081,7 +2071,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2101,127 +2091,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>142</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>144</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>145</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>147</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>149</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>150</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>151</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>152</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>153</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>154</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>155</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>157</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>159</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>161</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>163</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2231,17 +2221,162 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2256,17 +2391,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2486,17 +2621,257 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2511,17 +2886,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2536,52 +2911,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2596,81 +2971,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="B6" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>142</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>191</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>195</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>196</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2678,1268 +3053,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>198</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>201</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="B20" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="B21" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>205</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>206</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>210</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s">
-        <v>211</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s">
-        <v>217</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s">
-        <v>219</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>220</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s">
-        <v>221</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>223</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>226</v>
+        <v>178</v>
       </c>
       <c r="B39" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="B40" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="B41" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>230</v>
+        <v>182</v>
       </c>
       <c r="B42" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="B43" t="s">
-        <v>232</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>233</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="B46" t="s">
-        <v>235</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="B47" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>237</v>
+        <v>189</v>
       </c>
       <c r="B48" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>238</v>
+        <v>190</v>
       </c>
       <c r="B49" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>239</v>
+        <v>191</v>
       </c>
       <c r="B50" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="B51" t="s">
-        <v>241</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>242</v>
+        <v>194</v>
       </c>
       <c r="B52" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>243</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>244</v>
+        <v>196</v>
       </c>
       <c r="B55" t="s">
-        <v>245</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>198</v>
       </c>
       <c r="B56" t="s">
-        <v>247</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>248</v>
+        <v>200</v>
       </c>
       <c r="B57" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>249</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>250</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>251</v>
+        <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>252</v>
+        <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>253</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>254</v>
+        <v>206</v>
       </c>
       <c r="B64" t="s">
-        <v>255</v>
+        <v>207</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>256</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>257</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="B67" t="s">
-        <v>259</v>
+        <v>211</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>260</v>
+        <v>212</v>
       </c>
       <c r="B68" t="s">
-        <v>261</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="B69" t="s">
-        <v>259</v>
+        <v>211</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>263</v>
+        <v>215</v>
       </c>
       <c r="B70" t="s">
-        <v>261</v>
+        <v>213</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>264</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>265</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>266</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="B77" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="B78" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>271</v>
+        <v>223</v>
       </c>
       <c r="B79" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>272</v>
+        <v>224</v>
       </c>
       <c r="B80" t="s">
-        <v>273</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="B81" t="s">
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="B82" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>277</v>
+        <v>229</v>
       </c>
       <c r="B83" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="B84" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="B85" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>280</v>
+        <v>232</v>
       </c>
       <c r="B86" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="B87" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>282</v>
+        <v>234</v>
       </c>
       <c r="B88" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="B89" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="B90" t="s">
-        <v>285</v>
+        <v>237</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="B91" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>287</v>
+        <v>239</v>
       </c>
       <c r="B92" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>289</v>
+        <v>241</v>
       </c>
       <c r="B94" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>290</v>
+        <v>242</v>
       </c>
       <c r="B95" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="B96" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="B97" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>293</v>
+        <v>245</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="B99" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="B100" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>296</v>
+        <v>248</v>
       </c>
       <c r="B101" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>298</v>
+        <v>250</v>
       </c>
       <c r="B102" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>299</v>
+        <v>251</v>
       </c>
       <c r="B103" t="s">
-        <v>219</v>
+        <v>171</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>300</v>
+        <v>252</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>301</v>
+        <v>253</v>
       </c>
       <c r="B106" t="s">
-        <v>302</v>
+        <v>254</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>303</v>
+        <v>255</v>
       </c>
       <c r="B107" t="s">
-        <v>304</v>
+        <v>256</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>305</v>
+        <v>257</v>
       </c>
       <c r="B108" t="s">
-        <v>306</v>
+        <v>258</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>307</v>
+        <v>259</v>
       </c>
       <c r="B109" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>309</v>
+        <v>261</v>
       </c>
       <c r="B110" t="s">
-        <v>310</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="B111" t="s">
-        <v>312</v>
+        <v>264</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>313</v>
+        <v>265</v>
       </c>
       <c r="B112" t="s">
-        <v>314</v>
+        <v>266</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>315</v>
+        <v>267</v>
       </c>
       <c r="B113" t="s">
-        <v>241</v>
+        <v>193</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>316</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>317</v>
+        <v>269</v>
       </c>
       <c r="B116" t="s">
-        <v>232</v>
+        <v>184</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>318</v>
+        <v>270</v>
       </c>
       <c r="B117" t="s">
-        <v>319</v>
+        <v>271</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>320</v>
+        <v>272</v>
       </c>
       <c r="B118" t="s">
-        <v>321</v>
+        <v>273</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>322</v>
+        <v>274</v>
       </c>
       <c r="B119" t="s">
-        <v>323</v>
+        <v>275</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="B120" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>326</v>
+        <v>278</v>
       </c>
       <c r="B121" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>328</v>
+        <v>280</v>
       </c>
       <c r="B122" t="s">
-        <v>329</v>
+        <v>281</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="B123" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>331</v>
+        <v>283</v>
       </c>
       <c r="B124" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="B125" t="s">
-        <v>329</v>
+        <v>281</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>333</v>
+        <v>285</v>
       </c>
       <c r="B126" t="s">
-        <v>334</v>
+        <v>286</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="B127" t="s">
-        <v>336</v>
+        <v>288</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>337</v>
+        <v>289</v>
       </c>
       <c r="B128" t="s">
-        <v>338</v>
+        <v>290</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>339</v>
+        <v>291</v>
       </c>
       <c r="B129" t="s">
-        <v>340</v>
+        <v>292</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="B130" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>293</v>
+        <v>245</v>
       </c>
       <c r="B131" t="s">
-        <v>343</v>
+        <v>295</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>294</v>
+        <v>246</v>
       </c>
       <c r="B132" t="s">
-        <v>344</v>
+        <v>296</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>296</v>
+        <v>248</v>
       </c>
       <c r="B133" t="s">
-        <v>345</v>
+        <v>297</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>295</v>
+        <v>247</v>
       </c>
       <c r="B134" t="s">
-        <v>346</v>
+        <v>298</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>347</v>
+        <v>299</v>
       </c>
       <c r="B135" t="s">
-        <v>232</v>
+        <v>184</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="B136" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>350</v>
+        <v>302</v>
       </c>
       <c r="B137" t="s">
-        <v>351</v>
+        <v>303</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="B138" t="s">
-        <v>353</v>
+        <v>305</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>354</v>
+        <v>306</v>
       </c>
       <c r="B139" t="s">
-        <v>355</v>
+        <v>307</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>356</v>
+        <v>308</v>
       </c>
       <c r="B140" t="s">
-        <v>357</v>
+        <v>309</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>358</v>
+        <v>310</v>
       </c>
       <c r="B141" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>359</v>
+        <v>311</v>
       </c>
       <c r="B142" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="B143" t="s">
-        <v>329</v>
+        <v>281</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="B144" t="s">
-        <v>334</v>
+        <v>286</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="B145" t="s">
-        <v>336</v>
+        <v>288</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>363</v>
+        <v>315</v>
       </c>
       <c r="B146" t="s">
-        <v>338</v>
+        <v>290</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>364</v>
+        <v>316</v>
       </c>
       <c r="B147" t="s">
-        <v>340</v>
+        <v>292</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>365</v>
+        <v>317</v>
       </c>
       <c r="B148" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>366</v>
+        <v>318</v>
       </c>
       <c r="B149" t="s">
-        <v>367</v>
+        <v>319</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>368</v>
+        <v>320</v>
       </c>
       <c r="B150" t="s">
-        <v>369</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>370</v>
+        <v>322</v>
       </c>
       <c r="B151" t="s">
-        <v>371</v>
+        <v>323</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>372</v>
+        <v>324</v>
       </c>
       <c r="B152" t="s">
-        <v>373</v>
+        <v>325</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>374</v>
+        <v>326</v>
       </c>
       <c r="B153" t="s">
-        <v>375</v>
+        <v>327</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>376</v>
+        <v>328</v>
       </c>
       <c r="B154" t="s">
-        <v>377</v>
+        <v>329</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>378</v>
+        <v>330</v>
       </c>
       <c r="B155" t="s">
-        <v>379</v>
+        <v>331</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="B156" t="s">
-        <v>381</v>
+        <v>333</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>382</v>
+        <v>334</v>
       </c>
       <c r="B157" t="s">
-        <v>383</v>
+        <v>335</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>384</v>
+        <v>336</v>
       </c>
       <c r="B158" t="s">
-        <v>385</v>
+        <v>337</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>386</v>
+        <v>338</v>
       </c>
       <c r="B159" t="s">
-        <v>387</v>
+        <v>339</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>388</v>
+        <v>340</v>
       </c>
       <c r="B160" t="s">
-        <v>389</v>
+        <v>341</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="B161" t="s">
-        <v>391</v>
+        <v>343</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>392</v>
+        <v>344</v>
       </c>
       <c r="B162" t="s">
-        <v>393</v>
+        <v>345</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="B163" t="s">
-        <v>395</v>
+        <v>347</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>396</v>
+        <v>348</v>
       </c>
       <c r="B164" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>398</v>
+        <v>350</v>
       </c>
       <c r="B165" t="s">
-        <v>399</v>
+        <v>351</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>400</v>
+        <v>352</v>
       </c>
       <c r="B166" t="s">
-        <v>373</v>
+        <v>325</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>401</v>
+        <v>353</v>
       </c>
       <c r="B167" t="s">
-        <v>355</v>
+        <v>307</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>402</v>
+        <v>354</v>
       </c>
       <c r="B168" t="s">
-        <v>357</v>
+        <v>309</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>403</v>
+        <v>355</v>
       </c>
       <c r="B169" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>404</v>
+        <v>356</v>
       </c>
       <c r="B170" t="s">
-        <v>405</v>
+        <v>357</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>406</v>
+        <v>358</v>
       </c>
       <c r="B171" t="s">
-        <v>407</v>
+        <v>359</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>408</v>
+        <v>360</v>
       </c>
       <c r="B172" t="s">
-        <v>409</v>
+        <v>361</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>410</v>
+        <v>362</v>
       </c>
       <c r="B173" t="s">
-        <v>411</v>
+        <v>363</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>412</v>
+        <v>364</v>
       </c>
       <c r="B174" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>413</v>
+        <v>365</v>
       </c>
       <c r="B175" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>414</v>
+        <v>366</v>
       </c>
       <c r="B176" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>415</v>
+        <v>367</v>
       </c>
       <c r="B177" t="s">
-        <v>367</v>
+        <v>319</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>416</v>
+        <v>368</v>
       </c>
       <c r="B178" t="s">
-        <v>351</v>
+        <v>303</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>417</v>
+        <v>369</v>
       </c>
       <c r="B179" t="s">
-        <v>418</v>
+        <v>370</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>419</v>
+        <v>371</v>
       </c>
       <c r="B180" t="s">
-        <v>355</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -3949,76 +4324,12 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>431</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -4028,12 +4339,479 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>432</v>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D5" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D6" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C7" t="s">
+        <v>384</v>
+      </c>
+      <c r="D7" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>387</v>
+      </c>
+      <c r="C9" t="s">
+        <v>357</v>
+      </c>
+      <c r="D9" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>388</v>
+      </c>
+      <c r="C10" t="s">
+        <v>389</v>
+      </c>
+      <c r="D10" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>390</v>
+      </c>
+      <c r="C11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C12" t="s">
+        <v>393</v>
+      </c>
+      <c r="D12" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" t="s">
+        <v>394</v>
+      </c>
+      <c r="C13" t="s">
+        <v>359</v>
+      </c>
+      <c r="D13" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" t="s">
+        <v>395</v>
+      </c>
+      <c r="C14" t="s">
+        <v>396</v>
+      </c>
+      <c r="D14" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>397</v>
+      </c>
+      <c r="C15" t="s">
+        <v>361</v>
+      </c>
+      <c r="D15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" t="s">
+        <v>398</v>
+      </c>
+      <c r="C16" t="s">
+        <v>363</v>
+      </c>
+      <c r="D16" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" t="s">
+        <v>399</v>
+      </c>
+      <c r="C17" t="s">
+        <v>400</v>
+      </c>
+      <c r="D17" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C18" t="s">
+        <v>305</v>
+      </c>
+      <c r="D18" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" t="s">
+        <v>402</v>
+      </c>
+      <c r="C19" t="s">
+        <v>303</v>
+      </c>
+      <c r="D19" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" t="s">
+        <v>403</v>
+      </c>
+      <c r="C20" t="s">
+        <v>404</v>
+      </c>
+      <c r="D20" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" t="s">
+        <v>405</v>
+      </c>
+      <c r="C21" t="s">
+        <v>406</v>
+      </c>
+      <c r="D21" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" t="s">
+        <v>407</v>
+      </c>
+      <c r="C22" t="s">
+        <v>408</v>
+      </c>
+      <c r="D22" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" t="s">
+        <v>409</v>
+      </c>
+      <c r="C23" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" t="s">
+        <v>410</v>
+      </c>
+      <c r="C24" t="s">
+        <v>411</v>
+      </c>
+      <c r="D24" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" t="s">
+        <v>412</v>
+      </c>
+      <c r="C25" t="s">
+        <v>277</v>
+      </c>
+      <c r="D25" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>413</v>
+      </c>
+      <c r="C26" t="s">
+        <v>279</v>
+      </c>
+      <c r="D26" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>414</v>
+      </c>
+      <c r="C27" t="s">
+        <v>370</v>
+      </c>
+      <c r="D27" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s">
+        <v>415</v>
+      </c>
+      <c r="C28" t="s">
+        <v>281</v>
+      </c>
+      <c r="D28" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>416</v>
+      </c>
+      <c r="C29" t="s">
+        <v>286</v>
+      </c>
+      <c r="D29" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>417</v>
+      </c>
+      <c r="C30" t="s">
+        <v>288</v>
+      </c>
+      <c r="D30" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" t="s">
+        <v>418</v>
+      </c>
+      <c r="C31" t="s">
+        <v>290</v>
+      </c>
+      <c r="D31" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" t="s">
+        <v>419</v>
+      </c>
+      <c r="C32" t="s">
+        <v>292</v>
+      </c>
+      <c r="D32" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>420</v>
+      </c>
+      <c r="C33" t="s">
+        <v>294</v>
+      </c>
+      <c r="D33" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" t="s">
+        <v>421</v>
+      </c>
+      <c r="C34" t="s">
+        <v>319</v>
+      </c>
+      <c r="D34" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" t="s">
+        <v>422</v>
+      </c>
+      <c r="C35" t="s">
+        <v>423</v>
+      </c>
+      <c r="D35" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" t="s">
+        <v>424</v>
+      </c>
+      <c r="C36" t="s">
+        <v>425</v>
+      </c>
+      <c r="D36" t="s">
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4043,46 +4821,12 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4092,458 +4836,482 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B5" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="B6" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="B7" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="B8" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B9" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="B10" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="B11" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B12" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B13" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="B14" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B15" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="B16" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="B17" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B18" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B19" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B20" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="B21" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="B22" t="s">
-        <v>427</v>
+        <v>460</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="B23" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B24" t="s">
-        <v>427</v>
+        <v>465</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B25" t="s">
-        <v>427</v>
+        <v>467</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B26" t="s">
-        <v>427</v>
+        <v>467</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B27" t="s">
-        <v>427</v>
+        <v>467</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B28" t="s">
-        <v>304</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B29" t="s">
-        <v>304</v>
+        <v>467</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B30" t="s">
-        <v>304</v>
+        <v>467</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B31" t="s">
-        <v>304</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B32" t="s">
-        <v>304</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B33" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B34" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B35" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B36" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B37" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B38" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B39" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B40" t="s">
-        <v>297</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B41" t="s">
-        <v>297</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B42" t="s">
-        <v>297</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B43" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B44" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B45" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B46" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B47" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B48" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B49" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B50" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B51" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B52" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B53" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B55" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B56" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B57" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B58" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B59" t="s">
-        <v>297</v>
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B60" t="s">
-        <v>297</v>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>503</v>
+      </c>
+      <c r="B61" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>504</v>
+      </c>
+      <c r="B62" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>505</v>
+      </c>
+      <c r="B63" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -4633,7 +5401,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4649,276 +5417,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4933,7 +5431,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4943,7 +5441,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -4958,7 +5456,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4973,282 +5471,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A67"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>127</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -30,16 +30,17 @@
     <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
     <sheet name="Project Summary" sheetId="22" r:id="rId22"/>
     <sheet name="Design Params and Codes" sheetId="23" r:id="rId23"/>
-    <sheet name="Register Summary" sheetId="24" r:id="rId24"/>
-    <sheet name="DFT Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="Nesto Usage Report" sheetId="26" r:id="rId26"/>
+    <sheet name="DRM Summary" sheetId="24" r:id="rId24"/>
+    <sheet name="Register Summary" sheetId="25" r:id="rId25"/>
+    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
+    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="607">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -131,10 +132,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -146,19 +147,388 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -279,139 +649,94 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>DRM Efficiency Summary</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
   </si>
   <si>
-    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
-    <t>DRM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
-  </si>
-  <si>
-    <t>DFT Efficiency</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
   </si>
   <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
+    <t>{'cells': 25, 'bytes': 25.0, 'noconns': 62, 'efficiency': '69.0%'}</t>
   </si>
   <si>
     <t>Project Summary</t>
@@ -624,231 +949,234 @@
     <t>workers</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>skip_serdes</t>
+  </si>
+  <si>
+    <t>Package</t>
+  </si>
+  <si>
+    <t>package_name</t>
+  </si>
+  <si>
+    <t>TDFN1232</t>
+  </si>
+  <si>
+    <t>package_size</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>downbond</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>project_reference</t>
+  </si>
+  <si>
+    <t>CELV</t>
+  </si>
+  <si>
+    <t>TaRoom</t>
+  </si>
+  <si>
+    <t>ground</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>CELGabsmax</t>
+  </si>
+  <si>
+    <t>CELGabsmin</t>
+  </si>
+  <si>
+    <t>SUBabsmax</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>SUBabsmin</t>
+  </si>
+  <si>
+    <t>-0.3</t>
+  </si>
+  <si>
+    <t>CELSUBabsmax</t>
+  </si>
+  <si>
+    <t>CELSUBabsmin</t>
+  </si>
+  <si>
+    <t>FETcalculator</t>
+  </si>
+  <si>
+    <t>chip_insert</t>
+  </si>
+  <si>
+    <t>design_revision</t>
+  </si>
+  <si>
+    <t>factory_revision</t>
+  </si>
+  <si>
+    <t>Register</t>
+  </si>
+  <si>
+    <t>registermap_security</t>
+  </si>
+  <si>
+    <t>registermap_reset</t>
+  </si>
+  <si>
+    <t>registermap_chipid</t>
+  </si>
+  <si>
+    <t>registermap_address</t>
+  </si>
+  <si>
+    <t>fixed</t>
+  </si>
+  <si>
+    <t>slave_address</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>register_address0</t>
+  </si>
+  <si>
+    <t>register_address1</t>
+  </si>
+  <si>
+    <t>register_address2</t>
+  </si>
+  <si>
+    <t>register_address3</t>
+  </si>
+  <si>
+    <t>register_address4</t>
+  </si>
+  <si>
+    <t>register_address5</t>
+  </si>
+  <si>
+    <t>register_address6</t>
+  </si>
+  <si>
+    <t>register_address7</t>
+  </si>
+  <si>
+    <t>start_address</t>
+  </si>
+  <si>
+    <t>0x0F</t>
+  </si>
+  <si>
+    <t>architecture</t>
+  </si>
+  <si>
+    <t>securitysequence_bool</t>
+  </si>
+  <si>
+    <t>security</t>
+  </si>
+  <si>
+    <t>registermap_password0</t>
+  </si>
+  <si>
+    <t>registermap_password1</t>
+  </si>
+  <si>
+    <t>registermap_password2</t>
+  </si>
+  <si>
+    <t>registermap_password3</t>
+  </si>
+  <si>
+    <t>registermap_chipid_lsb</t>
+  </si>
+  <si>
+    <t>registermap_chipid_msb</t>
+  </si>
+  <si>
+    <t>registermap_factoryid</t>
+  </si>
+  <si>
+    <t>registermap_revision</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>register_software_reset</t>
+  </si>
+  <si>
+    <t>register_vmax</t>
+  </si>
+  <si>
+    <t>Vanguard</t>
+  </si>
+  <si>
+    <t>PROJECTbg</t>
+  </si>
+  <si>
+    <t>1.198</t>
+  </si>
+  <si>
+    <t>REFERENCEccpcode</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>REFERENCEccncode</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>HVNPN21_5vbe</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>HVNPN21_5vbetc</t>
+  </si>
+  <si>
+    <t>-2.1</t>
+  </si>
+  <si>
+    <t>VTNnch5i</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>MODULEdiesizefill</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>leveloffset</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>skip_serdes</t>
-  </si>
-  <si>
-    <t>Package</t>
-  </si>
-  <si>
-    <t>package_name</t>
-  </si>
-  <si>
-    <t>TDFN1232</t>
-  </si>
-  <si>
-    <t>package_size</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>downbond</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>project</t>
-  </si>
-  <si>
-    <t>project_reference</t>
-  </si>
-  <si>
-    <t>CELV</t>
-  </si>
-  <si>
-    <t>TaRoom</t>
-  </si>
-  <si>
-    <t>ground</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>CELGabsmax</t>
-  </si>
-  <si>
-    <t>CELGabsmin</t>
-  </si>
-  <si>
-    <t>SUBabsmax</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>SUBabsmin</t>
-  </si>
-  <si>
-    <t>-0.3</t>
-  </si>
-  <si>
-    <t>CELSUBabsmax</t>
-  </si>
-  <si>
-    <t>CELSUBabsmin</t>
-  </si>
-  <si>
-    <t>FETcalculator</t>
-  </si>
-  <si>
-    <t>chip_insert</t>
-  </si>
-  <si>
-    <t>design_revision</t>
-  </si>
-  <si>
-    <t>factory_revision</t>
-  </si>
-  <si>
-    <t>Register</t>
-  </si>
-  <si>
-    <t>registermap_security</t>
-  </si>
-  <si>
-    <t>registermap_reset</t>
-  </si>
-  <si>
-    <t>registermap_chipid</t>
-  </si>
-  <si>
-    <t>registermap_address</t>
-  </si>
-  <si>
-    <t>fixed</t>
-  </si>
-  <si>
-    <t>slave_address</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>register_address0</t>
-  </si>
-  <si>
-    <t>register_address1</t>
-  </si>
-  <si>
-    <t>register_address2</t>
-  </si>
-  <si>
-    <t>register_address3</t>
-  </si>
-  <si>
-    <t>register_address4</t>
-  </si>
-  <si>
-    <t>register_address5</t>
-  </si>
-  <si>
-    <t>register_address6</t>
-  </si>
-  <si>
-    <t>register_address7</t>
-  </si>
-  <si>
-    <t>start_address</t>
-  </si>
-  <si>
-    <t>0x0F</t>
-  </si>
-  <si>
-    <t>architecture</t>
-  </si>
-  <si>
-    <t>securitysequence_bool</t>
-  </si>
-  <si>
-    <t>security</t>
-  </si>
-  <si>
-    <t>registermap_password0</t>
-  </si>
-  <si>
-    <t>registermap_password1</t>
-  </si>
-  <si>
-    <t>registermap_password2</t>
-  </si>
-  <si>
-    <t>registermap_password3</t>
-  </si>
-  <si>
-    <t>registermap_chipid_lsb</t>
-  </si>
-  <si>
-    <t>registermap_chipid_msb</t>
-  </si>
-  <si>
-    <t>registermap_factoryid</t>
-  </si>
-  <si>
-    <t>registermap_revision</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>register_software_reset</t>
-  </si>
-  <si>
-    <t>register_vmax</t>
-  </si>
-  <si>
-    <t>Vanguard</t>
-  </si>
-  <si>
-    <t>PROJECTbg</t>
-  </si>
-  <si>
-    <t>1.198</t>
-  </si>
-  <si>
-    <t>REFERENCEccpcode</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>REFERENCEccncode</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>HVNPN21_5vbe</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>HVNPN21_5vbetc</t>
-  </si>
-  <si>
-    <t>-2.1</t>
-  </si>
-  <si>
-    <t>VTNnch5i</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>MODULEdiesizefill</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>leveloffset</t>
-  </si>
-  <si>
     <t>DefaultAddresses</t>
   </si>
   <si>
@@ -1161,27 +1489,51 @@
     <t>measure_reset_command</t>
   </si>
   <si>
+    <t>DRM Summary</t>
+  </si>
+  <si>
+    <t>Addresses</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Instance</t>
+  </si>
+  <si>
+    <t>TMB</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>DRM to Memory Check</t>
+  </si>
+  <si>
+    <t>TOTAL dec</t>
+  </si>
+  <si>
+    <t>Allowed &lt;= 61</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
     <t>Register Summary</t>
   </si>
   <si>
     <t>DFT Summary</t>
   </si>
   <si>
-    <t>Addresses</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Instance</t>
-  </si>
-  <si>
     <t>TMA</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>dft_hex0x01</t>
   </si>
   <si>
@@ -1194,12 +1546,6 @@
     <t>DFTtm8t</t>
   </si>
   <si>
-    <t>dft_hex0x1A</t>
-  </si>
-  <si>
-    <t>0x1A</t>
-  </si>
-  <si>
     <t>dft_hex0x03</t>
   </si>
   <si>
@@ -1230,12 +1576,6 @@
     <t>dft_hex0x08</t>
   </si>
   <si>
-    <t>dft_hex0x1B</t>
-  </si>
-  <si>
-    <t>0x1B</t>
-  </si>
-  <si>
     <t>dft_hex0x09</t>
   </si>
   <si>
@@ -1251,15 +1591,6 @@
     <t>dft_hex0x0C</t>
   </si>
   <si>
-    <t>dft_hex0x1C</t>
-  </si>
-  <si>
-    <t>dft_hex0x1D</t>
-  </si>
-  <si>
-    <t>0x1D</t>
-  </si>
-  <si>
     <t>dft_hex0x0D</t>
   </si>
   <si>
@@ -1275,21 +1606,12 @@
     <t>dft_hex0x0F</t>
   </si>
   <si>
-    <t>dft_hex0x1E</t>
-  </si>
-  <si>
-    <t>0x1E</t>
-  </si>
-  <si>
     <t>dft_hex0x10</t>
   </si>
   <si>
     <t>dft_hex0x11</t>
   </si>
   <si>
-    <t>dft_hex0x1F</t>
-  </si>
-  <si>
     <t>dft_hex0x12</t>
   </si>
   <si>
@@ -1311,12 +1633,6 @@
     <t>dft_hex0x18</t>
   </si>
   <si>
-    <t>dft_hex0x20</t>
-  </si>
-  <si>
-    <t>0x20</t>
-  </si>
-  <si>
     <t>dft_hex0x19</t>
   </si>
   <si>
@@ -1338,36 +1654,33 @@
     <t>1082</t>
   </si>
   <si>
+    <t>inv</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>dbuf</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>noconn</t>
   </si>
   <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>inv</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>dbuf</t>
-  </si>
-  <si>
-    <t>122</t>
+    <t>107</t>
   </si>
   <si>
     <t>nor3</t>
   </si>
   <si>
-    <t>61</t>
-  </si>
-  <si>
     <t>dftprobeModel0</t>
   </si>
   <si>
@@ -1404,24 +1717,15 @@
     <t>dftmodule</t>
   </si>
   <si>
-    <t>32</t>
+    <t>25</t>
   </si>
   <si>
     <t>dfthijack</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>dff</t>
   </si>
   <si>
-    <t>drmmodule</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>tie</t>
   </si>
   <si>
@@ -1440,15 +1744,12 @@
     <t>dftprobeModel2</t>
   </si>
   <si>
-    <t>7</t>
+    <t>PEBBLEtielo</t>
   </si>
   <si>
     <t>resistor</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>oneshot</t>
   </si>
   <si>
@@ -1498,6 +1799,9 @@
   </si>
   <si>
     <t>capacitorfixed</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>voltage2current</t>
@@ -1931,7 +2235,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1951,7 +2255,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1966,7 +2270,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -1981,17 +2285,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2006,12 +2310,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2026,17 +2330,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2051,12 +2355,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2071,7 +2375,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2091,127 +2395,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>75</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2221,162 +2525,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2391,17 +2550,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2621,257 +2780,222 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>100</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>78</v>
+      <c r="A7" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
+      <c r="A10" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>85</v>
+      <c r="A14" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>107</v>
+      <c r="A17" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>109</v>
+      <c r="A21" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>110</v>
+      <c r="A23" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>111</v>
+      <c r="A26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>113</v>
+      <c r="A29" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>88</v>
+      <c r="A32" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>114</v>
+        <v>221</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>115</v>
+      <c r="A39" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>117</v>
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>118</v>
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>108</v>
+      <c r="A48" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>105</v>
+      <c r="A51" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>117</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>110</v>
+      <c r="A55" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>101</v>
+      <c r="A58" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>103</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2886,17 +3010,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2911,52 +3035,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>130</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -2971,81 +3095,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>134</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>245</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>247</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>249</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>142</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>251</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>147</v>
+        <v>255</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>256</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3053,1268 +3177,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>150</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>151</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>153</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>154</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>155</v>
+        <v>263</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>264</v>
       </c>
       <c r="B21" t="s">
-        <v>138</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>157</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>159</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>161</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>162</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s">
-        <v>163</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>165</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>166</v>
+        <v>274</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>168</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s">
-        <v>169</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>170</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>172</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s">
-        <v>173</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>174</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s">
-        <v>175</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>177</v>
+        <v>285</v>
       </c>
       <c r="B38" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="B39" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>180</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>181</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>182</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>183</v>
+        <v>291</v>
       </c>
       <c r="B43" t="s">
-        <v>184</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>185</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>294</v>
       </c>
       <c r="B46" t="s">
-        <v>187</v>
+        <v>295</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>188</v>
+        <v>296</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>189</v>
+        <v>297</v>
       </c>
       <c r="B48" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>190</v>
+        <v>298</v>
       </c>
       <c r="B49" t="s">
-        <v>138</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>191</v>
+        <v>299</v>
       </c>
       <c r="B50" t="s">
-        <v>138</v>
+        <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>192</v>
+        <v>300</v>
       </c>
       <c r="B51" t="s">
-        <v>193</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>194</v>
+        <v>302</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>195</v>
+        <v>303</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>196</v>
+        <v>304</v>
       </c>
       <c r="B55" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>198</v>
+        <v>306</v>
       </c>
       <c r="B56" t="s">
-        <v>199</v>
+        <v>307</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>200</v>
+        <v>308</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>201</v>
+        <v>309</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>202</v>
+        <v>310</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>203</v>
+        <v>311</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>312</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>205</v>
+        <v>313</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>206</v>
+        <v>314</v>
       </c>
       <c r="B64" t="s">
-        <v>207</v>
+        <v>315</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>208</v>
+        <v>316</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>209</v>
+        <v>317</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>210</v>
+        <v>318</v>
       </c>
       <c r="B67" t="s">
-        <v>211</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>212</v>
+        <v>320</v>
       </c>
       <c r="B68" t="s">
-        <v>213</v>
+        <v>321</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>214</v>
+        <v>322</v>
       </c>
       <c r="B69" t="s">
-        <v>211</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>215</v>
+        <v>323</v>
       </c>
       <c r="B70" t="s">
-        <v>213</v>
+        <v>321</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>216</v>
+        <v>324</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>217</v>
+        <v>325</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>218</v>
+        <v>326</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>219</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>220</v>
+        <v>328</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>221</v>
+        <v>329</v>
       </c>
       <c r="B77" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>222</v>
+        <v>330</v>
       </c>
       <c r="B78" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>223</v>
+        <v>331</v>
       </c>
       <c r="B79" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>224</v>
+        <v>332</v>
       </c>
       <c r="B80" t="s">
-        <v>225</v>
+        <v>333</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>226</v>
+        <v>334</v>
       </c>
       <c r="B81" t="s">
-        <v>227</v>
+        <v>335</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>228</v>
+        <v>336</v>
       </c>
       <c r="B82" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>229</v>
+        <v>337</v>
       </c>
       <c r="B83" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>230</v>
+        <v>338</v>
       </c>
       <c r="B84" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>231</v>
+        <v>339</v>
       </c>
       <c r="B85" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>232</v>
+        <v>340</v>
       </c>
       <c r="B86" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>233</v>
+        <v>341</v>
       </c>
       <c r="B87" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>234</v>
+        <v>342</v>
       </c>
       <c r="B88" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>235</v>
+        <v>343</v>
       </c>
       <c r="B89" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>236</v>
+        <v>344</v>
       </c>
       <c r="B90" t="s">
-        <v>237</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>238</v>
+        <v>346</v>
       </c>
       <c r="B91" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>239</v>
+        <v>347</v>
       </c>
       <c r="B92" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>240</v>
+        <v>348</v>
       </c>
       <c r="B93" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>241</v>
+        <v>349</v>
       </c>
       <c r="B94" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>242</v>
+        <v>350</v>
       </c>
       <c r="B95" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="B96" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>244</v>
+        <v>352</v>
       </c>
       <c r="B97" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>245</v>
+        <v>353</v>
       </c>
       <c r="B98" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>246</v>
+        <v>354</v>
       </c>
       <c r="B99" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>247</v>
+        <v>355</v>
       </c>
       <c r="B100" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>248</v>
+        <v>356</v>
       </c>
       <c r="B101" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>250</v>
+        <v>358</v>
       </c>
       <c r="B102" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>251</v>
+        <v>359</v>
       </c>
       <c r="B103" t="s">
-        <v>171</v>
+        <v>279</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>252</v>
+        <v>360</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>253</v>
+        <v>361</v>
       </c>
       <c r="B106" t="s">
-        <v>254</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>255</v>
+        <v>363</v>
       </c>
       <c r="B107" t="s">
-        <v>256</v>
+        <v>364</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>257</v>
+        <v>365</v>
       </c>
       <c r="B108" t="s">
-        <v>258</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>259</v>
+        <v>367</v>
       </c>
       <c r="B109" t="s">
-        <v>260</v>
+        <v>368</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>261</v>
+        <v>369</v>
       </c>
       <c r="B110" t="s">
-        <v>262</v>
+        <v>370</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>263</v>
+        <v>371</v>
       </c>
       <c r="B111" t="s">
-        <v>264</v>
+        <v>372</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>265</v>
+        <v>373</v>
       </c>
       <c r="B112" t="s">
-        <v>266</v>
+        <v>374</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>267</v>
+        <v>375</v>
       </c>
       <c r="B113" t="s">
-        <v>193</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>268</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>136</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>269</v>
+        <v>378</v>
       </c>
       <c r="B116" t="s">
-        <v>184</v>
+        <v>292</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>270</v>
+        <v>379</v>
       </c>
       <c r="B117" t="s">
-        <v>271</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>272</v>
+        <v>381</v>
       </c>
       <c r="B118" t="s">
-        <v>273</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>274</v>
+        <v>383</v>
       </c>
       <c r="B119" t="s">
-        <v>275</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>276</v>
+        <v>385</v>
       </c>
       <c r="B120" t="s">
-        <v>277</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>278</v>
+        <v>387</v>
       </c>
       <c r="B121" t="s">
-        <v>279</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>280</v>
+        <v>389</v>
       </c>
       <c r="B122" t="s">
-        <v>281</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>282</v>
+        <v>391</v>
       </c>
       <c r="B123" t="s">
-        <v>277</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>283</v>
+        <v>392</v>
       </c>
       <c r="B124" t="s">
-        <v>279</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>284</v>
+        <v>393</v>
       </c>
       <c r="B125" t="s">
-        <v>281</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>285</v>
+        <v>394</v>
       </c>
       <c r="B126" t="s">
-        <v>286</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>287</v>
+        <v>396</v>
       </c>
       <c r="B127" t="s">
-        <v>288</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>289</v>
+        <v>398</v>
       </c>
       <c r="B128" t="s">
-        <v>290</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>291</v>
+        <v>400</v>
       </c>
       <c r="B129" t="s">
-        <v>292</v>
+        <v>401</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>293</v>
+        <v>402</v>
       </c>
       <c r="B130" t="s">
-        <v>294</v>
+        <v>403</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>245</v>
+        <v>353</v>
       </c>
       <c r="B131" t="s">
-        <v>295</v>
+        <v>404</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>246</v>
+        <v>354</v>
       </c>
       <c r="B132" t="s">
-        <v>296</v>
+        <v>405</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>248</v>
+        <v>356</v>
       </c>
       <c r="B133" t="s">
-        <v>297</v>
+        <v>406</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>247</v>
+        <v>355</v>
       </c>
       <c r="B134" t="s">
-        <v>298</v>
+        <v>407</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>299</v>
+        <v>408</v>
       </c>
       <c r="B135" t="s">
-        <v>184</v>
+        <v>292</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>300</v>
+        <v>409</v>
       </c>
       <c r="B136" t="s">
-        <v>301</v>
+        <v>410</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>302</v>
+        <v>411</v>
       </c>
       <c r="B137" t="s">
-        <v>303</v>
+        <v>412</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>304</v>
+        <v>413</v>
       </c>
       <c r="B138" t="s">
-        <v>305</v>
+        <v>414</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>306</v>
+        <v>415</v>
       </c>
       <c r="B139" t="s">
-        <v>307</v>
+        <v>416</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>308</v>
+        <v>417</v>
       </c>
       <c r="B140" t="s">
-        <v>309</v>
+        <v>418</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>310</v>
+        <v>419</v>
       </c>
       <c r="B141" t="s">
-        <v>277</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>311</v>
+        <v>420</v>
       </c>
       <c r="B142" t="s">
-        <v>279</v>
+        <v>388</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>312</v>
+        <v>421</v>
       </c>
       <c r="B143" t="s">
-        <v>281</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>313</v>
+        <v>422</v>
       </c>
       <c r="B144" t="s">
-        <v>286</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>314</v>
+        <v>423</v>
       </c>
       <c r="B145" t="s">
-        <v>288</v>
+        <v>397</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>315</v>
+        <v>424</v>
       </c>
       <c r="B146" t="s">
-        <v>290</v>
+        <v>399</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>316</v>
+        <v>425</v>
       </c>
       <c r="B147" t="s">
-        <v>292</v>
+        <v>401</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>317</v>
+        <v>426</v>
       </c>
       <c r="B148" t="s">
-        <v>294</v>
+        <v>403</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>318</v>
+        <v>427</v>
       </c>
       <c r="B149" t="s">
-        <v>319</v>
+        <v>428</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>320</v>
+        <v>429</v>
       </c>
       <c r="B150" t="s">
-        <v>321</v>
+        <v>430</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>322</v>
+        <v>431</v>
       </c>
       <c r="B151" t="s">
-        <v>323</v>
+        <v>432</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>324</v>
+        <v>433</v>
       </c>
       <c r="B152" t="s">
-        <v>325</v>
+        <v>434</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>326</v>
+        <v>435</v>
       </c>
       <c r="B153" t="s">
-        <v>327</v>
+        <v>436</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>328</v>
+        <v>437</v>
       </c>
       <c r="B154" t="s">
-        <v>329</v>
+        <v>438</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>330</v>
+        <v>439</v>
       </c>
       <c r="B155" t="s">
-        <v>331</v>
+        <v>440</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>332</v>
+        <v>441</v>
       </c>
       <c r="B156" t="s">
-        <v>333</v>
+        <v>442</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>334</v>
+        <v>443</v>
       </c>
       <c r="B157" t="s">
-        <v>335</v>
+        <v>444</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>336</v>
+        <v>445</v>
       </c>
       <c r="B158" t="s">
-        <v>337</v>
+        <v>446</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>338</v>
+        <v>447</v>
       </c>
       <c r="B159" t="s">
-        <v>339</v>
+        <v>448</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>340</v>
+        <v>449</v>
       </c>
       <c r="B160" t="s">
-        <v>341</v>
+        <v>450</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>342</v>
+        <v>451</v>
       </c>
       <c r="B161" t="s">
-        <v>343</v>
+        <v>452</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>344</v>
+        <v>453</v>
       </c>
       <c r="B162" t="s">
-        <v>345</v>
+        <v>454</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>346</v>
+        <v>455</v>
       </c>
       <c r="B163" t="s">
-        <v>347</v>
+        <v>456</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>348</v>
+        <v>457</v>
       </c>
       <c r="B164" t="s">
-        <v>349</v>
+        <v>458</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>350</v>
+        <v>459</v>
       </c>
       <c r="B165" t="s">
-        <v>351</v>
+        <v>460</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>352</v>
+        <v>461</v>
       </c>
       <c r="B166" t="s">
-        <v>325</v>
+        <v>434</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>353</v>
+        <v>462</v>
       </c>
       <c r="B167" t="s">
-        <v>307</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>354</v>
+        <v>463</v>
       </c>
       <c r="B168" t="s">
-        <v>309</v>
+        <v>418</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>355</v>
+        <v>464</v>
       </c>
       <c r="B169" t="s">
-        <v>167</v>
+        <v>275</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>356</v>
+        <v>465</v>
       </c>
       <c r="B170" t="s">
-        <v>357</v>
+        <v>466</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>358</v>
+        <v>467</v>
       </c>
       <c r="B171" t="s">
-        <v>359</v>
+        <v>468</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>360</v>
+        <v>469</v>
       </c>
       <c r="B172" t="s">
-        <v>361</v>
+        <v>470</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>362</v>
+        <v>471</v>
       </c>
       <c r="B173" t="s">
-        <v>363</v>
+        <v>472</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>364</v>
+        <v>473</v>
       </c>
       <c r="B174" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>365</v>
+        <v>474</v>
       </c>
       <c r="B175" t="s">
-        <v>277</v>
+        <v>386</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>366</v>
+        <v>475</v>
       </c>
       <c r="B176" t="s">
-        <v>279</v>
+        <v>388</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>367</v>
+        <v>476</v>
       </c>
       <c r="B177" t="s">
-        <v>319</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>368</v>
+        <v>477</v>
       </c>
       <c r="B178" t="s">
-        <v>303</v>
+        <v>412</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>369</v>
+        <v>478</v>
       </c>
       <c r="B179" t="s">
-        <v>370</v>
+        <v>479</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>371</v>
+        <v>480</v>
       </c>
       <c r="B180" t="s">
-        <v>307</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -4324,12 +4448,76 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -4339,479 +4527,12 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" t="s">
-        <v>379</v>
-      </c>
-      <c r="C5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D5" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" t="s">
-        <v>381</v>
-      </c>
-      <c r="C6" t="s">
-        <v>309</v>
-      </c>
-      <c r="D6" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" t="s">
-        <v>383</v>
-      </c>
-      <c r="C7" t="s">
-        <v>384</v>
-      </c>
-      <c r="D7" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" t="s">
-        <v>385</v>
-      </c>
-      <c r="C8" t="s">
-        <v>167</v>
-      </c>
-      <c r="D8" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>387</v>
-      </c>
-      <c r="C9" t="s">
-        <v>357</v>
-      </c>
-      <c r="D9" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>388</v>
-      </c>
-      <c r="C10" t="s">
-        <v>389</v>
-      </c>
-      <c r="D10" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" t="s">
-        <v>390</v>
-      </c>
-      <c r="C11" t="s">
-        <v>391</v>
-      </c>
-      <c r="D11" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" t="s">
-        <v>392</v>
-      </c>
-      <c r="C12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D12" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" t="s">
-        <v>394</v>
-      </c>
-      <c r="C13" t="s">
-        <v>359</v>
-      </c>
-      <c r="D13" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" t="s">
-        <v>395</v>
-      </c>
-      <c r="C14" t="s">
-        <v>396</v>
-      </c>
-      <c r="D14" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>397</v>
-      </c>
-      <c r="C15" t="s">
-        <v>361</v>
-      </c>
-      <c r="D15" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" t="s">
-        <v>398</v>
-      </c>
-      <c r="C16" t="s">
-        <v>363</v>
-      </c>
-      <c r="D16" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>111</v>
-      </c>
-      <c r="B17" t="s">
-        <v>399</v>
-      </c>
-      <c r="C17" t="s">
-        <v>400</v>
-      </c>
-      <c r="D17" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" t="s">
-        <v>401</v>
-      </c>
-      <c r="C18" t="s">
-        <v>305</v>
-      </c>
-      <c r="D18" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" t="s">
-        <v>402</v>
-      </c>
-      <c r="C19" t="s">
-        <v>303</v>
-      </c>
-      <c r="D19" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" t="s">
-        <v>403</v>
-      </c>
-      <c r="C20" t="s">
-        <v>404</v>
-      </c>
-      <c r="D20" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" t="s">
-        <v>405</v>
-      </c>
-      <c r="C21" t="s">
-        <v>406</v>
-      </c>
-      <c r="D21" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" t="s">
-        <v>407</v>
-      </c>
-      <c r="C22" t="s">
-        <v>408</v>
-      </c>
-      <c r="D22" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>114</v>
-      </c>
-      <c r="B23" t="s">
-        <v>409</v>
-      </c>
-      <c r="C23" t="s">
-        <v>237</v>
-      </c>
-      <c r="D23" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>114</v>
-      </c>
-      <c r="B24" t="s">
-        <v>410</v>
-      </c>
-      <c r="C24" t="s">
-        <v>411</v>
-      </c>
-      <c r="D24" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>116</v>
-      </c>
-      <c r="B25" t="s">
-        <v>412</v>
-      </c>
-      <c r="C25" t="s">
-        <v>277</v>
-      </c>
-      <c r="D25" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" t="s">
-        <v>413</v>
-      </c>
-      <c r="C26" t="s">
-        <v>279</v>
-      </c>
-      <c r="D26" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" t="s">
-        <v>414</v>
-      </c>
-      <c r="C27" t="s">
-        <v>370</v>
-      </c>
-      <c r="D27" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>92</v>
-      </c>
-      <c r="B28" t="s">
-        <v>415</v>
-      </c>
-      <c r="C28" t="s">
-        <v>281</v>
-      </c>
-      <c r="D28" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
-        <v>416</v>
-      </c>
-      <c r="C29" t="s">
-        <v>286</v>
-      </c>
-      <c r="D29" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" t="s">
-        <v>417</v>
-      </c>
-      <c r="C30" t="s">
-        <v>288</v>
-      </c>
-      <c r="D30" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>119</v>
-      </c>
-      <c r="B31" t="s">
-        <v>418</v>
-      </c>
-      <c r="C31" t="s">
-        <v>290</v>
-      </c>
-      <c r="D31" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" t="s">
-        <v>419</v>
-      </c>
-      <c r="C32" t="s">
-        <v>292</v>
-      </c>
-      <c r="D32" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" t="s">
-        <v>420</v>
-      </c>
-      <c r="C33" t="s">
-        <v>294</v>
-      </c>
-      <c r="D33" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>120</v>
-      </c>
-      <c r="B34" t="s">
-        <v>421</v>
-      </c>
-      <c r="C34" t="s">
-        <v>319</v>
-      </c>
-      <c r="D34" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>120</v>
-      </c>
-      <c r="B35" t="s">
-        <v>422</v>
-      </c>
-      <c r="C35" t="s">
-        <v>423</v>
-      </c>
-      <c r="D35" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" t="s">
-        <v>424</v>
-      </c>
-      <c r="C36" t="s">
-        <v>425</v>
-      </c>
-      <c r="D36" t="s">
-        <v>382</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -4821,12 +4542,396 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" t="s">
+        <v>496</v>
+      </c>
+      <c r="C5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" t="s">
+        <v>498</v>
+      </c>
+      <c r="C6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" t="s">
+        <v>500</v>
+      </c>
+      <c r="C7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D7" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>502</v>
+      </c>
+      <c r="C8" t="s">
+        <v>466</v>
+      </c>
+      <c r="D8" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>503</v>
+      </c>
+      <c r="C9" t="s">
+        <v>504</v>
+      </c>
+      <c r="D9" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" t="s">
+        <v>505</v>
+      </c>
+      <c r="C10" t="s">
+        <v>506</v>
+      </c>
+      <c r="D10" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11" t="s">
+        <v>507</v>
+      </c>
+      <c r="C11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D11" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" t="s">
+        <v>509</v>
+      </c>
+      <c r="C12" t="s">
+        <v>468</v>
+      </c>
+      <c r="D12" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>510</v>
+      </c>
+      <c r="C13" t="s">
+        <v>470</v>
+      </c>
+      <c r="D13" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B14" t="s">
+        <v>511</v>
+      </c>
+      <c r="C14" t="s">
+        <v>472</v>
+      </c>
+      <c r="D14" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" t="s">
+        <v>512</v>
+      </c>
+      <c r="C15" t="s">
+        <v>513</v>
+      </c>
+      <c r="D15" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" t="s">
+        <v>514</v>
+      </c>
+      <c r="C16" t="s">
+        <v>414</v>
+      </c>
+      <c r="D16" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" t="s">
+        <v>515</v>
+      </c>
+      <c r="C17" t="s">
+        <v>516</v>
+      </c>
+      <c r="D17" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>220</v>
+      </c>
+      <c r="B18" t="s">
+        <v>517</v>
+      </c>
+      <c r="C18" t="s">
+        <v>518</v>
+      </c>
+      <c r="D18" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" t="s">
+        <v>519</v>
+      </c>
+      <c r="C19" t="s">
+        <v>345</v>
+      </c>
+      <c r="D19" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>221</v>
+      </c>
+      <c r="B20" t="s">
+        <v>520</v>
+      </c>
+      <c r="C20" t="s">
+        <v>386</v>
+      </c>
+      <c r="D20" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C21" t="s">
+        <v>388</v>
+      </c>
+      <c r="D21" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" t="s">
+        <v>522</v>
+      </c>
+      <c r="C22" t="s">
+        <v>390</v>
+      </c>
+      <c r="D22" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>523</v>
+      </c>
+      <c r="C23" t="s">
+        <v>395</v>
+      </c>
+      <c r="D23" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>524</v>
+      </c>
+      <c r="C24" t="s">
+        <v>397</v>
+      </c>
+      <c r="D24" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25" t="s">
+        <v>525</v>
+      </c>
+      <c r="C25" t="s">
+        <v>399</v>
+      </c>
+      <c r="D25" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" t="s">
+        <v>526</v>
+      </c>
+      <c r="C26" t="s">
+        <v>401</v>
+      </c>
+      <c r="D26" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" t="s">
+        <v>527</v>
+      </c>
+      <c r="C27" t="s">
+        <v>403</v>
+      </c>
+      <c r="D27" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>228</v>
+      </c>
+      <c r="B28" t="s">
+        <v>528</v>
+      </c>
+      <c r="C28" t="s">
+        <v>428</v>
+      </c>
+      <c r="D28" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>167</v>
+      </c>
+      <c r="B29" t="s">
+        <v>529</v>
+      </c>
+      <c r="C29" t="s">
+        <v>530</v>
+      </c>
+      <c r="D29" t="s">
+        <v>499</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4836,482 +4941,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>427</v>
+        <v>532</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>428</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>429</v>
+        <v>534</v>
       </c>
       <c r="B5" t="s">
-        <v>430</v>
+        <v>535</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>431</v>
+        <v>536</v>
       </c>
       <c r="B6" t="s">
-        <v>432</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>433</v>
+        <v>538</v>
       </c>
       <c r="B7" t="s">
-        <v>434</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>435</v>
+        <v>540</v>
       </c>
       <c r="B8" t="s">
-        <v>436</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>437</v>
+        <v>542</v>
       </c>
       <c r="B9" t="s">
-        <v>438</v>
+        <v>543</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>439</v>
+        <v>544</v>
       </c>
       <c r="B10" t="s">
-        <v>440</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>441</v>
+        <v>545</v>
       </c>
       <c r="B11" t="s">
-        <v>440</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>442</v>
+        <v>546</v>
       </c>
       <c r="B12" t="s">
-        <v>443</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>444</v>
+        <v>548</v>
       </c>
       <c r="B13" t="s">
-        <v>445</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>446</v>
+        <v>550</v>
       </c>
       <c r="B14" t="s">
-        <v>447</v>
+        <v>551</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>448</v>
+        <v>552</v>
       </c>
       <c r="B15" t="s">
-        <v>449</v>
+        <v>553</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>450</v>
+        <v>554</v>
       </c>
       <c r="B16" t="s">
-        <v>451</v>
+        <v>555</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>452</v>
+        <v>556</v>
       </c>
       <c r="B17" t="s">
-        <v>453</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>454</v>
+        <v>558</v>
       </c>
       <c r="B18" t="s">
-        <v>455</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>456</v>
+        <v>559</v>
       </c>
       <c r="B19" t="s">
-        <v>455</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>457</v>
+        <v>560</v>
       </c>
       <c r="B20" t="s">
-        <v>458</v>
+        <v>561</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>459</v>
+        <v>562</v>
       </c>
       <c r="B21" t="s">
-        <v>460</v>
+        <v>561</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>461</v>
+        <v>563</v>
       </c>
       <c r="B22" t="s">
-        <v>460</v>
+        <v>564</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>462</v>
+        <v>565</v>
       </c>
       <c r="B23" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>464</v>
+        <v>566</v>
       </c>
       <c r="B24" t="s">
-        <v>465</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>466</v>
+        <v>567</v>
       </c>
       <c r="B25" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>468</v>
+        <v>568</v>
       </c>
       <c r="B26" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>469</v>
+        <v>569</v>
       </c>
       <c r="B27" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>470</v>
+        <v>570</v>
       </c>
       <c r="B28" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>471</v>
+        <v>571</v>
       </c>
       <c r="B29" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>472</v>
+        <v>572</v>
       </c>
       <c r="B30" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>473</v>
+        <v>573</v>
       </c>
       <c r="B31" t="s">
-        <v>256</v>
+        <v>364</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>474</v>
+        <v>574</v>
       </c>
       <c r="B32" t="s">
-        <v>256</v>
+        <v>364</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>475</v>
+        <v>575</v>
       </c>
       <c r="B33" t="s">
-        <v>256</v>
+        <v>364</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>476</v>
+        <v>576</v>
       </c>
       <c r="B34" t="s">
-        <v>256</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>477</v>
+        <v>577</v>
       </c>
       <c r="B35" t="s">
-        <v>256</v>
+        <v>364</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>478</v>
+        <v>578</v>
       </c>
       <c r="B36" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>479</v>
+        <v>579</v>
       </c>
       <c r="B37" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>480</v>
+        <v>580</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>481</v>
+        <v>581</v>
       </c>
       <c r="B39" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>482</v>
+        <v>582</v>
       </c>
       <c r="B40" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>483</v>
+        <v>583</v>
       </c>
       <c r="B41" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>484</v>
+        <v>584</v>
       </c>
       <c r="B42" t="s">
-        <v>179</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>485</v>
+        <v>585</v>
       </c>
       <c r="B43" t="s">
-        <v>249</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>486</v>
+        <v>586</v>
       </c>
       <c r="B44" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>487</v>
+        <v>587</v>
       </c>
       <c r="B45" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>488</v>
+        <v>588</v>
       </c>
       <c r="B46" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>489</v>
+        <v>589</v>
       </c>
       <c r="B47" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>490</v>
+        <v>590</v>
       </c>
       <c r="B48" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>491</v>
+        <v>591</v>
       </c>
       <c r="B49" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>492</v>
+        <v>592</v>
       </c>
       <c r="B50" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>493</v>
+        <v>593</v>
       </c>
       <c r="B51" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>494</v>
+        <v>594</v>
       </c>
       <c r="B52" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>495</v>
+        <v>595</v>
       </c>
       <c r="B53" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>496</v>
+        <v>596</v>
       </c>
       <c r="B54" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>497</v>
+        <v>597</v>
       </c>
       <c r="B55" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>498</v>
+        <v>598</v>
       </c>
       <c r="B56" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>499</v>
+        <v>599</v>
       </c>
       <c r="B57" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="B58" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>501</v>
+        <v>601</v>
       </c>
       <c r="B59" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>502</v>
+        <v>602</v>
       </c>
       <c r="B60" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>503</v>
+        <v>603</v>
       </c>
       <c r="B61" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>504</v>
+        <v>604</v>
       </c>
       <c r="B62" t="s">
-        <v>249</v>
+        <v>357</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>505</v>
+        <v>605</v>
       </c>
       <c r="B63" t="s">
-        <v>249</v>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>606</v>
+      </c>
+      <c r="B64" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -5401,7 +5514,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -5417,6 +5530,326 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -5426,22 +5859,52 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5451,17 +5914,52 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -5471,17 +5969,342 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -30,17 +30,16 @@
     <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
     <sheet name="Project Summary" sheetId="22" r:id="rId22"/>
     <sheet name="Design Params and Codes" sheetId="23" r:id="rId23"/>
-    <sheet name="DRM Summary" sheetId="24" r:id="rId24"/>
-    <sheet name="Register Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
-    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
+    <sheet name="Register Summary" sheetId="24" r:id="rId24"/>
+    <sheet name="DFT Summary" sheetId="25" r:id="rId25"/>
+    <sheet name="Nesto Usage Report" sheetId="26" r:id="rId26"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="434">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -132,10 +131,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
-  </si>
-  <si>
-    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
+  </si>
+  <si>
+    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -147,388 +146,19 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
-  </si>
-  <si>
-    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.fcm(59)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_bottom(60)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.blank_refresh(61)</t>
-  </si>
-  <si>
-    <t>Floating pin XU21.i0(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU22.i0(49)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XU11.enable_switchb(102)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.mode_hiccup(45)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.blank_thermal(46)</t>
-  </si>
-  <si>
-    <t>Floating pin XU10.enable_switch(58)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(35)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(34)</t>
-  </si>
-  <si>
-    <t>Floating pin XU2.adjust_resistor(33)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(50)</t>
-  </si>
-  <si>
-    <t>Floating pin XU4.adjust_resistor(49)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
-  </si>
-  <si>
-    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.halfway(36)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
+    <t>No Floating Output Nets found.</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -649,112 +279,94 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
+  </si>
+  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
+    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>DFM Efficiency Summary</t>
+  </si>
+  <si>
     <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
   </si>
   <si>
-    <t>DFT Efficiency</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
-  </si>
-  <si>
-    <t>DFM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 25, 'bytes': 25.0, 'noconns': 62, 'efficiency': '69.0%'}</t>
-  </si>
-  <si>
     <t>Project Summary</t>
   </si>
   <si>
     <t>Package Stats</t>
   </si>
   <si>
-    <t>needed: 2</t>
+    <t>needed: 0</t>
   </si>
   <si>
     <t>spares: 0</t>
   </si>
   <si>
-    <t>algorithm: 6 - Piggybacks</t>
-  </si>
-  <si>
-    <t>piggyback: ['DFTSCL', 'DFTSDA']</t>
+    <t>algorithm: 0 - No compression needed</t>
+  </si>
+  <si>
+    <t>piggyback: []</t>
   </si>
   <si>
     <t>user_pads: 12</t>
@@ -784,18 +396,18 @@
     <t>add_dft</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>add_dbufdft</t>
+  </si>
+  <si>
+    <t>dft_ignore_bricks</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>add_dbufdft</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>dft_ignore_bricks</t>
-  </si>
-  <si>
     <t>dft_measure</t>
   </si>
   <si>
@@ -1489,7 +1101,10 @@
     <t>measure_reset_command</t>
   </si>
   <si>
-    <t>DRM Summary</t>
+    <t>Register Summary</t>
+  </si>
+  <si>
+    <t>DFT Summary</t>
   </si>
   <si>
     <t>Addresses</t>
@@ -1501,255 +1116,126 @@
     <t>Instance</t>
   </si>
   <si>
-    <t>TMB</t>
+    <t>TMA</t>
   </si>
   <si>
     <t>type</t>
   </si>
   <si>
-    <t>7</t>
+    <t>Nesto Usage Report</t>
+  </si>
+  <si>
+    <t>Nesto</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>pinprobe</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>inv</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>noconn</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>dbuf</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>nor3</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>delayfixed</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>nand3</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>celeranoconn</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>srlatch</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>nor2</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>wrapper</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>dff</t>
+  </si>
+  <si>
+    <t>drmmodule</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>tie</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>datamap0</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
+    <t>resistor</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>DRM to Memory Check</t>
-  </si>
-  <si>
-    <t>TOTAL dec</t>
-  </si>
-  <si>
-    <t>Allowed &lt;= 61</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>Register Summary</t>
-  </si>
-  <si>
-    <t>DFT Summary</t>
-  </si>
-  <si>
-    <t>TMA</t>
-  </si>
-  <si>
-    <t>dft_hex0x01</t>
-  </si>
-  <si>
-    <t>DFTtm8</t>
-  </si>
-  <si>
-    <t>dft_hex0x02</t>
-  </si>
-  <si>
-    <t>DFTtm8t</t>
-  </si>
-  <si>
-    <t>dft_hex0x03</t>
-  </si>
-  <si>
-    <t>DFTtm8d</t>
-  </si>
-  <si>
-    <t>dft_hex0x04</t>
-  </si>
-  <si>
-    <t>dft_hex0x05</t>
-  </si>
-  <si>
-    <t>0x05</t>
-  </si>
-  <si>
-    <t>dft_hex0x06</t>
-  </si>
-  <si>
-    <t>0x06</t>
-  </si>
-  <si>
-    <t>dft_hex0x07</t>
-  </si>
-  <si>
-    <t>0x07</t>
-  </si>
-  <si>
-    <t>dft_hex0x08</t>
-  </si>
-  <si>
-    <t>dft_hex0x09</t>
-  </si>
-  <si>
-    <t>dft_hex0x0A</t>
-  </si>
-  <si>
-    <t>dft_hex0x0B</t>
-  </si>
-  <si>
-    <t>0x0B</t>
-  </si>
-  <si>
-    <t>dft_hex0x0C</t>
-  </si>
-  <si>
-    <t>dft_hex0x0D</t>
-  </si>
-  <si>
-    <t>0x0D</t>
-  </si>
-  <si>
-    <t>dft_hex0x0E</t>
-  </si>
-  <si>
-    <t>0x0E</t>
-  </si>
-  <si>
-    <t>dft_hex0x0F</t>
-  </si>
-  <si>
-    <t>dft_hex0x10</t>
-  </si>
-  <si>
-    <t>dft_hex0x11</t>
-  </si>
-  <si>
-    <t>dft_hex0x12</t>
-  </si>
-  <si>
-    <t>dft_hex0x13</t>
-  </si>
-  <si>
-    <t>dft_hex0x14</t>
-  </si>
-  <si>
-    <t>dft_hex0x15</t>
-  </si>
-  <si>
-    <t>dft_hex0x16</t>
-  </si>
-  <si>
-    <t>dft_hex0x17</t>
-  </si>
-  <si>
-    <t>dft_hex0x18</t>
-  </si>
-  <si>
-    <t>dft_hex0x19</t>
-  </si>
-  <si>
-    <t>0x19</t>
-  </si>
-  <si>
-    <t>Nesto Usage Report</t>
-  </si>
-  <si>
-    <t>Nesto</t>
-  </si>
-  <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>pinprobe</t>
-  </si>
-  <si>
-    <t>1082</t>
-  </si>
-  <si>
-    <t>inv</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>dbuf</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>noconn</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>nor3</t>
-  </si>
-  <si>
-    <t>dftprobeModel0</t>
-  </si>
-  <si>
-    <t>delayfixed</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>nand3</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>celeranoconn</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>srlatch</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>nor2</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>dftmodule</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>dfthijack</t>
-  </si>
-  <si>
-    <t>dff</t>
-  </si>
-  <si>
-    <t>tie</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>datamap0</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>dftprobeModel2</t>
-  </si>
-  <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>resistor</t>
-  </si>
-  <si>
     <t>oneshot</t>
   </si>
   <si>
@@ -1780,9 +1266,6 @@
     <t>amux2</t>
   </si>
   <si>
-    <t>wrapper</t>
-  </si>
-  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1799,9 +1282,6 @@
   </si>
   <si>
     <t>capacitorfixed</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>voltage2current</t>
@@ -2235,7 +1715,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2255,7 +1735,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2270,7 +1750,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2285,17 +1765,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2310,12 +1790,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2330,17 +1810,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2355,12 +1835,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2375,7 +1855,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2395,127 +1875,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>177</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>178</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>179</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>180</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>182</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>183</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>184</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>185</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>187</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>188</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>190</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>191</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>193</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>194</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>196</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>197</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>199</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2525,17 +2005,162 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2550,17 +2175,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2780,222 +2405,17 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>227</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3010,17 +2430,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3035,52 +2455,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>232</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>236</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>240</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3095,81 +2515,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>242</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>247</v>
+        <v>118</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>249</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s">
-        <v>246</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>250</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>251</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>252</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>253</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>255</v>
+        <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>256</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3177,1268 +2597,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>257</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>259</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>260</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>261</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>262</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s">
-        <v>248</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
-        <v>246</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>265</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>266</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>267</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>268</v>
+        <v>139</v>
       </c>
       <c r="B27" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>269</v>
+        <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>270</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>272</v>
+        <v>143</v>
       </c>
       <c r="B30" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>273</v>
+        <v>144</v>
       </c>
       <c r="B31" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>274</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>275</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>276</v>
+        <v>147</v>
       </c>
       <c r="B33" t="s">
-        <v>277</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>278</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>279</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>280</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
-        <v>281</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>153</v>
       </c>
       <c r="B36" t="s">
-        <v>283</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>284</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>285</v>
+        <v>156</v>
       </c>
       <c r="B38" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>286</v>
+        <v>157</v>
       </c>
       <c r="B39" t="s">
-        <v>287</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>288</v>
+        <v>159</v>
       </c>
       <c r="B40" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>289</v>
+        <v>160</v>
       </c>
       <c r="B41" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>290</v>
+        <v>161</v>
       </c>
       <c r="B42" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>291</v>
+        <v>162</v>
       </c>
       <c r="B43" t="s">
-        <v>292</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>293</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>294</v>
+        <v>165</v>
       </c>
       <c r="B46" t="s">
-        <v>295</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>296</v>
+        <v>167</v>
       </c>
       <c r="B47" t="s">
-        <v>246</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>297</v>
+        <v>168</v>
       </c>
       <c r="B48" t="s">
-        <v>287</v>
+        <v>158</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>298</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
-        <v>246</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>299</v>
+        <v>170</v>
       </c>
       <c r="B50" t="s">
-        <v>246</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>300</v>
+        <v>171</v>
       </c>
       <c r="B51" t="s">
-        <v>301</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>302</v>
+        <v>173</v>
       </c>
       <c r="B52" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>303</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>304</v>
+        <v>175</v>
       </c>
       <c r="B55" t="s">
-        <v>305</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>306</v>
+        <v>177</v>
       </c>
       <c r="B56" t="s">
-        <v>307</v>
+        <v>178</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>308</v>
+        <v>179</v>
       </c>
       <c r="B57" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>309</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>310</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>311</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>312</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>313</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>314</v>
+        <v>185</v>
       </c>
       <c r="B64" t="s">
-        <v>315</v>
+        <v>186</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>316</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>317</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>318</v>
+        <v>189</v>
       </c>
       <c r="B67" t="s">
-        <v>319</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>320</v>
+        <v>191</v>
       </c>
       <c r="B68" t="s">
-        <v>321</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="B69" t="s">
-        <v>319</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>323</v>
+        <v>194</v>
       </c>
       <c r="B70" t="s">
-        <v>321</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>324</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>325</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>326</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>327</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>328</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>329</v>
+        <v>200</v>
       </c>
       <c r="B77" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>330</v>
+        <v>201</v>
       </c>
       <c r="B78" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>331</v>
+        <v>202</v>
       </c>
       <c r="B79" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>332</v>
+        <v>203</v>
       </c>
       <c r="B80" t="s">
-        <v>333</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>334</v>
+        <v>205</v>
       </c>
       <c r="B81" t="s">
-        <v>335</v>
+        <v>206</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>336</v>
+        <v>207</v>
       </c>
       <c r="B82" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>337</v>
+        <v>208</v>
       </c>
       <c r="B83" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>338</v>
+        <v>209</v>
       </c>
       <c r="B84" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>339</v>
+        <v>210</v>
       </c>
       <c r="B85" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>340</v>
+        <v>211</v>
       </c>
       <c r="B86" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>341</v>
+        <v>212</v>
       </c>
       <c r="B87" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>342</v>
+        <v>213</v>
       </c>
       <c r="B88" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="B89" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>344</v>
+        <v>215</v>
       </c>
       <c r="B90" t="s">
-        <v>345</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="B91" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>347</v>
+        <v>218</v>
       </c>
       <c r="B92" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>348</v>
+        <v>219</v>
       </c>
       <c r="B93" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>349</v>
+        <v>220</v>
       </c>
       <c r="B94" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>350</v>
+        <v>221</v>
       </c>
       <c r="B95" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>351</v>
+        <v>222</v>
       </c>
       <c r="B96" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>352</v>
+        <v>223</v>
       </c>
       <c r="B97" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>353</v>
+        <v>224</v>
       </c>
       <c r="B98" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>354</v>
+        <v>225</v>
       </c>
       <c r="B99" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>355</v>
+        <v>226</v>
       </c>
       <c r="B100" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>356</v>
+        <v>227</v>
       </c>
       <c r="B101" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>358</v>
+        <v>229</v>
       </c>
       <c r="B102" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>359</v>
+        <v>230</v>
       </c>
       <c r="B103" t="s">
-        <v>279</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>360</v>
+        <v>231</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>361</v>
+        <v>232</v>
       </c>
       <c r="B106" t="s">
-        <v>362</v>
+        <v>233</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>363</v>
+        <v>234</v>
       </c>
       <c r="B107" t="s">
-        <v>364</v>
+        <v>235</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>365</v>
+        <v>236</v>
       </c>
       <c r="B108" t="s">
-        <v>366</v>
+        <v>237</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>367</v>
+        <v>238</v>
       </c>
       <c r="B109" t="s">
-        <v>368</v>
+        <v>239</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>369</v>
+        <v>240</v>
       </c>
       <c r="B110" t="s">
-        <v>370</v>
+        <v>241</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>371</v>
+        <v>242</v>
       </c>
       <c r="B111" t="s">
-        <v>372</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>373</v>
+        <v>244</v>
       </c>
       <c r="B112" t="s">
-        <v>374</v>
+        <v>245</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>375</v>
+        <v>246</v>
       </c>
       <c r="B113" t="s">
-        <v>376</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>377</v>
+        <v>248</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>243</v>
+        <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>378</v>
+        <v>249</v>
       </c>
       <c r="B116" t="s">
-        <v>292</v>
+        <v>163</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>379</v>
+        <v>250</v>
       </c>
       <c r="B117" t="s">
-        <v>380</v>
+        <v>251</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>381</v>
+        <v>252</v>
       </c>
       <c r="B118" t="s">
-        <v>382</v>
+        <v>253</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>383</v>
+        <v>254</v>
       </c>
       <c r="B119" t="s">
-        <v>384</v>
+        <v>255</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>385</v>
+        <v>256</v>
       </c>
       <c r="B120" t="s">
-        <v>386</v>
+        <v>257</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>387</v>
+        <v>258</v>
       </c>
       <c r="B121" t="s">
-        <v>388</v>
+        <v>259</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>389</v>
+        <v>260</v>
       </c>
       <c r="B122" t="s">
-        <v>390</v>
+        <v>261</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>391</v>
+        <v>262</v>
       </c>
       <c r="B123" t="s">
-        <v>386</v>
+        <v>257</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>392</v>
+        <v>263</v>
       </c>
       <c r="B124" t="s">
-        <v>388</v>
+        <v>259</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>393</v>
+        <v>264</v>
       </c>
       <c r="B125" t="s">
-        <v>390</v>
+        <v>261</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>394</v>
+        <v>265</v>
       </c>
       <c r="B126" t="s">
-        <v>395</v>
+        <v>266</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>396</v>
+        <v>267</v>
       </c>
       <c r="B127" t="s">
-        <v>397</v>
+        <v>268</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>398</v>
+        <v>269</v>
       </c>
       <c r="B128" t="s">
-        <v>399</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>400</v>
+        <v>271</v>
       </c>
       <c r="B129" t="s">
-        <v>401</v>
+        <v>272</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>402</v>
+        <v>273</v>
       </c>
       <c r="B130" t="s">
-        <v>403</v>
+        <v>274</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>353</v>
+        <v>224</v>
       </c>
       <c r="B131" t="s">
-        <v>404</v>
+        <v>275</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>354</v>
+        <v>225</v>
       </c>
       <c r="B132" t="s">
-        <v>405</v>
+        <v>276</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>356</v>
+        <v>227</v>
       </c>
       <c r="B133" t="s">
-        <v>406</v>
+        <v>277</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>355</v>
+        <v>226</v>
       </c>
       <c r="B134" t="s">
-        <v>407</v>
+        <v>278</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>408</v>
+        <v>279</v>
       </c>
       <c r="B135" t="s">
-        <v>292</v>
+        <v>163</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>409</v>
+        <v>280</v>
       </c>
       <c r="B136" t="s">
-        <v>410</v>
+        <v>281</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>411</v>
+        <v>282</v>
       </c>
       <c r="B137" t="s">
-        <v>412</v>
+        <v>283</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>413</v>
+        <v>284</v>
       </c>
       <c r="B138" t="s">
-        <v>414</v>
+        <v>285</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>415</v>
+        <v>286</v>
       </c>
       <c r="B139" t="s">
-        <v>416</v>
+        <v>287</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>417</v>
+        <v>288</v>
       </c>
       <c r="B140" t="s">
-        <v>418</v>
+        <v>289</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>419</v>
+        <v>290</v>
       </c>
       <c r="B141" t="s">
-        <v>386</v>
+        <v>257</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>420</v>
+        <v>291</v>
       </c>
       <c r="B142" t="s">
-        <v>388</v>
+        <v>259</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>421</v>
+        <v>292</v>
       </c>
       <c r="B143" t="s">
-        <v>390</v>
+        <v>261</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>422</v>
+        <v>293</v>
       </c>
       <c r="B144" t="s">
-        <v>395</v>
+        <v>266</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>423</v>
+        <v>294</v>
       </c>
       <c r="B145" t="s">
-        <v>397</v>
+        <v>268</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>424</v>
+        <v>295</v>
       </c>
       <c r="B146" t="s">
-        <v>399</v>
+        <v>270</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="B147" t="s">
-        <v>401</v>
+        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>426</v>
+        <v>297</v>
       </c>
       <c r="B148" t="s">
-        <v>403</v>
+        <v>274</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>427</v>
+        <v>298</v>
       </c>
       <c r="B149" t="s">
-        <v>428</v>
+        <v>299</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>429</v>
+        <v>300</v>
       </c>
       <c r="B150" t="s">
-        <v>430</v>
+        <v>301</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>431</v>
+        <v>302</v>
       </c>
       <c r="B151" t="s">
-        <v>432</v>
+        <v>303</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>433</v>
+        <v>304</v>
       </c>
       <c r="B152" t="s">
-        <v>434</v>
+        <v>305</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>435</v>
+        <v>306</v>
       </c>
       <c r="B153" t="s">
-        <v>436</v>
+        <v>307</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>437</v>
+        <v>308</v>
       </c>
       <c r="B154" t="s">
-        <v>438</v>
+        <v>309</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>439</v>
+        <v>310</v>
       </c>
       <c r="B155" t="s">
-        <v>440</v>
+        <v>311</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>441</v>
+        <v>312</v>
       </c>
       <c r="B156" t="s">
-        <v>442</v>
+        <v>313</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>443</v>
+        <v>314</v>
       </c>
       <c r="B157" t="s">
-        <v>444</v>
+        <v>315</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>445</v>
+        <v>316</v>
       </c>
       <c r="B158" t="s">
-        <v>446</v>
+        <v>317</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>447</v>
+        <v>318</v>
       </c>
       <c r="B159" t="s">
-        <v>448</v>
+        <v>319</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>449</v>
+        <v>320</v>
       </c>
       <c r="B160" t="s">
-        <v>450</v>
+        <v>321</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>451</v>
+        <v>322</v>
       </c>
       <c r="B161" t="s">
-        <v>452</v>
+        <v>323</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>453</v>
+        <v>324</v>
       </c>
       <c r="B162" t="s">
-        <v>454</v>
+        <v>325</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>455</v>
+        <v>326</v>
       </c>
       <c r="B163" t="s">
-        <v>456</v>
+        <v>327</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>457</v>
+        <v>328</v>
       </c>
       <c r="B164" t="s">
-        <v>458</v>
+        <v>329</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>459</v>
+        <v>330</v>
       </c>
       <c r="B165" t="s">
-        <v>460</v>
+        <v>331</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>461</v>
+        <v>332</v>
       </c>
       <c r="B166" t="s">
-        <v>434</v>
+        <v>305</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>462</v>
+        <v>333</v>
       </c>
       <c r="B167" t="s">
-        <v>416</v>
+        <v>287</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>463</v>
+        <v>334</v>
       </c>
       <c r="B168" t="s">
-        <v>418</v>
+        <v>289</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>464</v>
+        <v>335</v>
       </c>
       <c r="B169" t="s">
-        <v>275</v>
+        <v>146</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>465</v>
+        <v>336</v>
       </c>
       <c r="B170" t="s">
-        <v>466</v>
+        <v>337</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>467</v>
+        <v>338</v>
       </c>
       <c r="B171" t="s">
-        <v>468</v>
+        <v>339</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>469</v>
+        <v>340</v>
       </c>
       <c r="B172" t="s">
-        <v>470</v>
+        <v>341</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>471</v>
+        <v>342</v>
       </c>
       <c r="B173" t="s">
-        <v>472</v>
+        <v>343</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>473</v>
+        <v>344</v>
       </c>
       <c r="B174" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>474</v>
+        <v>345</v>
       </c>
       <c r="B175" t="s">
-        <v>386</v>
+        <v>257</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>475</v>
+        <v>346</v>
       </c>
       <c r="B176" t="s">
-        <v>388</v>
+        <v>259</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>476</v>
+        <v>347</v>
       </c>
       <c r="B177" t="s">
-        <v>428</v>
+        <v>299</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>477</v>
+        <v>348</v>
       </c>
       <c r="B178" t="s">
-        <v>412</v>
+        <v>283</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>478</v>
+        <v>349</v>
       </c>
       <c r="B179" t="s">
-        <v>479</v>
+        <v>350</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>480</v>
+        <v>351</v>
       </c>
       <c r="B180" t="s">
-        <v>416</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -4448,76 +3868,12 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>492</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -4527,12 +3883,31 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -4542,396 +3917,12 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" t="s">
-        <v>496</v>
-      </c>
-      <c r="C5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D5" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B6" t="s">
-        <v>498</v>
-      </c>
-      <c r="C6" t="s">
-        <v>418</v>
-      </c>
-      <c r="D6" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>208</v>
-      </c>
-      <c r="B7" t="s">
-        <v>500</v>
-      </c>
-      <c r="C7" t="s">
-        <v>275</v>
-      </c>
-      <c r="D7" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>502</v>
-      </c>
-      <c r="C8" t="s">
-        <v>466</v>
-      </c>
-      <c r="D8" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>503</v>
-      </c>
-      <c r="C9" t="s">
-        <v>504</v>
-      </c>
-      <c r="D9" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>212</v>
-      </c>
-      <c r="B10" t="s">
-        <v>505</v>
-      </c>
-      <c r="C10" t="s">
-        <v>506</v>
-      </c>
-      <c r="D10" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>213</v>
-      </c>
-      <c r="B11" t="s">
-        <v>507</v>
-      </c>
-      <c r="C11" t="s">
-        <v>508</v>
-      </c>
-      <c r="D11" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>213</v>
-      </c>
-      <c r="B12" t="s">
-        <v>509</v>
-      </c>
-      <c r="C12" t="s">
-        <v>468</v>
-      </c>
-      <c r="D12" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>510</v>
-      </c>
-      <c r="C13" t="s">
-        <v>470</v>
-      </c>
-      <c r="D13" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>216</v>
-      </c>
-      <c r="B14" t="s">
-        <v>511</v>
-      </c>
-      <c r="C14" t="s">
-        <v>472</v>
-      </c>
-      <c r="D14" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>216</v>
-      </c>
-      <c r="B15" t="s">
-        <v>512</v>
-      </c>
-      <c r="C15" t="s">
-        <v>513</v>
-      </c>
-      <c r="D15" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>216</v>
-      </c>
-      <c r="B16" t="s">
-        <v>514</v>
-      </c>
-      <c r="C16" t="s">
-        <v>414</v>
-      </c>
-      <c r="D16" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>219</v>
-      </c>
-      <c r="B17" t="s">
-        <v>515</v>
-      </c>
-      <c r="C17" t="s">
-        <v>516</v>
-      </c>
-      <c r="D17" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>220</v>
-      </c>
-      <c r="B18" t="s">
-        <v>517</v>
-      </c>
-      <c r="C18" t="s">
-        <v>518</v>
-      </c>
-      <c r="D18" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" t="s">
-        <v>519</v>
-      </c>
-      <c r="C19" t="s">
-        <v>345</v>
-      </c>
-      <c r="D19" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>221</v>
-      </c>
-      <c r="B20" t="s">
-        <v>520</v>
-      </c>
-      <c r="C20" t="s">
-        <v>386</v>
-      </c>
-      <c r="D20" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>521</v>
-      </c>
-      <c r="C21" t="s">
-        <v>388</v>
-      </c>
-      <c r="D21" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>224</v>
-      </c>
-      <c r="B22" t="s">
-        <v>522</v>
-      </c>
-      <c r="C22" t="s">
-        <v>390</v>
-      </c>
-      <c r="D22" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" t="s">
-        <v>523</v>
-      </c>
-      <c r="C23" t="s">
-        <v>395</v>
-      </c>
-      <c r="D23" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" t="s">
-        <v>524</v>
-      </c>
-      <c r="C24" t="s">
-        <v>397</v>
-      </c>
-      <c r="D24" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B25" t="s">
-        <v>525</v>
-      </c>
-      <c r="C25" t="s">
-        <v>399</v>
-      </c>
-      <c r="D25" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>226</v>
-      </c>
-      <c r="B26" t="s">
-        <v>526</v>
-      </c>
-      <c r="C26" t="s">
-        <v>401</v>
-      </c>
-      <c r="D26" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>226</v>
-      </c>
-      <c r="B27" t="s">
-        <v>527</v>
-      </c>
-      <c r="C27" t="s">
-        <v>403</v>
-      </c>
-      <c r="D27" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>228</v>
-      </c>
-      <c r="B28" t="s">
-        <v>528</v>
-      </c>
-      <c r="C28" t="s">
-        <v>428</v>
-      </c>
-      <c r="D28" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>167</v>
-      </c>
-      <c r="B29" t="s">
-        <v>529</v>
-      </c>
-      <c r="C29" t="s">
-        <v>530</v>
-      </c>
-      <c r="D29" t="s">
-        <v>499</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>531</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4941,490 +3932,458 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>532</v>
+        <v>360</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>533</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>534</v>
+        <v>362</v>
       </c>
       <c r="B5" t="s">
-        <v>535</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>536</v>
+        <v>364</v>
       </c>
       <c r="B6" t="s">
-        <v>537</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>538</v>
+        <v>366</v>
       </c>
       <c r="B7" t="s">
-        <v>539</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>540</v>
+        <v>368</v>
       </c>
       <c r="B8" t="s">
-        <v>541</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>542</v>
+        <v>370</v>
       </c>
       <c r="B9" t="s">
-        <v>543</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>544</v>
+        <v>372</v>
       </c>
       <c r="B10" t="s">
-        <v>492</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>545</v>
+        <v>374</v>
       </c>
       <c r="B11" t="s">
-        <v>492</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>546</v>
+        <v>376</v>
       </c>
       <c r="B12" t="s">
-        <v>547</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>548</v>
+        <v>378</v>
       </c>
       <c r="B13" t="s">
-        <v>549</v>
+        <v>379</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>550</v>
+        <v>380</v>
       </c>
       <c r="B14" t="s">
-        <v>551</v>
+        <v>381</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>552</v>
+        <v>382</v>
       </c>
       <c r="B15" t="s">
-        <v>553</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>554</v>
+        <v>384</v>
       </c>
       <c r="B16" t="s">
-        <v>555</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>556</v>
+        <v>386</v>
       </c>
       <c r="B17" t="s">
-        <v>557</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>558</v>
+        <v>387</v>
       </c>
       <c r="B18" t="s">
-        <v>301</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>559</v>
+        <v>389</v>
       </c>
       <c r="B19" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>560</v>
+        <v>391</v>
       </c>
       <c r="B20" t="s">
-        <v>561</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>562</v>
+        <v>392</v>
       </c>
       <c r="B21" t="s">
-        <v>561</v>
+        <v>393</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>563</v>
+        <v>394</v>
       </c>
       <c r="B22" t="s">
-        <v>564</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>565</v>
+        <v>395</v>
       </c>
       <c r="B23" t="s">
-        <v>487</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>566</v>
+        <v>397</v>
       </c>
       <c r="B24" t="s">
-        <v>279</v>
+        <v>396</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>567</v>
+        <v>398</v>
       </c>
       <c r="B25" t="s">
-        <v>488</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>568</v>
+        <v>399</v>
       </c>
       <c r="B26" t="s">
-        <v>488</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>569</v>
+        <v>400</v>
       </c>
       <c r="B27" t="s">
-        <v>488</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>570</v>
+        <v>401</v>
       </c>
       <c r="B28" t="s">
-        <v>488</v>
+        <v>396</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>571</v>
+        <v>402</v>
       </c>
       <c r="B29" t="s">
-        <v>488</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>572</v>
+        <v>403</v>
       </c>
       <c r="B30" t="s">
-        <v>488</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>573</v>
+        <v>404</v>
       </c>
       <c r="B31" t="s">
-        <v>364</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>574</v>
+        <v>405</v>
       </c>
       <c r="B32" t="s">
-        <v>364</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>575</v>
+        <v>406</v>
       </c>
       <c r="B33" t="s">
-        <v>364</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>576</v>
+        <v>407</v>
       </c>
       <c r="B34" t="s">
-        <v>364</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>577</v>
+        <v>408</v>
       </c>
       <c r="B35" t="s">
-        <v>364</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>578</v>
+        <v>409</v>
       </c>
       <c r="B36" t="s">
-        <v>287</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>579</v>
+        <v>410</v>
       </c>
       <c r="B37" t="s">
-        <v>287</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>580</v>
+        <v>411</v>
       </c>
       <c r="B38" t="s">
-        <v>287</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>581</v>
+        <v>412</v>
       </c>
       <c r="B39" t="s">
-        <v>287</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>582</v>
+        <v>413</v>
       </c>
       <c r="B40" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>583</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>584</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>585</v>
+        <v>416</v>
       </c>
       <c r="B43" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>586</v>
+        <v>417</v>
       </c>
       <c r="B44" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>587</v>
+        <v>418</v>
       </c>
       <c r="B45" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>588</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>589</v>
+        <v>420</v>
       </c>
       <c r="B47" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>590</v>
+        <v>421</v>
       </c>
       <c r="B48" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>591</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>592</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>593</v>
+        <v>424</v>
       </c>
       <c r="B51" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>594</v>
+        <v>425</v>
       </c>
       <c r="B52" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>595</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>596</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>597</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>598</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>599</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>600</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>601</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>602</v>
+        <v>433</v>
       </c>
       <c r="B60" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>603</v>
-      </c>
-      <c r="B61" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>604</v>
-      </c>
-      <c r="B62" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>605</v>
-      </c>
-      <c r="B63" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>606</v>
-      </c>
-      <c r="B64" t="s">
-        <v>357</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -5514,7 +4473,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -5530,326 +4489,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -5859,52 +4498,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -5914,52 +4523,17 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>106</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5969,342 +4543,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>162</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -30,16 +30,17 @@
     <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
     <sheet name="Project Summary" sheetId="22" r:id="rId22"/>
     <sheet name="Design Params and Codes" sheetId="23" r:id="rId23"/>
-    <sheet name="Register Summary" sheetId="24" r:id="rId24"/>
-    <sheet name="DFT Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="Nesto Usage Report" sheetId="26" r:id="rId26"/>
+    <sheet name="DRM Summary" sheetId="24" r:id="rId24"/>
+    <sheet name="Register Summary" sheetId="25" r:id="rId25"/>
+    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
+    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="607">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -131,10 +132,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -146,19 +147,388 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -279,76 +649,94 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>DRM Efficiency Summary</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
   </si>
   <si>
-    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
-    <t>DRM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
-  </si>
-  <si>
-    <t>DFT Efficiency</t>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
   </si>
   <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+    <t>{'cells': 25, 'bytes': 25.0, 'noconns': 62, 'efficiency': '69.0%'}</t>
   </si>
   <si>
     <t>Project Summary</t>
@@ -357,16 +745,16 @@
     <t>Package Stats</t>
   </si>
   <si>
-    <t>needed: 0</t>
+    <t>needed: 2</t>
   </si>
   <si>
     <t>spares: 0</t>
   </si>
   <si>
-    <t>algorithm: 0 - No compression needed</t>
-  </si>
-  <si>
-    <t>piggyback: []</t>
+    <t>algorithm: 6 - Piggybacks</t>
+  </si>
+  <si>
+    <t>piggyback: ['DFTSCL', 'DFTSDA']</t>
   </si>
   <si>
     <t>user_pads: 12</t>
@@ -396,18 +784,18 @@
     <t>add_dft</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>add_dbufdft</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>add_dbufdft</t>
-  </si>
-  <si>
     <t>dft_ignore_bricks</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>dft_measure</t>
   </si>
   <si>
@@ -1101,25 +1489,154 @@
     <t>measure_reset_command</t>
   </si>
   <si>
+    <t>DRM Summary</t>
+  </si>
+  <si>
+    <t>Addresses</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Instance</t>
+  </si>
+  <si>
+    <t>TMB</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>DRM to Memory Check</t>
+  </si>
+  <si>
+    <t>TOTAL dec</t>
+  </si>
+  <si>
+    <t>Allowed &lt;= 61</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
     <t>Register Summary</t>
   </si>
   <si>
     <t>DFT Summary</t>
   </si>
   <si>
-    <t>Addresses</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Instance</t>
-  </si>
-  <si>
     <t>TMA</t>
   </si>
   <si>
-    <t>type</t>
+    <t>dft_hex0x01</t>
+  </si>
+  <si>
+    <t>DFTtm8</t>
+  </si>
+  <si>
+    <t>dft_hex0x02</t>
+  </si>
+  <si>
+    <t>DFTtm8t</t>
+  </si>
+  <si>
+    <t>dft_hex0x03</t>
+  </si>
+  <si>
+    <t>DFTtm8d</t>
+  </si>
+  <si>
+    <t>dft_hex0x04</t>
+  </si>
+  <si>
+    <t>dft_hex0x05</t>
+  </si>
+  <si>
+    <t>0x05</t>
+  </si>
+  <si>
+    <t>dft_hex0x06</t>
+  </si>
+  <si>
+    <t>0x06</t>
+  </si>
+  <si>
+    <t>dft_hex0x07</t>
+  </si>
+  <si>
+    <t>0x07</t>
+  </si>
+  <si>
+    <t>dft_hex0x08</t>
+  </si>
+  <si>
+    <t>dft_hex0x09</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B</t>
+  </si>
+  <si>
+    <t>0x0B</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D</t>
+  </si>
+  <si>
+    <t>0x0D</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E</t>
+  </si>
+  <si>
+    <t>0x0E</t>
+  </si>
+  <si>
+    <t>dft_hex0x0F</t>
+  </si>
+  <si>
+    <t>dft_hex0x10</t>
+  </si>
+  <si>
+    <t>dft_hex0x11</t>
+  </si>
+  <si>
+    <t>dft_hex0x12</t>
+  </si>
+  <si>
+    <t>dft_hex0x13</t>
+  </si>
+  <si>
+    <t>dft_hex0x14</t>
+  </si>
+  <si>
+    <t>dft_hex0x15</t>
+  </si>
+  <si>
+    <t>dft_hex0x16</t>
+  </si>
+  <si>
+    <t>dft_hex0x17</t>
+  </si>
+  <si>
+    <t>dft_hex0x18</t>
+  </si>
+  <si>
+    <t>dft_hex0x19</t>
+  </si>
+  <si>
+    <t>0x19</t>
   </si>
   <si>
     <t>Nesto Usage Report</t>
@@ -1143,28 +1660,28 @@
     <t>193</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>dbuf</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>noconn</t>
   </si>
   <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>dbuf</t>
-  </si>
-  <si>
-    <t>122</t>
+    <t>107</t>
   </si>
   <si>
     <t>nor3</t>
   </si>
   <si>
-    <t>61</t>
+    <t>dftprobeModel0</t>
   </si>
   <si>
     <t>delayfixed</t>
@@ -1197,75 +1714,75 @@
     <t>35</t>
   </si>
   <si>
+    <t>dftmodule</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>dfthijack</t>
+  </si>
+  <si>
+    <t>dff</t>
+  </si>
+  <si>
+    <t>tie</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>datamap0</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>dftprobeModel2</t>
+  </si>
+  <si>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
+    <t>resistor</t>
+  </si>
+  <si>
+    <t>oneshot</t>
+  </si>
+  <si>
+    <t>fetdn</t>
+  </si>
+  <si>
+    <t>currentlimitfet</t>
+  </si>
+  <si>
+    <t>comparatornoctlpins</t>
+  </si>
+  <si>
+    <t>ESDminiClamp6</t>
+  </si>
+  <si>
+    <t>timingskew</t>
+  </si>
+  <si>
+    <t>switchpulldown</t>
+  </si>
+  <si>
+    <t>resistordivider</t>
+  </si>
+  <si>
+    <t>delayclock</t>
+  </si>
+  <si>
+    <t>amux2</t>
+  </si>
+  <si>
     <t>wrapper</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>dff</t>
-  </si>
-  <si>
-    <t>drmmodule</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>tie</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>datamap0</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>resistor</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>oneshot</t>
-  </si>
-  <si>
-    <t>fetdn</t>
-  </si>
-  <si>
-    <t>currentlimitfet</t>
-  </si>
-  <si>
-    <t>comparatornoctlpins</t>
-  </si>
-  <si>
-    <t>ESDminiClamp6</t>
-  </si>
-  <si>
-    <t>timingskew</t>
-  </si>
-  <si>
-    <t>switchpulldown</t>
-  </si>
-  <si>
-    <t>resistordivider</t>
-  </si>
-  <si>
-    <t>delayclock</t>
-  </si>
-  <si>
-    <t>amux2</t>
-  </si>
-  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1282,6 +1799,9 @@
   </si>
   <si>
     <t>capacitorfixed</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>voltage2current</t>
@@ -1715,7 +2235,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1735,7 +2255,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1750,7 +2270,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -1765,17 +2285,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -1790,12 +2310,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -1810,17 +2330,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1835,12 +2355,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -1855,7 +2375,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1875,127 +2395,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>75</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2005,162 +2525,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2175,17 +2550,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2405,17 +2780,222 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2430,17 +3010,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2455,52 +3035,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -2515,81 +3095,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>245</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>247</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>249</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>251</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>253</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>255</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>256</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2597,1268 +3177,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>133</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>134</v>
+        <v>263</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>264</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>136</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>138</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>143</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>145</v>
+        <v>274</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>156</v>
+        <v>285</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>157</v>
+        <v>286</v>
       </c>
       <c r="B39" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>159</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>160</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>161</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>162</v>
+        <v>291</v>
       </c>
       <c r="B43" t="s">
-        <v>163</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>164</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>165</v>
+        <v>294</v>
       </c>
       <c r="B46" t="s">
-        <v>166</v>
+        <v>295</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>167</v>
+        <v>296</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>168</v>
+        <v>297</v>
       </c>
       <c r="B48" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>298</v>
       </c>
       <c r="B49" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>299</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>171</v>
+        <v>300</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>173</v>
+        <v>302</v>
       </c>
       <c r="B52" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>174</v>
+        <v>303</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>175</v>
+        <v>304</v>
       </c>
       <c r="B55" t="s">
-        <v>176</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>177</v>
+        <v>306</v>
       </c>
       <c r="B56" t="s">
-        <v>178</v>
+        <v>307</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>179</v>
+        <v>308</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>180</v>
+        <v>309</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>181</v>
+        <v>310</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>182</v>
+        <v>311</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>183</v>
+        <v>312</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>184</v>
+        <v>313</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="B64" t="s">
-        <v>186</v>
+        <v>315</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>187</v>
+        <v>316</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>188</v>
+        <v>317</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>189</v>
+        <v>318</v>
       </c>
       <c r="B67" t="s">
-        <v>190</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>191</v>
+        <v>320</v>
       </c>
       <c r="B68" t="s">
-        <v>192</v>
+        <v>321</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="B69" t="s">
-        <v>190</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="B70" t="s">
-        <v>192</v>
+        <v>321</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>195</v>
+        <v>324</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>196</v>
+        <v>325</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>197</v>
+        <v>326</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>198</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>199</v>
+        <v>328</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>200</v>
+        <v>329</v>
       </c>
       <c r="B77" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>201</v>
+        <v>330</v>
       </c>
       <c r="B78" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>202</v>
+        <v>331</v>
       </c>
       <c r="B79" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>203</v>
+        <v>332</v>
       </c>
       <c r="B80" t="s">
-        <v>204</v>
+        <v>333</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>205</v>
+        <v>334</v>
       </c>
       <c r="B81" t="s">
-        <v>206</v>
+        <v>335</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>207</v>
+        <v>336</v>
       </c>
       <c r="B82" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>208</v>
+        <v>337</v>
       </c>
       <c r="B83" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="B84" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>210</v>
+        <v>339</v>
       </c>
       <c r="B85" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>211</v>
+        <v>340</v>
       </c>
       <c r="B86" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>212</v>
+        <v>341</v>
       </c>
       <c r="B87" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>213</v>
+        <v>342</v>
       </c>
       <c r="B88" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="B89" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>215</v>
+        <v>344</v>
       </c>
       <c r="B90" t="s">
-        <v>216</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>217</v>
+        <v>346</v>
       </c>
       <c r="B91" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>218</v>
+        <v>347</v>
       </c>
       <c r="B92" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>219</v>
+        <v>348</v>
       </c>
       <c r="B93" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>220</v>
+        <v>349</v>
       </c>
       <c r="B94" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>221</v>
+        <v>350</v>
       </c>
       <c r="B95" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>222</v>
+        <v>351</v>
       </c>
       <c r="B96" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>223</v>
+        <v>352</v>
       </c>
       <c r="B97" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>224</v>
+        <v>353</v>
       </c>
       <c r="B98" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>225</v>
+        <v>354</v>
       </c>
       <c r="B99" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>226</v>
+        <v>355</v>
       </c>
       <c r="B100" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>227</v>
+        <v>356</v>
       </c>
       <c r="B101" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>229</v>
+        <v>358</v>
       </c>
       <c r="B102" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>230</v>
+        <v>359</v>
       </c>
       <c r="B103" t="s">
-        <v>150</v>
+        <v>279</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>231</v>
+        <v>360</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>232</v>
+        <v>361</v>
       </c>
       <c r="B106" t="s">
-        <v>233</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>234</v>
+        <v>363</v>
       </c>
       <c r="B107" t="s">
-        <v>235</v>
+        <v>364</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>236</v>
+        <v>365</v>
       </c>
       <c r="B108" t="s">
-        <v>237</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>238</v>
+        <v>367</v>
       </c>
       <c r="B109" t="s">
-        <v>239</v>
+        <v>368</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>240</v>
+        <v>369</v>
       </c>
       <c r="B110" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>242</v>
+        <v>371</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>372</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>244</v>
+        <v>373</v>
       </c>
       <c r="B112" t="s">
-        <v>245</v>
+        <v>374</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>246</v>
+        <v>375</v>
       </c>
       <c r="B113" t="s">
-        <v>247</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>248</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>249</v>
+        <v>378</v>
       </c>
       <c r="B116" t="s">
-        <v>163</v>
+        <v>292</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>250</v>
+        <v>379</v>
       </c>
       <c r="B117" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>252</v>
+        <v>381</v>
       </c>
       <c r="B118" t="s">
-        <v>253</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>254</v>
+        <v>383</v>
       </c>
       <c r="B119" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>256</v>
+        <v>385</v>
       </c>
       <c r="B120" t="s">
-        <v>257</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>258</v>
+        <v>387</v>
       </c>
       <c r="B121" t="s">
-        <v>259</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>260</v>
+        <v>389</v>
       </c>
       <c r="B122" t="s">
-        <v>261</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>262</v>
+        <v>391</v>
       </c>
       <c r="B123" t="s">
-        <v>257</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>263</v>
+        <v>392</v>
       </c>
       <c r="B124" t="s">
-        <v>259</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>264</v>
+        <v>393</v>
       </c>
       <c r="B125" t="s">
-        <v>261</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>265</v>
+        <v>394</v>
       </c>
       <c r="B126" t="s">
-        <v>266</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>267</v>
+        <v>396</v>
       </c>
       <c r="B127" t="s">
-        <v>268</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>269</v>
+        <v>398</v>
       </c>
       <c r="B128" t="s">
-        <v>270</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>271</v>
+        <v>400</v>
       </c>
       <c r="B129" t="s">
-        <v>272</v>
+        <v>401</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>273</v>
+        <v>402</v>
       </c>
       <c r="B130" t="s">
-        <v>274</v>
+        <v>403</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>224</v>
+        <v>353</v>
       </c>
       <c r="B131" t="s">
-        <v>275</v>
+        <v>404</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>225</v>
+        <v>354</v>
       </c>
       <c r="B132" t="s">
-        <v>276</v>
+        <v>405</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>227</v>
+        <v>356</v>
       </c>
       <c r="B133" t="s">
-        <v>277</v>
+        <v>406</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>226</v>
+        <v>355</v>
       </c>
       <c r="B134" t="s">
-        <v>278</v>
+        <v>407</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>279</v>
+        <v>408</v>
       </c>
       <c r="B135" t="s">
-        <v>163</v>
+        <v>292</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>280</v>
+        <v>409</v>
       </c>
       <c r="B136" t="s">
-        <v>281</v>
+        <v>410</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>282</v>
+        <v>411</v>
       </c>
       <c r="B137" t="s">
-        <v>283</v>
+        <v>412</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>284</v>
+        <v>413</v>
       </c>
       <c r="B138" t="s">
-        <v>285</v>
+        <v>414</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>286</v>
+        <v>415</v>
       </c>
       <c r="B139" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>288</v>
+        <v>417</v>
       </c>
       <c r="B140" t="s">
-        <v>289</v>
+        <v>418</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>290</v>
+        <v>419</v>
       </c>
       <c r="B141" t="s">
-        <v>257</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>291</v>
+        <v>420</v>
       </c>
       <c r="B142" t="s">
-        <v>259</v>
+        <v>388</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>292</v>
+        <v>421</v>
       </c>
       <c r="B143" t="s">
-        <v>261</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>293</v>
+        <v>422</v>
       </c>
       <c r="B144" t="s">
-        <v>266</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>294</v>
+        <v>423</v>
       </c>
       <c r="B145" t="s">
-        <v>268</v>
+        <v>397</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>295</v>
+        <v>424</v>
       </c>
       <c r="B146" t="s">
-        <v>270</v>
+        <v>399</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>296</v>
+        <v>425</v>
       </c>
       <c r="B147" t="s">
-        <v>272</v>
+        <v>401</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>297</v>
+        <v>426</v>
       </c>
       <c r="B148" t="s">
-        <v>274</v>
+        <v>403</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>298</v>
+        <v>427</v>
       </c>
       <c r="B149" t="s">
-        <v>299</v>
+        <v>428</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>300</v>
+        <v>429</v>
       </c>
       <c r="B150" t="s">
-        <v>301</v>
+        <v>430</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>302</v>
+        <v>431</v>
       </c>
       <c r="B151" t="s">
-        <v>303</v>
+        <v>432</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>304</v>
+        <v>433</v>
       </c>
       <c r="B152" t="s">
-        <v>305</v>
+        <v>434</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>306</v>
+        <v>435</v>
       </c>
       <c r="B153" t="s">
-        <v>307</v>
+        <v>436</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>308</v>
+        <v>437</v>
       </c>
       <c r="B154" t="s">
-        <v>309</v>
+        <v>438</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>310</v>
+        <v>439</v>
       </c>
       <c r="B155" t="s">
-        <v>311</v>
+        <v>440</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>312</v>
+        <v>441</v>
       </c>
       <c r="B156" t="s">
-        <v>313</v>
+        <v>442</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>314</v>
+        <v>443</v>
       </c>
       <c r="B157" t="s">
-        <v>315</v>
+        <v>444</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>316</v>
+        <v>445</v>
       </c>
       <c r="B158" t="s">
-        <v>317</v>
+        <v>446</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>318</v>
+        <v>447</v>
       </c>
       <c r="B159" t="s">
-        <v>319</v>
+        <v>448</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>320</v>
+        <v>449</v>
       </c>
       <c r="B160" t="s">
-        <v>321</v>
+        <v>450</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>322</v>
+        <v>451</v>
       </c>
       <c r="B161" t="s">
-        <v>323</v>
+        <v>452</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>324</v>
+        <v>453</v>
       </c>
       <c r="B162" t="s">
-        <v>325</v>
+        <v>454</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>326</v>
+        <v>455</v>
       </c>
       <c r="B163" t="s">
-        <v>327</v>
+        <v>456</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>328</v>
+        <v>457</v>
       </c>
       <c r="B164" t="s">
-        <v>329</v>
+        <v>458</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>330</v>
+        <v>459</v>
       </c>
       <c r="B165" t="s">
-        <v>331</v>
+        <v>460</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>332</v>
+        <v>461</v>
       </c>
       <c r="B166" t="s">
-        <v>305</v>
+        <v>434</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>333</v>
+        <v>462</v>
       </c>
       <c r="B167" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
       <c r="B168" t="s">
-        <v>289</v>
+        <v>418</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>335</v>
+        <v>464</v>
       </c>
       <c r="B169" t="s">
-        <v>146</v>
+        <v>275</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>336</v>
+        <v>465</v>
       </c>
       <c r="B170" t="s">
-        <v>337</v>
+        <v>466</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>338</v>
+        <v>467</v>
       </c>
       <c r="B171" t="s">
-        <v>339</v>
+        <v>468</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>340</v>
+        <v>469</v>
       </c>
       <c r="B172" t="s">
-        <v>341</v>
+        <v>470</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>342</v>
+        <v>471</v>
       </c>
       <c r="B173" t="s">
-        <v>343</v>
+        <v>472</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>344</v>
+        <v>473</v>
       </c>
       <c r="B174" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>345</v>
+        <v>474</v>
       </c>
       <c r="B175" t="s">
-        <v>257</v>
+        <v>386</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>346</v>
+        <v>475</v>
       </c>
       <c r="B176" t="s">
-        <v>259</v>
+        <v>388</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>347</v>
+        <v>476</v>
       </c>
       <c r="B177" t="s">
-        <v>299</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>348</v>
+        <v>477</v>
       </c>
       <c r="B178" t="s">
-        <v>283</v>
+        <v>412</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>349</v>
+        <v>478</v>
       </c>
       <c r="B179" t="s">
-        <v>350</v>
+        <v>479</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>351</v>
+        <v>480</v>
       </c>
       <c r="B180" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -3868,12 +4448,76 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -3883,31 +4527,12 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>358</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -3917,12 +4542,396 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" t="s">
+        <v>496</v>
+      </c>
+      <c r="C5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" t="s">
+        <v>498</v>
+      </c>
+      <c r="C6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B7" t="s">
+        <v>500</v>
+      </c>
+      <c r="C7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D7" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>502</v>
+      </c>
+      <c r="C8" t="s">
+        <v>466</v>
+      </c>
+      <c r="D8" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>503</v>
+      </c>
+      <c r="C9" t="s">
+        <v>504</v>
+      </c>
+      <c r="D9" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" t="s">
+        <v>505</v>
+      </c>
+      <c r="C10" t="s">
+        <v>506</v>
+      </c>
+      <c r="D10" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11" t="s">
+        <v>507</v>
+      </c>
+      <c r="C11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D11" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" t="s">
+        <v>509</v>
+      </c>
+      <c r="C12" t="s">
+        <v>468</v>
+      </c>
+      <c r="D12" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>510</v>
+      </c>
+      <c r="C13" t="s">
+        <v>470</v>
+      </c>
+      <c r="D13" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B14" t="s">
+        <v>511</v>
+      </c>
+      <c r="C14" t="s">
+        <v>472</v>
+      </c>
+      <c r="D14" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" t="s">
+        <v>512</v>
+      </c>
+      <c r="C15" t="s">
+        <v>513</v>
+      </c>
+      <c r="D15" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" t="s">
+        <v>514</v>
+      </c>
+      <c r="C16" t="s">
+        <v>414</v>
+      </c>
+      <c r="D16" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" t="s">
+        <v>515</v>
+      </c>
+      <c r="C17" t="s">
+        <v>516</v>
+      </c>
+      <c r="D17" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>220</v>
+      </c>
+      <c r="B18" t="s">
+        <v>517</v>
+      </c>
+      <c r="C18" t="s">
+        <v>518</v>
+      </c>
+      <c r="D18" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" t="s">
+        <v>519</v>
+      </c>
+      <c r="C19" t="s">
+        <v>345</v>
+      </c>
+      <c r="D19" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>221</v>
+      </c>
+      <c r="B20" t="s">
+        <v>520</v>
+      </c>
+      <c r="C20" t="s">
+        <v>386</v>
+      </c>
+      <c r="D20" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C21" t="s">
+        <v>388</v>
+      </c>
+      <c r="D21" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" t="s">
+        <v>522</v>
+      </c>
+      <c r="C22" t="s">
+        <v>390</v>
+      </c>
+      <c r="D22" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>523</v>
+      </c>
+      <c r="C23" t="s">
+        <v>395</v>
+      </c>
+      <c r="D23" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>524</v>
+      </c>
+      <c r="C24" t="s">
+        <v>397</v>
+      </c>
+      <c r="D24" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25" t="s">
+        <v>525</v>
+      </c>
+      <c r="C25" t="s">
+        <v>399</v>
+      </c>
+      <c r="D25" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" t="s">
+        <v>526</v>
+      </c>
+      <c r="C26" t="s">
+        <v>401</v>
+      </c>
+      <c r="D26" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" t="s">
+        <v>527</v>
+      </c>
+      <c r="C27" t="s">
+        <v>403</v>
+      </c>
+      <c r="D27" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>228</v>
+      </c>
+      <c r="B28" t="s">
+        <v>528</v>
+      </c>
+      <c r="C28" t="s">
+        <v>428</v>
+      </c>
+      <c r="D28" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>167</v>
+      </c>
+      <c r="B29" t="s">
+        <v>529</v>
+      </c>
+      <c r="C29" t="s">
+        <v>530</v>
+      </c>
+      <c r="D29" t="s">
+        <v>499</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3932,458 +4941,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>532</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>361</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>534</v>
       </c>
       <c r="B5" t="s">
-        <v>363</v>
+        <v>535</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>364</v>
+        <v>536</v>
       </c>
       <c r="B6" t="s">
-        <v>365</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>366</v>
+        <v>538</v>
       </c>
       <c r="B7" t="s">
-        <v>367</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>368</v>
+        <v>540</v>
       </c>
       <c r="B8" t="s">
-        <v>369</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>370</v>
+        <v>542</v>
       </c>
       <c r="B9" t="s">
-        <v>371</v>
+        <v>543</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>372</v>
+        <v>544</v>
       </c>
       <c r="B10" t="s">
-        <v>373</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>374</v>
+        <v>545</v>
       </c>
       <c r="B11" t="s">
-        <v>375</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>376</v>
+        <v>546</v>
       </c>
       <c r="B12" t="s">
-        <v>377</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>378</v>
+        <v>548</v>
       </c>
       <c r="B13" t="s">
-        <v>379</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>380</v>
+        <v>550</v>
       </c>
       <c r="B14" t="s">
-        <v>381</v>
+        <v>551</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>382</v>
+        <v>552</v>
       </c>
       <c r="B15" t="s">
-        <v>383</v>
+        <v>553</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>384</v>
+        <v>554</v>
       </c>
       <c r="B16" t="s">
-        <v>385</v>
+        <v>555</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>386</v>
+        <v>556</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>387</v>
+        <v>558</v>
       </c>
       <c r="B18" t="s">
-        <v>388</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>389</v>
+        <v>559</v>
       </c>
       <c r="B19" t="s">
-        <v>390</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>391</v>
+        <v>560</v>
       </c>
       <c r="B20" t="s">
-        <v>390</v>
+        <v>561</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>392</v>
+        <v>562</v>
       </c>
       <c r="B21" t="s">
-        <v>393</v>
+        <v>561</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>394</v>
+        <v>563</v>
       </c>
       <c r="B22" t="s">
-        <v>247</v>
+        <v>564</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>395</v>
+        <v>565</v>
       </c>
       <c r="B23" t="s">
-        <v>396</v>
+        <v>487</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>397</v>
+        <v>566</v>
       </c>
       <c r="B24" t="s">
-        <v>396</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>398</v>
+        <v>567</v>
       </c>
       <c r="B25" t="s">
-        <v>396</v>
+        <v>488</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>399</v>
+        <v>568</v>
       </c>
       <c r="B26" t="s">
-        <v>396</v>
+        <v>488</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>400</v>
+        <v>569</v>
       </c>
       <c r="B27" t="s">
-        <v>396</v>
+        <v>488</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>401</v>
+        <v>570</v>
       </c>
       <c r="B28" t="s">
-        <v>396</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>402</v>
+        <v>571</v>
       </c>
       <c r="B29" t="s">
-        <v>235</v>
+        <v>488</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>403</v>
+        <v>572</v>
       </c>
       <c r="B30" t="s">
-        <v>235</v>
+        <v>488</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>404</v>
+        <v>573</v>
       </c>
       <c r="B31" t="s">
-        <v>235</v>
+        <v>364</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>405</v>
+        <v>574</v>
       </c>
       <c r="B32" t="s">
-        <v>235</v>
+        <v>364</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>406</v>
+        <v>575</v>
       </c>
       <c r="B33" t="s">
-        <v>235</v>
+        <v>364</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>407</v>
+        <v>576</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>408</v>
+        <v>577</v>
       </c>
       <c r="B35" t="s">
-        <v>158</v>
+        <v>364</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>409</v>
+        <v>578</v>
       </c>
       <c r="B36" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>410</v>
+        <v>579</v>
       </c>
       <c r="B37" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>411</v>
+        <v>580</v>
       </c>
       <c r="B38" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>412</v>
+        <v>581</v>
       </c>
       <c r="B39" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>413</v>
+        <v>582</v>
       </c>
       <c r="B40" t="s">
-        <v>228</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>414</v>
+        <v>583</v>
       </c>
       <c r="B41" t="s">
-        <v>228</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>415</v>
+        <v>584</v>
       </c>
       <c r="B42" t="s">
-        <v>228</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>416</v>
+        <v>585</v>
       </c>
       <c r="B43" t="s">
-        <v>228</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>417</v>
+        <v>586</v>
       </c>
       <c r="B44" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>418</v>
+        <v>587</v>
       </c>
       <c r="B45" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>419</v>
+        <v>588</v>
       </c>
       <c r="B46" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>420</v>
+        <v>589</v>
       </c>
       <c r="B47" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>421</v>
+        <v>590</v>
       </c>
       <c r="B48" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>422</v>
+        <v>591</v>
       </c>
       <c r="B49" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>423</v>
+        <v>592</v>
       </c>
       <c r="B50" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>424</v>
+        <v>593</v>
       </c>
       <c r="B51" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>425</v>
+        <v>594</v>
       </c>
       <c r="B52" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>426</v>
+        <v>595</v>
       </c>
       <c r="B53" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>427</v>
+        <v>596</v>
       </c>
       <c r="B54" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>428</v>
+        <v>597</v>
       </c>
       <c r="B55" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>429</v>
+        <v>598</v>
       </c>
       <c r="B56" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>430</v>
+        <v>599</v>
       </c>
       <c r="B57" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>431</v>
+        <v>600</v>
       </c>
       <c r="B58" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>432</v>
+        <v>601</v>
       </c>
       <c r="B59" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>433</v>
+        <v>602</v>
       </c>
       <c r="B60" t="s">
-        <v>228</v>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>603</v>
+      </c>
+      <c r="B61" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>604</v>
+      </c>
+      <c r="B62" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>605</v>
+      </c>
+      <c r="B63" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>606</v>
+      </c>
+      <c r="B64" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -4473,7 +5514,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4489,6 +5530,326 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -4498,22 +5859,52 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -4523,17 +5914,52 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -4543,17 +5969,342 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="613">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -225,6 +225,18 @@
     <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.VSENSE(105)</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.IREPLICA(100)</t>
+  </si>
+  <si>
+    <t>Floating pin XNC66.noconn(66)</t>
+  </si>
+  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
@@ -282,22 +294,22 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+    <t>Floating pin XSERDESdftNoNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otpdone(otp_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_pgenb(otp_pgenb)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_clock_enable(otp_clock_enable)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
@@ -318,22 +330,22 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftNoNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
@@ -342,22 +354,22 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
@@ -438,6 +450,15 @@
     <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
   </si>
   <si>
+    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -498,22 +519,22 @@
     <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_pgenb - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_pgenb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
@@ -562,6 +583,9 @@
   </si>
   <si>
     <t>All Nestos have Verilog File</t>
+  </si>
+  <si>
+    <t>NESTO fetdn_359003a8 not found in verilog...</t>
   </si>
   <si>
     <t>Zero Length Verilog Files</t>
@@ -682,9 +706,6 @@
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
   </si>
   <si>
@@ -859,7 +880,7 @@
     <t>serdes_memory_program</t>
   </si>
   <si>
-    <t>Auto</t>
+    <t>Single</t>
   </si>
   <si>
     <t>serdes_memory_bist</t>
@@ -893,9 +914,6 @@
   </si>
   <si>
     <t>serdes_supply</t>
-  </si>
-  <si>
-    <t>Single</t>
   </si>
   <si>
     <t>serdes_split_vi2c_pad</t>
@@ -2235,7 +2253,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2255,7 +2273,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2270,7 +2288,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2285,17 +2303,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2310,12 +2328,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2330,17 +2348,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2350,17 +2368,22 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2375,7 +2398,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2395,127 +2418,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2530,7 +2553,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2550,17 +2573,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -2785,32 +2808,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -2820,37 +2843,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>212</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2860,62 +2883,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -2925,17 +2948,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -2945,57 +2968,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3010,17 +3033,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3035,52 +3058,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -3095,81 +3118,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B7" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B8" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B9" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B10" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B11" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3177,1268 +3200,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B20" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B21" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B41" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B43" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B46" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B47" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B48" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B49" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B50" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B51" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B52" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B55" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B56" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B57" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B64" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B67" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B68" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B69" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B70" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B77" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B78" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B79" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B80" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B81" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B82" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B83" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B84" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B85" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B86" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B87" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B88" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B89" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B90" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B91" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B92" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B93" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B94" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B95" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B96" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B97" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B98" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B99" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B100" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B101" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B102" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B103" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B106" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B107" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B108" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B109" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B110" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B111" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B112" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B113" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B116" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B117" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B118" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B119" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B120" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B121" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B122" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B123" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B124" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B125" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B126" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B127" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B128" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B129" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B130" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B131" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B132" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B133" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B134" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B135" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B136" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B137" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B138" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B139" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B140" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B141" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B142" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B143" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B144" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B145" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="B146" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B147" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B148" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B149" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B150" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B151" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B152" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B153" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B154" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B155" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B156" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B157" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B158" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B159" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B160" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B161" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B162" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B163" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B164" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B165" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B166" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B167" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B168" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B169" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B170" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B171" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B172" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B173" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B174" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B175" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B176" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B177" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B178" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B179" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B180" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -4453,47 +4476,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4501,15 +4524,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4517,7 +4540,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -4532,7 +4555,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -4547,68 +4570,68 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B5" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C5" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D5" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B6" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C6" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D6" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B7" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C7" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D7" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4616,13 +4639,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C8" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D8" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4630,55 +4653,55 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C9" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D9" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>212</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C10" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D10" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B11" t="s">
+        <v>513</v>
+      </c>
+      <c r="C11" t="s">
+        <v>514</v>
+      </c>
+      <c r="D11" t="s">
         <v>507</v>
-      </c>
-      <c r="C11" t="s">
-        <v>508</v>
-      </c>
-      <c r="D11" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B12" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C12" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D12" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4686,111 +4709,111 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C13" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D13" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B14" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C14" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D14" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B15" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C15" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D15" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B16" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C16" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D16" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B17" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C17" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D17" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B18" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C18" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="D18" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="C19" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D19" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C20" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D20" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4798,27 +4821,27 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="C21" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D21" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C22" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D22" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4826,13 +4849,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C23" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D23" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4840,83 +4863,83 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C24" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D24" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B25" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C25" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D25" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C26" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D26" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="C27" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D27" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B28" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="C28" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="D28" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B29" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="C29" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="D29" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -4931,7 +4954,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4941,490 +4964,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B5" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="B6" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="B7" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="B8" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B9" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B10" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B11" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B12" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B13" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="B14" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B15" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B16" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B17" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B18" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B19" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B20" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B21" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B22" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B23" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="B24" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B25" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="B26" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B27" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B28" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B29" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B30" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B31" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B33" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B34" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B35" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B36" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B37" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B38" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B39" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B40" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B41" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B42" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B43" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B44" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B45" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B46" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B47" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B48" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B49" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B50" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="B51" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="B52" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B53" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B54" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B55" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B56" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B57" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B58" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B59" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B60" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B61" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="B62" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B63" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="B64" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -5514,7 +5537,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -5674,132 +5697,132 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
+      <c r="A53" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
+      <c r="A63" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
+      <c r="A68" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -5813,43 +5836,63 @@
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5864,47 +5907,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -5919,47 +5962,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -5969,12 +6012,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:A84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -5984,22 +6027,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -6009,27 +6052,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -6039,17 +6082,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -6059,252 +6102,272 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>140</v>
+      <c r="A50" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
+      <c r="A55" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
+      <c r="A60" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>150</v>
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>154</v>
+      <c r="A70" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>162</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="596">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -225,18 +225,6 @@
     <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.VSENSE(105)</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.IREPLICA(100)</t>
-  </si>
-  <si>
-    <t>Floating pin XNC66.noconn(66)</t>
-  </si>
-  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
@@ -318,15 +306,6 @@
     <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
   </si>
   <si>
-    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
-  </si>
-  <si>
     <t>Floating Outputs</t>
   </si>
   <si>
@@ -348,9 +327,6 @@
     <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
-    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
-  </si>
-  <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
@@ -372,9 +348,6 @@
     <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>No Connects - Inputs</t>
   </si>
   <si>
@@ -450,15 +423,6 @@
     <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
   </si>
   <si>
-    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -513,12 +477,6 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
     <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -543,15 +501,6 @@
     <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
   </si>
   <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>Mixed Mode Conflicts</t>
   </si>
   <si>
@@ -583,9 +532,6 @@
   </si>
   <si>
     <t>All Nestos have Verilog File</t>
-  </si>
-  <si>
-    <t>NESTO fetdn_359003a8 not found in verilog...</t>
   </si>
   <si>
     <t>Zero Length Verilog Files</t>
@@ -704,6 +650,9 @@
   </si>
   <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
@@ -2253,7 +2202,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2273,7 +2222,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2288,7 +2237,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2303,17 +2252,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2328,12 +2277,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2348,17 +2297,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2368,22 +2317,17 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2398,7 +2342,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2418,127 +2362,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2553,7 +2497,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2573,17 +2517,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2808,32 +2752,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -2843,37 +2787,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>61</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2883,62 +2827,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -2948,17 +2892,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -2968,57 +2912,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3033,17 +2977,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -3058,52 +3002,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -3118,81 +3062,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="B5" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="B7" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="B8" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="B9" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="B10" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B11" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3200,1268 +3144,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="B21" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="B36" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="B39" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="B41" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B42" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="B43" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="B46" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="B47" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="B48" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="B49" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="B50" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="B51" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="B52" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="B55" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="B56" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="B57" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="B64" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="B67" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="B68" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="B69" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B70" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="B77" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="B78" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="B79" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="B80" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="B81" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="B82" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="B83" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="B84" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="B85" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B86" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="B87" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="B88" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="B89" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="B90" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="B91" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="B92" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="B93" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="B94" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="B95" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="B96" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="B97" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="B98" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B99" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="B100" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B101" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="B102" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="B103" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="B106" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="B107" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="B108" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="B109" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="B110" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="B111" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="B112" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B113" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="B116" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="B117" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="B118" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="B119" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="B120" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="B121" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="B122" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="B123" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="B124" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="B125" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="B126" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="B127" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="B128" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="B129" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="B130" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="B131" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B132" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B133" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="B134" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="B135" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="B136" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="B137" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="B138" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="B139" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="B140" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="B141" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="B142" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="B143" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="B144" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="B145" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="B146" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="B147" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="B148" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="B149" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="B150" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="B151" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="B152" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="B153" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="B154" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="B155" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="B156" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="B157" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="B158" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="B159" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="B160" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="B161" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="B162" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="B163" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="B164" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="B165" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="B166" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="B167" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="B168" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="B169" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="B170" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="B171" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="B172" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="B173" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="B174" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="B175" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="B176" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="B177" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="B178" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="B179" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="B180" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -4476,47 +4420,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4524,15 +4468,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4540,7 +4484,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -4555,7 +4499,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -4570,68 +4514,68 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="B5" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="C5" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="D5" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="B6" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="C6" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="D6" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="B7" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="C7" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="D7" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4639,13 +4583,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="C8" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="D8" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4653,55 +4597,55 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="C9" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="D9" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="C10" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="D10" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="B11" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="C11" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="D11" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="C12" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="D12" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4709,111 +4653,111 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="C13" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="D13" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B14" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="C14" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="D14" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B15" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="C15" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="D15" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B16" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="C16" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="D16" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="C17" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="D17" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="C18" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="D18" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="C19" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="D19" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="C20" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="D20" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4821,27 +4765,27 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="C21" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="D21" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="C22" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="D22" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4849,13 +4793,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="C23" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="D23" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4863,83 +4807,83 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="C24" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="D24" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="C25" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D25" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="B26" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="C26" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="D26" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="B27" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="C27" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="D27" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="B28" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="C28" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="D28" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B29" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="C29" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="D29" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -4954,7 +4898,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4964,490 +4908,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="B5" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="B6" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="B7" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="B8" t="s">
-        <v>547</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="B9" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="B10" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="B11" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="B12" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="B13" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="B14" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="B15" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="B16" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="B17" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="B18" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="B19" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="B20" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="B21" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="B22" t="s">
-        <v>570</v>
+        <v>553</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>571</v>
+        <v>554</v>
       </c>
       <c r="B23" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>572</v>
+        <v>555</v>
       </c>
       <c r="B24" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>573</v>
+        <v>556</v>
       </c>
       <c r="B25" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="B26" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="B27" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
       <c r="B28" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>577</v>
+        <v>560</v>
       </c>
       <c r="B29" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
       <c r="B30" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
       <c r="B31" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>580</v>
+        <v>563</v>
       </c>
       <c r="B32" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>581</v>
+        <v>564</v>
       </c>
       <c r="B33" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>582</v>
+        <v>565</v>
       </c>
       <c r="B34" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>583</v>
+        <v>566</v>
       </c>
       <c r="B35" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
       <c r="B36" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="B37" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
       <c r="B38" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="B39" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="B40" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>589</v>
+        <v>572</v>
       </c>
       <c r="B41" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="B42" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="B43" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="B44" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="B45" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="B46" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
       <c r="B47" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="B48" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="B49" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="B50" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="B51" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
       <c r="B52" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
       <c r="B53" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
       <c r="B54" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="B55" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="B56" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="B57" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="B58" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="B59" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>608</v>
+        <v>591</v>
       </c>
       <c r="B60" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="B61" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="B62" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="B63" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B64" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5537,7 +5481,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A85"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -5697,132 +5641,132 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="1" t="s">
-        <v>19</v>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>73</v>
+      <c r="A58" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>77</v>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -5836,63 +5780,28 @@
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5902,52 +5811,47 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5957,52 +5861,47 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -6012,12 +5911,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A84"/>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6027,22 +5926,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -6052,27 +5951,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -6082,17 +5981,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -6102,272 +6001,227 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>138</v>
+      <c r="A38" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>16</v>
+      <c r="A40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>17</v>
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>141</v>
+      <c r="A45" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>18</v>
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>19</v>
+      <c r="A50" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>147</v>
+      <c r="A55" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>151</v>
+      <c r="A60" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>26</v>
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="1" t="s">
-        <v>83</v>
+      <c r="A70" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="597">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -282,22 +282,22 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftNoNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otpdone(otp_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_pgenb(otp_pgenb)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_clock_enable(otp_clock_enable)</t>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
@@ -309,43 +309,43 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftNoNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
@@ -477,22 +477,22 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_pgenb - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_pgenb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
@@ -829,40 +829,43 @@
     <t>serdes_memory_program</t>
   </si>
   <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>serdes_memory_bist</t>
+  </si>
+  <si>
+    <t>serdes_address</t>
+  </si>
+  <si>
+    <t>serdes_password</t>
+  </si>
+  <si>
+    <t>0x03</t>
+  </si>
+  <si>
+    <t>serdes_pad</t>
+  </si>
+  <si>
+    <t>dedicated</t>
+  </si>
+  <si>
+    <t>serdes_vmax</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>serdes_clock</t>
+  </si>
+  <si>
+    <t>3200</t>
+  </si>
+  <si>
+    <t>serdes_supply</t>
+  </si>
+  <si>
     <t>Single</t>
-  </si>
-  <si>
-    <t>serdes_memory_bist</t>
-  </si>
-  <si>
-    <t>serdes_address</t>
-  </si>
-  <si>
-    <t>serdes_password</t>
-  </si>
-  <si>
-    <t>0x03</t>
-  </si>
-  <si>
-    <t>serdes_pad</t>
-  </si>
-  <si>
-    <t>dedicated</t>
-  </si>
-  <si>
-    <t>serdes_vmax</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>serdes_clock</t>
-  </si>
-  <si>
-    <t>3200</t>
-  </si>
-  <si>
-    <t>serdes_supply</t>
   </si>
   <si>
     <t>serdes_split_vi2c_pad</t>
@@ -3304,17 +3307,17 @@
         <v>272</v>
       </c>
       <c r="B36" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s">
         <v>238</v>
@@ -3322,15 +3325,15 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s">
         <v>244</v>
@@ -3338,7 +3341,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B41" t="s">
         <v>244</v>
@@ -3346,7 +3349,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B42" t="s">
         <v>244</v>
@@ -3354,15 +3357,15 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B43" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3375,15 +3378,15 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B46" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s">
         <v>236</v>
@@ -3391,15 +3394,15 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B48" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B49" t="s">
         <v>236</v>
@@ -3407,7 +3410,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B50" t="s">
         <v>236</v>
@@ -3415,15 +3418,15 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B51" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B52" t="s">
         <v>238</v>
@@ -3431,7 +3434,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3444,23 +3447,23 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B56" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B57" t="s">
         <v>238</v>
@@ -3468,7 +3471,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3481,97 +3484,97 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B64" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B67" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B68" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B69" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B70" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3584,7 +3587,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B77" t="s">
         <v>238</v>
@@ -3592,7 +3595,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B78" t="s">
         <v>238</v>
@@ -3600,7 +3603,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B79" t="s">
         <v>238</v>
@@ -3608,23 +3611,23 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B80" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B81" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B82" t="s">
         <v>244</v>
@@ -3632,7 +3635,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B83" t="s">
         <v>244</v>
@@ -3640,7 +3643,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B84" t="s">
         <v>244</v>
@@ -3648,7 +3651,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B85" t="s">
         <v>244</v>
@@ -3656,7 +3659,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B86" t="s">
         <v>244</v>
@@ -3664,7 +3667,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B87" t="s">
         <v>244</v>
@@ -3672,7 +3675,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B88" t="s">
         <v>244</v>
@@ -3680,7 +3683,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B89" t="s">
         <v>244</v>
@@ -3688,15 +3691,15 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B90" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B91" t="s">
         <v>244</v>
@@ -3704,7 +3707,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B92" t="s">
         <v>238</v>
@@ -3712,7 +3715,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B93" t="s">
         <v>238</v>
@@ -3720,7 +3723,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B94" t="s">
         <v>244</v>
@@ -3728,7 +3731,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B95" t="s">
         <v>244</v>
@@ -3736,7 +3739,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B96" t="s">
         <v>244</v>
@@ -3744,7 +3747,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B97" t="s">
         <v>244</v>
@@ -3752,7 +3755,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B98" t="s">
         <v>244</v>
@@ -3760,7 +3763,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B99" t="s">
         <v>244</v>
@@ -3768,7 +3771,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B100" t="s">
         <v>244</v>
@@ -3776,15 +3779,15 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B101" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B102" t="s">
         <v>238</v>
@@ -3792,7 +3795,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B103" t="s">
         <v>269</v>
@@ -3800,7 +3803,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3813,71 +3816,71 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B106" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B107" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B108" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B109" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B110" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B111" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B112" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B113" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -3890,431 +3893,431 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B116" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B117" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B118" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B119" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B120" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B121" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B122" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B123" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B124" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B125" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B126" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B127" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B128" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B129" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B135" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B137" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B138" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B139" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B140" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B141" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B142" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B143" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B144" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B145" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B146" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B147" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B148" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B149" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B150" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B151" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B152" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B153" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B154" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B155" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B156" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B157" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B158" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B159" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B160" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B161" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B162" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B163" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B164" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B165" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B166" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B167" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B168" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B169" t="s">
         <v>265</v>
@@ -4322,39 +4325,39 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B170" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B171" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B172" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B173" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B174" t="s">
         <v>244</v>
@@ -4362,50 +4365,50 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B175" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B176" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B177" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B178" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B179" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B180" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -4420,47 +4423,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>269</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4468,15 +4471,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4484,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -4499,7 +4502,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -4514,26 +4517,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4541,13 +4544,13 @@
         <v>195</v>
       </c>
       <c r="B5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4555,13 +4558,13 @@
         <v>195</v>
       </c>
       <c r="B6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4569,13 +4572,13 @@
         <v>198</v>
       </c>
       <c r="B7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C7" t="s">
         <v>265</v>
       </c>
       <c r="D7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4583,13 +4586,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
+        <v>492</v>
+      </c>
+      <c r="C8" t="s">
+        <v>456</v>
+      </c>
+      <c r="D8" t="s">
         <v>491</v>
-      </c>
-      <c r="C8" t="s">
-        <v>455</v>
-      </c>
-      <c r="D8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4597,13 +4600,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4611,13 +4614,13 @@
         <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4625,13 +4628,13 @@
         <v>203</v>
       </c>
       <c r="B11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4639,13 +4642,13 @@
         <v>203</v>
       </c>
       <c r="B12" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C12" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D12" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4653,13 +4656,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C13" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4667,13 +4670,13 @@
         <v>206</v>
       </c>
       <c r="B14" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D14" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4681,13 +4684,13 @@
         <v>206</v>
       </c>
       <c r="B15" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4695,13 +4698,13 @@
         <v>206</v>
       </c>
       <c r="B16" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C16" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D16" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4709,13 +4712,13 @@
         <v>209</v>
       </c>
       <c r="B17" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C17" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4723,13 +4726,13 @@
         <v>210</v>
       </c>
       <c r="B18" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C18" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D18" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4737,13 +4740,13 @@
         <v>210</v>
       </c>
       <c r="B19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -4751,13 +4754,13 @@
         <v>211</v>
       </c>
       <c r="B20" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D20" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4765,13 +4768,13 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D21" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -4779,13 +4782,13 @@
         <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C22" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D22" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4793,13 +4796,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C23" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4807,13 +4810,13 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C24" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D24" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -4821,13 +4824,13 @@
         <v>215</v>
       </c>
       <c r="B25" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C25" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D25" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -4835,13 +4838,13 @@
         <v>216</v>
       </c>
       <c r="B26" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C26" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D26" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -4849,13 +4852,13 @@
         <v>216</v>
       </c>
       <c r="B27" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C27" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D27" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -4863,13 +4866,13 @@
         <v>218</v>
       </c>
       <c r="B28" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C28" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D28" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4877,13 +4880,13 @@
         <v>157</v>
       </c>
       <c r="B29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D29" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -4898,7 +4901,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4908,167 +4911,167 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B13" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B16" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B18" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B20" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
+        <v>552</v>
+      </c>
+      <c r="B21" t="s">
         <v>551</v>
-      </c>
-      <c r="B21" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B22" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B24" t="s">
         <v>269</v>
@@ -5076,322 +5079,322 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B25" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B26" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B27" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B28" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B29" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B30" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B31" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B32" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B33" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B34" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B35" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B38" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B42" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B44" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B45" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B46" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B47" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B48" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B49" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B50" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B51" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B52" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B53" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B54" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B55" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B56" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B57" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B58" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B59" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B60" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B61" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B62" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B63" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B64" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="598">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -613,6 +613,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/WALTZ/verilog5/fetdriver_e53ed485.v:218: error: Unknown module type: fet_fetdriver_e53ed485_Xpmos0
+2 error(s) during elaboration.
+*** These modules were missing:
+        fet_fetdriver_e53ed485_Xpmos0 referenced 1 times.
+***
 </t>
   </si>
   <si>
@@ -2360,7 +2369,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2486,6 +2495,11 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2514,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2520,17 +2534,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2755,32 +2769,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -2790,37 +2804,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2830,62 +2844,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -2895,17 +2909,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -2915,47 +2929,47 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -2965,7 +2979,7 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2980,17 +2994,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3005,52 +3019,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -3065,81 +3079,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" t="s">
         <v>245</v>
-      </c>
-      <c r="B11" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3147,1268 +3161,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B20" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B39" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B47" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B48" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B51" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B52" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B56" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B57" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B64" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B67" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B68" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B69" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B70" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B77" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B78" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B79" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B80" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B81" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B82" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B83" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B84" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B85" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B86" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B87" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B88" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B89" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B90" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B91" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B93" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B94" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B95" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B96" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B97" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B98" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B99" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B100" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B101" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B102" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B106" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B107" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B108" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B109" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B110" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B111" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B112" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B113" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B116" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B117" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B118" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B119" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B120" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B121" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B122" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B123" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B124" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B125" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B126" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B127" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B128" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B135" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B136" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B137" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B138" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B139" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B140" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B141" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B142" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B143" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B144" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B145" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B146" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B147" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B148" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B149" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B150" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B151" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B152" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B153" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B154" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B155" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B156" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B157" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B158" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B159" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B160" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B161" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B162" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B163" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B164" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B165" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B166" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B167" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B168" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B169" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B170" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B171" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B172" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B173" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B174" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B175" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B176" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B177" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B178" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B179" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B180" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -4423,47 +4437,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4471,15 +4485,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4487,7 +4501,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -4502,7 +4516,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -4517,68 +4531,68 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4586,13 +4600,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
+        <v>493</v>
+      </c>
+      <c r="C8" t="s">
+        <v>457</v>
+      </c>
+      <c r="D8" t="s">
         <v>492</v>
-      </c>
-      <c r="C8" t="s">
-        <v>456</v>
-      </c>
-      <c r="D8" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4600,55 +4614,55 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C12" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4656,111 +4670,111 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B14" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D14" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C15" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D15" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B16" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D16" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C17" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C18" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D18" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D19" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C20" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D20" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4768,27 +4782,27 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C21" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D21" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C22" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D22" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4796,13 +4810,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C23" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4810,69 +4824,69 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C24" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D24" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C25" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D25" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B26" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C26" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D26" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B27" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C27" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D27" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B28" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D28" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4880,13 +4894,13 @@
         <v>157</v>
       </c>
       <c r="B29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C29" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D29" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -4901,7 +4915,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4911,490 +4925,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B8" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B13" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B15" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B16" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B17" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B20" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
+        <v>553</v>
+      </c>
+      <c r="B21" t="s">
         <v>552</v>
-      </c>
-      <c r="B21" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B22" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B25" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B26" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B28" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B29" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B30" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B31" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B32" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B33" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B34" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B35" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B37" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B39" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B40" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B44" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B45" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B46" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B47" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B48" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B49" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B50" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B51" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B52" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B53" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B54" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B55" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B56" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B57" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B58" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B59" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B60" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B61" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B62" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B63" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B64" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Summary.xlsx
+++ b/WALTZ/project/Summary.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="577">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -282,24 +282,9 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
     <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
-  </si>
-  <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
   </si>
   <si>
@@ -309,43 +294,13 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftYesNo.tdo(tdo_noconn)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdo_noconn - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdo", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
@@ -477,22 +432,7 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
@@ -613,15 +553,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog5/fetdriver_e53ed485.v:218: error: Unknown module type: fet_fetdriver_e53ed485_Xpmos0
-2 error(s) during elaboration.
-*** These modules were missing:
-        fet_fetdriver_e53ed485_Xpmos0 referenced 1 times.
-***
 </t>
   </si>
   <si>
@@ -2214,7 +2145,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2234,7 +2165,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2249,7 +2180,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2264,17 +2195,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2289,12 +2220,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2309,17 +2240,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2334,12 +2265,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2354,7 +2285,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2369,137 +2300,132 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2514,7 +2440,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2534,17 +2460,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2769,32 +2695,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -2804,37 +2730,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -2844,62 +2770,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -2909,17 +2835,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -2929,57 +2855,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2994,17 +2920,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3019,52 +2945,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3079,81 +3005,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="B6" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="B7" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="B8" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="B11" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3161,1268 +3087,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="